--- a/BOM/Valkyrie V2 Build Guide.xlsx
+++ b/BOM/Valkyrie V2 Build Guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10859" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95A3D8D0-C378-4EA7-836D-47F8E150FF4A}"/>
+  <xr:revisionPtr revIDLastSave="10868" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83D55CA6-5518-4AC7-ACBB-233CAF335060}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="13" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="52" r:id="rId1"/>
@@ -39,7 +39,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COMPLETE PARTS LIST'!$A$1:$K$158</definedName>
     <definedName name="ExternalData_1" localSheetId="12" hidden="1">'Firmware Configuration'!$A$1:$B$163</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'V2 Printed Parts'!$A$1:$H$111</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'V2 Printed Parts'!$A$1:$H$112</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'COMPLETE PARTS LIST'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3744" uniqueCount="1938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3748" uniqueCount="1939">
   <si>
     <t>BULD ORDER RECOMMENDATION</t>
   </si>
@@ -6099,6 +6099,9 @@
   </si>
   <si>
     <t>Note: Thise are generic values. Check the values for your specific brand</t>
+  </si>
+  <si>
+    <t>V205 Z Bump Stop</t>
   </si>
 </sst>
 </file>
@@ -7170,7 +7173,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="436">
+  <cellXfs count="433">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
@@ -8019,17 +8022,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -8058,20 +8053,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -8093,116 +8091,11 @@
   </cellStyles>
   <dxfs count="149">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -8543,60 +8436,115 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -8800,13 +8748,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10127,6 +10068,63 @@
           <bgColor auto="1"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -11550,80 +11548,80 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J157" totalsRowShown="0" headerRowDxfId="147" dataDxfId="145" headerRowBorderDxfId="146" tableBorderDxfId="144" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J157" totalsRowShown="0" headerRowDxfId="144" dataDxfId="142" headerRowBorderDxfId="143" tableBorderDxfId="141" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J157" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J157">
     <sortCondition ref="A1:A157"/>
   </sortState>
   <tableColumns count="10">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="142"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="BOM Qty Required" dataDxfId="141" dataCellStyle="Normal 7"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="140"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="139"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="138">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="140"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="139"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="BOM Qty Required" dataDxfId="138" dataCellStyle="Normal 7"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="137"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="136"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="135">
       <calculatedColumnFormula>D2*E2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="137" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="136"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Size" dataDxfId="135" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="134"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="134" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="133"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Pack Size" dataDxfId="132" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN / ISO" dataDxfId="131"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D54" totalsRowShown="0" headerRowDxfId="75" tableBorderDxfId="74" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D54" totalsRowShown="0" headerRowDxfId="72" tableBorderDxfId="71" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D54" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D54">
     <sortCondition ref="B1:B54"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="73" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="71" totalsRowDxfId="70" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="70" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="68" totalsRowDxfId="67" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D76" totalsRowShown="0" headerRowDxfId="69" tableBorderDxfId="68" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D76" totalsRowShown="0" headerRowDxfId="66" tableBorderDxfId="65" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D76" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D76">
     <sortCondition ref="B1:B76"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="67" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="65" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="61" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:I111" totalsRowCount="1" headerRowDxfId="63">
-  <autoFilter ref="A1:I110" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I110">
-    <sortCondition ref="A1:A110"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:I112" totalsRowCount="1" headerRowDxfId="60">
+  <autoFilter ref="A1:I111" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I111">
+    <sortCondition ref="A1:A111"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="62" totalsRowDxfId="61"/>
-    <tableColumn id="3" xr3:uid="{AE4E9077-B04D-4FB7-A226-807DE24B3CEE}" name="Filament Type" dataDxfId="60" totalsRowDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="58" totalsRowDxfId="57"/>
-    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="Weight Tot" totalsRowFunction="custom" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Normal 7">
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" totalsRowLabel="Valkyrie V2" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{AE4E9077-B04D-4FB7-A226-807DE24B3CEE}" name="Filament Type" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="53"/>
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="52" totalsRowDxfId="51" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="Weight Tot" totalsRowFunction="custom" dataDxfId="50" totalsRowDxfId="1" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[Weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="0">
       <calculatedColumnFormula>$L$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{CBC7571F-19BC-4246-AB6F-92AD07297E48}" name="Time Total" totalsRowFunction="sum" dataDxfId="47" totalsRowDxfId="46">
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="48" totalsRowDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{CBC7571F-19BC-4246-AB6F-92AD07297E48}" name="Time Total" totalsRowFunction="sum" dataDxfId="46" totalsRowDxfId="45">
       <calculatedColumnFormula>Table6[[#This Row],[Time/item]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11635,8 +11633,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{698A4938-9A62-487C-AAA1-610F09C9455D}" name="config" displayName="config" ref="A1:B163" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:B163" xr:uid="{698A4938-9A62-487C-AAA1-610F09C9455D}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{84F550F2-8A0D-46D7-A276-CE01FDFC905C}" uniqueName="1" name="CODE" queryTableFieldId="1" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{16061B4E-F1A4-4033-984D-4285ADE764E8}" uniqueName="2" name="COMMENT" queryTableFieldId="2" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{84F550F2-8A0D-46D7-A276-CE01FDFC905C}" uniqueName="1" name="CODE" queryTableFieldId="1" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{16061B4E-F1A4-4033-984D-4285ADE764E8}" uniqueName="2" name="COMMENT" queryTableFieldId="2" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11649,7 +11647,7 @@
     <sortCondition ref="A1:A13"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{8D8B2F09-EE52-45AA-BAA6-D22E0DE184E9}" name="Macro" dataDxfId="147"/>
     <tableColumn id="1" xr3:uid="{E1FF070C-6993-4332-802B-B4D29E1606E7}" name="Function"/>
     <tableColumn id="3" xr3:uid="{8FBB1689-4854-43C5-AC93-F6E571CF242D}" name="Description"/>
   </tableColumns>
@@ -11664,8 +11662,8 @@
     <sortCondition ref="A16:A32"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{A5B4F8F7-1DD2-464C-B2BB-DB18FF666977}" name="Gcode" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="146"/>
+    <tableColumn id="6" xr3:uid="{A5B4F8F7-1DD2-464C-B2BB-DB18FF666977}" name="Gcode" dataDxfId="145"/>
     <tableColumn id="3" xr3:uid="{5B376876-1002-41A2-9B1B-97FBB74534E9}" name="Description"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -11698,58 +11696,58 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{0CF7ACA6-2A91-46C9-BFD2-3A02E58BAA06}" name="Table21" displayName="Table21" ref="A1:J120" totalsRowShown="0" headerRowDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{0CF7ACA6-2A91-46C9-BFD2-3A02E58BAA06}" name="Table21" displayName="Table21" ref="A1:J120" totalsRowShown="0" headerRowDxfId="42">
   <autoFilter ref="A1:J120" xr:uid="{0CF7ACA6-2A91-46C9-BFD2-3A02E58BAA06}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{07401D67-326A-456C-83EE-6254807B759D}" name="Type" dataDxfId="42" dataCellStyle="Normal 13"/>
-    <tableColumn id="2" xr3:uid="{01841385-7AF0-4832-AD07-D9B6A289B738}" name="Device" dataDxfId="41" dataCellStyle="Normal 13"/>
-    <tableColumn id="3" xr3:uid="{4EBC60AB-DBDA-46AD-8145-0260DB456AC9}" name="Ident" dataDxfId="40" dataCellStyle="Normal 13"/>
-    <tableColumn id="4" xr3:uid="{27974694-306B-43D4-9D9F-3BC67D1A167D}" name="Connector" dataDxfId="39" dataCellStyle="Normal 13"/>
-    <tableColumn id="5" xr3:uid="{247A2715-9549-43E9-BC8D-C5AF905911E6}" name="From" dataDxfId="38" dataCellStyle="Normal 13"/>
-    <tableColumn id="6" xr3:uid="{CAED148B-51FF-46DC-A56B-A5F88498E2F4}" name="Wire size AWG" dataDxfId="37" dataCellStyle="Normal 13"/>
-    <tableColumn id="7" xr3:uid="{A8E15565-9D43-4F89-9D4B-714FAEED327C}" name="Color" dataDxfId="36" dataCellStyle="Normal 13"/>
-    <tableColumn id="8" xr3:uid="{EF11CEA0-492E-4C41-811D-955E5C409484}" name="Length mm" dataDxfId="35" dataCellStyle="Normal 13"/>
-    <tableColumn id="9" xr3:uid="{B64154E3-1929-4FEB-B7E7-B1FCB2AE49D2}" name="Destination pin" dataDxfId="34" dataCellStyle="Normal 13"/>
-    <tableColumn id="10" xr3:uid="{1768166D-BE53-4B2E-9459-10942122F8E6}" name="Comment" dataDxfId="33" dataCellStyle="Normal 13"/>
+    <tableColumn id="1" xr3:uid="{07401D67-326A-456C-83EE-6254807B759D}" name="Type" dataDxfId="41" dataCellStyle="Normal 13"/>
+    <tableColumn id="2" xr3:uid="{01841385-7AF0-4832-AD07-D9B6A289B738}" name="Device" dataDxfId="40" dataCellStyle="Normal 13"/>
+    <tableColumn id="3" xr3:uid="{4EBC60AB-DBDA-46AD-8145-0260DB456AC9}" name="Ident" dataDxfId="39" dataCellStyle="Normal 13"/>
+    <tableColumn id="4" xr3:uid="{27974694-306B-43D4-9D9F-3BC67D1A167D}" name="Connector" dataDxfId="38" dataCellStyle="Normal 13"/>
+    <tableColumn id="5" xr3:uid="{247A2715-9549-43E9-BC8D-C5AF905911E6}" name="From" dataDxfId="37" dataCellStyle="Normal 13"/>
+    <tableColumn id="6" xr3:uid="{CAED148B-51FF-46DC-A56B-A5F88498E2F4}" name="Wire size AWG" dataDxfId="36" dataCellStyle="Normal 13"/>
+    <tableColumn id="7" xr3:uid="{A8E15565-9D43-4F89-9D4B-714FAEED327C}" name="Color" dataDxfId="35" dataCellStyle="Normal 13"/>
+    <tableColumn id="8" xr3:uid="{EF11CEA0-492E-4C41-811D-955E5C409484}" name="Length mm" dataDxfId="34" dataCellStyle="Normal 13"/>
+    <tableColumn id="9" xr3:uid="{B64154E3-1929-4FEB-B7E7-B1FCB2AE49D2}" name="Destination pin" dataDxfId="33" dataCellStyle="Normal 13"/>
+    <tableColumn id="10" xr3:uid="{1768166D-BE53-4B2E-9459-10942122F8E6}" name="Comment" dataDxfId="32" dataCellStyle="Normal 13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{824DC2E7-B869-4223-8CA0-8BB231246BE6}" name="Table43" displayName="Table43" ref="A4:G37" totalsRowShown="0" headerRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{824DC2E7-B869-4223-8CA0-8BB231246BE6}" name="Table43" displayName="Table43" ref="A4:G37" totalsRowShown="0" headerRowBorderDxfId="31">
   <autoFilter ref="A4:G37" xr:uid="{9F2F2CC6-19FD-46E3-8A6D-884FD4A96CE0}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AE39532B-D989-4297-B014-612247804D38}" name="Type" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{AE39532B-D989-4297-B014-612247804D38}" name="Type" dataDxfId="30"/>
     <tableColumn id="2" xr3:uid="{299576E6-0ACD-495A-89C7-26F593973C04}" name="Component"/>
-    <tableColumn id="5" xr3:uid="{25D583BA-BC0F-45C1-8195-BA00EEE7001D}" name="Pin" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{07FBDE4D-2555-4C8A-8314-D8A735D09CA9}" name="AWG" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{C8C1F170-B800-45DE-8C38-42F23A1A89F1}" name="Wire Colour" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{7E640059-24DB-480D-83B2-FC35DE245721}" name="Wire Length CM" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{7C27CE98-27C4-49E7-9D13-ADA6DCAD2043}" name="Device/Pin" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{25D583BA-BC0F-45C1-8195-BA00EEE7001D}" name="Pin" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{07FBDE4D-2555-4C8A-8314-D8A735D09CA9}" name="AWG" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{C8C1F170-B800-45DE-8C38-42F23A1A89F1}" name="Wire Colour" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{7E640059-24DB-480D-83B2-FC35DE245721}" name="Wire Length CM" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{7C27CE98-27C4-49E7-9D13-ADA6DCAD2043}" name="Device/Pin" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="133" dataDxfId="132" tableBorderDxfId="131" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="130" dataDxfId="129" tableBorderDxfId="128" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="130"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="129"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="128" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="127"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="127"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="126"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Length" dataDxfId="125" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="QTY" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{427AA7E7-4B6F-49B8-9DC6-E235BC0A0D08}" name="Table24" displayName="Table24" ref="A1:K28" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{427AA7E7-4B6F-49B8-9DC6-E235BC0A0D08}" name="Table24" displayName="Table24" ref="A1:K28" totalsRowShown="0" headerRowDxfId="24" tableBorderDxfId="23">
   <autoFilter ref="A1:K28" xr:uid="{427AA7E7-4B6F-49B8-9DC6-E235BC0A0D08}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K28">
     <sortCondition ref="A1:A28"/>
@@ -11757,147 +11755,147 @@
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{0AC7D7D1-3190-41C5-9975-24147A54C056}" name="Filament Type"/>
     <tableColumn id="2" xr3:uid="{D66FB001-1FEC-40AF-949E-BB59CCC75E2E}" name="Molecular Structure"/>
-    <tableColumn id="3" xr3:uid="{A44746CA-A486-4625-A4CC-A4E89629782E}" name="Glass Transition Temp TG (°C)" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{C6A806F7-B772-4828-BD95-E901C555F863}" name="Rec Nozzle Temp (°C)" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{DAC70B55-849D-492E-9A23-0C7F6D7110B2}" name="Rec Bed Temp (°C)" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{6F076EC0-EAA1-4A79-B345-5220FDBDB46C}" name="Rec Chamber Temp (°C)" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{3E379A13-7EC9-410A-82E9-4A6F2F0B7AFD}" name="Drying Temp (°C)" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{D68119B6-45F8-4815-9604-9BA3D3A92BDE}" name="Drying Time" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{A44746CA-A486-4625-A4CC-A4E89629782E}" name="Glass Transition Temp TG (°C)" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{C6A806F7-B772-4828-BD95-E901C555F863}" name="Rec Nozzle Temp (°C)" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{DAC70B55-849D-492E-9A23-0C7F6D7110B2}" name="Rec Bed Temp (°C)" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{6F076EC0-EAA1-4A79-B345-5220FDBDB46C}" name="Rec Chamber Temp (°C)" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{3E379A13-7EC9-410A-82E9-4A6F2F0B7AFD}" name="Drying Temp (°C)" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{D68119B6-45F8-4815-9604-9BA3D3A92BDE}" name="Drying Time" dataDxfId="17"/>
     <tableColumn id="10" xr3:uid="{B1E70FD4-ACF1-4077-9522-368B3634FFFA}" name="Density (g/cm³)"/>
-    <tableColumn id="11" xr3:uid="{D6022B5B-D011-40B5-B8ED-B637E41F532E}" name="HDT @ 1.82 MPa (°C)" dataDxfId="7"/>
-    <tableColumn id="12" xr3:uid="{C5CB8044-3259-41D9-9397-59316D1AFD81}" name="HDT @ 0.45 MPa (°C)" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{D6022B5B-D011-40B5-B8ED-B637E41F532E}" name="HDT @ 1.82 MPa (°C)" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{C5CB8044-3259-41D9-9397-59316D1AFD81}" name="HDT @ 0.45 MPa (°C)" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{19F8394B-1B62-4BEB-A334-6062DEDDDBA5}" name="Table123" displayName="Table123" ref="A1:D35" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" headerRowCellStyle="Normal 11" dataCellStyle="Normal 11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{19F8394B-1B62-4BEB-A334-6062DEDDDBA5}" name="Table123" displayName="Table123" ref="A1:D35" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" headerRowCellStyle="Normal 11" dataCellStyle="Normal 11">
   <autoFilter ref="A1:D35" xr:uid="{38BAB44D-6344-4462-B6CF-4425327389D2}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{36E8D78F-CA45-4D9B-919D-2E47181ACCD1}" name="Specifications" dataDxfId="20" dataCellStyle="Normal 11"/>
-    <tableColumn id="3" xr3:uid="{88A0399B-7F60-46B2-B934-CEA97414F015}" name="Valkyrie V2" dataDxfId="19" dataCellStyle="Normal 11"/>
-    <tableColumn id="7" xr3:uid="{93940A86-4E51-46CD-A0F3-59BF366154DD}" name="BNC3D Epsilon" dataDxfId="18" dataCellStyle="Normal 11"/>
-    <tableColumn id="8" xr3:uid="{3F1776C0-4EBB-4F42-9FC4-8D5F10306432}" name="22 Idex V3" dataDxfId="17" dataCellStyle="Normal 11"/>
+    <tableColumn id="1" xr3:uid="{36E8D78F-CA45-4D9B-919D-2E47181ACCD1}" name="Specifications" dataDxfId="12" dataCellStyle="Normal 11"/>
+    <tableColumn id="3" xr3:uid="{88A0399B-7F60-46B2-B934-CEA97414F015}" name="Valkyrie V2" dataDxfId="11" dataCellStyle="Normal 11"/>
+    <tableColumn id="7" xr3:uid="{93940A86-4E51-46CD-A0F3-59BF366154DD}" name="BNC3D Epsilon" dataDxfId="10" dataCellStyle="Normal 11"/>
+    <tableColumn id="8" xr3:uid="{3F1776C0-4EBB-4F42-9FC4-8D5F10306432}" name="22 Idex V3" dataDxfId="9" dataCellStyle="Normal 11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38BAB44D-6344-4462-B6CF-4425327389D2}" name="Table1" displayName="Table1" ref="A1:E35" totalsRowShown="0" headerRowDxfId="16" dataDxfId="15" headerRowCellStyle="Normal 11" dataCellStyle="Normal 11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{38BAB44D-6344-4462-B6CF-4425327389D2}" name="Table1" displayName="Table1" ref="A1:E35" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7" headerRowCellStyle="Normal 11" dataCellStyle="Normal 11">
   <autoFilter ref="A1:E35" xr:uid="{38BAB44D-6344-4462-B6CF-4425327389D2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9DD46C98-7270-4D40-85B0-564C1B03A5A4}" name="Specifications" dataDxfId="14" dataCellStyle="Normal 11"/>
-    <tableColumn id="3" xr3:uid="{940A67A0-059D-4D5A-9618-9FCF1D2C1CC2}" name="Valkyrie V2" dataDxfId="13" dataCellStyle="Normal 11"/>
-    <tableColumn id="4" xr3:uid="{6B92122F-701E-46B1-8344-9B3555981CE9}" name="Hevort" dataDxfId="12" dataCellStyle="Normal 11"/>
-    <tableColumn id="5" xr3:uid="{F6EAF2DA-D52C-4BDC-9928-641779055403}" name="Voron 2.4" dataDxfId="11" dataCellStyle="Normal 11"/>
-    <tableColumn id="6" xr3:uid="{FA9F67FD-C9D7-4C39-8C62-BAB502105479}" name="RatRig V3" dataDxfId="10" dataCellStyle="Normal 11"/>
+    <tableColumn id="1" xr3:uid="{9DD46C98-7270-4D40-85B0-564C1B03A5A4}" name="Specifications" dataDxfId="6" dataCellStyle="Normal 11"/>
+    <tableColumn id="3" xr3:uid="{940A67A0-059D-4D5A-9618-9FCF1D2C1CC2}" name="Valkyrie V2" dataDxfId="5" dataCellStyle="Normal 11"/>
+    <tableColumn id="4" xr3:uid="{6B92122F-701E-46B1-8344-9B3555981CE9}" name="Hevort" dataDxfId="4" dataCellStyle="Normal 11"/>
+    <tableColumn id="5" xr3:uid="{F6EAF2DA-D52C-4BDC-9928-641779055403}" name="Voron 2.4" dataDxfId="3" dataCellStyle="Normal 11"/>
+    <tableColumn id="6" xr3:uid="{FA9F67FD-C9D7-4C39-8C62-BAB502105479}" name="RatRig V3" dataDxfId="2" dataCellStyle="Normal 11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D47" totalsRowShown="0" headerRowDxfId="126" tableBorderDxfId="125" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D47" totalsRowShown="0" headerRowDxfId="123" tableBorderDxfId="122" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D47" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D47">
     <sortCondition ref="B1:B47"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="124" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="123" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="122" totalsRowDxfId="121" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="121" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="120" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="119" totalsRowDxfId="118" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D59" totalsRowShown="0" headerRowDxfId="120" dataDxfId="119" tableBorderDxfId="118" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D59" totalsRowShown="0" headerRowDxfId="117" dataDxfId="116" tableBorderDxfId="115" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D59" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D59">
     <sortCondition ref="B1:B59"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" dataDxfId="117" totalsRowDxfId="116" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" dataDxfId="115" totalsRowDxfId="114" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="113" totalsRowDxfId="112" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" dataDxfId="114" totalsRowDxfId="113" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" dataDxfId="112" totalsRowDxfId="111" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="110" totalsRowDxfId="109" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D33" totalsRowShown="0" headerRowDxfId="111" dataDxfId="110" tableBorderDxfId="109" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D33" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107" tableBorderDxfId="106" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D33" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D33">
     <sortCondition ref="B1:B33"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" dataDxfId="108" totalsRowDxfId="107" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" dataDxfId="106" totalsRowDxfId="105" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="104" totalsRowDxfId="103" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" dataDxfId="105" totalsRowDxfId="104" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" dataDxfId="103" totalsRowDxfId="102" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="101" totalsRowDxfId="100" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B35:D44" totalsRowShown="0" headerRowDxfId="102" dataDxfId="101" tableBorderDxfId="100" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B35:D44" totalsRowShown="0" headerRowDxfId="99" dataDxfId="98" tableBorderDxfId="97" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B35:D44" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B36:D44">
     <sortCondition ref="B35:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" dataDxfId="99" totalsRowDxfId="98" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" dataDxfId="97" totalsRowDxfId="96" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" dataDxfId="96" totalsRowDxfId="95" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" dataDxfId="94" totalsRowDxfId="93" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="92" totalsRowDxfId="91" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D68" totalsRowShown="0" headerRowDxfId="93" tableBorderDxfId="92" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D68" totalsRowShown="0" headerRowDxfId="90" tableBorderDxfId="89" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D68" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D68">
     <sortCondition ref="B1:B68"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="91" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="90" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="89" totalsRowDxfId="88" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="88" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="87" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="86" totalsRowDxfId="85" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D11" totalsRowShown="0" headerRowDxfId="87" tableBorderDxfId="86" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D11" totalsRowShown="0" headerRowDxfId="84" tableBorderDxfId="83" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D11" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D11">
     <sortCondition ref="B1:B11"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="85" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="84" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="83" totalsRowDxfId="82" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="82" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="81" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="80" totalsRowDxfId="79" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A7720F7C-DDE4-480A-9200-E1A2AB06F106}" name="Table9131718192024" displayName="Table9131718192024" ref="B1:D12" totalsRowShown="0" headerRowDxfId="81" tableBorderDxfId="80" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{A7720F7C-DDE4-480A-9200-E1A2AB06F106}" name="Table9131718192024" displayName="Table9131718192024" ref="B1:D12" totalsRowShown="0" headerRowDxfId="78" tableBorderDxfId="77" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D12" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D12">
     <sortCondition ref="B1:B12"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{DE5B6A3D-F02B-442F-8F0E-2D97466E9D55}" name="Part name" totalsRowDxfId="79" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{CD84E571-7957-4B8F-9F34-DA3FA6BF0E23}" name="Description" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{52F63DEF-0CA0-45D5-85B8-E41A21AD2000}" name="BOM Quantity" dataDxfId="77" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{DE5B6A3D-F02B-442F-8F0E-2D97466E9D55}" name="Part name" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{CD84E571-7957-4B8F-9F34-DA3FA6BF0E23}" name="Description" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{52F63DEF-0CA0-45D5-85B8-E41A21AD2000}" name="BOM Quantity" dataDxfId="74" totalsRowDxfId="73" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -14000,7 +13998,7 @@
     <tabColor rgb="FF92D050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -17444,26 +17442,28 @@
         <v>751</v>
       </c>
       <c r="C109" s="231" t="s">
-        <v>885</v>
+        <v>1938</v>
       </c>
       <c r="D109" s="44">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E109" s="32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" s="42">
         <f>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</f>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="G109" s="37">
         <f>$L$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</f>
-        <v>2.73</v>
-      </c>
-      <c r="H109" s="38"/>
+        <v>1.56</v>
+      </c>
+      <c r="H109" s="38">
+        <v>6.9444444444444441E-3</v>
+      </c>
       <c r="I109" s="167">
         <f>Table6[[#This Row],[Time/item]]*Table6[[#This Row],[QTY]]</f>
-        <v>0</v>
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="J109" s="167"/>
     </row>
@@ -17475,21 +17475,21 @@
         <v>751</v>
       </c>
       <c r="C110" s="231" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D110" s="44">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E110" s="32">
         <v>1</v>
       </c>
       <c r="F110" s="42">
         <f>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</f>
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G110" s="37">
         <f>$L$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</f>
-        <v>0.26</v>
+        <v>2.73</v>
       </c>
       <c r="H110" s="38"/>
       <c r="I110" s="167">
@@ -17499,38 +17499,67 @@
       <c r="J110" s="167"/>
     </row>
     <row r="111" spans="1:10">
-      <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
-      <c r="E111" s="1">
+      <c r="A111" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="C111" s="231" t="s">
+        <v>886</v>
+      </c>
+      <c r="D111" s="44">
+        <v>2</v>
+      </c>
+      <c r="E111" s="32">
+        <v>1</v>
+      </c>
+      <c r="F111" s="42">
+        <f>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</f>
+        <v>2</v>
+      </c>
+      <c r="G111" s="37">
+        <f>$L$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</f>
+        <v>0.26</v>
+      </c>
+      <c r="H111" s="38"/>
+      <c r="I111" s="167">
+        <f>Table6[[#This Row],[Time/item]]*Table6[[#This Row],[QTY]]</f>
+        <v>0</v>
+      </c>
+      <c r="J111" s="167"/>
+    </row>
+    <row r="112" spans="1:10">
+      <c r="A112" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="E112" s="1">
         <f>SUBTOTAL(109,Table6[QTY])</f>
-        <v>150</v>
-      </c>
-      <c r="F111" s="39" t="str">
+        <v>153</v>
+      </c>
+      <c r="F112" s="39" t="str">
         <f>SUBTOTAL(109,Table6[Weight Tot])&amp;"g"</f>
-        <v>1051g</v>
-      </c>
-      <c r="G111" s="37">
+        <v>1063g</v>
+      </c>
+      <c r="G112" s="37">
         <f>SUBTOTAL(109,Table6[Cost/part])</f>
-        <v>136.63</v>
-      </c>
-      <c r="H111" s="43">
+        <v>138.19</v>
+      </c>
+      <c r="H112" s="43">
         <f>SUBTOTAL(109,Table6[Time/item])</f>
-        <v>1.4618055555555556</v>
-      </c>
-      <c r="I111" s="43">
+        <v>1.46875</v>
+      </c>
+      <c r="I112" s="43">
         <f>SUBTOTAL(109,Table6[Time Total])</f>
-        <v>1.5034722222222223</v>
-      </c>
-      <c r="J111" s="167"/>
-    </row>
-    <row r="112" spans="1:10">
-      <c r="A112" s="384"/>
-      <c r="B112" s="1"/>
+        <v>1.5243055555555556</v>
+      </c>
       <c r="J112" s="167"/>
     </row>
     <row r="113" spans="1:10">
-      <c r="A113" s="47"/>
+      <c r="A113" s="384"/>
+      <c r="B113" s="1"/>
       <c r="J113" s="167"/>
     </row>
     <row r="114" spans="1:10">
@@ -17538,6 +17567,7 @@
       <c r="J114" s="167"/>
     </row>
     <row r="115" spans="1:10">
+      <c r="A115" s="47"/>
       <c r="J115" s="167"/>
     </row>
     <row r="116" spans="1:10">
@@ -17554,6 +17584,9 @@
     </row>
     <row r="120" spans="1:10">
       <c r="J120" s="167"/>
+    </row>
+    <row r="121" spans="1:10">
+      <c r="J121" s="167"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23930,976 +23963,976 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="35.25" customHeight="1" thickBot="1">
-      <c r="A1" s="415" t="s">
+      <c r="A1" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="B1" s="415" t="s">
+      <c r="B1" s="4" t="s">
         <v>1851</v>
       </c>
-      <c r="C1" s="423" t="s">
+      <c r="C1" s="419" t="s">
         <v>1892</v>
       </c>
-      <c r="D1" s="423" t="s">
+      <c r="D1" s="419" t="s">
         <v>1893</v>
       </c>
-      <c r="E1" s="423" t="s">
+      <c r="E1" s="419" t="s">
         <v>1895</v>
       </c>
-      <c r="F1" s="423" t="s">
+      <c r="F1" s="419" t="s">
         <v>1894</v>
       </c>
-      <c r="G1" s="428" t="s">
+      <c r="G1" s="424" t="s">
         <v>1852</v>
       </c>
-      <c r="H1" s="429" t="s">
+      <c r="H1" s="425" t="s">
         <v>1534</v>
       </c>
-      <c r="I1" s="415" t="s">
+      <c r="I1" s="4" t="s">
         <v>1853</v>
       </c>
-      <c r="J1" s="415" t="s">
+      <c r="J1" s="4" t="s">
         <v>1854</v>
       </c>
-      <c r="K1" s="415" t="s">
+      <c r="K1" s="4" t="s">
         <v>1855</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="416" t="s">
+      <c r="A2" t="s">
         <v>1523</v>
       </c>
-      <c r="B2" s="416" t="s">
+      <c r="B2" t="s">
         <v>1856</v>
       </c>
-      <c r="C2" s="419">
+      <c r="C2" s="415">
         <v>105</v>
       </c>
-      <c r="D2" s="424" t="s">
+      <c r="D2" s="420" t="s">
         <v>1896</v>
       </c>
-      <c r="E2" s="424" t="s">
+      <c r="E2" s="420" t="s">
         <v>1857</v>
       </c>
-      <c r="F2" s="424" t="s">
+      <c r="F2" s="420" t="s">
         <v>1897</v>
       </c>
-      <c r="G2" s="430" t="s">
+      <c r="G2" s="426" t="s">
         <v>1858</v>
       </c>
-      <c r="H2" s="431">
+      <c r="H2" s="427">
         <v>6</v>
       </c>
-      <c r="I2" s="416">
+      <c r="I2">
         <v>1.05</v>
       </c>
-      <c r="J2" s="417">
+      <c r="J2" s="414">
         <v>90</v>
       </c>
-      <c r="K2" s="417">
+      <c r="K2" s="414">
         <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="416" t="s">
+      <c r="A3" t="s">
         <v>1539</v>
       </c>
-      <c r="B3" s="416" t="s">
+      <c r="B3" t="s">
         <v>1856</v>
       </c>
-      <c r="C3" s="420">
+      <c r="C3" s="416">
         <v>102</v>
       </c>
-      <c r="D3" s="425" t="s">
+      <c r="D3" s="421" t="s">
         <v>1898</v>
       </c>
-      <c r="E3" s="425" t="s">
+      <c r="E3" s="421" t="s">
         <v>1857</v>
       </c>
-      <c r="F3" s="425" t="s">
+      <c r="F3" s="421" t="s">
         <v>1899</v>
       </c>
-      <c r="G3" s="432" t="s">
+      <c r="G3" s="428" t="s">
         <v>1858</v>
       </c>
-      <c r="H3" s="433">
+      <c r="H3" s="429">
         <v>6</v>
       </c>
-      <c r="I3" s="416">
+      <c r="I3">
         <v>1.08</v>
       </c>
-      <c r="J3" s="417">
+      <c r="J3" s="414">
         <v>91</v>
       </c>
-      <c r="K3" s="417">
+      <c r="K3" s="414">
         <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="416" t="s">
+      <c r="A4" t="s">
         <v>1859</v>
       </c>
-      <c r="B4" s="416" t="s">
+      <c r="B4" t="s">
         <v>1860</v>
       </c>
-      <c r="C4" s="420">
+      <c r="C4" s="416">
         <v>85</v>
       </c>
-      <c r="D4" s="425" t="s">
+      <c r="D4" s="421" t="s">
         <v>1900</v>
       </c>
-      <c r="E4" s="425" t="s">
+      <c r="E4" s="421" t="s">
         <v>1861</v>
       </c>
-      <c r="F4" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="432" t="s">
+      <c r="F4" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="428" t="s">
         <v>1862</v>
       </c>
-      <c r="H4" s="433">
+      <c r="H4" s="429">
         <v>6</v>
       </c>
-      <c r="I4" s="416">
+      <c r="I4">
         <v>1.27</v>
       </c>
-      <c r="J4" s="417">
+      <c r="J4" s="414">
         <v>60</v>
       </c>
-      <c r="K4" s="417">
+      <c r="K4" s="414">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="416" t="s">
+      <c r="A5" t="s">
         <v>803</v>
       </c>
-      <c r="B5" s="416" t="s">
+      <c r="B5" t="s">
         <v>1856</v>
       </c>
-      <c r="C5" s="420">
+      <c r="C5" s="416">
         <v>80</v>
       </c>
-      <c r="D5" s="425" t="s">
+      <c r="D5" s="421" t="s">
         <v>1901</v>
       </c>
-      <c r="E5" s="425" t="s">
+      <c r="E5" s="421" t="s">
         <v>1863</v>
       </c>
-      <c r="F5" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="432" t="s">
+      <c r="F5" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="428" t="s">
         <v>1864</v>
       </c>
-      <c r="H5" s="433">
+      <c r="H5" s="429">
         <v>6</v>
       </c>
-      <c r="I5" s="416">
+      <c r="I5">
         <v>1.29</v>
       </c>
-      <c r="J5" s="417">
+      <c r="J5" s="414">
         <v>77</v>
       </c>
-      <c r="K5" s="417">
+      <c r="K5" s="414">
         <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="416" t="s">
+      <c r="A6" t="s">
         <v>1541</v>
       </c>
-      <c r="B6" s="416" t="s">
+      <c r="B6" t="s">
         <v>1856</v>
       </c>
-      <c r="C6" s="420">
+      <c r="C6" s="416">
         <v>100</v>
       </c>
-      <c r="D6" s="425" t="s">
+      <c r="D6" s="421" t="s">
         <v>1902</v>
       </c>
-      <c r="E6" s="425" t="s">
+      <c r="E6" s="421" t="s">
         <v>1857</v>
       </c>
-      <c r="F6" s="425" t="s">
+      <c r="F6" s="421" t="s">
         <v>1899</v>
       </c>
-      <c r="G6" s="432" t="s">
+      <c r="G6" s="428" t="s">
         <v>1865</v>
       </c>
-      <c r="H6" s="433">
+      <c r="H6" s="429">
         <v>6</v>
       </c>
-      <c r="I6" s="416">
+      <c r="I6">
         <v>1.04</v>
       </c>
-      <c r="J6" s="417">
+      <c r="J6" s="414">
         <v>80</v>
       </c>
-      <c r="K6" s="417">
+      <c r="K6" s="414">
         <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="416" t="s">
+      <c r="A7" t="s">
         <v>1929</v>
       </c>
-      <c r="B7" s="416" t="s">
+      <c r="B7" t="s">
         <v>1860</v>
       </c>
-      <c r="C7" s="420">
+      <c r="C7" s="416">
         <v>40</v>
       </c>
-      <c r="D7" s="425" t="s">
+      <c r="D7" s="421" t="s">
         <v>1903</v>
       </c>
-      <c r="E7" s="425" t="s">
+      <c r="E7" s="421" t="s">
         <v>1869</v>
       </c>
-      <c r="F7" s="425" t="s">
+      <c r="F7" s="421" t="s">
         <v>1905</v>
       </c>
-      <c r="G7" s="432" t="s">
+      <c r="G7" s="428" t="s">
         <v>1870</v>
       </c>
-      <c r="H7" s="433">
+      <c r="H7" s="429">
         <v>10</v>
       </c>
-      <c r="I7" s="416">
+      <c r="I7">
         <v>1.02</v>
       </c>
-      <c r="J7" s="417">
+      <c r="J7" s="414">
         <v>52</v>
       </c>
-      <c r="K7" s="417">
+      <c r="K7" s="414">
         <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="416" t="s">
+      <c r="A8" t="s">
         <v>1930</v>
       </c>
-      <c r="B8" s="416" t="s">
+      <c r="B8" t="s">
         <v>1860</v>
       </c>
-      <c r="C8" s="420">
+      <c r="C8" s="416">
         <v>50</v>
       </c>
-      <c r="D8" s="425" t="s">
+      <c r="D8" s="421" t="s">
         <v>1903</v>
       </c>
-      <c r="E8" s="425" t="s">
+      <c r="E8" s="421" t="s">
         <v>1866</v>
       </c>
-      <c r="F8" s="425" t="s">
+      <c r="F8" s="421" t="s">
         <v>1869</v>
       </c>
-      <c r="G8" s="432" t="s">
+      <c r="G8" s="428" t="s">
         <v>1867</v>
       </c>
-      <c r="H8" s="433">
+      <c r="H8" s="429">
         <v>12</v>
       </c>
-      <c r="I8" s="416">
+      <c r="I8">
         <v>1.1299999999999999</v>
       </c>
-      <c r="J8" s="417">
+      <c r="J8" s="414">
         <v>60</v>
       </c>
-      <c r="K8" s="417">
+      <c r="K8" s="414">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="416" t="s">
+      <c r="A9" t="s">
         <v>1868</v>
       </c>
-      <c r="B9" s="416" t="s">
+      <c r="B9" t="s">
         <v>1860</v>
       </c>
-      <c r="C9" s="420">
+      <c r="C9" s="416">
         <v>50</v>
       </c>
-      <c r="D9" s="425" t="s">
+      <c r="D9" s="421" t="s">
         <v>1904</v>
       </c>
-      <c r="E9" s="425" t="s">
+      <c r="E9" s="421" t="s">
         <v>1866</v>
       </c>
-      <c r="F9" s="425" t="s">
+      <c r="F9" s="421" t="s">
         <v>1861</v>
       </c>
-      <c r="G9" s="432" t="s">
+      <c r="G9" s="428" t="s">
         <v>1867</v>
       </c>
-      <c r="H9" s="433">
+      <c r="H9" s="429">
         <v>12</v>
       </c>
-      <c r="I9" s="416">
+      <c r="I9">
         <v>1.22</v>
       </c>
-      <c r="J9" s="417">
+      <c r="J9" s="414">
         <v>175</v>
       </c>
-      <c r="K9" s="417">
+      <c r="K9" s="414">
         <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="416" t="s">
+      <c r="A10" t="s">
         <v>1538</v>
       </c>
-      <c r="B10" s="416" t="s">
+      <c r="B10" t="s">
         <v>1856</v>
       </c>
-      <c r="C10" s="420">
+      <c r="C10" s="416">
         <v>147</v>
       </c>
-      <c r="D10" s="425" t="s">
+      <c r="D10" s="421" t="s">
         <v>1906</v>
       </c>
-      <c r="E10" s="425" t="s">
+      <c r="E10" s="421" t="s">
         <v>1871</v>
       </c>
-      <c r="F10" s="425" t="s">
+      <c r="F10" s="421" t="s">
         <v>1883</v>
       </c>
-      <c r="G10" s="432" t="s">
+      <c r="G10" s="428" t="s">
         <v>1872</v>
       </c>
-      <c r="H10" s="433">
+      <c r="H10" s="429">
         <v>8</v>
       </c>
-      <c r="I10" s="416">
+      <c r="I10">
         <v>1.21</v>
       </c>
-      <c r="J10" s="417">
+      <c r="J10" s="414">
         <v>135</v>
       </c>
-      <c r="K10" s="417">
+      <c r="K10" s="414">
         <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="416" t="s">
+      <c r="A11" t="s">
         <v>1849</v>
       </c>
-      <c r="B11" s="416" t="s">
+      <c r="B11" t="s">
         <v>1856</v>
       </c>
-      <c r="C11" s="420">
+      <c r="C11" s="416">
         <v>78</v>
       </c>
-      <c r="D11" s="425" t="s">
+      <c r="D11" s="421" t="s">
         <v>1901</v>
       </c>
-      <c r="E11" s="425" t="s">
+      <c r="E11" s="421" t="s">
         <v>1863</v>
       </c>
-      <c r="F11" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="432" t="s">
+      <c r="F11" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="428" t="s">
         <v>1864</v>
       </c>
-      <c r="H11" s="433">
+      <c r="H11" s="429">
         <v>6</v>
       </c>
-      <c r="I11" s="416">
+      <c r="I11">
         <v>1.24</v>
       </c>
-      <c r="J11" s="417">
+      <c r="J11" s="414">
         <v>72</v>
       </c>
-      <c r="K11" s="417">
+      <c r="K11" s="414">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="416" t="s">
+      <c r="A12" t="s">
         <v>1536</v>
       </c>
-      <c r="B12" s="416" t="s">
+      <c r="B12" t="s">
         <v>1860</v>
       </c>
-      <c r="C12" s="420">
+      <c r="C12" s="416">
         <v>143</v>
       </c>
-      <c r="D12" s="425" t="s">
+      <c r="D12" s="421" t="s">
         <v>1907</v>
       </c>
-      <c r="E12" s="425" t="s">
+      <c r="E12" s="421" t="s">
         <v>1873</v>
       </c>
-      <c r="F12" s="425" t="s">
+      <c r="F12" s="421" t="s">
         <v>1908</v>
       </c>
-      <c r="G12" s="432" t="s">
+      <c r="G12" s="428" t="s">
         <v>1874</v>
       </c>
-      <c r="H12" s="433">
+      <c r="H12" s="429">
         <v>8</v>
       </c>
-      <c r="I12" s="416">
+      <c r="I12">
         <v>1.31</v>
       </c>
-      <c r="J12" s="417">
+      <c r="J12" s="414">
         <v>155</v>
       </c>
-      <c r="K12" s="417">
+      <c r="K12" s="414">
         <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="416" t="s">
+      <c r="A13" t="s">
         <v>1875</v>
       </c>
-      <c r="B13" s="418" t="s">
+      <c r="B13" s="1" t="s">
         <v>1928</v>
       </c>
-      <c r="C13" s="420">
+      <c r="C13" s="416">
         <v>161</v>
       </c>
-      <c r="D13" s="425" t="s">
+      <c r="D13" s="421" t="s">
         <v>1909</v>
       </c>
-      <c r="E13" s="425" t="s">
+      <c r="E13" s="421" t="s">
         <v>1876</v>
       </c>
-      <c r="F13" s="425" t="s">
+      <c r="F13" s="421" t="s">
         <v>1876</v>
       </c>
-      <c r="G13" s="432" t="s">
+      <c r="G13" s="428" t="s">
         <v>1874</v>
       </c>
-      <c r="H13" s="433">
+      <c r="H13" s="429">
         <v>8</v>
       </c>
-      <c r="I13" s="416">
+      <c r="I13">
         <v>1.28</v>
       </c>
-      <c r="J13" s="417">
+      <c r="J13" s="414">
         <v>157</v>
       </c>
-      <c r="K13" s="417">
+      <c r="K13" s="414">
         <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="416" t="s">
+      <c r="A14" t="s">
         <v>1877</v>
       </c>
-      <c r="B14" s="416" t="s">
+      <c r="B14" t="s">
         <v>1856</v>
       </c>
-      <c r="C14" s="420">
+      <c r="C14" s="416">
         <v>225</v>
       </c>
-      <c r="D14" s="425" t="s">
+      <c r="D14" s="421" t="s">
         <v>1910</v>
       </c>
-      <c r="E14" s="425" t="s">
+      <c r="E14" s="421" t="s">
         <v>1878</v>
       </c>
-      <c r="F14" s="425" t="s">
+      <c r="F14" s="421" t="s">
         <v>1911</v>
       </c>
-      <c r="G14" s="432" t="s">
+      <c r="G14" s="428" t="s">
         <v>1879</v>
       </c>
-      <c r="H14" s="433">
+      <c r="H14" s="429">
         <v>6</v>
       </c>
-      <c r="I14" s="416">
+      <c r="I14">
         <v>1.38</v>
       </c>
-      <c r="J14" s="417">
+      <c r="J14" s="414">
         <v>207</v>
       </c>
-      <c r="K14" s="417">
+      <c r="K14" s="414">
         <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="416" t="s">
+      <c r="A15" t="s">
         <v>1931</v>
       </c>
-      <c r="B15" s="416" t="s">
+      <c r="B15" t="s">
         <v>1860</v>
       </c>
-      <c r="C15" s="420">
+      <c r="C15" s="416">
         <v>77</v>
       </c>
-      <c r="D15" s="425" t="s">
+      <c r="D15" s="421" t="s">
         <v>1912</v>
       </c>
-      <c r="E15" s="425" t="s">
+      <c r="E15" s="421" t="s">
         <v>1858</v>
       </c>
-      <c r="F15" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="432" t="s">
+      <c r="F15" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="428" t="s">
         <v>1880</v>
       </c>
-      <c r="H15" s="433">
+      <c r="H15" s="429">
         <v>6</v>
       </c>
-      <c r="I15" s="416">
+      <c r="I15">
         <v>1.35</v>
       </c>
-      <c r="J15" s="417">
+      <c r="J15" s="414">
         <v>72</v>
       </c>
-      <c r="K15" s="417">
+      <c r="K15" s="414">
         <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="416" t="s">
+      <c r="A16" t="s">
         <v>1529</v>
       </c>
-      <c r="B16" s="416" t="s">
+      <c r="B16" t="s">
         <v>1856</v>
       </c>
-      <c r="C16" s="420">
+      <c r="C16" s="416">
         <v>77</v>
       </c>
-      <c r="D16" s="425" t="s">
+      <c r="D16" s="421" t="s">
         <v>1913</v>
       </c>
-      <c r="E16" s="425" t="s">
+      <c r="E16" s="421" t="s">
         <v>1863</v>
       </c>
-      <c r="F16" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="432" t="s">
+      <c r="F16" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="428" t="s">
         <v>1864</v>
       </c>
-      <c r="H16" s="433">
+      <c r="H16" s="429">
         <v>6</v>
       </c>
-      <c r="I16" s="416">
+      <c r="I16">
         <v>1.28</v>
       </c>
-      <c r="J16" s="417">
+      <c r="J16" s="414">
         <v>70</v>
       </c>
-      <c r="K16" s="417">
+      <c r="K16" s="414">
         <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="416" t="s">
+      <c r="A17" t="s">
         <v>1530</v>
       </c>
-      <c r="B17" s="416" t="s">
+      <c r="B17" t="s">
         <v>1860</v>
       </c>
-      <c r="C17" s="420">
+      <c r="C17" s="416">
         <v>57</v>
       </c>
-      <c r="D17" s="425" t="s">
+      <c r="D17" s="421" t="s">
         <v>1900</v>
       </c>
-      <c r="E17" s="425" t="s">
+      <c r="E17" s="421" t="s">
         <v>1881</v>
       </c>
-      <c r="F17" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="432" t="s">
+      <c r="F17" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="428" t="s">
         <v>1882</v>
       </c>
-      <c r="H17" s="433">
+      <c r="H17" s="429">
         <v>6</v>
       </c>
-      <c r="I17" s="416">
+      <c r="I17">
         <v>1.25</v>
       </c>
-      <c r="J17" s="417">
+      <c r="J17" s="414">
         <v>53</v>
       </c>
-      <c r="K17" s="417">
+      <c r="K17" s="414">
         <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="416" t="s">
+      <c r="A18" t="s">
         <v>1933</v>
       </c>
-      <c r="B18" s="416" t="s">
+      <c r="B18" t="s">
         <v>1860</v>
       </c>
-      <c r="C18" s="420">
+      <c r="C18" s="416">
         <v>-60</v>
       </c>
-      <c r="D18" s="425" t="s">
+      <c r="D18" s="421" t="s">
         <v>1914</v>
       </c>
-      <c r="E18" s="425" t="s">
+      <c r="E18" s="421" t="s">
         <v>1883</v>
       </c>
-      <c r="F18" s="425" t="s">
+      <c r="F18" s="421" t="s">
         <v>1866</v>
       </c>
-      <c r="G18" s="432" t="s">
+      <c r="G18" s="428" t="s">
         <v>1867</v>
       </c>
-      <c r="H18" s="433">
+      <c r="H18" s="429">
         <v>6</v>
       </c>
-      <c r="I18" s="416">
+      <c r="I18">
         <v>1.42</v>
       </c>
-      <c r="J18" s="417">
+      <c r="J18" s="414">
         <v>110</v>
       </c>
-      <c r="K18" s="417">
+      <c r="K18" s="414">
         <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="416" t="s">
+      <c r="A19" t="s">
         <v>1850</v>
       </c>
-      <c r="B19" s="416" t="s">
+      <c r="B19" t="s">
         <v>1860</v>
       </c>
-      <c r="C19" s="420">
+      <c r="C19" s="416">
         <v>105</v>
       </c>
-      <c r="D19" s="425" t="s">
+      <c r="D19" s="421" t="s">
         <v>1915</v>
       </c>
-      <c r="E19" s="425" t="s">
+      <c r="E19" s="421" t="s">
         <v>1884</v>
       </c>
-      <c r="F19" s="425" t="s">
+      <c r="F19" s="421" t="s">
         <v>1916</v>
       </c>
-      <c r="G19" s="432" t="s">
+      <c r="G19" s="428" t="s">
         <v>1857</v>
       </c>
-      <c r="H19" s="433">
+      <c r="H19" s="429">
         <v>10</v>
       </c>
-      <c r="I19" s="416">
+      <c r="I19">
         <v>1.17</v>
       </c>
-      <c r="J19" s="417">
+      <c r="J19" s="414">
         <v>112</v>
       </c>
-      <c r="K19" s="417">
+      <c r="K19" s="414">
         <v>215</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="416" t="s">
+      <c r="A20" t="s">
         <v>1932</v>
       </c>
-      <c r="B20" s="416" t="s">
+      <c r="B20" t="s">
         <v>1860</v>
       </c>
-      <c r="C20" s="420">
+      <c r="C20" s="416">
         <v>85</v>
       </c>
-      <c r="D20" s="425" t="s">
+      <c r="D20" s="421" t="s">
         <v>1917</v>
       </c>
-      <c r="E20" s="425" t="s">
+      <c r="E20" s="421" t="s">
         <v>1885</v>
       </c>
-      <c r="F20" s="425" t="s">
+      <c r="F20" s="421" t="s">
         <v>1866</v>
       </c>
-      <c r="G20" s="432" t="s">
+      <c r="G20" s="428" t="s">
         <v>1871</v>
       </c>
-      <c r="H20" s="433">
+      <c r="H20" s="429">
         <v>8</v>
       </c>
-      <c r="I20" s="416">
+      <c r="I20">
         <v>1.37</v>
       </c>
-      <c r="J20" s="417">
+      <c r="J20" s="414">
         <v>120</v>
       </c>
-      <c r="K20" s="417">
+      <c r="K20" s="414">
         <v>220</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="418" t="s">
+      <c r="A21" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B21" s="416" t="s">
+      <c r="B21" t="s">
         <v>1860</v>
       </c>
-      <c r="C21" s="420">
+      <c r="C21" s="416">
         <v>85</v>
       </c>
-      <c r="D21" s="425" t="s">
+      <c r="D21" s="421" t="s">
         <v>1918</v>
       </c>
-      <c r="E21" s="425" t="s">
+      <c r="E21" s="421" t="s">
         <v>1876</v>
       </c>
-      <c r="F21" s="425" t="s">
+      <c r="F21" s="421" t="s">
         <v>1866</v>
       </c>
-      <c r="G21" s="432" t="s">
+      <c r="G21" s="428" t="s">
         <v>1871</v>
       </c>
-      <c r="H21" s="433">
+      <c r="H21" s="429">
         <v>8</v>
       </c>
-      <c r="I21" s="416">
+      <c r="I21">
         <v>1.44</v>
       </c>
-      <c r="J21" s="417">
+      <c r="J21" s="414">
         <v>240</v>
       </c>
-      <c r="K21" s="417">
+      <c r="K21" s="414">
         <v>267</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="416" t="s">
+      <c r="A22" t="s">
         <v>1535</v>
       </c>
-      <c r="B22" s="416" t="s">
+      <c r="B22" t="s">
         <v>1856</v>
       </c>
-      <c r="C22" s="420">
+      <c r="C22" s="416">
         <v>220</v>
       </c>
-      <c r="D22" s="425" t="s">
+      <c r="D22" s="421" t="s">
         <v>1919</v>
       </c>
-      <c r="E22" s="425" t="s">
+      <c r="E22" s="421" t="s">
         <v>1878</v>
       </c>
-      <c r="F22" s="425" t="s">
+      <c r="F22" s="421" t="s">
         <v>1920</v>
       </c>
-      <c r="G22" s="432" t="s">
+      <c r="G22" s="428" t="s">
         <v>1879</v>
       </c>
-      <c r="H22" s="433">
+      <c r="H22" s="429">
         <v>6</v>
       </c>
-      <c r="I22" s="416">
+      <c r="I22">
         <v>1.3</v>
       </c>
-      <c r="J22" s="417">
+      <c r="J22" s="414">
         <v>210</v>
       </c>
-      <c r="K22" s="417">
+      <c r="K22" s="414">
         <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="416" t="s">
+      <c r="A23" t="s">
         <v>1537</v>
       </c>
-      <c r="B23" s="416" t="s">
+      <c r="B23" t="s">
         <v>1856</v>
       </c>
-      <c r="C23" s="420">
+      <c r="C23" s="416">
         <v>185</v>
       </c>
-      <c r="D23" s="425" t="s">
+      <c r="D23" s="421" t="s">
         <v>1921</v>
       </c>
-      <c r="E23" s="425" t="s">
+      <c r="E23" s="421" t="s">
         <v>1879</v>
       </c>
-      <c r="F23" s="425" t="s">
+      <c r="F23" s="421" t="s">
         <v>1878</v>
       </c>
-      <c r="G23" s="432" t="s">
+      <c r="G23" s="428" t="s">
         <v>1885</v>
       </c>
-      <c r="H23" s="433">
+      <c r="H23" s="429">
         <v>6</v>
       </c>
-      <c r="I23" s="416">
+      <c r="I23">
         <v>1.25</v>
       </c>
-      <c r="J23" s="417">
+      <c r="J23" s="414">
         <v>177</v>
       </c>
-      <c r="K23" s="417">
+      <c r="K23" s="414">
         <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="416" t="s">
+      <c r="A24" t="s">
         <v>1540</v>
       </c>
-      <c r="B24" s="416" t="s">
+      <c r="B24" t="s">
         <v>1860</v>
       </c>
-      <c r="C24" s="421"/>
-      <c r="D24" s="425" t="s">
+      <c r="C24" s="417"/>
+      <c r="D24" s="421" t="s">
         <v>1903</v>
       </c>
-      <c r="E24" s="425" t="s">
+      <c r="E24" s="421" t="s">
         <v>1886</v>
       </c>
-      <c r="F24" s="425" t="s">
+      <c r="F24" s="421" t="s">
         <v>1922</v>
       </c>
-      <c r="G24" s="432" t="s">
+      <c r="G24" s="428" t="s">
         <v>1858</v>
       </c>
-      <c r="H24" s="433">
+      <c r="H24" s="429">
         <v>6</v>
       </c>
-      <c r="I24" s="416">
+      <c r="I24">
         <v>1.76</v>
       </c>
-      <c r="J24" s="417">
+      <c r="J24" s="414">
         <v>107</v>
       </c>
-      <c r="K24" s="417">
+      <c r="K24" s="414">
         <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="416" t="s">
+      <c r="A25" t="s">
         <v>1887</v>
       </c>
-      <c r="B25" s="416" t="s">
+      <c r="B25" t="s">
         <v>1888</v>
       </c>
-      <c r="C25" s="421"/>
-      <c r="D25" s="425" t="s">
+      <c r="C25" s="417"/>
+      <c r="D25" s="421" t="s">
         <v>1896</v>
       </c>
-      <c r="E25" s="425" t="s">
+      <c r="E25" s="421" t="s">
         <v>1881</v>
       </c>
-      <c r="F25" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G25" s="432" t="s">
+      <c r="F25" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G25" s="428" t="s">
         <v>1865</v>
       </c>
-      <c r="H25" s="433">
+      <c r="H25" s="429">
         <v>6</v>
       </c>
-      <c r="I25" s="416">
+      <c r="I25">
         <v>1.18</v>
       </c>
-      <c r="J25" s="417" t="s">
+      <c r="J25" s="414" t="s">
         <v>1889</v>
       </c>
-      <c r="K25" s="417" t="s">
+      <c r="K25" s="414" t="s">
         <v>1889</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="416" t="s">
+      <c r="A26" t="s">
         <v>1533</v>
       </c>
-      <c r="B26" s="416" t="s">
+      <c r="B26" t="s">
         <v>1888</v>
       </c>
-      <c r="C26" s="421"/>
-      <c r="D26" s="425" t="s">
+      <c r="C26" s="417"/>
+      <c r="D26" s="421" t="s">
         <v>1923</v>
       </c>
-      <c r="E26" s="425" t="s">
+      <c r="E26" s="421" t="s">
         <v>1881</v>
       </c>
-      <c r="F26" s="427" t="s">
-        <v>1</v>
-      </c>
-      <c r="G26" s="432" t="s">
+      <c r="F26" s="423" t="s">
+        <v>1</v>
+      </c>
+      <c r="G26" s="428" t="s">
         <v>1865</v>
       </c>
-      <c r="H26" s="433">
+      <c r="H26" s="429">
         <v>6</v>
       </c>
-      <c r="I26" s="416">
+      <c r="I26">
         <v>1.22</v>
       </c>
-      <c r="J26" s="417" t="s">
+      <c r="J26" s="414" t="s">
         <v>1889</v>
       </c>
-      <c r="K26" s="417" t="s">
+      <c r="K26" s="414" t="s">
         <v>1889</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="416" t="s">
+      <c r="A27" t="s">
         <v>1890</v>
       </c>
-      <c r="B27" s="416" t="s">
+      <c r="B27" t="s">
         <v>1856</v>
       </c>
-      <c r="C27" s="420">
+      <c r="C27" s="416">
         <v>216</v>
       </c>
-      <c r="D27" s="425" t="s">
+      <c r="D27" s="421" t="s">
         <v>1924</v>
       </c>
-      <c r="E27" s="425" t="s">
+      <c r="E27" s="421" t="s">
         <v>1878</v>
       </c>
-      <c r="F27" s="425" t="s">
+      <c r="F27" s="421" t="s">
         <v>1925</v>
       </c>
-      <c r="G27" s="432" t="s">
+      <c r="G27" s="428" t="s">
         <v>1879</v>
       </c>
-      <c r="H27" s="433">
+      <c r="H27" s="429">
         <v>6</v>
       </c>
-      <c r="I27" s="416">
+      <c r="I27">
         <v>1.28</v>
       </c>
-      <c r="J27" s="417">
+      <c r="J27" s="414">
         <v>205</v>
       </c>
-      <c r="K27" s="417">
+      <c r="K27" s="414">
         <v>213</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A28" s="416" t="s">
+      <c r="A28" t="s">
         <v>1891</v>
       </c>
-      <c r="B28" s="416" t="s">
+      <c r="B28" t="s">
         <v>1856</v>
       </c>
-      <c r="C28" s="422">
+      <c r="C28" s="418">
         <v>181</v>
       </c>
-      <c r="D28" s="426" t="s">
+      <c r="D28" s="422" t="s">
         <v>1926</v>
       </c>
-      <c r="E28" s="426" t="s">
+      <c r="E28" s="422" t="s">
         <v>1879</v>
       </c>
-      <c r="F28" s="426" t="s">
+      <c r="F28" s="422" t="s">
         <v>1927</v>
       </c>
-      <c r="G28" s="434" t="s">
+      <c r="G28" s="430" t="s">
         <v>1885</v>
       </c>
-      <c r="H28" s="435">
+      <c r="H28" s="431">
         <v>6</v>
       </c>
-      <c r="I28" s="416">
+      <c r="I28">
         <v>1.34</v>
       </c>
-      <c r="J28" s="417">
+      <c r="J28" s="414">
         <v>170</v>
       </c>
-      <c r="K28" s="417">
+      <c r="K28" s="414">
         <v>178</v>
       </c>
     </row>
@@ -34675,11 +34708,11 @@
       <c r="E33" s="29"/>
     </row>
     <row r="34" spans="1:5" ht="19.5" thickBot="1">
-      <c r="B34" s="414" t="s">
+      <c r="B34" s="432" t="s">
         <v>552</v>
       </c>
-      <c r="C34" s="414"/>
-      <c r="D34" s="414"/>
+      <c r="C34" s="432"/>
+      <c r="D34" s="432"/>
     </row>
     <row r="35" spans="1:5" ht="30">
       <c r="A35" s="225"/>

--- a/BOM/Valkyrie V2 Build Guide.xlsx
+++ b/BOM/Valkyrie V2 Build Guide.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10872" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D9A92D6-2FA1-405A-9FEF-ECFBA5000332}"/>
+  <xr:revisionPtr revIDLastSave="10873" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA6627CD-FF2C-4926-8AAE-C67853D688C7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="11" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="52" r:id="rId1"/>
@@ -8782,6 +8782,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
@@ -8791,13 +8794,14 @@
       <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -8817,10 +8821,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -8860,6 +8860,24 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -8968,29 +8986,8 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9009,6 +9006,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9067,9 +9067,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9086,6 +9083,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9144,9 +9144,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9163,6 +9160,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9221,9 +9221,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9240,6 +9237,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9298,9 +9298,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9317,6 +9314,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -9375,15 +9375,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9402,6 +9393,7 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9454,6 +9446,14 @@
       </font>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color rgb="FF000000"/>
@@ -9504,15 +9504,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9531,6 +9522,7 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9583,6 +9575,14 @@
       </font>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color rgb="FF000000"/>
@@ -9617,15 +9617,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9644,6 +9635,7 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -9696,6 +9688,14 @@
       </font>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color rgb="FF000000"/>
@@ -9730,9 +9730,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -9749,6 +9746,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -10083,13 +10083,6 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -10114,6 +10107,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -10326,8 +10326,8 @@
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1724025</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
       <xdr:row>195</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
@@ -11529,6 +11529,10 @@
 </namedSheetViews>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{DBE9A247-92C8-4088-ACE5-271A69C73D57}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
   <queryTableRefresh nextId="3">
@@ -11541,7 +11545,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J157" totalsRowShown="0" headerRowDxfId="147" dataDxfId="146" headerRowBorderDxfId="144" tableBorderDxfId="145" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:J157" totalsRowShown="0" headerRowDxfId="147" dataDxfId="145" headerRowBorderDxfId="146" tableBorderDxfId="144" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:J157" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J157">
     <sortCondition ref="A1:A157"/>
@@ -11573,7 +11577,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="73" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="70" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="71" totalsRowDxfId="70" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11588,7 +11592,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="67" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="64" totalsRowDxfId="65" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="65" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11601,20 +11605,20 @@
     <sortCondition ref="A1:A111"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" totalsRowLabel="Valkyrie V2" dataDxfId="61" totalsRowDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{AE4E9077-B04D-4FB7-A226-807DE24B3CEE}" name="Filament Type" dataDxfId="59" totalsRowDxfId="60"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="57" totalsRowDxfId="58"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" totalsRowLabel="Valkyrie V2" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{AE4E9077-B04D-4FB7-A226-807DE24B3CEE}" name="Filament Type" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="58" totalsRowDxfId="57"/>
     <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="54" totalsRowDxfId="55" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="Weight Tot" totalsRowFunction="custom" dataDxfId="52" totalsRowDxfId="53" dataCellStyle="Normal 7">
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="QTY" totalsRowFunction="sum" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="Weight Tot" totalsRowFunction="custom" dataDxfId="53" totalsRowDxfId="52" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[Weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="50" totalsRowDxfId="51">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="51" totalsRowDxfId="50">
       <calculatedColumnFormula>$L$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="48" totalsRowDxfId="49"/>
-    <tableColumn id="5" xr3:uid="{CBC7571F-19BC-4246-AB6F-92AD07297E48}" name="Time Total" totalsRowFunction="sum" dataDxfId="46" totalsRowDxfId="47">
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time/item" totalsRowFunction="sum" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{CBC7571F-19BC-4246-AB6F-92AD07297E48}" name="Time Total" totalsRowFunction="sum" dataDxfId="47" totalsRowDxfId="46">
       <calculatedColumnFormula>Table6[[#This Row],[Time/item]]*Table6[[#This Row],[QTY]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -11798,7 +11802,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="124" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="123" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="121" totalsRowDxfId="122" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="122" totalsRowDxfId="121" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11811,9 +11815,9 @@
     <sortCondition ref="B1:B59"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" dataDxfId="116" totalsRowDxfId="117" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" dataDxfId="114" totalsRowDxfId="115" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="112" totalsRowDxfId="113" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" dataDxfId="117" totalsRowDxfId="116" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" dataDxfId="115" totalsRowDxfId="114" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="113" totalsRowDxfId="112" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11826,9 +11830,9 @@
     <sortCondition ref="B1:B33"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" dataDxfId="107" totalsRowDxfId="108" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" dataDxfId="105" totalsRowDxfId="106" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="103" totalsRowDxfId="104" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" dataDxfId="108" totalsRowDxfId="107" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" dataDxfId="106" totalsRowDxfId="105" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="104" totalsRowDxfId="103" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11841,9 +11845,9 @@
     <sortCondition ref="B35:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" dataDxfId="98" totalsRowDxfId="99" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" dataDxfId="96" totalsRowDxfId="97" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="94" totalsRowDxfId="95" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" dataDxfId="99" totalsRowDxfId="98" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" dataDxfId="97" totalsRowDxfId="96" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="95" totalsRowDxfId="94" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11858,7 +11862,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="91" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="90" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="88" totalsRowDxfId="89" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="89" totalsRowDxfId="88" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11873,7 +11877,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="85" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="84" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="82" totalsRowDxfId="83" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="83" totalsRowDxfId="82" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11888,7 +11892,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DE5B6A3D-F02B-442F-8F0E-2D97466E9D55}" name="Part name" totalsRowDxfId="79" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{CD84E571-7957-4B8F-9F34-DA3FA6BF0E23}" name="Description" totalsRowDxfId="78" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{52F63DEF-0CA0-45D5-85B8-E41A21AD2000}" name="BOM Quantity" dataDxfId="76" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{52F63DEF-0CA0-45D5-85B8-E41A21AD2000}" name="BOM Quantity" dataDxfId="77" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -19406,7 +19410,7 @@
     <col min="1" max="1" width="14.140625" style="83" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="83" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.42578125" style="83" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="83" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="83" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" style="83" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="83" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" style="93" bestFit="1" customWidth="1"/>
@@ -36136,5 +36140,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{104F2E57-B689-41C7-9E9B-C2B84A40008B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{104F2E57-B689-41C7-9E9B-C2B84A40008B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/BOM/Valkyrie V2 Build Guide.xlsx
+++ b/BOM/Valkyrie V2 Build Guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11925" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C31E46F-3861-4239-B493-3C4F617BD276}"/>
+  <xr:revisionPtr revIDLastSave="11926" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE31993B-7684-4AAF-8E38-CAC161F15383}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="36000" yWindow="0" windowWidth="21600" windowHeight="11295" firstSheet="15" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="52" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3853" uniqueCount="2009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3852" uniqueCount="2008">
   <si>
     <t>BULD ORDER RECOMMENDATION</t>
   </si>
@@ -6592,9 +6592,6 @@
   </si>
   <si>
     <t>AB motor cover cover?</t>
-  </si>
-  <si>
-    <t>Deisgn?</t>
   </si>
   <si>
     <t>Bed fuse</t>
@@ -18266,9 +18263,9 @@
     <hyperlink ref="K20" location="INDEX!A1" display="INDEX" xr:uid="{BD619518-AB10-4FF5-B7AB-B7A36FF693FD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="44" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -32512,7 +32509,7 @@
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.39370078740157483" header="0.11811023622047245" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" r:id="rId160"/>
+  <pageSetup paperSize="9" scale="43" fitToHeight="0" orientation="portrait" r:id="rId160"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Aptos Black,Regular"&amp;14VALKYRIE V2 - HW BOM</oddHeader>
     <oddFooter>&amp;CV2 BETA&amp;R&amp;P of &amp;N</oddFooter>
@@ -33327,7 +33324,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="62.140625" customWidth="1"/>
@@ -33582,22 +33579,22 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -33608,11 +33605,6 @@
     <row r="46" spans="1:1">
       <c r="A46" t="s">
         <v>2007</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>2008</v>
       </c>
     </row>
   </sheetData>

--- a/BOM/Valkyrie V2 Build Guide.xlsx
+++ b/BOM/Valkyrie V2 Build Guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11970" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{633A85F9-B5EF-48E3-B300-3936EC5131DD}"/>
+  <xr:revisionPtr revIDLastSave="11971" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A71402B8-9E38-4E95-9D2D-E22A34A7C64D}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="1" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="52" r:id="rId1"/>
@@ -36,16 +36,6 @@
     <sheet name="Tools &amp; Misc" sheetId="30" r:id="rId21"/>
     <sheet name="RECOMMEND SPARES" sheetId="55" r:id="rId22"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId23"/>
-    <externalReference r:id="rId24"/>
-    <externalReference r:id="rId25"/>
-    <externalReference r:id="rId26"/>
-    <externalReference r:id="rId27"/>
-    <externalReference r:id="rId28"/>
-    <externalReference r:id="rId29"/>
-    <externalReference r:id="rId30"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COMPLETE PARTS LIST'!$A$1:$K$160</definedName>
     <definedName name="ExternalData_1" localSheetId="12" hidden="1">'Firmware Configuration'!$A$1:$B$163</definedName>
@@ -8446,9 +8436,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -8582,6 +8569,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="15">
@@ -12111,110 +12101,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Duet 3 6HC Configuration"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Duet 3 6HC connections"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Macro &amp; system names "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Filament Material Guide"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Mains Wiring C"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="V2 NEW FEATURES"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Recomended spares "/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="FRONT PAGE"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{27F7A75C-E459-4D9D-9A0C-6BE28065E6EE}">
@@ -12999,10 +12885,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -13014,10 +12900,10 @@
       <c r="B2" s="6" t="s">
         <v>638</v>
       </c>
-      <c r="C2" s="402" t="s">
+      <c r="C2" s="401" t="s">
         <v>639</v>
       </c>
-      <c r="D2" s="415">
+      <c r="D2" s="414">
         <v>6</v>
       </c>
       <c r="E2" s="24" t="s">
@@ -13028,16 +12914,16 @@
       <c r="A3" s="167" t="s">
         <v>420</v>
       </c>
-      <c r="B3" s="390" t="s">
+      <c r="B3" s="389" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="390" t="s">
+      <c r="C3" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D3" s="390">
-        <v>1</v>
-      </c>
-      <c r="E3" s="408" t="s">
+      <c r="D3" s="389">
+        <v>1</v>
+      </c>
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -13048,13 +12934,13 @@
       <c r="B4" t="s">
         <v>640</v>
       </c>
-      <c r="C4" s="390" t="s">
+      <c r="C4" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D4" s="390">
+      <c r="D4" s="389">
         <v>4</v>
       </c>
-      <c r="E4" s="408" t="s">
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -13062,36 +12948,36 @@
       <c r="A5" s="167" t="s">
         <v>426</v>
       </c>
-      <c r="B5" s="390" t="s">
+      <c r="B5" s="389" t="s">
         <v>371</v>
       </c>
-      <c r="C5" s="390" t="s">
+      <c r="C5" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D5" s="390">
+      <c r="D5" s="389">
         <v>3</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
       <c r="B6" s="6" t="s">
         <v>641</v>
       </c>
-      <c r="C6" s="390" t="s">
+      <c r="C6" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D6" s="390">
+      <c r="D6" s="389">
         <v>1</v>
       </c>
       <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="390" t="s">
+      <c r="B7" s="389" t="s">
         <v>642</v>
       </c>
-      <c r="C7" s="390" t="s">
+      <c r="C7" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D7" s="2">
@@ -13101,26 +12987,26 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11"/>
-      <c r="B8" s="390" t="s">
+      <c r="B8" s="389" t="s">
         <v>643</v>
       </c>
-      <c r="C8" s="390" t="s">
+      <c r="C8" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D8" s="390">
+      <c r="D8" s="389">
         <v>1</v>
       </c>
       <c r="E8" s="25"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="11"/>
-      <c r="B9" s="391" t="s">
+      <c r="B9" s="390" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="390" t="s">
+      <c r="C9" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D9" s="390">
+      <c r="D9" s="389">
         <v>1</v>
       </c>
       <c r="E9" s="25"/>
@@ -13130,33 +13016,33 @@
       <c r="B10" s="15" t="s">
         <v>645</v>
       </c>
-      <c r="C10" s="390" t="s">
+      <c r="C10" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D10" s="390">
+      <c r="D10" s="389">
         <v>1</v>
       </c>
       <c r="E10" s="25"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="11"/>
-      <c r="B11" s="390" t="s">
+      <c r="B11" s="389" t="s">
         <v>646</v>
       </c>
-      <c r="C11" s="390" t="s">
+      <c r="C11" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D11" s="389">
+      <c r="D11" s="388">
         <v>1</v>
       </c>
       <c r="E11" s="25"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="11"/>
-      <c r="B12" s="390" t="s">
+      <c r="B12" s="389" t="s">
         <v>647</v>
       </c>
-      <c r="C12" s="390" t="s">
+      <c r="C12" s="389" t="s">
         <v>644</v>
       </c>
       <c r="D12" s="2">
@@ -13168,13 +13054,13 @@
       <c r="A13" s="167" t="s">
         <v>436</v>
       </c>
-      <c r="B13" s="390" t="s">
+      <c r="B13" s="389" t="s">
         <v>648</v>
       </c>
-      <c r="C13" s="390" t="s">
+      <c r="C13" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D13" s="389">
+      <c r="D13" s="388">
         <v>1</v>
       </c>
       <c r="E13" s="25"/>
@@ -13184,10 +13070,10 @@
       <c r="B14" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="390" t="s">
+      <c r="C14" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D14" s="390">
+      <c r="D14" s="389">
         <v>1</v>
       </c>
       <c r="E14" s="25"/>
@@ -13197,36 +13083,36 @@
       <c r="B15" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="C15" s="390" t="s">
+      <c r="C15" s="389" t="s">
         <v>644</v>
       </c>
-      <c r="D15" s="390">
-        <v>1</v>
-      </c>
-      <c r="E15" s="413"/>
+      <c r="D15" s="389">
+        <v>1</v>
+      </c>
+      <c r="E15" s="412"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11"/>
       <c r="B16" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="C16" s="390" t="s">
+      <c r="C16" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D16" s="390">
+      <c r="D16" s="389">
         <v>5</v>
       </c>
-      <c r="E16" s="413"/>
+      <c r="E16" s="412"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="11"/>
       <c r="B17" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="C17" s="390" t="s">
+      <c r="C17" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D17" s="390">
+      <c r="D17" s="389">
         <v>10</v>
       </c>
       <c r="E17" s="25"/>
@@ -13236,23 +13122,23 @@
       <c r="B18" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="C18" s="390" t="s">
+      <c r="C18" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D18" s="390">
+      <c r="D18" s="389">
         <v>5</v>
       </c>
       <c r="E18" s="25"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="11"/>
-      <c r="B19" s="390" t="s">
+      <c r="B19" s="389" t="s">
         <v>650</v>
       </c>
-      <c r="C19" s="390" t="s">
+      <c r="C19" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D19" s="390">
+      <c r="D19" s="389">
         <v>5</v>
       </c>
       <c r="E19" s="25"/>
@@ -13262,7 +13148,7 @@
       <c r="B20" t="s">
         <v>651</v>
       </c>
-      <c r="C20" s="390" t="s">
+      <c r="C20" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D20">
@@ -13275,7 +13161,7 @@
       <c r="B21" t="s">
         <v>652</v>
       </c>
-      <c r="C21" s="390" t="s">
+      <c r="C21" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D21">
@@ -13288,7 +13174,7 @@
       <c r="B22" t="s">
         <v>653</v>
       </c>
-      <c r="C22" s="390" t="s">
+      <c r="C22" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D22">
@@ -13301,62 +13187,62 @@
       <c r="B23" t="s">
         <v>654</v>
       </c>
-      <c r="C23" s="390" t="s">
+      <c r="C23" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
-      <c r="E23" s="413"/>
+      <c r="E23" s="412"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="11"/>
       <c r="B24" t="s">
         <v>655</v>
       </c>
-      <c r="C24" s="390" t="s">
+      <c r="C24" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
-      <c r="E24" s="413"/>
+      <c r="E24" s="412"/>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="11"/>
       <c r="B25" t="s">
         <v>656</v>
       </c>
-      <c r="C25" s="390" t="s">
+      <c r="C25" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
-      <c r="E25" s="413"/>
+      <c r="E25" s="412"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="11"/>
       <c r="B26" t="s">
         <v>657</v>
       </c>
-      <c r="C26" s="390" t="s">
+      <c r="C26" s="389" t="s">
         <v>639</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26" s="413"/>
+      <c r="E26" s="412"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="11"/>
       <c r="B27" t="s">
         <v>658</v>
       </c>
-      <c r="C27" s="390" t="s">
+      <c r="C27" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D27" s="390">
+      <c r="D27" s="389">
         <v>2</v>
       </c>
       <c r="E27" s="25"/>
@@ -13369,10 +13255,10 @@
       <c r="B28" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="390" t="s">
+      <c r="C28" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D28" s="390">
+      <c r="D28" s="389">
         <v>2</v>
       </c>
       <c r="E28" s="68"/>
@@ -13382,10 +13268,10 @@
       <c r="B29" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C29" s="390" t="s">
+      <c r="C29" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D29" s="390">
+      <c r="D29" s="389">
         <v>1</v>
       </c>
       <c r="E29" s="68"/>
@@ -13395,10 +13281,10 @@
       <c r="B30" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="C30" s="390" t="s">
+      <c r="C30" s="389" t="s">
         <v>639</v>
       </c>
-      <c r="D30" s="390">
+      <c r="D30" s="389">
         <v>2</v>
       </c>
       <c r="E30" s="25"/>
@@ -13408,10 +13294,10 @@
       <c r="B31" s="87" t="s">
         <v>202</v>
       </c>
-      <c r="C31" s="390" t="s">
+      <c r="C31" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D31" s="390">
+      <c r="D31" s="389">
         <v>1</v>
       </c>
       <c r="E31" s="25"/>
@@ -13421,10 +13307,10 @@
       <c r="B32" t="s">
         <v>661</v>
       </c>
-      <c r="C32" s="390" t="s">
+      <c r="C32" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D32" s="390">
+      <c r="D32" s="389">
         <v>2</v>
       </c>
       <c r="E32" s="25"/>
@@ -13434,10 +13320,10 @@
       <c r="B33" t="s">
         <v>662</v>
       </c>
-      <c r="C33" s="390" t="s">
+      <c r="C33" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D33" s="390">
+      <c r="D33" s="389">
         <v>2</v>
       </c>
       <c r="E33" s="25"/>
@@ -13447,10 +13333,10 @@
       <c r="B34" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="C34" s="390" t="s">
+      <c r="C34" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D34" s="390">
+      <c r="D34" s="389">
         <v>2</v>
       </c>
       <c r="E34" s="25"/>
@@ -13460,36 +13346,36 @@
       <c r="B35" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C35" s="390" t="s">
+      <c r="C35" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D35" s="390">
+      <c r="D35" s="389">
         <v>2</v>
       </c>
       <c r="E35" s="25"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="11"/>
-      <c r="B36" s="390" t="s">
+      <c r="B36" s="389" t="s">
         <v>665</v>
       </c>
-      <c r="C36" s="390" t="s">
+      <c r="C36" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D36" s="390">
+      <c r="D36" s="389">
         <v>2</v>
       </c>
       <c r="E36" s="25"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="11"/>
-      <c r="B37" s="390" t="s">
+      <c r="B37" s="389" t="s">
         <v>666</v>
       </c>
-      <c r="C37" s="390" t="s">
+      <c r="C37" s="389" t="s">
         <v>481</v>
       </c>
-      <c r="D37" s="390">
+      <c r="D37" s="389">
         <v>2</v>
       </c>
       <c r="E37" s="25"/>
@@ -13674,10 +13560,10 @@
     </row>
     <row r="54" spans="1:5" ht="15.75" thickBot="1">
       <c r="A54" s="27"/>
-      <c r="B54" s="410" t="s">
+      <c r="B54" s="409" t="s">
         <v>683</v>
       </c>
-      <c r="C54" s="410" t="s">
+      <c r="C54" s="409" t="s">
         <v>684</v>
       </c>
       <c r="D54" s="22">
@@ -13734,10 +13620,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -13749,7 +13635,7 @@
       <c r="B2" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="390"/>
+      <c r="C2" s="389"/>
       <c r="D2" s="7">
         <v>18</v>
       </c>
@@ -13764,11 +13650,11 @@
       <c r="B3" t="s">
         <v>640</v>
       </c>
-      <c r="C3" s="390"/>
+      <c r="C3" s="389"/>
       <c r="D3" s="7">
         <v>17</v>
       </c>
-      <c r="E3" s="408" t="s">
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -13776,14 +13662,14 @@
       <c r="A4" s="167" t="s">
         <v>423</v>
       </c>
-      <c r="B4" s="390" t="s">
+      <c r="B4" s="389" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="390"/>
+      <c r="C4" s="389"/>
       <c r="D4" s="7">
         <v>2</v>
       </c>
-      <c r="E4" s="408" t="s">
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -13794,18 +13680,18 @@
       <c r="B5" t="s">
         <v>685</v>
       </c>
-      <c r="C5" s="390"/>
+      <c r="C5" s="389"/>
       <c r="D5" s="7">
         <v>2</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="390" t="s">
+      <c r="B6" s="389" t="s">
         <v>686</v>
       </c>
-      <c r="C6" s="390"/>
+      <c r="C6" s="389"/>
       <c r="D6" s="7">
         <v>1</v>
       </c>
@@ -13813,10 +13699,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="390" t="s">
+      <c r="B7" s="389" t="s">
         <v>687</v>
       </c>
-      <c r="C7" s="390"/>
+      <c r="C7" s="389"/>
       <c r="D7" s="7">
         <v>4</v>
       </c>
@@ -13827,7 +13713,7 @@
       <c r="B8" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="C8" s="390"/>
+      <c r="C8" s="389"/>
       <c r="D8" s="7">
         <v>6</v>
       </c>
@@ -13838,7 +13724,7 @@
       <c r="B9" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="C9" s="390"/>
+      <c r="C9" s="389"/>
       <c r="D9" s="7">
         <v>6</v>
       </c>
@@ -13849,7 +13735,7 @@
       <c r="B10" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="C10" s="416" t="s">
+      <c r="C10" s="415" t="s">
         <v>690</v>
       </c>
       <c r="D10" s="7">
@@ -13862,7 +13748,7 @@
       <c r="B11" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="390"/>
+      <c r="C11" s="389"/>
       <c r="D11" s="7">
         <v>1</v>
       </c>
@@ -13876,7 +13762,7 @@
       <c r="C12" s="15" t="s">
         <v>692</v>
       </c>
-      <c r="D12" s="389">
+      <c r="D12" s="388">
         <v>1</v>
       </c>
       <c r="E12" s="25"/>
@@ -13888,20 +13774,20 @@
       <c r="B13" s="12" t="s">
         <v>693</v>
       </c>
-      <c r="C13" s="390" t="s">
+      <c r="C13" s="389" t="s">
         <v>694</v>
       </c>
-      <c r="D13" s="389">
+      <c r="D13" s="388">
         <v>1</v>
       </c>
       <c r="E13" s="25"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11"/>
-      <c r="B14" s="390" t="s">
+      <c r="B14" s="389" t="s">
         <v>140</v>
       </c>
-      <c r="C14" s="390"/>
+      <c r="C14" s="389"/>
       <c r="D14" s="7">
         <v>1</v>
       </c>
@@ -13909,10 +13795,10 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="11"/>
-      <c r="B15" s="390" t="s">
+      <c r="B15" s="389" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="390"/>
+      <c r="C15" s="389"/>
       <c r="D15" s="7">
         <v>1</v>
       </c>
@@ -13942,10 +13828,10 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="11"/>
-      <c r="B18" s="390" t="s">
+      <c r="B18" s="389" t="s">
         <v>228</v>
       </c>
-      <c r="C18" s="390"/>
+      <c r="C18" s="389"/>
       <c r="D18" s="7">
         <v>10</v>
       </c>
@@ -13956,7 +13842,7 @@
       <c r="B19" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="390"/>
+      <c r="C19" s="389"/>
       <c r="D19" s="7">
         <v>19</v>
       </c>
@@ -13964,10 +13850,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="11"/>
-      <c r="B20" s="390" t="s">
+      <c r="B20" s="389" t="s">
         <v>543</v>
       </c>
-      <c r="C20" s="390"/>
+      <c r="C20" s="389"/>
       <c r="D20" s="7">
         <v>6</v>
       </c>
@@ -13975,10 +13861,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="11"/>
-      <c r="B21" s="390" t="s">
+      <c r="B21" s="389" t="s">
         <v>504</v>
       </c>
-      <c r="C21" s="390"/>
+      <c r="C21" s="389"/>
       <c r="D21" s="7">
         <v>15</v>
       </c>
@@ -13986,10 +13872,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="11"/>
-      <c r="B22" s="390" t="s">
+      <c r="B22" s="389" t="s">
         <v>696</v>
       </c>
-      <c r="C22" s="390"/>
+      <c r="C22" s="389"/>
       <c r="D22" s="7">
         <v>16</v>
       </c>
@@ -14000,7 +13886,7 @@
       <c r="B23" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="C23" s="390"/>
+      <c r="C23" s="389"/>
       <c r="D23" s="7">
         <v>4</v>
       </c>
@@ -14011,7 +13897,7 @@
       <c r="B24" t="s">
         <v>697</v>
       </c>
-      <c r="C24" s="390"/>
+      <c r="C24" s="389"/>
       <c r="D24" s="7">
         <v>6</v>
       </c>
@@ -14022,7 +13908,7 @@
       <c r="B25" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="C25" s="390"/>
+      <c r="C25" s="389"/>
       <c r="D25" s="7">
         <v>4</v>
       </c>
@@ -14033,7 +13919,7 @@
       <c r="B26" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="C26" s="390"/>
+      <c r="C26" s="389"/>
       <c r="D26" s="7">
         <v>2</v>
       </c>
@@ -14044,7 +13930,7 @@
       <c r="B27" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="C27" s="390"/>
+      <c r="C27" s="389"/>
       <c r="D27" s="7">
         <v>6</v>
       </c>
@@ -14052,10 +13938,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="11"/>
-      <c r="B28" s="390" t="s">
+      <c r="B28" s="389" t="s">
         <v>260</v>
       </c>
-      <c r="C28" s="390"/>
+      <c r="C28" s="389"/>
       <c r="D28" s="7">
         <v>16</v>
       </c>
@@ -14066,7 +13952,7 @@
       <c r="B29" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C29" s="390"/>
+      <c r="C29" s="389"/>
       <c r="D29" s="7">
         <v>54</v>
       </c>
@@ -14077,7 +13963,7 @@
       <c r="B30" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="C30" s="390"/>
+      <c r="C30" s="389"/>
       <c r="D30" s="7">
         <v>80</v>
       </c>
@@ -14088,7 +13974,7 @@
       <c r="B31" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="C31" s="390"/>
+      <c r="C31" s="389"/>
       <c r="D31" s="7">
         <v>14</v>
       </c>
@@ -14096,10 +13982,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="11"/>
-      <c r="B32" s="390" t="s">
+      <c r="B32" s="389" t="s">
         <v>698</v>
       </c>
-      <c r="C32" s="390"/>
+      <c r="C32" s="389"/>
       <c r="D32" s="7">
         <v>44</v>
       </c>
@@ -14107,10 +13993,10 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1">
       <c r="A33" s="27"/>
-      <c r="B33" s="410" t="s">
+      <c r="B33" s="409" t="s">
         <v>699</v>
       </c>
-      <c r="C33" s="410"/>
+      <c r="C33" s="409"/>
       <c r="D33" s="28">
         <v>17</v>
       </c>
@@ -14118,10 +14004,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="136"/>
-      <c r="B34" s="383" t="s">
+      <c r="B34" s="382" t="s">
         <v>700</v>
       </c>
-      <c r="C34" s="383" t="s">
+      <c r="C34" s="382" t="s">
         <v>701</v>
       </c>
       <c r="D34" s="64">
@@ -14339,7 +14225,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="11"/>
-      <c r="B51" s="390" t="s">
+      <c r="B51" s="389" t="s">
         <v>719</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -14352,10 +14238,10 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="11"/>
-      <c r="B52" s="390" t="s">
+      <c r="B52" s="389" t="s">
         <v>720</v>
       </c>
-      <c r="C52" s="390" t="s">
+      <c r="C52" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D52" s="7">
@@ -14368,7 +14254,7 @@
       <c r="B53" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="C53" s="390" t="s">
+      <c r="C53" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D53" s="7">
@@ -14378,7 +14264,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="11"/>
-      <c r="B54" s="390" t="s">
+      <c r="B54" s="389" t="s">
         <v>722</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -14391,7 +14277,7 @@
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="11"/>
-      <c r="B55" s="390" t="s">
+      <c r="B55" s="389" t="s">
         <v>723</v>
       </c>
       <c r="C55" s="2" t="s">
@@ -14404,7 +14290,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="11"/>
-      <c r="B56" s="390" t="s">
+      <c r="B56" s="389" t="s">
         <v>724</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -14417,7 +14303,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="11"/>
-      <c r="B57" s="390" t="s">
+      <c r="B57" s="389" t="s">
         <v>725</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -14430,7 +14316,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="11"/>
-      <c r="B58" s="390" t="s">
+      <c r="B58" s="389" t="s">
         <v>726</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -14443,7 +14329,7 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="11"/>
-      <c r="B59" s="390" t="s">
+      <c r="B59" s="389" t="s">
         <v>727</v>
       </c>
       <c r="C59" s="2" t="s">
@@ -14456,7 +14342,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="11"/>
-      <c r="B60" s="390" t="s">
+      <c r="B60" s="389" t="s">
         <v>728</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -14469,7 +14355,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="11"/>
-      <c r="B61" s="390" t="s">
+      <c r="B61" s="389" t="s">
         <v>729</v>
       </c>
       <c r="C61" s="2" t="s">
@@ -14482,7 +14368,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="11"/>
-      <c r="B62" s="390" t="s">
+      <c r="B62" s="389" t="s">
         <v>730</v>
       </c>
       <c r="C62" s="2" t="s">
@@ -14495,7 +14381,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="11"/>
-      <c r="B63" s="390" t="s">
+      <c r="B63" s="389" t="s">
         <v>731</v>
       </c>
       <c r="C63" s="2" t="s">
@@ -14508,7 +14394,7 @@
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="11"/>
-      <c r="B64" s="390" t="s">
+      <c r="B64" s="389" t="s">
         <v>732</v>
       </c>
       <c r="C64" s="2" t="s">
@@ -14521,7 +14407,7 @@
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="11"/>
-      <c r="B65" s="390" t="s">
+      <c r="B65" s="389" t="s">
         <v>733</v>
       </c>
       <c r="C65" s="2" t="s">
@@ -14534,7 +14420,7 @@
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="11"/>
-      <c r="B66" s="390" t="s">
+      <c r="B66" s="389" t="s">
         <v>734</v>
       </c>
       <c r="C66" s="2" t="s">
@@ -14547,7 +14433,7 @@
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="11"/>
-      <c r="B67" s="390" t="s">
+      <c r="B67" s="389" t="s">
         <v>735</v>
       </c>
       <c r="C67" s="2" t="s">
@@ -14560,7 +14446,7 @@
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="11"/>
-      <c r="B68" s="390" t="s">
+      <c r="B68" s="389" t="s">
         <v>736</v>
       </c>
       <c r="C68" s="2" t="s">
@@ -14573,7 +14459,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="11"/>
-      <c r="B69" s="390" t="s">
+      <c r="B69" s="389" t="s">
         <v>737</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -14589,7 +14475,7 @@
       <c r="B70" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="C70" s="390" t="s">
+      <c r="C70" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D70" s="7">
@@ -14602,7 +14488,7 @@
       <c r="B71" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="C71" s="390" t="s">
+      <c r="C71" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D71" s="7">
@@ -14615,7 +14501,7 @@
       <c r="B72" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="C72" s="390" t="s">
+      <c r="C72" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D72" s="7">
@@ -14628,7 +14514,7 @@
       <c r="B73" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="C73" s="390" t="s">
+      <c r="C73" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D73" s="7">
@@ -14641,7 +14527,7 @@
       <c r="B74" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="C74" s="390" t="s">
+      <c r="C74" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D74" s="7">
@@ -14651,7 +14537,7 @@
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="11"/>
-      <c r="B75" s="390" t="s">
+      <c r="B75" s="389" t="s">
         <v>743</v>
       </c>
       <c r="C75" s="2" t="s">
@@ -14664,7 +14550,7 @@
     </row>
     <row r="76" spans="1:5" ht="15.75" thickBot="1">
       <c r="A76" s="27"/>
-      <c r="B76" s="410" t="s">
+      <c r="B76" s="409" t="s">
         <v>744</v>
       </c>
       <c r="C76" s="22" t="s">
@@ -16296,7 +16182,9 @@
       <c r="E44" s="15">
         <v>1</v>
       </c>
-      <c r="F44" s="15"/>
+      <c r="F44" s="15">
+        <v>23</v>
+      </c>
       <c r="G44" s="40">
         <f>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</f>
         <v>0</v>
@@ -17866,7 +17754,7 @@
         <f>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[QTY]])</f>
         <v>47</v>
       </c>
-      <c r="G95" s="381">
+      <c r="G95" s="380">
         <v>0</v>
       </c>
       <c r="H95" s="37">
@@ -18386,7 +18274,7 @@
       </c>
       <c r="F112" s="39" t="str">
         <f>SUBTOTAL(109,Table6[Weight MT])&amp;"g"</f>
-        <v>822g</v>
+        <v>845g</v>
       </c>
       <c r="G112" s="39" t="str">
         <f>SUBTOTAL(109,Table6[Weight HT])&amp;"g"</f>
@@ -18407,7 +18295,7 @@
       <c r="K112" s="93"/>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" s="417"/>
+      <c r="A113" s="416"/>
       <c r="B113" s="1"/>
       <c r="F113" t="s">
         <v>796</v>
@@ -20314,13 +20202,13 @@
       <c r="A2" s="243" t="s">
         <v>1210</v>
       </c>
-      <c r="B2" s="418" t="s">
+      <c r="B2" s="417" t="s">
         <v>1211</v>
       </c>
       <c r="C2" s="245" t="s">
         <v>1212</v>
       </c>
-      <c r="D2" s="419" t="s">
+      <c r="D2" s="418" t="s">
         <v>1213</v>
       </c>
       <c r="E2" s="246" t="s">
@@ -20335,7 +20223,7 @@
       <c r="H2" s="247">
         <v>500</v>
       </c>
-      <c r="I2" s="419" t="s">
+      <c r="I2" s="418" t="s">
         <v>1216</v>
       </c>
       <c r="J2" s="248"/>
@@ -20344,13 +20232,13 @@
       <c r="A3" s="251" t="s">
         <v>1210</v>
       </c>
-      <c r="B3" s="420" t="s">
+      <c r="B3" s="419" t="s">
         <v>1211</v>
       </c>
-      <c r="C3" s="421" t="s">
+      <c r="C3" s="420" t="s">
         <v>1217</v>
       </c>
-      <c r="D3" s="422" t="s">
+      <c r="D3" s="421" t="s">
         <v>1213</v>
       </c>
       <c r="E3" s="254" t="s">
@@ -20365,22 +20253,22 @@
       <c r="H3" s="255">
         <v>500</v>
       </c>
-      <c r="I3" s="422" t="s">
+      <c r="I3" s="421" t="s">
         <v>1220</v>
       </c>
       <c r="J3" s="256"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="423" t="s">
+      <c r="A4" s="422" t="s">
         <v>1210</v>
       </c>
-      <c r="B4" s="424" t="s">
+      <c r="B4" s="423" t="s">
         <v>1221</v>
       </c>
       <c r="C4" s="245" t="s">
         <v>1217</v>
       </c>
-      <c r="D4" s="424" t="s">
+      <c r="D4" s="423" t="s">
         <v>1222</v>
       </c>
       <c r="E4" s="246" t="s">
@@ -20401,16 +20289,16 @@
       <c r="J4" s="248"/>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="425" t="s">
+      <c r="A5" s="424" t="s">
         <v>1210</v>
       </c>
-      <c r="B5" s="426" t="s">
+      <c r="B5" s="425" t="s">
         <v>1221</v>
       </c>
       <c r="C5" s="253" t="s">
         <v>1212</v>
       </c>
-      <c r="D5" s="426" t="s">
+      <c r="D5" s="425" t="s">
         <v>1222</v>
       </c>
       <c r="E5" s="254" t="s">
@@ -20431,7 +20319,7 @@
       <c r="J5" s="256"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="423" t="s">
+      <c r="A6" s="422" t="s">
         <v>1226</v>
       </c>
       <c r="B6" s="244" t="s">
@@ -20440,7 +20328,7 @@
       <c r="C6" s="245" t="s">
         <v>1217</v>
       </c>
-      <c r="D6" s="419" t="s">
+      <c r="D6" s="418" t="s">
         <v>1228</v>
       </c>
       <c r="E6" s="246" t="s">
@@ -20452,22 +20340,22 @@
       <c r="G6" s="246" t="s">
         <v>1219</v>
       </c>
-      <c r="H6" s="427" t="s">
+      <c r="H6" s="426" t="s">
         <v>1229</v>
       </c>
       <c r="I6" s="300" t="s">
         <v>1230</v>
       </c>
-      <c r="J6" s="428"/>
+      <c r="J6" s="427"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="429" t="s">
+      <c r="A7" s="428" t="s">
         <v>1226</v>
       </c>
       <c r="B7" s="81" t="s">
         <v>1227</v>
       </c>
-      <c r="C7" s="430" t="s">
+      <c r="C7" s="429" t="s">
         <v>1231</v>
       </c>
       <c r="D7" s="300" t="s">
@@ -20482,16 +20370,16 @@
       <c r="G7" s="82" t="s">
         <v>1215</v>
       </c>
-      <c r="H7" s="431" t="s">
+      <c r="H7" s="430" t="s">
         <v>1229</v>
       </c>
       <c r="I7" s="300" t="s">
         <v>1233</v>
       </c>
-      <c r="J7" s="432"/>
+      <c r="J7" s="431"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="429" t="s">
+      <c r="A8" s="428" t="s">
         <v>1210</v>
       </c>
       <c r="B8" s="293" t="s">
@@ -20521,19 +20409,19 @@
       <c r="J8" s="250"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="425" t="s">
+      <c r="A9" s="424" t="s">
         <v>1210</v>
       </c>
-      <c r="B9" s="426" t="s">
+      <c r="B9" s="425" t="s">
         <v>1234</v>
       </c>
-      <c r="C9" s="421" t="s">
+      <c r="C9" s="420" t="s">
         <v>1231</v>
       </c>
-      <c r="D9" s="422" t="s">
+      <c r="D9" s="421" t="s">
         <v>1228</v>
       </c>
-      <c r="E9" s="426" t="s">
+      <c r="E9" s="425" t="s">
         <v>1232</v>
       </c>
       <c r="F9" s="255">
@@ -20545,7 +20433,7 @@
       <c r="H9" s="255">
         <v>750</v>
       </c>
-      <c r="I9" s="422" t="s">
+      <c r="I9" s="421" t="s">
         <v>1236</v>
       </c>
       <c r="J9" s="256"/>
@@ -20566,7 +20454,7 @@
       <c r="E10" s="246" t="s">
         <v>1241</v>
       </c>
-      <c r="F10" s="427" t="s">
+      <c r="F10" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G10" s="246" t="s">
@@ -20596,7 +20484,7 @@
       <c r="E11" s="82" t="s">
         <v>1246</v>
       </c>
-      <c r="F11" s="431" t="s">
+      <c r="F11" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G11" s="82" t="s">
@@ -20626,7 +20514,7 @@
       <c r="E12" s="82" t="s">
         <v>1249</v>
       </c>
-      <c r="F12" s="431" t="s">
+      <c r="F12" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G12" s="82" t="s">
@@ -20656,7 +20544,7 @@
       <c r="E13" s="254" t="s">
         <v>1252</v>
       </c>
-      <c r="F13" s="433" t="s">
+      <c r="F13" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G13" s="254" t="s">
@@ -20686,7 +20574,7 @@
       <c r="E14" s="246" t="s">
         <v>1241</v>
       </c>
-      <c r="F14" s="427" t="s">
+      <c r="F14" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G14" s="246" t="s">
@@ -20716,7 +20604,7 @@
       <c r="E15" s="82" t="s">
         <v>1246</v>
       </c>
-      <c r="F15" s="431" t="s">
+      <c r="F15" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G15" s="82" t="s">
@@ -20746,7 +20634,7 @@
       <c r="E16" s="82" t="s">
         <v>1249</v>
       </c>
-      <c r="F16" s="431" t="s">
+      <c r="F16" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G16" s="82" t="s">
@@ -20776,7 +20664,7 @@
       <c r="E17" s="254" t="s">
         <v>1252</v>
       </c>
-      <c r="F17" s="433" t="s">
+      <c r="F17" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G17" s="254" t="s">
@@ -20926,13 +20814,13 @@
       <c r="E22" s="246" t="s">
         <v>1241</v>
       </c>
-      <c r="F22" s="427" t="s">
+      <c r="F22" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G22" s="246" t="s">
         <v>1259</v>
       </c>
-      <c r="H22" s="427" t="s">
+      <c r="H22" s="426" t="s">
         <v>1266</v>
       </c>
       <c r="I22" s="246" t="s">
@@ -20956,13 +20844,13 @@
       <c r="E23" s="82" t="s">
         <v>1246</v>
       </c>
-      <c r="F23" s="431" t="s">
+      <c r="F23" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G23" s="82" t="s">
         <v>1219</v>
       </c>
-      <c r="H23" s="431" t="s">
+      <c r="H23" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I23" s="82" t="s">
@@ -20986,13 +20874,13 @@
       <c r="E24" s="82" t="s">
         <v>1249</v>
       </c>
-      <c r="F24" s="431" t="s">
+      <c r="F24" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G24" s="82" t="s">
         <v>1261</v>
       </c>
-      <c r="H24" s="431" t="s">
+      <c r="H24" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I24" s="82" t="s">
@@ -21016,13 +20904,13 @@
       <c r="E25" s="254" t="s">
         <v>1252</v>
       </c>
-      <c r="F25" s="433" t="s">
+      <c r="F25" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G25" s="254" t="s">
         <v>1215</v>
       </c>
-      <c r="H25" s="433" t="s">
+      <c r="H25" s="432" t="s">
         <v>1266</v>
       </c>
       <c r="I25" s="254" t="s">
@@ -21046,13 +20934,13 @@
       <c r="E26" s="246" t="s">
         <v>1241</v>
       </c>
-      <c r="F26" s="427" t="s">
+      <c r="F26" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G26" s="246" t="s">
         <v>1259</v>
       </c>
-      <c r="H26" s="427" t="s">
+      <c r="H26" s="426" t="s">
         <v>1266</v>
       </c>
       <c r="I26" s="246" t="s">
@@ -21076,13 +20964,13 @@
       <c r="E27" s="82" t="s">
         <v>1246</v>
       </c>
-      <c r="F27" s="431" t="s">
+      <c r="F27" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G27" s="82" t="s">
         <v>1219</v>
       </c>
-      <c r="H27" s="431" t="s">
+      <c r="H27" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I27" s="82" t="s">
@@ -21106,13 +20994,13 @@
       <c r="E28" s="82" t="s">
         <v>1249</v>
       </c>
-      <c r="F28" s="431" t="s">
+      <c r="F28" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G28" s="82" t="s">
         <v>1261</v>
       </c>
-      <c r="H28" s="431" t="s">
+      <c r="H28" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I28" s="82" t="s">
@@ -21136,13 +21024,13 @@
       <c r="E29" s="254" t="s">
         <v>1252</v>
       </c>
-      <c r="F29" s="433" t="s">
+      <c r="F29" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G29" s="254" t="s">
         <v>1215</v>
       </c>
-      <c r="H29" s="433" t="s">
+      <c r="H29" s="432" t="s">
         <v>1266</v>
       </c>
       <c r="I29" s="254" t="s">
@@ -21166,13 +21054,13 @@
       <c r="E30" s="246" t="s">
         <v>1241</v>
       </c>
-      <c r="F30" s="427" t="s">
+      <c r="F30" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G30" s="246" t="s">
         <v>1259</v>
       </c>
-      <c r="H30" s="427" t="s">
+      <c r="H30" s="426" t="s">
         <v>1266</v>
       </c>
       <c r="I30" s="246" t="s">
@@ -21196,13 +21084,13 @@
       <c r="E31" s="82" t="s">
         <v>1246</v>
       </c>
-      <c r="F31" s="431" t="s">
+      <c r="F31" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G31" s="82" t="s">
         <v>1219</v>
       </c>
-      <c r="H31" s="431" t="s">
+      <c r="H31" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I31" s="82" t="s">
@@ -21226,13 +21114,13 @@
       <c r="E32" s="82" t="s">
         <v>1249</v>
       </c>
-      <c r="F32" s="431" t="s">
+      <c r="F32" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="G32" s="82" t="s">
         <v>1261</v>
       </c>
-      <c r="H32" s="431" t="s">
+      <c r="H32" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I32" s="82" t="s">
@@ -21256,13 +21144,13 @@
       <c r="E33" s="254" t="s">
         <v>1252</v>
       </c>
-      <c r="F33" s="433" t="s">
+      <c r="F33" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G33" s="254" t="s">
         <v>1215</v>
       </c>
-      <c r="H33" s="433" t="s">
+      <c r="H33" s="432" t="s">
         <v>1266</v>
       </c>
       <c r="I33" s="254" t="s">
@@ -21271,12 +21159,12 @@
       <c r="J33" s="256"/>
     </row>
     <row r="34" spans="1:10">
-      <c r="A34" s="423" t="s">
+      <c r="A34" s="422" t="s">
         <v>1271</v>
       </c>
       <c r="B34" s="244"/>
       <c r="C34" s="245"/>
-      <c r="D34" s="419" t="s">
+      <c r="D34" s="418" t="s">
         <v>1272</v>
       </c>
       <c r="E34" s="246" t="s">
@@ -21289,7 +21177,7 @@
       <c r="J34" s="248"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="429" t="s">
+      <c r="A35" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C35" s="196"/>
@@ -21305,7 +21193,7 @@
       <c r="J35" s="250"/>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="429" t="s">
+      <c r="A36" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C36" s="196"/>
@@ -21334,18 +21222,18 @@
       <c r="F37" s="86"/>
       <c r="H37" s="86"/>
       <c r="I37" s="82"/>
-      <c r="J37" s="432"/>
+      <c r="J37" s="431"/>
     </row>
     <row r="38" spans="1:10">
-      <c r="A38" s="425" t="s">
+      <c r="A38" s="424" t="s">
         <v>1271</v>
       </c>
       <c r="B38" s="252"/>
       <c r="C38" s="253"/>
-      <c r="D38" s="422" t="s">
+      <c r="D38" s="421" t="s">
         <v>1279</v>
       </c>
-      <c r="E38" s="422" t="s">
+      <c r="E38" s="421" t="s">
         <v>1280</v>
       </c>
       <c r="F38" s="255"/>
@@ -21355,12 +21243,12 @@
       <c r="J38" s="256"/>
     </row>
     <row r="39" spans="1:10">
-      <c r="A39" s="423" t="s">
+      <c r="A39" s="422" t="s">
         <v>1271</v>
       </c>
       <c r="B39" s="244"/>
       <c r="C39" s="245"/>
-      <c r="D39" s="419" t="s">
+      <c r="D39" s="418" t="s">
         <v>1281</v>
       </c>
       <c r="E39" s="246" t="s">
@@ -21373,7 +21261,7 @@
       <c r="J39" s="248"/>
     </row>
     <row r="40" spans="1:10">
-      <c r="A40" s="429" t="s">
+      <c r="A40" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C40" s="196"/>
@@ -21389,7 +21277,7 @@
       <c r="J40" s="250"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="A41" s="429" t="s">
+      <c r="A41" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C41" s="196"/>
@@ -21405,7 +21293,7 @@
       <c r="J41" s="250"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="A42" s="429" t="s">
+      <c r="A42" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C42" s="196"/>
@@ -21421,15 +21309,15 @@
       <c r="J42" s="250"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="A43" s="425" t="s">
+      <c r="A43" s="424" t="s">
         <v>1271</v>
       </c>
       <c r="B43" s="252"/>
       <c r="C43" s="253"/>
-      <c r="D43" s="422" t="s">
+      <c r="D43" s="421" t="s">
         <v>1287</v>
       </c>
-      <c r="E43" s="422" t="s">
+      <c r="E43" s="421" t="s">
         <v>1280</v>
       </c>
       <c r="F43" s="255"/>
@@ -21448,7 +21336,7 @@
       <c r="C44" s="245" t="s">
         <v>1273</v>
       </c>
-      <c r="D44" s="419" t="s">
+      <c r="D44" s="418" t="s">
         <v>1290</v>
       </c>
       <c r="E44" s="246" t="s">
@@ -21460,7 +21348,7 @@
       <c r="G44" s="246" t="s">
         <v>1215</v>
       </c>
-      <c r="H44" s="427" t="s">
+      <c r="H44" s="426" t="s">
         <v>1266</v>
       </c>
       <c r="I44" s="259" t="s">
@@ -21469,20 +21357,20 @@
       <c r="J44" s="248"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="A45" s="429" t="s">
+      <c r="A45" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="B45" s="293"/>
-      <c r="C45" s="430"/>
+      <c r="C45" s="429"/>
       <c r="D45" s="300" t="s">
         <v>1292</v>
       </c>
       <c r="E45" s="300" t="s">
         <v>1293</v>
       </c>
-      <c r="F45" s="431"/>
+      <c r="F45" s="430"/>
       <c r="G45" s="300"/>
-      <c r="H45" s="431"/>
+      <c r="H45" s="430"/>
       <c r="I45" s="300"/>
       <c r="J45" s="250"/>
     </row>
@@ -21508,7 +21396,7 @@
       <c r="G46" s="82" t="s">
         <v>1219</v>
       </c>
-      <c r="H46" s="431" t="s">
+      <c r="H46" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I46" s="260" t="s">
@@ -21538,7 +21426,7 @@
       <c r="G47" s="82" t="s">
         <v>1261</v>
       </c>
-      <c r="H47" s="431" t="s">
+      <c r="H47" s="430" t="s">
         <v>1266</v>
       </c>
       <c r="I47" s="260" t="s">
@@ -21547,15 +21435,15 @@
       <c r="J47" s="250"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="A48" s="425" t="s">
+      <c r="A48" s="424" t="s">
         <v>1271</v>
       </c>
       <c r="B48" s="252"/>
       <c r="C48" s="253"/>
-      <c r="D48" s="422" t="s">
+      <c r="D48" s="421" t="s">
         <v>1300</v>
       </c>
-      <c r="E48" s="422" t="s">
+      <c r="E48" s="421" t="s">
         <v>1280</v>
       </c>
       <c r="F48" s="255"/>
@@ -21565,12 +21453,12 @@
       <c r="J48" s="256"/>
     </row>
     <row r="49" spans="1:18">
-      <c r="A49" s="423" t="s">
+      <c r="A49" s="422" t="s">
         <v>1271</v>
       </c>
       <c r="B49" s="244"/>
       <c r="C49" s="245"/>
-      <c r="D49" s="419" t="s">
+      <c r="D49" s="418" t="s">
         <v>1301</v>
       </c>
       <c r="E49" s="246" t="s">
@@ -21643,7 +21531,7 @@
       <c r="J51" s="250"/>
     </row>
     <row r="52" spans="1:18">
-      <c r="A52" s="429" t="s">
+      <c r="A52" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C52" s="196"/>
@@ -21659,15 +21547,15 @@
       <c r="J52" s="250"/>
     </row>
     <row r="53" spans="1:18">
-      <c r="A53" s="425" t="s">
+      <c r="A53" s="424" t="s">
         <v>1271</v>
       </c>
       <c r="B53" s="252"/>
       <c r="C53" s="253"/>
-      <c r="D53" s="422" t="s">
+      <c r="D53" s="421" t="s">
         <v>1311</v>
       </c>
-      <c r="E53" s="422" t="s">
+      <c r="E53" s="421" t="s">
         <v>1280</v>
       </c>
       <c r="F53" s="255"/>
@@ -21677,12 +21565,12 @@
       <c r="J53" s="256"/>
     </row>
     <row r="54" spans="1:18">
-      <c r="A54" s="423" t="s">
+      <c r="A54" s="422" t="s">
         <v>1271</v>
       </c>
       <c r="B54" s="244"/>
       <c r="C54" s="245"/>
-      <c r="D54" s="419" t="s">
+      <c r="D54" s="418" t="s">
         <v>1312</v>
       </c>
       <c r="E54" s="246" t="s">
@@ -21755,7 +21643,7 @@
       <c r="J56" s="250"/>
     </row>
     <row r="57" spans="1:18">
-      <c r="A57" s="429" t="s">
+      <c r="A57" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C57" s="196"/>
@@ -21771,15 +21659,15 @@
       <c r="J57" s="250"/>
     </row>
     <row r="58" spans="1:18">
-      <c r="A58" s="425" t="s">
+      <c r="A58" s="424" t="s">
         <v>1271</v>
       </c>
       <c r="B58" s="252"/>
       <c r="C58" s="253"/>
-      <c r="D58" s="422" t="s">
+      <c r="D58" s="421" t="s">
         <v>1321</v>
       </c>
-      <c r="E58" s="422" t="s">
+      <c r="E58" s="421" t="s">
         <v>1280</v>
       </c>
       <c r="F58" s="255"/>
@@ -21789,12 +21677,12 @@
       <c r="J58" s="256"/>
     </row>
     <row r="59" spans="1:18">
-      <c r="A59" s="423" t="s">
+      <c r="A59" s="422" t="s">
         <v>1271</v>
       </c>
       <c r="B59" s="244"/>
       <c r="C59" s="245"/>
-      <c r="D59" s="419" t="s">
+      <c r="D59" s="418" t="s">
         <v>1322</v>
       </c>
       <c r="E59" s="246" t="s">
@@ -21807,7 +21695,7 @@
       <c r="J59" s="248"/>
     </row>
     <row r="60" spans="1:18">
-      <c r="A60" s="429" t="s">
+      <c r="A60" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C60" s="196"/>
@@ -21823,7 +21711,7 @@
       <c r="J60" s="242"/>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="429" t="s">
+      <c r="A61" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C61" s="196"/>
@@ -21842,13 +21730,13 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="429" t="s">
+      <c r="A62" s="428" t="s">
         <v>1327</v>
       </c>
       <c r="B62" s="293" t="s">
         <v>1328</v>
       </c>
-      <c r="C62" s="430" t="s">
+      <c r="C62" s="429" t="s">
         <v>1329</v>
       </c>
       <c r="D62" s="260" t="s">
@@ -22213,15 +22101,15 @@
       <c r="J77" s="277"/>
     </row>
     <row r="78" spans="1:10">
-      <c r="A78" s="425" t="s">
+      <c r="A78" s="424" t="s">
         <v>1271</v>
       </c>
       <c r="B78" s="252"/>
       <c r="C78" s="253"/>
-      <c r="D78" s="422" t="s">
+      <c r="D78" s="421" t="s">
         <v>1367</v>
       </c>
-      <c r="E78" s="422" t="s">
+      <c r="E78" s="421" t="s">
         <v>1280</v>
       </c>
       <c r="F78" s="255"/>
@@ -22231,7 +22119,7 @@
       <c r="J78" s="256"/>
     </row>
     <row r="79" spans="1:10">
-      <c r="A79" s="423" t="s">
+      <c r="A79" s="422" t="s">
         <v>1368</v>
       </c>
       <c r="B79" s="244" t="s">
@@ -22240,7 +22128,7 @@
       <c r="C79" s="245" t="s">
         <v>1</v>
       </c>
-      <c r="D79" s="419" t="s">
+      <c r="D79" s="418" t="s">
         <v>1370</v>
       </c>
       <c r="E79" s="246" t="s">
@@ -22261,7 +22149,7 @@
       <c r="J79" s="248"/>
     </row>
     <row r="80" spans="1:10">
-      <c r="A80" s="425" t="s">
+      <c r="A80" s="424" t="s">
         <v>1368</v>
       </c>
       <c r="B80" s="252" t="s">
@@ -22270,7 +22158,7 @@
       <c r="C80" s="253" t="s">
         <v>1373</v>
       </c>
-      <c r="D80" s="422" t="s">
+      <c r="D80" s="421" t="s">
         <v>1374</v>
       </c>
       <c r="E80" s="254" t="s">
@@ -22291,16 +22179,16 @@
       <c r="J80" s="256"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="423" t="s">
+      <c r="A81" s="422" t="s">
         <v>1327</v>
       </c>
-      <c r="B81" s="424" t="s">
+      <c r="B81" s="423" t="s">
         <v>1377</v>
       </c>
-      <c r="C81" s="434" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="419" t="s">
+      <c r="C81" s="433" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="418" t="s">
         <v>1378</v>
       </c>
       <c r="E81" s="246" t="s">
@@ -22312,23 +22200,23 @@
       <c r="G81" s="246" t="s">
         <v>1219</v>
       </c>
-      <c r="H81" s="427">
+      <c r="H81" s="426">
         <v>800</v>
       </c>
-      <c r="I81" s="419"/>
-      <c r="J81" s="428"/>
+      <c r="I81" s="418"/>
+      <c r="J81" s="427"/>
     </row>
     <row r="82" spans="1:14">
-      <c r="A82" s="425" t="s">
+      <c r="A82" s="424" t="s">
         <v>1327</v>
       </c>
-      <c r="B82" s="426" t="s">
+      <c r="B82" s="425" t="s">
         <v>1377</v>
       </c>
-      <c r="C82" s="421" t="s">
+      <c r="C82" s="420" t="s">
         <v>1373</v>
       </c>
-      <c r="D82" s="422" t="s">
+      <c r="D82" s="421" t="s">
         <v>1379</v>
       </c>
       <c r="E82" s="254" t="s">
@@ -22340,21 +22228,21 @@
       <c r="G82" s="254" t="s">
         <v>1215</v>
       </c>
-      <c r="H82" s="433">
+      <c r="H82" s="432">
         <v>800</v>
       </c>
-      <c r="I82" s="422"/>
+      <c r="I82" s="421"/>
       <c r="J82" s="256"/>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="423" t="s">
+      <c r="A83" s="422" t="s">
         <v>1271</v>
       </c>
       <c r="B83" s="244"/>
       <c r="C83" s="245" t="s">
         <v>1</v>
       </c>
-      <c r="D83" s="419" t="s">
+      <c r="D83" s="418" t="s">
         <v>1380</v>
       </c>
       <c r="E83" s="246" t="s">
@@ -22366,10 +22254,10 @@
       </c>
       <c r="H83" s="247"/>
       <c r="I83" s="246"/>
-      <c r="J83" s="428"/>
+      <c r="J83" s="427"/>
     </row>
     <row r="84" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A84" s="429" t="s">
+      <c r="A84" s="428" t="s">
         <v>1271</v>
       </c>
       <c r="C84" s="196" t="s">
@@ -22426,7 +22314,7 @@
       <c r="M85" s="279" t="s">
         <v>1388</v>
       </c>
-      <c r="N85" s="428" t="s">
+      <c r="N85" s="427" t="s">
         <v>1389</v>
       </c>
     </row>
@@ -22467,7 +22355,7 @@
       <c r="M86" s="281" t="s">
         <v>1388</v>
       </c>
-      <c r="N86" s="432" t="s">
+      <c r="N86" s="431" t="s">
         <v>1389</v>
       </c>
     </row>
@@ -22506,7 +22394,7 @@
       <c r="M87" s="281" t="s">
         <v>1388</v>
       </c>
-      <c r="N87" s="432" t="s">
+      <c r="N87" s="431" t="s">
         <v>1389</v>
       </c>
     </row>
@@ -22545,7 +22433,7 @@
       <c r="M88" s="283" t="s">
         <v>1388</v>
       </c>
-      <c r="N88" s="435" t="s">
+      <c r="N88" s="434" t="s">
         <v>1389</v>
       </c>
     </row>
@@ -22790,7 +22678,7 @@
       <c r="C98" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="D98" s="422" t="s">
+      <c r="D98" s="421" t="s">
         <v>1424</v>
       </c>
       <c r="E98" s="254" t="s">
@@ -22820,7 +22708,7 @@
       <c r="C99" s="245" t="s">
         <v>1373</v>
       </c>
-      <c r="D99" s="419" t="s">
+      <c r="D99" s="418" t="s">
         <v>1428</v>
       </c>
       <c r="E99" s="246" t="s">
@@ -22850,7 +22738,7 @@
       <c r="C100" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="D100" s="422" t="s">
+      <c r="D100" s="421" t="s">
         <v>1430</v>
       </c>
       <c r="E100" s="254" t="s">
@@ -22880,7 +22768,7 @@
       <c r="C101" s="245" t="s">
         <v>1373</v>
       </c>
-      <c r="D101" s="419" t="s">
+      <c r="D101" s="418" t="s">
         <v>1434</v>
       </c>
       <c r="E101" s="246" t="s">
@@ -22910,7 +22798,7 @@
       <c r="C102" s="253" t="s">
         <v>1</v>
       </c>
-      <c r="D102" s="422" t="s">
+      <c r="D102" s="421" t="s">
         <v>1436</v>
       </c>
       <c r="E102" s="254" t="s">
@@ -22931,10 +22819,10 @@
       <c r="J102" s="256"/>
     </row>
     <row r="103" spans="1:10">
-      <c r="A103" s="423" t="s">
+      <c r="A103" s="422" t="s">
         <v>1288</v>
       </c>
-      <c r="B103" s="424" t="s">
+      <c r="B103" s="423" t="s">
         <v>1439</v>
       </c>
       <c r="C103" s="245" t="s">
@@ -22961,10 +22849,10 @@
       <c r="J103" s="248"/>
     </row>
     <row r="104" spans="1:10">
-      <c r="A104" s="425" t="s">
+      <c r="A104" s="424" t="s">
         <v>1288</v>
       </c>
-      <c r="B104" s="426" t="s">
+      <c r="B104" s="425" t="s">
         <v>1439</v>
       </c>
       <c r="C104" s="253" t="s">
@@ -22991,7 +22879,7 @@
       <c r="J104" s="256"/>
     </row>
     <row r="105" spans="1:10">
-      <c r="A105" s="423" t="s">
+      <c r="A105" s="422" t="s">
         <v>1288</v>
       </c>
       <c r="B105" s="244" t="s">
@@ -23021,7 +22909,7 @@
       <c r="J105" s="248"/>
     </row>
     <row r="106" spans="1:10">
-      <c r="A106" s="425" t="s">
+      <c r="A106" s="424" t="s">
         <v>1288</v>
       </c>
       <c r="B106" s="252" t="s">
@@ -23051,7 +22939,7 @@
       <c r="J106" s="256"/>
     </row>
     <row r="107" spans="1:10">
-      <c r="A107" s="423" t="s">
+      <c r="A107" s="422" t="s">
         <v>1288</v>
       </c>
       <c r="B107" s="244" t="s">
@@ -23066,13 +22954,13 @@
       <c r="E107" s="246" t="s">
         <v>1442</v>
       </c>
-      <c r="F107" s="427" t="s">
+      <c r="F107" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G107" s="246" t="s">
         <v>1306</v>
       </c>
-      <c r="H107" s="427" t="s">
+      <c r="H107" s="426" t="s">
         <v>1266</v>
       </c>
       <c r="I107" s="246" t="s">
@@ -23081,7 +22969,7 @@
       <c r="J107" s="248"/>
     </row>
     <row r="108" spans="1:10">
-      <c r="A108" s="425" t="s">
+      <c r="A108" s="424" t="s">
         <v>1288</v>
       </c>
       <c r="B108" s="252" t="s">
@@ -23096,13 +22984,13 @@
       <c r="E108" s="254" t="s">
         <v>1455</v>
       </c>
-      <c r="F108" s="433" t="s">
+      <c r="F108" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G108" s="254" t="s">
         <v>1306</v>
       </c>
-      <c r="H108" s="433" t="s">
+      <c r="H108" s="432" t="s">
         <v>1266</v>
       </c>
       <c r="I108" s="254" t="s">
@@ -23111,7 +22999,7 @@
       <c r="J108" s="256"/>
     </row>
     <row r="109" spans="1:10">
-      <c r="A109" s="423" t="s">
+      <c r="A109" s="422" t="s">
         <v>1288</v>
       </c>
       <c r="B109" s="244" t="s">
@@ -23141,7 +23029,7 @@
       <c r="J109" s="248"/>
     </row>
     <row r="110" spans="1:10">
-      <c r="A110" s="425" t="s">
+      <c r="A110" s="424" t="s">
         <v>1288</v>
       </c>
       <c r="B110" s="252" t="s">
@@ -23186,7 +23074,7 @@
       <c r="E111" s="246" t="s">
         <v>1375</v>
       </c>
-      <c r="F111" s="427" t="s">
+      <c r="F111" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G111" s="246" t="s">
@@ -23216,7 +23104,7 @@
       <c r="E112" s="254" t="s">
         <v>1223</v>
       </c>
-      <c r="F112" s="433" t="s">
+      <c r="F112" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G112" s="254" t="s">
@@ -23225,7 +23113,7 @@
       <c r="H112" s="255">
         <v>150</v>
       </c>
-      <c r="I112" s="422" t="s">
+      <c r="I112" s="421" t="s">
         <v>1465</v>
       </c>
       <c r="J112" s="256"/>
@@ -23240,17 +23128,17 @@
       <c r="C113" s="245" t="s">
         <v>1217</v>
       </c>
-      <c r="D113" s="419" t="s">
+      <c r="D113" s="418" t="s">
         <v>1468</v>
       </c>
       <c r="E113" s="246" t="s">
         <v>1223</v>
       </c>
-      <c r="F113" s="427" t="s">
+      <c r="F113" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G113" s="246"/>
-      <c r="H113" s="427" t="s">
+      <c r="H113" s="426" t="s">
         <v>1266</v>
       </c>
       <c r="I113" s="246" t="s">
@@ -23268,17 +23156,17 @@
       <c r="C114" s="253" t="s">
         <v>1390</v>
       </c>
-      <c r="D114" s="422" t="s">
+      <c r="D114" s="421" t="s">
         <v>1470</v>
       </c>
       <c r="E114" s="254">
         <v>12</v>
       </c>
-      <c r="F114" s="433" t="s">
+      <c r="F114" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G114" s="254"/>
-      <c r="H114" s="433" t="s">
+      <c r="H114" s="432" t="s">
         <v>1266</v>
       </c>
       <c r="I114" s="254" t="s">
@@ -23287,48 +23175,48 @@
       <c r="J114" s="256"/>
     </row>
     <row r="115" spans="1:10">
-      <c r="A115" s="423" t="s">
+      <c r="A115" s="422" t="s">
         <v>1226</v>
       </c>
-      <c r="B115" s="424" t="s">
+      <c r="B115" s="423" t="s">
         <v>1472</v>
       </c>
-      <c r="C115" s="434"/>
-      <c r="D115" s="419" t="s">
+      <c r="C115" s="433"/>
+      <c r="D115" s="418" t="s">
         <v>1473</v>
       </c>
       <c r="E115" s="246" t="s">
         <v>1474</v>
       </c>
-      <c r="F115" s="427" t="s">
+      <c r="F115" s="426" t="s">
         <v>1242</v>
       </c>
       <c r="G115" s="246"/>
       <c r="H115" s="247">
         <v>600</v>
       </c>
-      <c r="I115" s="419" t="s">
+      <c r="I115" s="418" t="s">
         <v>1472</v>
       </c>
-      <c r="J115" s="428" t="s">
+      <c r="J115" s="427" t="s">
         <v>1475</v>
       </c>
     </row>
     <row r="116" spans="1:10">
-      <c r="A116" s="429" t="s">
+      <c r="A116" s="428" t="s">
         <v>1226</v>
       </c>
       <c r="B116" s="293" t="s">
         <v>1472</v>
       </c>
-      <c r="C116" s="430"/>
+      <c r="C116" s="429"/>
       <c r="D116" s="300" t="s">
         <v>1473</v>
       </c>
       <c r="E116" s="82" t="s">
         <v>1476</v>
       </c>
-      <c r="F116" s="431" t="s">
+      <c r="F116" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="H116" s="86">
@@ -23337,25 +23225,25 @@
       <c r="I116" s="300" t="s">
         <v>1472</v>
       </c>
-      <c r="J116" s="432" t="s">
+      <c r="J116" s="431" t="s">
         <v>1475</v>
       </c>
     </row>
     <row r="117" spans="1:10">
-      <c r="A117" s="429" t="s">
+      <c r="A117" s="428" t="s">
         <v>1226</v>
       </c>
       <c r="B117" s="293" t="s">
         <v>1472</v>
       </c>
-      <c r="C117" s="430"/>
+      <c r="C117" s="429"/>
       <c r="D117" s="300" t="s">
         <v>1473</v>
       </c>
       <c r="E117" s="82" t="s">
         <v>1477</v>
       </c>
-      <c r="F117" s="431" t="s">
+      <c r="F117" s="430" t="s">
         <v>1242</v>
       </c>
       <c r="H117" s="86">
@@ -23364,35 +23252,35 @@
       <c r="I117" s="300" t="s">
         <v>1472</v>
       </c>
-      <c r="J117" s="432" t="s">
+      <c r="J117" s="431" t="s">
         <v>1475</v>
       </c>
     </row>
     <row r="118" spans="1:10">
-      <c r="A118" s="425" t="s">
+      <c r="A118" s="424" t="s">
         <v>1226</v>
       </c>
-      <c r="B118" s="426" t="s">
+      <c r="B118" s="425" t="s">
         <v>1472</v>
       </c>
-      <c r="C118" s="421"/>
-      <c r="D118" s="422" t="s">
+      <c r="C118" s="420"/>
+      <c r="D118" s="421" t="s">
         <v>1473</v>
       </c>
       <c r="E118" s="254" t="s">
         <v>1223</v>
       </c>
-      <c r="F118" s="433" t="s">
+      <c r="F118" s="432" t="s">
         <v>1242</v>
       </c>
       <c r="G118" s="254"/>
       <c r="H118" s="255">
         <v>600</v>
       </c>
-      <c r="I118" s="422" t="s">
+      <c r="I118" s="421" t="s">
         <v>1472</v>
       </c>
-      <c r="J118" s="435" t="s">
+      <c r="J118" s="434" t="s">
         <v>1475</v>
       </c>
     </row>
@@ -26332,200 +26220,200 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="436" t="s">
+      <c r="A1" s="435" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="437" t="s">
+      <c r="B1" s="436" t="s">
         <v>895</v>
       </c>
-      <c r="C1" s="437" t="s">
+      <c r="C1" s="436" t="s">
         <v>1702</v>
       </c>
       <c r="D1" s="70" t="s">
         <v>1703</v>
       </c>
-      <c r="E1" s="438"/>
-      <c r="F1" s="438" t="s">
+      <c r="E1" s="437"/>
+      <c r="F1" s="437" t="s">
         <v>1704</v>
       </c>
-      <c r="G1" s="438" t="s">
+      <c r="G1" s="437" t="s">
         <v>1705</v>
       </c>
-      <c r="H1" s="438"/>
-      <c r="I1" s="438"/>
+      <c r="H1" s="437"/>
+      <c r="I1" s="437"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="436" t="s">
+      <c r="A2" s="435" t="s">
         <v>1706</v>
       </c>
-      <c r="B2" s="439">
-        <v>1</v>
-      </c>
-      <c r="C2" s="439" t="s">
+      <c r="B2" s="438">
+        <v>1</v>
+      </c>
+      <c r="C2" s="438" t="s">
         <v>1707</v>
       </c>
       <c r="D2" s="72">
         <v>2</v>
       </c>
-      <c r="E2" s="438"/>
-      <c r="F2" s="438" t="s">
+      <c r="E2" s="437"/>
+      <c r="F2" s="437" t="s">
         <v>1708</v>
       </c>
-      <c r="G2" s="438" t="s">
+      <c r="G2" s="437" t="s">
         <v>1709</v>
       </c>
-      <c r="H2" s="438" t="s">
+      <c r="H2" s="437" t="s">
         <v>1710</v>
       </c>
-      <c r="I2" s="438"/>
+      <c r="I2" s="437"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="436" t="s">
+      <c r="A3" s="435" t="s">
         <v>1711</v>
       </c>
-      <c r="B3" s="439" t="s">
+      <c r="B3" s="438" t="s">
         <v>1712</v>
       </c>
-      <c r="C3" s="439"/>
+      <c r="C3" s="438"/>
       <c r="D3" s="72" t="s">
         <v>1713</v>
       </c>
-      <c r="E3" s="438"/>
-      <c r="F3" s="438"/>
-      <c r="G3" s="438" t="s">
+      <c r="E3" s="437"/>
+      <c r="F3" s="437"/>
+      <c r="G3" s="437" t="s">
         <v>1714</v>
       </c>
-      <c r="H3" s="438" t="s">
+      <c r="H3" s="437" t="s">
         <v>1715</v>
       </c>
-      <c r="I3" s="438"/>
+      <c r="I3" s="437"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="436" t="s">
+      <c r="A4" s="435" t="s">
         <v>1716</v>
       </c>
-      <c r="B4" s="439">
+      <c r="B4" s="438">
         <v>450</v>
       </c>
-      <c r="C4" s="439">
+      <c r="C4" s="438">
         <v>300</v>
       </c>
       <c r="D4" s="72" t="s">
         <v>1717</v>
       </c>
-      <c r="E4" s="438"/>
-      <c r="F4" s="440" t="s">
+      <c r="E4" s="437"/>
+      <c r="F4" s="439" t="s">
         <v>1718</v>
       </c>
-      <c r="G4" s="438" t="s">
+      <c r="G4" s="437" t="s">
         <v>774</v>
       </c>
-      <c r="H4" s="438" t="s">
+      <c r="H4" s="437" t="s">
         <v>1719</v>
       </c>
-      <c r="I4" s="438"/>
+      <c r="I4" s="437"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="436" t="s">
+      <c r="A5" s="435" t="s">
         <v>1720</v>
       </c>
-      <c r="B5" s="439" t="s">
+      <c r="B5" s="438" t="s">
         <v>1721</v>
       </c>
-      <c r="C5" s="439">
+      <c r="C5" s="438">
         <v>120</v>
       </c>
       <c r="D5" s="72" t="s">
         <v>1722</v>
       </c>
-      <c r="E5" s="438"/>
-      <c r="F5" s="440" t="s">
+      <c r="E5" s="437"/>
+      <c r="F5" s="439" t="s">
         <v>1723</v>
       </c>
-      <c r="G5" s="438" t="s">
+      <c r="G5" s="437" t="s">
         <v>1724</v>
       </c>
-      <c r="H5" s="438" t="s">
+      <c r="H5" s="437" t="s">
         <v>1725</v>
       </c>
-      <c r="I5" s="438"/>
+      <c r="I5" s="437"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
-      <c r="A6" s="436" t="s">
+      <c r="A6" s="435" t="s">
         <v>1726</v>
       </c>
-      <c r="B6" s="439">
+      <c r="B6" s="438">
         <v>100</v>
       </c>
-      <c r="C6" s="439">
+      <c r="C6" s="438">
         <v>60</v>
       </c>
       <c r="D6" s="72" t="s">
         <v>1727</v>
       </c>
-      <c r="E6" s="438"/>
-      <c r="F6" s="440" t="s">
+      <c r="E6" s="437"/>
+      <c r="F6" s="439" t="s">
         <v>1728</v>
       </c>
-      <c r="G6" s="438" t="s">
+      <c r="G6" s="437" t="s">
         <v>644</v>
       </c>
-      <c r="H6" s="438"/>
-      <c r="I6" s="438"/>
+      <c r="H6" s="437"/>
+      <c r="I6" s="437"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="436" t="s">
+      <c r="A7" s="435" t="s">
         <v>1729</v>
       </c>
-      <c r="B7" s="439" t="s">
+      <c r="B7" s="438" t="s">
         <v>1730</v>
       </c>
-      <c r="C7" s="439" t="s">
+      <c r="C7" s="438" t="s">
         <v>1731</v>
       </c>
       <c r="D7" s="72" t="s">
         <v>1732</v>
       </c>
-      <c r="E7" s="438"/>
-      <c r="F7" s="440" t="s">
+      <c r="E7" s="437"/>
+      <c r="F7" s="439" t="s">
         <v>1733</v>
       </c>
-      <c r="G7" s="438" t="s">
+      <c r="G7" s="437" t="s">
         <v>1734</v>
       </c>
-      <c r="H7" s="438" t="s">
+      <c r="H7" s="437" t="s">
         <v>1735</v>
       </c>
-      <c r="I7" s="438"/>
+      <c r="I7" s="437"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="436" t="s">
+      <c r="A8" s="435" t="s">
         <v>1736</v>
       </c>
-      <c r="B8" s="439" t="s">
+      <c r="B8" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="C8" s="439" t="s">
+      <c r="C8" s="438" t="s">
         <v>1738</v>
       </c>
       <c r="D8" s="72" t="s">
         <v>1739</v>
       </c>
-      <c r="E8" s="438"/>
-      <c r="F8" s="438"/>
-      <c r="G8" s="438" t="s">
+      <c r="E8" s="437"/>
+      <c r="F8" s="437"/>
+      <c r="G8" s="437" t="s">
         <v>1740</v>
       </c>
-      <c r="H8" s="438" t="s">
+      <c r="H8" s="437" t="s">
         <v>1741</v>
       </c>
-      <c r="I8" s="438"/>
+      <c r="I8" s="437"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="436" t="s">
+      <c r="A9" s="435" t="s">
         <v>1742</v>
       </c>
-      <c r="B9" s="441" t="s">
+      <c r="B9" s="440" t="s">
         <v>1743</v>
       </c>
       <c r="C9" s="74" t="s">
@@ -26534,241 +26422,241 @@
       <c r="D9" s="72" t="s">
         <v>1745</v>
       </c>
-      <c r="E9" s="438"/>
-      <c r="F9" s="438"/>
-      <c r="G9" s="438" t="s">
+      <c r="E9" s="437"/>
+      <c r="F9" s="437"/>
+      <c r="G9" s="437" t="s">
         <v>1746</v>
       </c>
-      <c r="H9" s="438" t="s">
+      <c r="H9" s="437" t="s">
         <v>1747</v>
       </c>
-      <c r="I9" s="438"/>
+      <c r="I9" s="437"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
-      <c r="A10" s="436" t="s">
+      <c r="A10" s="435" t="s">
         <v>1748</v>
       </c>
-      <c r="B10" s="439" t="s">
+      <c r="B10" s="438" t="s">
         <v>1749</v>
       </c>
-      <c r="C10" s="439" t="s">
+      <c r="C10" s="438" t="s">
         <v>1738</v>
       </c>
       <c r="D10" s="72" t="s">
         <v>1749</v>
       </c>
-      <c r="E10" s="438"/>
-      <c r="F10" s="438"/>
-      <c r="G10" s="438" t="s">
+      <c r="E10" s="437"/>
+      <c r="F10" s="437"/>
+      <c r="G10" s="437" t="s">
         <v>1750</v>
       </c>
-      <c r="H10" s="438"/>
-      <c r="I10" s="438"/>
+      <c r="H10" s="437"/>
+      <c r="I10" s="437"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="436" t="s">
+      <c r="A11" s="435" t="s">
         <v>1751</v>
       </c>
-      <c r="B11" s="439" t="s">
+      <c r="B11" s="438" t="s">
         <v>1749</v>
       </c>
-      <c r="C11" s="439" t="s">
+      <c r="C11" s="438" t="s">
         <v>1738</v>
       </c>
       <c r="D11" s="72" t="s">
         <v>1752</v>
       </c>
-      <c r="E11" s="438"/>
-      <c r="F11" s="440" t="s">
+      <c r="E11" s="437"/>
+      <c r="F11" s="439" t="s">
         <v>1753</v>
       </c>
-      <c r="G11" s="438" t="s">
+      <c r="G11" s="437" t="s">
         <v>1750</v>
       </c>
-      <c r="H11" s="438" t="s">
+      <c r="H11" s="437" t="s">
         <v>1754</v>
       </c>
-      <c r="I11" s="438"/>
+      <c r="I11" s="437"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="442" t="s">
+      <c r="A12" s="441" t="s">
         <v>1755</v>
       </c>
-      <c r="B12" s="441" t="s">
+      <c r="B12" s="440" t="s">
         <v>1756</v>
       </c>
-      <c r="C12" s="439"/>
+      <c r="C12" s="438"/>
       <c r="D12" s="72" t="s">
         <v>1757</v>
       </c>
-      <c r="E12" s="438"/>
-      <c r="F12" s="440" t="s">
+      <c r="E12" s="437"/>
+      <c r="F12" s="439" t="s">
         <v>1758</v>
       </c>
-      <c r="G12" s="438" t="s">
+      <c r="G12" s="437" t="s">
         <v>1759</v>
       </c>
-      <c r="H12" s="438" t="s">
+      <c r="H12" s="437" t="s">
         <v>1760</v>
       </c>
-      <c r="I12" s="438"/>
+      <c r="I12" s="437"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="436" t="s">
+      <c r="A13" s="435" t="s">
         <v>1761</v>
       </c>
-      <c r="B13" s="439" t="s">
+      <c r="B13" s="438" t="s">
         <v>1762</v>
       </c>
-      <c r="C13" s="439" t="s">
+      <c r="C13" s="438" t="s">
         <v>1763</v>
       </c>
       <c r="D13" s="72" t="s">
         <v>1762</v>
       </c>
-      <c r="E13" s="438"/>
-      <c r="F13" s="440" t="s">
+      <c r="E13" s="437"/>
+      <c r="F13" s="439" t="s">
         <v>1764</v>
       </c>
-      <c r="G13" s="438" t="s">
+      <c r="G13" s="437" t="s">
         <v>1765</v>
       </c>
-      <c r="H13" s="438" t="s">
+      <c r="H13" s="437" t="s">
         <v>1766</v>
       </c>
-      <c r="I13" s="438"/>
+      <c r="I13" s="437"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="436" t="s">
+      <c r="A14" s="435" t="s">
         <v>1767</v>
       </c>
-      <c r="B14" s="439" t="s">
+      <c r="B14" s="438" t="s">
         <v>1768</v>
       </c>
-      <c r="C14" s="439" t="s">
+      <c r="C14" s="438" t="s">
         <v>1769</v>
       </c>
       <c r="D14" s="72" t="s">
         <v>1770</v>
       </c>
-      <c r="E14" s="438"/>
-      <c r="F14" s="438"/>
-      <c r="G14" s="438" t="s">
+      <c r="E14" s="437"/>
+      <c r="F14" s="437"/>
+      <c r="G14" s="437" t="s">
         <v>1771</v>
       </c>
-      <c r="H14" s="438" t="s">
+      <c r="H14" s="437" t="s">
         <v>1772</v>
       </c>
-      <c r="I14" s="438"/>
+      <c r="I14" s="437"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="76" t="s">
         <v>1773</v>
       </c>
-      <c r="B15" s="439" t="s">
+      <c r="B15" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="C15" s="439"/>
+      <c r="C15" s="438"/>
       <c r="D15" s="72" t="s">
         <v>1737</v>
       </c>
-      <c r="E15" s="438"/>
-      <c r="F15" s="440" t="s">
+      <c r="E15" s="437"/>
+      <c r="F15" s="439" t="s">
         <v>1774</v>
       </c>
-      <c r="G15" s="438" t="s">
+      <c r="G15" s="437" t="s">
         <v>1775</v>
       </c>
-      <c r="H15" s="438" t="s">
+      <c r="H15" s="437" t="s">
         <v>1776</v>
       </c>
-      <c r="I15" s="438"/>
+      <c r="I15" s="437"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="436" t="s">
+      <c r="A16" s="435" t="s">
         <v>1777</v>
       </c>
-      <c r="B16" s="439" t="s">
+      <c r="B16" s="438" t="s">
         <v>1778</v>
       </c>
-      <c r="C16" s="439"/>
+      <c r="C16" s="438"/>
       <c r="D16" s="72" t="s">
         <v>1779</v>
       </c>
-      <c r="E16" s="438"/>
-      <c r="F16" s="440" t="s">
+      <c r="E16" s="437"/>
+      <c r="F16" s="439" t="s">
         <v>1780</v>
       </c>
-      <c r="G16" s="438" t="s">
+      <c r="G16" s="437" t="s">
         <v>1781</v>
       </c>
-      <c r="H16" s="438" t="s">
+      <c r="H16" s="437" t="s">
         <v>1782</v>
       </c>
-      <c r="I16" s="438"/>
+      <c r="I16" s="437"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="436" t="s">
+      <c r="A17" s="435" t="s">
         <v>1783</v>
       </c>
-      <c r="B17" s="439" t="s">
+      <c r="B17" s="438" t="s">
         <v>1784</v>
       </c>
-      <c r="C17" s="439"/>
+      <c r="C17" s="438"/>
       <c r="D17" s="72" t="s">
         <v>1785</v>
       </c>
-      <c r="E17" s="438"/>
-      <c r="F17" s="438"/>
-      <c r="G17" s="438" t="s">
+      <c r="E17" s="437"/>
+      <c r="F17" s="437"/>
+      <c r="G17" s="437" t="s">
         <v>1786</v>
       </c>
-      <c r="H17" s="438"/>
-      <c r="I17" s="438"/>
+      <c r="H17" s="437"/>
+      <c r="I17" s="437"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="436" t="s">
+      <c r="A18" s="435" t="s">
         <v>1787</v>
       </c>
-      <c r="B18" s="439" t="s">
+      <c r="B18" s="438" t="s">
         <v>1788</v>
       </c>
-      <c r="C18" s="439"/>
+      <c r="C18" s="438"/>
       <c r="D18" s="72" t="s">
         <v>1789</v>
       </c>
-      <c r="E18" s="438"/>
-      <c r="F18" s="438"/>
-      <c r="G18" s="438" t="s">
+      <c r="E18" s="437"/>
+      <c r="F18" s="437"/>
+      <c r="G18" s="437" t="s">
         <v>1790</v>
       </c>
-      <c r="H18" s="438" t="s">
+      <c r="H18" s="437" t="s">
         <v>1791</v>
       </c>
-      <c r="I18" s="438"/>
+      <c r="I18" s="437"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="436" t="s">
+      <c r="A19" s="435" t="s">
         <v>1792</v>
       </c>
-      <c r="B19" s="439" t="s">
+      <c r="B19" s="438" t="s">
         <v>1793</v>
       </c>
-      <c r="C19" s="439" t="s">
+      <c r="C19" s="438" t="s">
         <v>1794</v>
       </c>
-      <c r="D19" s="439" t="s">
+      <c r="D19" s="438" t="s">
         <v>1794</v>
       </c>
-      <c r="E19" s="438"/>
-      <c r="F19" s="438"/>
-      <c r="G19" s="438" t="s">
+      <c r="E19" s="437"/>
+      <c r="F19" s="437"/>
+      <c r="G19" s="437" t="s">
         <v>1795</v>
       </c>
-      <c r="H19" s="438" t="s">
+      <c r="H19" s="437" t="s">
         <v>1796</v>
       </c>
-      <c r="I19" s="438"/>
+      <c r="I19" s="437"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="76" t="s">
@@ -26777,27 +26665,27 @@
       <c r="B20" s="72" t="s">
         <v>1798</v>
       </c>
-      <c r="C20" s="439" t="s">
+      <c r="C20" s="438" t="s">
         <v>1799</v>
       </c>
       <c r="D20" s="72" t="s">
         <v>1800</v>
       </c>
-      <c r="E20" s="438"/>
-      <c r="F20" s="438"/>
-      <c r="G20" s="438" t="s">
+      <c r="E20" s="437"/>
+      <c r="F20" s="437"/>
+      <c r="G20" s="437" t="s">
         <v>1801</v>
       </c>
-      <c r="H20" s="438" t="s">
+      <c r="H20" s="437" t="s">
         <v>1802</v>
       </c>
-      <c r="I20" s="438"/>
+      <c r="I20" s="437"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="436" t="s">
+      <c r="A21" s="435" t="s">
         <v>1803</v>
       </c>
-      <c r="B21" s="439" t="s">
+      <c r="B21" s="438" t="s">
         <v>1752</v>
       </c>
       <c r="C21" s="77" t="s">
@@ -26806,589 +26694,589 @@
       <c r="D21" s="72" t="s">
         <v>1805</v>
       </c>
-      <c r="E21" s="438"/>
-      <c r="F21" s="440" t="s">
+      <c r="E21" s="437"/>
+      <c r="F21" s="439" t="s">
         <v>1806</v>
       </c>
-      <c r="G21" s="438" t="s">
+      <c r="G21" s="437" t="s">
         <v>1807</v>
       </c>
-      <c r="H21" s="438"/>
-      <c r="I21" s="438"/>
+      <c r="H21" s="437"/>
+      <c r="I21" s="437"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="436" t="s">
+      <c r="A22" s="435" t="s">
         <v>1808</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>1809</v>
       </c>
-      <c r="C22" s="439" t="s">
+      <c r="C22" s="438" t="s">
         <v>1810</v>
       </c>
       <c r="D22" s="72" t="s">
         <v>1811</v>
       </c>
-      <c r="E22" s="438"/>
-      <c r="F22" s="438"/>
-      <c r="G22" s="438" t="s">
+      <c r="E22" s="437"/>
+      <c r="F22" s="437"/>
+      <c r="G22" s="437" t="s">
         <v>1812</v>
       </c>
-      <c r="H22" s="438" t="s">
+      <c r="H22" s="437" t="s">
         <v>1813</v>
       </c>
-      <c r="I22" s="438"/>
+      <c r="I22" s="437"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="436" t="s">
+      <c r="A23" s="435" t="s">
         <v>1814</v>
       </c>
-      <c r="B23" s="439" t="s">
+      <c r="B23" s="438" t="s">
         <v>1752</v>
       </c>
-      <c r="C23" s="439" t="s">
+      <c r="C23" s="438" t="s">
         <v>1815</v>
       </c>
       <c r="D23" s="72" t="s">
         <v>1752</v>
       </c>
-      <c r="E23" s="438"/>
-      <c r="F23" s="438"/>
-      <c r="G23" s="438" t="s">
+      <c r="E23" s="437"/>
+      <c r="F23" s="437"/>
+      <c r="G23" s="437" t="s">
         <v>1816</v>
       </c>
-      <c r="H23" s="438" t="s">
+      <c r="H23" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I23" s="438"/>
+      <c r="I23" s="437"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="436" t="s">
+      <c r="A24" s="435" t="s">
         <v>1818</v>
       </c>
-      <c r="B24" s="439" t="s">
+      <c r="B24" s="438" t="s">
         <v>1752</v>
       </c>
-      <c r="C24" s="439"/>
+      <c r="C24" s="438"/>
       <c r="D24" s="72" t="s">
         <v>1752</v>
       </c>
-      <c r="E24" s="438"/>
-      <c r="F24" s="438"/>
-      <c r="G24" s="438" t="s">
+      <c r="E24" s="437"/>
+      <c r="F24" s="437"/>
+      <c r="G24" s="437" t="s">
         <v>1819</v>
       </c>
-      <c r="H24" s="438" t="s">
+      <c r="H24" s="437" t="s">
         <v>1820</v>
       </c>
-      <c r="I24" s="438"/>
+      <c r="I24" s="437"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="436" t="s">
+      <c r="A25" s="435" t="s">
         <v>1821</v>
       </c>
-      <c r="B25" s="439">
+      <c r="B25" s="438">
         <v>0.05</v>
       </c>
-      <c r="C25" s="439">
+      <c r="C25" s="438">
         <v>0.05</v>
       </c>
       <c r="D25" s="72">
         <v>0.04</v>
       </c>
-      <c r="E25" s="438"/>
-      <c r="F25" s="438"/>
-      <c r="G25" s="438" t="s">
+      <c r="E25" s="437"/>
+      <c r="F25" s="437"/>
+      <c r="G25" s="437" t="s">
         <v>1822</v>
       </c>
-      <c r="H25" s="438" t="s">
+      <c r="H25" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I25" s="438"/>
+      <c r="I25" s="437"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="436" t="s">
+      <c r="A26" s="435" t="s">
         <v>1823</v>
       </c>
-      <c r="B26" s="439" t="s">
+      <c r="B26" s="438" t="s">
         <v>1824</v>
       </c>
-      <c r="C26" s="439" t="s">
+      <c r="C26" s="438" t="s">
         <v>1825</v>
       </c>
       <c r="D26" s="72" t="s">
         <v>1737</v>
       </c>
-      <c r="E26" s="438"/>
-      <c r="F26" s="438"/>
-      <c r="G26" s="438" t="s">
+      <c r="E26" s="437"/>
+      <c r="F26" s="437"/>
+      <c r="G26" s="437" t="s">
         <v>1826</v>
       </c>
-      <c r="H26" s="438" t="s">
+      <c r="H26" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I26" s="438"/>
+      <c r="I26" s="437"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="436" t="s">
+      <c r="A27" s="435" t="s">
         <v>1827</v>
       </c>
-      <c r="B27" s="439" t="s">
+      <c r="B27" s="438" t="s">
         <v>1828</v>
       </c>
-      <c r="C27" s="439"/>
-      <c r="D27" s="439" t="s">
+      <c r="C27" s="438"/>
+      <c r="D27" s="438" t="s">
         <v>1828</v>
       </c>
-      <c r="E27" s="438"/>
-      <c r="F27" s="438"/>
-      <c r="G27" s="438" t="s">
+      <c r="E27" s="437"/>
+      <c r="F27" s="437"/>
+      <c r="G27" s="437" t="s">
         <v>1829</v>
       </c>
-      <c r="H27" s="438" t="s">
+      <c r="H27" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I27" s="438"/>
+      <c r="I27" s="437"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="436" t="s">
+      <c r="A28" s="435" t="s">
         <v>1830</v>
       </c>
-      <c r="B28" s="439" t="s">
+      <c r="B28" s="438" t="s">
         <v>1831</v>
       </c>
-      <c r="C28" s="439" t="s">
+      <c r="C28" s="438" t="s">
         <v>1832</v>
       </c>
       <c r="D28" s="72" t="s">
         <v>1831</v>
       </c>
-      <c r="E28" s="438"/>
-      <c r="F28" s="438" t="s">
+      <c r="E28" s="437"/>
+      <c r="F28" s="437" t="s">
         <v>1831</v>
       </c>
-      <c r="G28" s="438" t="s">
+      <c r="G28" s="437" t="s">
         <v>1833</v>
       </c>
-      <c r="H28" s="438" t="s">
+      <c r="H28" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I28" s="438"/>
+      <c r="I28" s="437"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
-      <c r="A29" s="436" t="s">
+      <c r="A29" s="435" t="s">
         <v>1834</v>
       </c>
-      <c r="B29" s="439" t="s">
+      <c r="B29" s="438" t="s">
         <v>1835</v>
       </c>
-      <c r="C29" s="439" t="s">
+      <c r="C29" s="438" t="s">
         <v>1836</v>
       </c>
       <c r="D29" s="72" t="s">
         <v>1837</v>
       </c>
-      <c r="E29" s="438"/>
-      <c r="F29" s="440" t="s">
+      <c r="E29" s="437"/>
+      <c r="F29" s="439" t="s">
         <v>1838</v>
       </c>
-      <c r="G29" s="438" t="s">
+      <c r="G29" s="437" t="s">
         <v>1839</v>
       </c>
-      <c r="H29" s="438"/>
-      <c r="I29" s="438"/>
+      <c r="H29" s="437"/>
+      <c r="I29" s="437"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="436" t="s">
+      <c r="A30" s="435" t="s">
         <v>1750</v>
       </c>
-      <c r="B30" s="439" t="s">
+      <c r="B30" s="438" t="s">
         <v>1840</v>
       </c>
-      <c r="C30" s="439" t="s">
+      <c r="C30" s="438" t="s">
         <v>1815</v>
       </c>
       <c r="D30" s="72" t="s">
         <v>1841</v>
       </c>
-      <c r="E30" s="438"/>
-      <c r="F30" s="440" t="s">
+      <c r="E30" s="437"/>
+      <c r="F30" s="439" t="s">
         <v>1842</v>
       </c>
-      <c r="G30" s="438" t="s">
+      <c r="G30" s="437" t="s">
         <v>1843</v>
       </c>
-      <c r="H30" s="438" t="s">
+      <c r="H30" s="437" t="s">
         <v>1844</v>
       </c>
-      <c r="I30" s="438"/>
+      <c r="I30" s="437"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="436" t="s">
+      <c r="A31" s="435" t="s">
         <v>1845</v>
       </c>
-      <c r="B31" s="439" t="s">
+      <c r="B31" s="438" t="s">
         <v>1846</v>
       </c>
-      <c r="C31" s="439" t="s">
+      <c r="C31" s="438" t="s">
         <v>1847</v>
       </c>
-      <c r="D31" s="439" t="s">
+      <c r="D31" s="438" t="s">
         <v>1846</v>
       </c>
-      <c r="E31" s="438"/>
-      <c r="F31" s="440" t="s">
+      <c r="E31" s="437"/>
+      <c r="F31" s="439" t="s">
         <v>1848</v>
       </c>
-      <c r="G31" s="438" t="s">
+      <c r="G31" s="437" t="s">
         <v>1849</v>
       </c>
-      <c r="H31" s="438" t="s">
+      <c r="H31" s="437" t="s">
         <v>1850</v>
       </c>
-      <c r="I31" s="438"/>
+      <c r="I31" s="437"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="436" t="s">
+      <c r="A32" s="435" t="s">
         <v>1851</v>
       </c>
-      <c r="B32" s="439" t="s">
+      <c r="B32" s="438" t="s">
         <v>1226</v>
       </c>
-      <c r="C32" s="439" t="s">
+      <c r="C32" s="438" t="s">
         <v>1852</v>
       </c>
       <c r="D32" s="72" t="s">
         <v>1475</v>
       </c>
-      <c r="E32" s="438"/>
-      <c r="F32" s="438"/>
-      <c r="G32" s="438" t="s">
+      <c r="E32" s="437"/>
+      <c r="F32" s="437"/>
+      <c r="G32" s="437" t="s">
         <v>1853</v>
       </c>
-      <c r="H32" s="438" t="s">
+      <c r="H32" s="437" t="s">
         <v>1854</v>
       </c>
-      <c r="I32" s="438"/>
+      <c r="I32" s="437"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="436" t="s">
+      <c r="A33" s="435" t="s">
         <v>1855</v>
       </c>
-      <c r="B33" s="439" t="s">
+      <c r="B33" s="438" t="s">
         <v>1856</v>
       </c>
-      <c r="C33" s="439" t="s">
+      <c r="C33" s="438" t="s">
         <v>1857</v>
       </c>
       <c r="D33" s="72" t="s">
         <v>1858</v>
       </c>
-      <c r="E33" s="438"/>
-      <c r="F33" s="440" t="s">
+      <c r="E33" s="437"/>
+      <c r="F33" s="439" t="s">
         <v>1859</v>
       </c>
-      <c r="G33" s="438" t="s">
+      <c r="G33" s="437" t="s">
         <v>1860</v>
       </c>
-      <c r="H33" s="438" t="s">
+      <c r="H33" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I33" s="438"/>
+      <c r="I33" s="437"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="436" t="s">
+      <c r="A34" s="435" t="s">
         <v>1861</v>
       </c>
-      <c r="B34" s="439" t="s">
+      <c r="B34" s="438" t="s">
         <v>1862</v>
       </c>
-      <c r="C34" s="439">
+      <c r="C34" s="438">
         <v>10305</v>
       </c>
       <c r="D34" s="72">
         <v>9800</v>
       </c>
-      <c r="E34" s="438"/>
-      <c r="F34" s="438"/>
-      <c r="G34" s="438" t="s">
+      <c r="E34" s="437"/>
+      <c r="F34" s="437"/>
+      <c r="G34" s="437" t="s">
         <v>1863</v>
       </c>
-      <c r="H34" s="438" t="s">
+      <c r="H34" s="437" t="s">
         <v>1864</v>
       </c>
-      <c r="I34" s="438"/>
+      <c r="I34" s="437"/>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
-      <c r="A35" s="436" t="s">
+      <c r="A35" s="435" t="s">
         <v>1865</v>
       </c>
-      <c r="B35" s="439">
+      <c r="B35" s="438">
         <v>1.75</v>
       </c>
-      <c r="C35" s="439">
+      <c r="C35" s="438">
         <v>2.85</v>
       </c>
       <c r="D35" s="72">
         <v>1.75</v>
       </c>
-      <c r="E35" s="438"/>
-      <c r="F35" s="438" t="s">
+      <c r="E35" s="437"/>
+      <c r="F35" s="437" t="s">
         <v>1866</v>
       </c>
-      <c r="G35" s="438" t="s">
+      <c r="G35" s="437" t="s">
         <v>1867</v>
       </c>
-      <c r="H35" s="438"/>
-      <c r="I35" s="438"/>
+      <c r="H35" s="437"/>
+      <c r="I35" s="437"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="436"/>
-      <c r="B36" s="439"/>
-      <c r="C36" s="439"/>
-      <c r="E36" s="438"/>
-      <c r="F36" s="438"/>
-      <c r="G36" s="438" t="s">
+      <c r="A36" s="435"/>
+      <c r="B36" s="438"/>
+      <c r="C36" s="438"/>
+      <c r="E36" s="437"/>
+      <c r="F36" s="437"/>
+      <c r="G36" s="437" t="s">
         <v>1868</v>
       </c>
-      <c r="H36" s="438" t="s">
+      <c r="H36" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I36" s="438"/>
+      <c r="I36" s="437"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="174" t="s">
         <v>411</v>
       </c>
-      <c r="B37" s="439"/>
-      <c r="C37" s="439"/>
-      <c r="E37" s="438"/>
-      <c r="F37" s="438"/>
-      <c r="G37" s="438" t="s">
+      <c r="B37" s="438"/>
+      <c r="C37" s="438"/>
+      <c r="E37" s="437"/>
+      <c r="F37" s="437"/>
+      <c r="G37" s="437" t="s">
         <v>1869</v>
       </c>
-      <c r="H37" s="438" t="s">
+      <c r="H37" s="437" t="s">
         <v>1870</v>
       </c>
-      <c r="I37" s="438"/>
+      <c r="I37" s="437"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="436"/>
-      <c r="B38" s="439"/>
-      <c r="C38" s="439"/>
-      <c r="E38" s="438"/>
-      <c r="F38" s="438"/>
-      <c r="G38" s="438" t="s">
+      <c r="A38" s="435"/>
+      <c r="B38" s="438"/>
+      <c r="C38" s="438"/>
+      <c r="E38" s="437"/>
+      <c r="F38" s="437"/>
+      <c r="G38" s="437" t="s">
         <v>1871</v>
       </c>
-      <c r="H38" s="438"/>
-      <c r="I38" s="438"/>
+      <c r="H38" s="437"/>
+      <c r="I38" s="437"/>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="436"/>
-      <c r="B39" s="439"/>
-      <c r="C39" s="439"/>
-      <c r="E39" s="438"/>
-      <c r="F39" s="438"/>
-      <c r="G39" s="438" t="s">
+      <c r="A39" s="435"/>
+      <c r="B39" s="438"/>
+      <c r="C39" s="438"/>
+      <c r="E39" s="437"/>
+      <c r="F39" s="437"/>
+      <c r="G39" s="437" t="s">
         <v>1872</v>
       </c>
-      <c r="H39" s="438" t="s">
+      <c r="H39" s="437" t="s">
         <v>1873</v>
       </c>
-      <c r="I39" s="438"/>
+      <c r="I39" s="437"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="436"/>
-      <c r="B40" s="439"/>
-      <c r="C40" s="439"/>
-      <c r="E40" s="438"/>
-      <c r="F40" s="438"/>
-      <c r="G40" s="438" t="s">
+      <c r="A40" s="435"/>
+      <c r="B40" s="438"/>
+      <c r="C40" s="438"/>
+      <c r="E40" s="437"/>
+      <c r="F40" s="437"/>
+      <c r="G40" s="437" t="s">
         <v>1874</v>
       </c>
-      <c r="H40" s="438" t="s">
+      <c r="H40" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I40" s="438"/>
+      <c r="I40" s="437"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="436"/>
-      <c r="B41" s="439"/>
-      <c r="C41" s="439"/>
-      <c r="E41" s="438"/>
-      <c r="F41" s="438"/>
-      <c r="G41" s="438" t="s">
+      <c r="A41" s="435"/>
+      <c r="B41" s="438"/>
+      <c r="C41" s="438"/>
+      <c r="E41" s="437"/>
+      <c r="F41" s="437"/>
+      <c r="G41" s="437" t="s">
         <v>1875</v>
       </c>
-      <c r="H41" s="438" t="s">
+      <c r="H41" s="437" t="s">
         <v>1876</v>
       </c>
-      <c r="I41" s="438"/>
+      <c r="I41" s="437"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="436"/>
-      <c r="B42" s="439"/>
-      <c r="C42" s="439"/>
-      <c r="E42" s="438"/>
-      <c r="F42" s="438"/>
-      <c r="G42" s="438" t="s">
+      <c r="A42" s="435"/>
+      <c r="B42" s="438"/>
+      <c r="C42" s="438"/>
+      <c r="E42" s="437"/>
+      <c r="F42" s="437"/>
+      <c r="G42" s="437" t="s">
         <v>1877</v>
       </c>
-      <c r="H42" s="438" t="s">
+      <c r="H42" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I42" s="438"/>
+      <c r="I42" s="437"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="436"/>
-      <c r="B43" s="439"/>
-      <c r="C43" s="439"/>
-      <c r="E43" s="438"/>
-      <c r="F43" s="438"/>
-      <c r="G43" s="438" t="s">
+      <c r="A43" s="435"/>
+      <c r="B43" s="438"/>
+      <c r="C43" s="438"/>
+      <c r="E43" s="437"/>
+      <c r="F43" s="437"/>
+      <c r="G43" s="437" t="s">
         <v>1878</v>
       </c>
-      <c r="H43" s="438" t="s">
+      <c r="H43" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I43" s="438"/>
+      <c r="I43" s="437"/>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="436"/>
-      <c r="B44" s="439"/>
-      <c r="C44" s="439"/>
-      <c r="E44" s="438"/>
-      <c r="F44" s="438"/>
-      <c r="G44" s="438" t="s">
+      <c r="A44" s="435"/>
+      <c r="B44" s="438"/>
+      <c r="C44" s="438"/>
+      <c r="E44" s="437"/>
+      <c r="F44" s="437"/>
+      <c r="G44" s="437" t="s">
         <v>1879</v>
       </c>
-      <c r="H44" s="438"/>
-      <c r="I44" s="438"/>
+      <c r="H44" s="437"/>
+      <c r="I44" s="437"/>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="436"/>
-      <c r="B45" s="439"/>
-      <c r="C45" s="439"/>
-      <c r="E45" s="438"/>
-      <c r="F45" s="438"/>
-      <c r="G45" s="438" t="s">
+      <c r="A45" s="435"/>
+      <c r="B45" s="438"/>
+      <c r="C45" s="438"/>
+      <c r="E45" s="437"/>
+      <c r="F45" s="437"/>
+      <c r="G45" s="437" t="s">
         <v>1880</v>
       </c>
-      <c r="H45" s="438" t="s">
+      <c r="H45" s="437" t="s">
         <v>1881</v>
       </c>
-      <c r="I45" s="438"/>
+      <c r="I45" s="437"/>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="436"/>
-      <c r="B46" s="439"/>
-      <c r="C46" s="439"/>
-      <c r="E46" s="438"/>
-      <c r="F46" s="438"/>
-      <c r="G46" s="438" t="s">
+      <c r="A46" s="435"/>
+      <c r="B46" s="438"/>
+      <c r="C46" s="438"/>
+      <c r="E46" s="437"/>
+      <c r="F46" s="437"/>
+      <c r="G46" s="437" t="s">
         <v>1882</v>
       </c>
-      <c r="H46" s="438" t="s">
+      <c r="H46" s="437" t="s">
         <v>1883</v>
       </c>
-      <c r="I46" s="438"/>
+      <c r="I46" s="437"/>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="436"/>
-      <c r="B47" s="439"/>
-      <c r="C47" s="439"/>
-      <c r="E47" s="438"/>
-      <c r="F47" s="438"/>
-      <c r="G47" s="438" t="s">
+      <c r="A47" s="435"/>
+      <c r="B47" s="438"/>
+      <c r="C47" s="438"/>
+      <c r="E47" s="437"/>
+      <c r="F47" s="437"/>
+      <c r="G47" s="437" t="s">
         <v>1884</v>
       </c>
-      <c r="H47" s="438" t="s">
+      <c r="H47" s="437" t="s">
         <v>1885</v>
       </c>
-      <c r="I47" s="438"/>
+      <c r="I47" s="437"/>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="436"/>
-      <c r="B48" s="439"/>
-      <c r="C48" s="439"/>
-      <c r="E48" s="438"/>
-      <c r="F48" s="438"/>
-      <c r="G48" s="438" t="s">
+      <c r="A48" s="435"/>
+      <c r="B48" s="438"/>
+      <c r="C48" s="438"/>
+      <c r="E48" s="437"/>
+      <c r="F48" s="437"/>
+      <c r="G48" s="437" t="s">
         <v>1886</v>
       </c>
-      <c r="H48" s="438" t="s">
+      <c r="H48" s="437" t="s">
         <v>1887</v>
       </c>
-      <c r="I48" s="438"/>
+      <c r="I48" s="437"/>
     </row>
     <row r="49" spans="6:9">
-      <c r="F49" s="438"/>
-      <c r="G49" s="438" t="s">
+      <c r="F49" s="437"/>
+      <c r="G49" s="437" t="s">
         <v>1888</v>
       </c>
-      <c r="H49" s="438" t="s">
+      <c r="H49" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I49" s="438"/>
+      <c r="I49" s="437"/>
     </row>
     <row r="50" spans="6:9">
-      <c r="F50" s="438"/>
-      <c r="G50" s="438" t="s">
+      <c r="F50" s="437"/>
+      <c r="G50" s="437" t="s">
         <v>1889</v>
       </c>
-      <c r="H50" s="438" t="s">
+      <c r="H50" s="437" t="s">
         <v>1890</v>
       </c>
-      <c r="I50" s="438"/>
+      <c r="I50" s="437"/>
     </row>
     <row r="51" spans="6:9">
-      <c r="F51" s="438"/>
-      <c r="G51" s="438" t="s">
+      <c r="F51" s="437"/>
+      <c r="G51" s="437" t="s">
         <v>1891</v>
       </c>
-      <c r="H51" s="438" t="s">
+      <c r="H51" s="437" t="s">
         <v>1817</v>
       </c>
-      <c r="I51" s="438"/>
+      <c r="I51" s="437"/>
     </row>
     <row r="52" spans="6:9">
-      <c r="F52" s="438"/>
-      <c r="G52" s="438" t="s">
+      <c r="F52" s="437"/>
+      <c r="G52" s="437" t="s">
         <v>1892</v>
       </c>
-      <c r="H52" s="438"/>
-      <c r="I52" s="438"/>
+      <c r="H52" s="437"/>
+      <c r="I52" s="437"/>
     </row>
     <row r="53" spans="6:9">
-      <c r="F53" s="438"/>
-      <c r="G53" s="438" t="s">
+      <c r="F53" s="437"/>
+      <c r="G53" s="437" t="s">
         <v>1893</v>
       </c>
-      <c r="H53" s="438" t="s">
+      <c r="H53" s="437" t="s">
         <v>1894</v>
       </c>
-      <c r="I53" s="438"/>
+      <c r="I53" s="437"/>
     </row>
     <row r="54" spans="6:9">
-      <c r="F54" s="438"/>
-      <c r="G54" s="438" t="s">
+      <c r="F54" s="437"/>
+      <c r="G54" s="437" t="s">
         <v>1895</v>
       </c>
-      <c r="H54" s="438" t="s">
+      <c r="H54" s="437" t="s">
         <v>1896</v>
       </c>
-      <c r="I54" s="438"/>
+      <c r="I54" s="437"/>
     </row>
     <row r="55" spans="6:9">
-      <c r="F55" s="438"/>
-      <c r="G55" s="438" t="s">
+      <c r="F55" s="437"/>
+      <c r="G55" s="437" t="s">
         <v>1897</v>
       </c>
-      <c r="H55" s="438" t="s">
+      <c r="H55" s="437" t="s">
         <v>1898</v>
       </c>
-      <c r="I55" s="438"/>
+      <c r="I55" s="437"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27428,31 +27316,31 @@
       <c r="A1" s="304" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="382" t="s">
+      <c r="B1" s="381" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="382" t="s">
+      <c r="E1" s="381" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="382" t="s">
+      <c r="F1" s="381" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="383" t="s">
+      <c r="G1" s="382" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="384" t="s">
+      <c r="H1" s="383" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="382" t="s">
+      <c r="I1" s="381" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="385" t="s">
+      <c r="J1" s="384" t="s">
         <v>30</v>
       </c>
     </row>
@@ -27603,7 +27491,7 @@
       <c r="G6" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="386" t="s">
+      <c r="H6" s="385" t="s">
         <v>44</v>
       </c>
       <c r="I6" s="156">
@@ -27615,7 +27503,7 @@
       <c r="A7" s="305" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="387" t="s">
+      <c r="B7" s="386" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="306">
@@ -27634,7 +27522,7 @@
       <c r="G7" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="386" t="s">
+      <c r="H7" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I7" s="156">
@@ -27646,7 +27534,7 @@
       <c r="A8" s="305" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="387" t="s">
+      <c r="B8" s="386" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="313">
@@ -27677,7 +27565,7 @@
       <c r="A9" s="305" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="388" t="s">
+      <c r="B9" s="387" t="s">
         <v>51</v>
       </c>
       <c r="C9" s="315">
@@ -27708,7 +27596,7 @@
       <c r="A10" s="305" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="388" t="s">
+      <c r="B10" s="387" t="s">
         <v>53</v>
       </c>
       <c r="C10" s="315">
@@ -27758,7 +27646,7 @@
       <c r="G11" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="H11" s="386" t="s">
+      <c r="H11" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I11" s="156">
@@ -27773,7 +27661,7 @@
       <c r="B12" s="147" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="389">
+      <c r="C12" s="388">
         <v>2</v>
       </c>
       <c r="D12" s="307">
@@ -27835,7 +27723,7 @@
       <c r="B14" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="389">
+      <c r="C14" s="388">
         <v>5</v>
       </c>
       <c r="D14" s="307">
@@ -27866,7 +27754,7 @@
       <c r="B15" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="389">
+      <c r="C15" s="388">
         <v>2</v>
       </c>
       <c r="D15" s="307">
@@ -27897,7 +27785,7 @@
       <c r="B16" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="389">
+      <c r="C16" s="388">
         <v>2</v>
       </c>
       <c r="D16" s="307">
@@ -27928,7 +27816,7 @@
       <c r="B17" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="389">
+      <c r="C17" s="388">
         <v>5</v>
       </c>
       <c r="D17" s="307">
@@ -27959,7 +27847,7 @@
       <c r="B18" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="389">
+      <c r="C18" s="388">
         <v>2</v>
       </c>
       <c r="D18" s="307">
@@ -27990,7 +27878,7 @@
       <c r="B19" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="389">
+      <c r="C19" s="388">
         <v>7</v>
       </c>
       <c r="D19" s="307">
@@ -28021,7 +27909,7 @@
       <c r="B20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="389">
+      <c r="C20" s="388">
         <v>7</v>
       </c>
       <c r="D20" s="307">
@@ -28052,7 +27940,7 @@
       <c r="B21" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="389">
+      <c r="C21" s="388">
         <v>7</v>
       </c>
       <c r="D21" s="307">
@@ -28083,7 +27971,7 @@
       <c r="B22" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="389">
+      <c r="C22" s="388">
         <v>5</v>
       </c>
       <c r="D22" s="307">
@@ -28114,7 +28002,7 @@
       <c r="B23" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="389">
+      <c r="C23" s="388">
         <v>5</v>
       </c>
       <c r="D23" s="307">
@@ -28145,7 +28033,7 @@
       <c r="B24" s="147" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="389">
+      <c r="C24" s="388">
         <v>2</v>
       </c>
       <c r="D24" s="307">
@@ -28176,7 +28064,7 @@
       <c r="B25" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="389">
+      <c r="C25" s="388">
         <v>2</v>
       </c>
       <c r="D25" s="307">
@@ -28238,7 +28126,7 @@
       <c r="B27" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="C27" s="389">
+      <c r="C27" s="388">
         <v>2</v>
       </c>
       <c r="D27" s="307">
@@ -28359,7 +28247,7 @@
       <c r="A31" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B31" s="388" t="s">
+      <c r="B31" s="387" t="s">
         <v>97</v>
       </c>
       <c r="C31" s="317">
@@ -28378,7 +28266,7 @@
       <c r="G31" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="H31" s="390" t="s">
+      <c r="H31" s="389" t="s">
         <v>99</v>
       </c>
       <c r="I31" s="157">
@@ -28390,7 +28278,7 @@
       <c r="A32" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="388" t="s">
+      <c r="B32" s="387" t="s">
         <v>100</v>
       </c>
       <c r="C32" s="317">
@@ -28409,7 +28297,7 @@
       <c r="G32" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="H32" s="390" t="s">
+      <c r="H32" s="389" t="s">
         <v>99</v>
       </c>
       <c r="I32" s="157">
@@ -28421,7 +28309,7 @@
       <c r="A33" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="388" t="s">
+      <c r="B33" s="387" t="s">
         <v>102</v>
       </c>
       <c r="C33" s="317">
@@ -28440,7 +28328,7 @@
       <c r="G33" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="390" t="s">
+      <c r="H33" s="389" t="s">
         <v>99</v>
       </c>
       <c r="I33" s="156">
@@ -28593,7 +28481,7 @@
         <v>1.4</v>
       </c>
       <c r="G38" s="54"/>
-      <c r="H38" s="386"/>
+      <c r="H38" s="385"/>
       <c r="I38" s="157">
         <v>1</v>
       </c>
@@ -28603,10 +28491,10 @@
       <c r="A39" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B39" s="390" t="s">
+      <c r="B39" s="389" t="s">
         <v>113</v>
       </c>
-      <c r="C39" s="389">
+      <c r="C39" s="388">
         <v>1</v>
       </c>
       <c r="D39" s="307">
@@ -28622,7 +28510,7 @@
       <c r="G39" s="54" t="s">
         <v>114</v>
       </c>
-      <c r="H39" s="390" t="s">
+      <c r="H39" s="389" t="s">
         <v>115</v>
       </c>
       <c r="I39" s="156">
@@ -28634,10 +28522,10 @@
       <c r="A40" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B40" s="390" t="s">
+      <c r="B40" s="389" t="s">
         <v>116</v>
       </c>
-      <c r="C40" s="389">
+      <c r="C40" s="388">
         <v>1</v>
       </c>
       <c r="D40" s="307">
@@ -28653,7 +28541,7 @@
       <c r="G40" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="H40" s="390" t="s">
+      <c r="H40" s="389" t="s">
         <v>118</v>
       </c>
       <c r="I40" s="156">
@@ -28684,7 +28572,7 @@
       <c r="G41" s="54" t="s">
         <v>120</v>
       </c>
-      <c r="H41" s="386" t="s">
+      <c r="H41" s="385" t="s">
         <v>121</v>
       </c>
       <c r="I41" s="156">
@@ -28696,7 +28584,7 @@
       <c r="A42" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B42" s="390" t="s">
+      <c r="B42" s="389" t="s">
         <v>122</v>
       </c>
       <c r="C42" s="7">
@@ -28715,7 +28603,7 @@
       <c r="G42" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="H42" s="390" t="s">
+      <c r="H42" s="389" t="s">
         <v>99</v>
       </c>
       <c r="I42" s="156">
@@ -28727,7 +28615,7 @@
       <c r="A43" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B43" s="391" t="s">
+      <c r="B43" s="390" t="s">
         <v>124</v>
       </c>
       <c r="C43" s="317">
@@ -28746,7 +28634,7 @@
       <c r="G43" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="H43" s="386" t="s">
+      <c r="H43" s="385" t="s">
         <v>126</v>
       </c>
       <c r="I43" s="156">
@@ -28777,7 +28665,7 @@
       <c r="G44" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="386" t="s">
+      <c r="H44" s="385" t="s">
         <v>129</v>
       </c>
       <c r="I44" s="156">
@@ -28808,7 +28696,7 @@
       <c r="G45" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="H45" s="386" t="s">
+      <c r="H45" s="385" t="s">
         <v>129</v>
       </c>
       <c r="I45" s="157">
@@ -28820,7 +28708,7 @@
       <c r="A46" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B46" s="392" t="s">
+      <c r="B46" s="391" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="321">
@@ -28839,7 +28727,7 @@
       <c r="G46" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="H46" s="386" t="s">
+      <c r="H46" s="385" t="s">
         <v>134</v>
       </c>
       <c r="I46" s="156">
@@ -28870,7 +28758,7 @@
       <c r="G47" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="H47" s="393" t="s">
+      <c r="H47" s="392" t="s">
         <v>137</v>
       </c>
       <c r="I47" s="156">
@@ -28901,7 +28789,7 @@
       <c r="G48" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="H48" s="386" t="s">
+      <c r="H48" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I48" s="156">
@@ -29099,7 +28987,7 @@
       <c r="A55" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="387" t="s">
+      <c r="B55" s="386" t="s">
         <v>155</v>
       </c>
       <c r="C55" s="307">
@@ -29118,7 +29006,7 @@
       <c r="G55" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="H55" s="386" t="s">
+      <c r="H55" s="385" t="s">
         <v>157</v>
       </c>
       <c r="I55" s="156">
@@ -29130,7 +29018,7 @@
       <c r="A56" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="394" t="s">
+      <c r="B56" s="393" t="s">
         <v>158</v>
       </c>
       <c r="C56" s="306">
@@ -29149,7 +29037,7 @@
       <c r="G56" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="H56" s="386" t="s">
+      <c r="H56" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I56" s="156">
@@ -29180,7 +29068,7 @@
       <c r="G57" s="54" t="s">
         <v>160</v>
       </c>
-      <c r="H57" s="386" t="s">
+      <c r="H57" s="385" t="s">
         <v>161</v>
       </c>
       <c r="I57" s="156">
@@ -29195,7 +29083,7 @@
       <c r="B58" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="C58" s="389">
+      <c r="C58" s="388">
         <v>1</v>
       </c>
       <c r="D58" s="307">
@@ -29211,7 +29099,7 @@
       <c r="G58" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="H58" s="386" t="s">
+      <c r="H58" s="385" t="s">
         <v>161</v>
       </c>
       <c r="I58" s="157">
@@ -29223,10 +29111,10 @@
       <c r="A59" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="392" t="s">
+      <c r="B59" s="391" t="s">
         <v>164</v>
       </c>
-      <c r="C59" s="389">
+      <c r="C59" s="388">
         <v>1</v>
       </c>
       <c r="D59" s="307">
@@ -29242,7 +29130,7 @@
       <c r="G59" s="54" t="s">
         <v>165</v>
       </c>
-      <c r="H59" s="390" t="s">
+      <c r="H59" s="389" t="s">
         <v>166</v>
       </c>
       <c r="I59" s="156">
@@ -29254,10 +29142,10 @@
       <c r="A60" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="391" t="s">
+      <c r="B60" s="390" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="395">
+      <c r="C60" s="394">
         <v>1</v>
       </c>
       <c r="D60" s="307">
@@ -29273,7 +29161,7 @@
       <c r="G60" s="54" t="s">
         <v>168</v>
       </c>
-      <c r="H60" s="386"/>
+      <c r="H60" s="385"/>
       <c r="I60" s="156">
         <v>1</v>
       </c>
@@ -29287,7 +29175,7 @@
       <c r="B61" s="320" t="s">
         <v>169</v>
       </c>
-      <c r="C61" s="395">
+      <c r="C61" s="394">
         <v>1</v>
       </c>
       <c r="D61" s="307">
@@ -29303,7 +29191,7 @@
       <c r="G61" s="54" t="s">
         <v>170</v>
       </c>
-      <c r="H61" s="386" t="s">
+      <c r="H61" s="385" t="s">
         <v>171</v>
       </c>
       <c r="I61" s="156">
@@ -29315,7 +29203,7 @@
       <c r="A62" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B62" s="388" t="s">
+      <c r="B62" s="387" t="s">
         <v>172</v>
       </c>
       <c r="C62" s="315">
@@ -29346,7 +29234,7 @@
       <c r="A63" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="388" t="s">
+      <c r="B63" s="387" t="s">
         <v>175</v>
       </c>
       <c r="C63" s="315">
@@ -29480,7 +29368,7 @@
       <c r="D67" s="307">
         <v>1</v>
       </c>
-      <c r="E67" s="396">
+      <c r="E67" s="395">
         <v>6.5</v>
       </c>
       <c r="F67" s="308">
@@ -29489,7 +29377,7 @@
       <c r="G67" s="54" t="s">
         <v>186</v>
       </c>
-      <c r="H67" s="396" t="s">
+      <c r="H67" s="395" t="s">
         <v>187</v>
       </c>
       <c r="I67" s="156">
@@ -29505,13 +29393,13 @@
       <c r="B68" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="C68" s="389">
+      <c r="C68" s="388">
         <v>1</v>
       </c>
       <c r="D68" s="307">
         <v>1</v>
       </c>
-      <c r="E68" s="397">
+      <c r="E68" s="396">
         <v>16</v>
       </c>
       <c r="F68" s="308">
@@ -29533,16 +29421,16 @@
       <c r="A69" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B69" s="390" t="s">
+      <c r="B69" s="389" t="s">
         <v>191</v>
       </c>
-      <c r="C69" s="389">
+      <c r="C69" s="388">
         <v>1</v>
       </c>
       <c r="D69" s="307">
         <v>1</v>
       </c>
-      <c r="E69" s="397">
+      <c r="E69" s="396">
         <v>33.700000000000003</v>
       </c>
       <c r="F69" s="308">
@@ -29564,7 +29452,7 @@
       <c r="A70" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B70" s="388" t="s">
+      <c r="B70" s="387" t="s">
         <v>193</v>
       </c>
       <c r="C70" s="317">
@@ -29583,7 +29471,7 @@
       <c r="G70" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="H70" s="398" t="s">
+      <c r="H70" s="397" t="s">
         <v>195</v>
       </c>
       <c r="I70" s="157">
@@ -29595,7 +29483,7 @@
       <c r="A71" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B71" s="390" t="s">
+      <c r="B71" s="389" t="s">
         <v>196</v>
       </c>
       <c r="C71" s="7">
@@ -29614,7 +29502,7 @@
       <c r="G71" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="H71" s="390" t="s">
+      <c r="H71" s="389" t="s">
         <v>47</v>
       </c>
       <c r="I71" s="156">
@@ -29626,7 +29514,7 @@
       <c r="A72" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B72" s="394" t="s">
+      <c r="B72" s="393" t="s">
         <v>198</v>
       </c>
       <c r="C72" s="317">
@@ -29645,7 +29533,7 @@
       <c r="G72" s="54" t="s">
         <v>199</v>
       </c>
-      <c r="H72" s="386" t="s">
+      <c r="H72" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I72" s="156">
@@ -29657,7 +29545,7 @@
       <c r="A73" s="316" t="s">
         <v>55</v>
       </c>
-      <c r="B73" s="394" t="s">
+      <c r="B73" s="393" t="s">
         <v>200</v>
       </c>
       <c r="C73" s="317">
@@ -29675,7 +29563,7 @@
       <c r="G73" s="219" t="s">
         <v>201</v>
       </c>
-      <c r="H73" s="386" t="s">
+      <c r="H73" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I73" s="157">
@@ -29691,10 +29579,10 @@
       <c r="B74" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="C74" s="399">
-        <v>1</v>
-      </c>
-      <c r="D74" s="400">
+      <c r="C74" s="398">
+        <v>1</v>
+      </c>
+      <c r="D74" s="399">
         <v>1</v>
       </c>
       <c r="E74" s="342">
@@ -29785,7 +29673,7 @@
       <c r="A77" s="305" t="s">
         <v>204</v>
       </c>
-      <c r="B77" s="390" t="s">
+      <c r="B77" s="389" t="s">
         <v>211</v>
       </c>
       <c r="C77" s="307">
@@ -29903,7 +29791,7 @@
       <c r="G80" s="54" t="s">
         <v>219</v>
       </c>
-      <c r="H80" s="386" t="s">
+      <c r="H80" s="385" t="s">
         <v>217</v>
       </c>
       <c r="I80" s="156">
@@ -30309,7 +30197,7 @@
       <c r="A93" s="305" t="s">
         <v>204</v>
       </c>
-      <c r="B93" s="387" t="s">
+      <c r="B93" s="386" t="s">
         <v>244</v>
       </c>
       <c r="C93" s="307">
@@ -30342,7 +30230,7 @@
       <c r="A94" s="316" t="s">
         <v>204</v>
       </c>
-      <c r="B94" s="391" t="s">
+      <c r="B94" s="390" t="s">
         <v>246</v>
       </c>
       <c r="C94" s="307">
@@ -30394,7 +30282,7 @@
       <c r="G95" s="55" t="s">
         <v>249</v>
       </c>
-      <c r="H95" s="386" t="s">
+      <c r="H95" s="385" t="s">
         <v>207</v>
       </c>
       <c r="I95" s="156">
@@ -30408,7 +30296,7 @@
       <c r="A96" s="316" t="s">
         <v>204</v>
       </c>
-      <c r="B96" s="387" t="s">
+      <c r="B96" s="386" t="s">
         <v>250</v>
       </c>
       <c r="C96" s="307">
@@ -30624,7 +30512,7 @@
       <c r="G102" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="H102" s="386" t="s">
+      <c r="H102" s="385" t="s">
         <v>217</v>
       </c>
       <c r="I102" s="156">
@@ -30768,7 +30656,7 @@
       <c r="A107" s="316" t="s">
         <v>204</v>
       </c>
-      <c r="B107" s="388" t="s">
+      <c r="B107" s="387" t="s">
         <v>272</v>
       </c>
       <c r="C107" s="315">
@@ -30801,7 +30689,7 @@
       <c r="A108" s="316" t="s">
         <v>204</v>
       </c>
-      <c r="B108" s="388" t="s">
+      <c r="B108" s="387" t="s">
         <v>274</v>
       </c>
       <c r="C108" s="315">
@@ -30834,7 +30722,7 @@
       <c r="A109" s="316" t="s">
         <v>204</v>
       </c>
-      <c r="B109" s="388" t="s">
+      <c r="B109" s="387" t="s">
         <v>276</v>
       </c>
       <c r="C109" s="315">
@@ -30950,7 +30838,7 @@
       <c r="G112" s="55" t="s">
         <v>285</v>
       </c>
-      <c r="H112" s="386" t="s">
+      <c r="H112" s="385" t="s">
         <v>283</v>
       </c>
       <c r="I112" s="156">
@@ -30981,7 +30869,7 @@
       <c r="G113" s="55" t="s">
         <v>287</v>
       </c>
-      <c r="H113" s="386" t="s">
+      <c r="H113" s="385" t="s">
         <v>283</v>
       </c>
       <c r="I113" s="156">
@@ -31012,7 +30900,7 @@
       <c r="G114" s="55" t="s">
         <v>289</v>
       </c>
-      <c r="H114" s="386" t="s">
+      <c r="H114" s="385" t="s">
         <v>283</v>
       </c>
       <c r="I114" s="156">
@@ -31043,7 +30931,7 @@
       <c r="G115" s="55" t="s">
         <v>291</v>
       </c>
-      <c r="H115" s="386" t="s">
+      <c r="H115" s="385" t="s">
         <v>283</v>
       </c>
       <c r="I115" s="156">
@@ -31074,7 +30962,7 @@
       <c r="G116" s="56" t="s">
         <v>294</v>
       </c>
-      <c r="H116" s="386" t="s">
+      <c r="H116" s="385" t="s">
         <v>295</v>
       </c>
       <c r="I116" s="156">
@@ -31105,7 +30993,7 @@
       <c r="G117" s="56" t="s">
         <v>297</v>
       </c>
-      <c r="H117" s="386" t="s">
+      <c r="H117" s="385" t="s">
         <v>295</v>
       </c>
       <c r="I117" s="156">
@@ -31167,7 +31055,7 @@
       <c r="G119" s="55" t="s">
         <v>302</v>
       </c>
-      <c r="H119" s="386" t="s">
+      <c r="H119" s="385" t="s">
         <v>207</v>
       </c>
       <c r="I119" s="156">
@@ -31241,7 +31129,7 @@
       <c r="A122" s="305" t="s">
         <v>303</v>
       </c>
-      <c r="B122" s="392" t="s">
+      <c r="B122" s="391" t="s">
         <v>309</v>
       </c>
       <c r="C122" s="321">
@@ -31260,7 +31148,7 @@
       <c r="G122" s="56" t="s">
         <v>310</v>
       </c>
-      <c r="H122" s="386" t="s">
+      <c r="H122" s="385" t="s">
         <v>311</v>
       </c>
       <c r="I122" s="156">
@@ -31272,7 +31160,7 @@
       <c r="A123" s="316" t="s">
         <v>303</v>
       </c>
-      <c r="B123" s="394" t="s">
+      <c r="B123" s="393" t="s">
         <v>312</v>
       </c>
       <c r="C123" s="359">
@@ -31291,7 +31179,7 @@
       <c r="G123" s="56" t="s">
         <v>313</v>
       </c>
-      <c r="H123" s="386" t="s">
+      <c r="H123" s="385" t="s">
         <v>314</v>
       </c>
       <c r="I123" s="156">
@@ -31303,7 +31191,7 @@
       <c r="A124" s="316" t="s">
         <v>303</v>
       </c>
-      <c r="B124" s="392" t="s">
+      <c r="B124" s="391" t="s">
         <v>315</v>
       </c>
       <c r="C124" s="321">
@@ -31322,7 +31210,7 @@
       <c r="G124" s="54" t="s">
         <v>316</v>
       </c>
-      <c r="H124" s="386" t="s">
+      <c r="H124" s="385" t="s">
         <v>317</v>
       </c>
       <c r="I124" s="156">
@@ -31384,7 +31272,7 @@
       <c r="G126" s="54" t="s">
         <v>322</v>
       </c>
-      <c r="H126" s="386" t="s">
+      <c r="H126" s="385" t="s">
         <v>323</v>
       </c>
       <c r="I126" s="156">
@@ -31415,7 +31303,7 @@
       <c r="G127" s="54" t="s">
         <v>324</v>
       </c>
-      <c r="H127" s="386" t="s">
+      <c r="H127" s="385" t="s">
         <v>323</v>
       </c>
       <c r="I127" s="156">
@@ -31446,7 +31334,7 @@
       <c r="G128" s="54" t="s">
         <v>326</v>
       </c>
-      <c r="H128" s="386" t="s">
+      <c r="H128" s="385" t="s">
         <v>317</v>
       </c>
       <c r="I128" s="156">
@@ -31458,7 +31346,7 @@
       <c r="A129" s="316" t="s">
         <v>327</v>
       </c>
-      <c r="B129" s="401" t="s">
+      <c r="B129" s="400" t="s">
         <v>328</v>
       </c>
       <c r="C129" s="360">
@@ -31477,7 +31365,7 @@
       <c r="G129" s="56" t="s">
         <v>329</v>
       </c>
-      <c r="H129" s="390" t="s">
+      <c r="H129" s="389" t="s">
         <v>330</v>
       </c>
       <c r="I129" s="156">
@@ -31508,7 +31396,7 @@
       <c r="G130" s="56" t="s">
         <v>332</v>
       </c>
-      <c r="H130" s="386" t="s">
+      <c r="H130" s="385" t="s">
         <v>333</v>
       </c>
       <c r="I130" s="156">
@@ -31539,7 +31427,7 @@
       <c r="G131" s="56" t="s">
         <v>335</v>
       </c>
-      <c r="H131" s="386" t="s">
+      <c r="H131" s="385" t="s">
         <v>336</v>
       </c>
       <c r="I131" s="156">
@@ -31570,7 +31458,7 @@
       <c r="G132" s="56" t="s">
         <v>338</v>
       </c>
-      <c r="H132" s="386" t="s">
+      <c r="H132" s="385" t="s">
         <v>336</v>
       </c>
       <c r="I132" s="156">
@@ -31601,7 +31489,7 @@
       <c r="G133" s="56" t="s">
         <v>340</v>
       </c>
-      <c r="H133" s="386" t="s">
+      <c r="H133" s="385" t="s">
         <v>336</v>
       </c>
       <c r="I133" s="156">
@@ -31632,7 +31520,7 @@
       <c r="G134" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="H134" s="386" t="s">
+      <c r="H134" s="385" t="s">
         <v>343</v>
       </c>
       <c r="I134" s="156">
@@ -31663,7 +31551,7 @@
       <c r="G135" s="56" t="s">
         <v>345</v>
       </c>
-      <c r="H135" s="386" t="s">
+      <c r="H135" s="385" t="s">
         <v>336</v>
       </c>
       <c r="I135" s="156">
@@ -31694,7 +31582,7 @@
       <c r="G136" s="56" t="s">
         <v>347</v>
       </c>
-      <c r="H136" s="386" t="s">
+      <c r="H136" s="385" t="s">
         <v>336</v>
       </c>
       <c r="I136" s="156">
@@ -31725,7 +31613,7 @@
       <c r="G137" s="56" t="s">
         <v>349</v>
       </c>
-      <c r="H137" s="386" t="s">
+      <c r="H137" s="385" t="s">
         <v>336</v>
       </c>
       <c r="I137" s="156">
@@ -31737,7 +31625,7 @@
       <c r="A138" s="316" t="s">
         <v>327</v>
       </c>
-      <c r="B138" s="388" t="s">
+      <c r="B138" s="387" t="s">
         <v>350</v>
       </c>
       <c r="C138" s="315">
@@ -31756,7 +31644,7 @@
       <c r="G138" s="56" t="s">
         <v>351</v>
       </c>
-      <c r="H138" s="390" t="s">
+      <c r="H138" s="389" t="s">
         <v>330</v>
       </c>
       <c r="I138" s="156">
@@ -31787,7 +31675,7 @@
       <c r="G139" s="56" t="s">
         <v>353</v>
       </c>
-      <c r="H139" s="386" t="s">
+      <c r="H139" s="385" t="s">
         <v>354</v>
       </c>
       <c r="I139" s="156">
@@ -31818,7 +31706,7 @@
       <c r="G140" s="57" t="s">
         <v>356</v>
       </c>
-      <c r="H140" s="386" t="s">
+      <c r="H140" s="385" t="s">
         <v>357</v>
       </c>
       <c r="I140" s="156">
@@ -31849,7 +31737,7 @@
       <c r="G141" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="H141" s="386" t="s">
+      <c r="H141" s="385" t="s">
         <v>360</v>
       </c>
       <c r="I141" s="156">
@@ -31880,7 +31768,7 @@
       <c r="G142" s="54" t="s">
         <v>362</v>
       </c>
-      <c r="H142" s="390" t="s">
+      <c r="H142" s="389" t="s">
         <v>330</v>
       </c>
       <c r="I142" s="156">
@@ -31898,7 +31786,7 @@
       <c r="C143" s="362">
         <v>1</v>
       </c>
-      <c r="D143" s="389">
+      <c r="D143" s="388">
         <v>1</v>
       </c>
       <c r="E143" s="340">
@@ -31921,13 +31809,13 @@
       <c r="A144" s="363" t="s">
         <v>365</v>
       </c>
-      <c r="B144" s="402" t="s">
+      <c r="B144" s="401" t="s">
         <v>366</v>
       </c>
-      <c r="C144" s="403">
+      <c r="C144" s="402">
         <v>2</v>
       </c>
-      <c r="D144" s="403">
+      <c r="D144" s="402">
         <v>1</v>
       </c>
       <c r="E144" s="308">
@@ -31940,13 +31828,13 @@
       <c r="G144" s="56" t="s">
         <v>367</v>
       </c>
-      <c r="H144" s="404" t="s">
+      <c r="H144" s="403" t="s">
         <v>368</v>
       </c>
-      <c r="I144" s="397">
+      <c r="I144" s="396">
         <v>10</v>
       </c>
-      <c r="J144" s="405"/>
+      <c r="J144" s="404"/>
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="305" t="s">
@@ -31983,7 +31871,7 @@
       <c r="A146" s="305" t="s">
         <v>365</v>
       </c>
-      <c r="B146" s="388" t="s">
+      <c r="B146" s="387" t="s">
         <v>371</v>
       </c>
       <c r="C146" s="307">
@@ -32002,7 +31890,7 @@
       <c r="G146" s="56" t="s">
         <v>372</v>
       </c>
-      <c r="H146" s="386" t="s">
+      <c r="H146" s="385" t="s">
         <v>373</v>
       </c>
       <c r="I146" s="156">
@@ -32014,7 +31902,7 @@
       <c r="A147" s="316" t="s">
         <v>365</v>
       </c>
-      <c r="B147" s="388" t="s">
+      <c r="B147" s="387" t="s">
         <v>374</v>
       </c>
       <c r="C147" s="307">
@@ -32033,7 +31921,7 @@
       <c r="G147" s="56" t="s">
         <v>375</v>
       </c>
-      <c r="H147" s="386" t="s">
+      <c r="H147" s="385" t="s">
         <v>373</v>
       </c>
       <c r="I147" s="156">
@@ -32045,7 +31933,7 @@
       <c r="A148" s="305" t="s">
         <v>365</v>
       </c>
-      <c r="B148" s="388" t="s">
+      <c r="B148" s="387" t="s">
         <v>376</v>
       </c>
       <c r="C148" s="307">
@@ -32064,7 +31952,7 @@
       <c r="G148" s="56" t="s">
         <v>377</v>
       </c>
-      <c r="H148" s="386" t="s">
+      <c r="H148" s="385" t="s">
         <v>373</v>
       </c>
       <c r="I148" s="156">
@@ -32076,7 +31964,7 @@
       <c r="A149" s="305" t="s">
         <v>365</v>
       </c>
-      <c r="B149" s="388" t="s">
+      <c r="B149" s="387" t="s">
         <v>378</v>
       </c>
       <c r="C149" s="307">
@@ -32095,7 +31983,7 @@
       <c r="G149" s="56" t="s">
         <v>379</v>
       </c>
-      <c r="H149" s="386" t="s">
+      <c r="H149" s="385" t="s">
         <v>373</v>
       </c>
       <c r="I149" s="156">
@@ -32126,7 +32014,7 @@
       <c r="G150" s="56" t="s">
         <v>381</v>
       </c>
-      <c r="H150" s="386" t="s">
+      <c r="H150" s="385" t="s">
         <v>382</v>
       </c>
       <c r="I150" s="156">
@@ -32169,7 +32057,7 @@
       <c r="A152" s="305" t="s">
         <v>387</v>
       </c>
-      <c r="B152" s="394" t="s">
+      <c r="B152" s="393" t="s">
         <v>388</v>
       </c>
       <c r="C152" s="317">
@@ -32188,7 +32076,7 @@
       <c r="G152" s="56" t="s">
         <v>389</v>
       </c>
-      <c r="H152" s="386" t="s">
+      <c r="H152" s="385" t="s">
         <v>390</v>
       </c>
       <c r="I152" s="157">
@@ -32200,7 +32088,7 @@
       <c r="A153" s="305" t="s">
         <v>387</v>
       </c>
-      <c r="B153" s="394" t="s">
+      <c r="B153" s="393" t="s">
         <v>391</v>
       </c>
       <c r="C153" s="306">
@@ -32219,7 +32107,7 @@
       <c r="G153" s="56" t="s">
         <v>392</v>
       </c>
-      <c r="H153" s="386" t="s">
+      <c r="H153" s="385" t="s">
         <v>393</v>
       </c>
       <c r="I153" s="156">
@@ -32281,7 +32169,7 @@
       <c r="G155" s="56" t="s">
         <v>398</v>
       </c>
-      <c r="H155" s="386" t="s">
+      <c r="H155" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I155" s="157">
@@ -32312,7 +32200,7 @@
       <c r="G156" s="56" t="s">
         <v>400</v>
       </c>
-      <c r="H156" s="386" t="s">
+      <c r="H156" s="385" t="s">
         <v>401</v>
       </c>
       <c r="I156" s="156">
@@ -32343,7 +32231,7 @@
       <c r="G157" s="65" t="s">
         <v>403</v>
       </c>
-      <c r="H157" s="386" t="s">
+      <c r="H157" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I157" s="157">
@@ -32374,7 +32262,7 @@
       <c r="G158" s="65" t="s">
         <v>405</v>
       </c>
-      <c r="H158" s="386" t="s">
+      <c r="H158" s="385" t="s">
         <v>47</v>
       </c>
       <c r="I158" s="157">
@@ -32722,48 +32610,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="436" t="s">
+      <c r="A1" s="435" t="s">
         <v>1701</v>
       </c>
-      <c r="B1" s="437" t="s">
+      <c r="B1" s="436" t="s">
         <v>895</v>
       </c>
-      <c r="C1" s="437" t="s">
+      <c r="C1" s="436" t="s">
         <v>1899</v>
       </c>
-      <c r="D1" s="437" t="s">
+      <c r="D1" s="436" t="s">
         <v>1900</v>
       </c>
-      <c r="E1" s="437" t="s">
+      <c r="E1" s="436" t="s">
         <v>1901</v>
       </c>
-      <c r="F1" s="438"/>
-      <c r="G1" s="438"/>
+      <c r="F1" s="437"/>
+      <c r="G1" s="437"/>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="436" t="s">
+      <c r="A2" s="435" t="s">
         <v>1706</v>
       </c>
-      <c r="B2" s="439">
-        <v>1</v>
-      </c>
-      <c r="C2" s="439">
-        <v>1</v>
-      </c>
-      <c r="D2" s="439">
-        <v>1</v>
-      </c>
-      <c r="E2" s="439">
-        <v>1</v>
-      </c>
-      <c r="F2" s="438"/>
-      <c r="G2" s="438"/>
+      <c r="B2" s="438">
+        <v>1</v>
+      </c>
+      <c r="C2" s="438">
+        <v>1</v>
+      </c>
+      <c r="D2" s="438">
+        <v>1</v>
+      </c>
+      <c r="E2" s="438">
+        <v>1</v>
+      </c>
+      <c r="F2" s="437"/>
+      <c r="G2" s="437"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="436" t="s">
+      <c r="A3" s="435" t="s">
         <v>1711</v>
       </c>
-      <c r="B3" s="439" t="s">
+      <c r="B3" s="438" t="s">
         <v>1712</v>
       </c>
       <c r="C3" s="73" t="s">
@@ -32772,309 +32660,309 @@
       <c r="D3" s="73" t="s">
         <v>1713</v>
       </c>
-      <c r="E3" s="439" t="s">
+      <c r="E3" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="F3" s="438"/>
-      <c r="G3" s="438"/>
+      <c r="F3" s="437"/>
+      <c r="G3" s="437"/>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="436" t="s">
+      <c r="A4" s="435" t="s">
         <v>1716</v>
       </c>
-      <c r="B4" s="439">
+      <c r="B4" s="438">
         <v>450</v>
       </c>
-      <c r="C4" s="439" t="s">
+      <c r="C4" s="438" t="s">
         <v>1903</v>
       </c>
-      <c r="D4" s="439">
+      <c r="D4" s="438">
         <v>285</v>
       </c>
-      <c r="E4" s="439">
+      <c r="E4" s="438">
         <v>285</v>
       </c>
-      <c r="F4" s="438"/>
-      <c r="G4" s="438"/>
+      <c r="F4" s="437"/>
+      <c r="G4" s="437"/>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="436" t="s">
+      <c r="A5" s="435" t="s">
         <v>1720</v>
       </c>
-      <c r="B5" s="439" t="s">
+      <c r="B5" s="438" t="s">
         <v>1721</v>
       </c>
-      <c r="C5" s="439">
+      <c r="C5" s="438">
         <v>150</v>
       </c>
-      <c r="D5" s="439" t="s">
+      <c r="D5" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E5" s="439">
+      <c r="E5" s="438">
         <v>157</v>
       </c>
-      <c r="F5" s="438"/>
-      <c r="G5" s="438"/>
+      <c r="F5" s="437"/>
+      <c r="G5" s="437"/>
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
-      <c r="A6" s="436" t="s">
+      <c r="A6" s="435" t="s">
         <v>1726</v>
       </c>
-      <c r="B6" s="439">
+      <c r="B6" s="438">
         <v>100</v>
       </c>
-      <c r="C6" s="439" t="s">
+      <c r="C6" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="D6" s="439" t="s">
+      <c r="D6" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E6" s="439" t="s">
+      <c r="E6" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="F6" s="438"/>
-      <c r="G6" s="438"/>
+      <c r="F6" s="437"/>
+      <c r="G6" s="437"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="436" t="s">
+      <c r="A7" s="435" t="s">
         <v>1729</v>
       </c>
-      <c r="B7" s="439" t="s">
+      <c r="B7" s="438" t="s">
         <v>1730</v>
       </c>
-      <c r="C7" s="439" t="s">
+      <c r="C7" s="438" t="s">
         <v>1904</v>
       </c>
-      <c r="D7" s="439" t="s">
+      <c r="D7" s="438" t="s">
         <v>1905</v>
       </c>
-      <c r="E7" s="439" t="s">
+      <c r="E7" s="438" t="s">
         <v>1906</v>
       </c>
-      <c r="F7" s="438"/>
-      <c r="G7" s="438"/>
+      <c r="F7" s="437"/>
+      <c r="G7" s="437"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="436" t="s">
+      <c r="A8" s="435" t="s">
         <v>1736</v>
       </c>
-      <c r="B8" s="439" t="s">
+      <c r="B8" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="C8" s="439" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="439" t="s">
+      <c r="C8" s="438" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="E8" s="439" t="s">
+      <c r="E8" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="F8" s="438"/>
-      <c r="G8" s="438"/>
+      <c r="F8" s="437"/>
+      <c r="G8" s="437"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="436" t="s">
+      <c r="A9" s="435" t="s">
         <v>1907</v>
       </c>
-      <c r="B9" s="439" t="s">
+      <c r="B9" s="438" t="s">
         <v>1908</v>
       </c>
-      <c r="C9" s="439" t="s">
+      <c r="C9" s="438" t="s">
         <v>1909</v>
       </c>
-      <c r="D9" s="439" t="s">
+      <c r="D9" s="438" t="s">
         <v>1910</v>
       </c>
-      <c r="E9" s="439" t="s">
+      <c r="E9" s="438" t="s">
         <v>1911</v>
       </c>
-      <c r="F9" s="438"/>
-      <c r="G9" s="438"/>
+      <c r="F9" s="437"/>
+      <c r="G9" s="437"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
-      <c r="A10" s="436" t="s">
+      <c r="A10" s="435" t="s">
         <v>1742</v>
       </c>
-      <c r="B10" s="441" t="s">
+      <c r="B10" s="440" t="s">
         <v>1743</v>
       </c>
-      <c r="C10" s="441" t="s">
+      <c r="C10" s="440" t="s">
         <v>1912</v>
       </c>
-      <c r="D10" s="441" t="s">
+      <c r="D10" s="440" t="s">
         <v>1913</v>
       </c>
-      <c r="E10" s="439" t="s">
+      <c r="E10" s="438" t="s">
         <v>1914</v>
       </c>
-      <c r="F10" s="438"/>
-      <c r="G10" s="438"/>
+      <c r="F10" s="437"/>
+      <c r="G10" s="437"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="436" t="s">
+      <c r="A11" s="435" t="s">
         <v>1748</v>
       </c>
-      <c r="B11" s="439" t="s">
+      <c r="B11" s="438" t="s">
         <v>1749</v>
       </c>
-      <c r="C11" s="439" t="s">
+      <c r="C11" s="438" t="s">
         <v>1915</v>
       </c>
-      <c r="D11" s="439" t="s">
+      <c r="D11" s="438" t="s">
         <v>1916</v>
       </c>
-      <c r="E11" s="439" t="s">
+      <c r="E11" s="438" t="s">
         <v>1917</v>
       </c>
-      <c r="F11" s="438"/>
-      <c r="G11" s="438"/>
+      <c r="F11" s="437"/>
+      <c r="G11" s="437"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="442" t="s">
+      <c r="A12" s="441" t="s">
         <v>1755</v>
       </c>
-      <c r="B12" s="441" t="s">
+      <c r="B12" s="440" t="s">
         <v>1756</v>
       </c>
       <c r="C12" s="75" t="s">
         <v>1918</v>
       </c>
-      <c r="D12" s="441" t="s">
+      <c r="D12" s="440" t="s">
         <v>1919</v>
       </c>
       <c r="E12" s="75" t="s">
         <v>1920</v>
       </c>
-      <c r="F12" s="438"/>
-      <c r="G12" s="438"/>
+      <c r="F12" s="437"/>
+      <c r="G12" s="437"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="436" t="s">
+      <c r="A13" s="435" t="s">
         <v>1761</v>
       </c>
-      <c r="B13" s="439" t="s">
+      <c r="B13" s="438" t="s">
         <v>1762</v>
       </c>
-      <c r="C13" s="439">
+      <c r="C13" s="438">
         <v>120</v>
       </c>
-      <c r="D13" s="439" t="s">
+      <c r="D13" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E13" s="439" t="s">
+      <c r="E13" s="438" t="s">
         <v>1921</v>
       </c>
-      <c r="F13" s="438"/>
-      <c r="G13" s="438"/>
+      <c r="F13" s="437"/>
+      <c r="G13" s="437"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="436" t="s">
+      <c r="A14" s="435" t="s">
         <v>1767</v>
       </c>
-      <c r="B14" s="439" t="s">
+      <c r="B14" s="438" t="s">
         <v>1768</v>
       </c>
-      <c r="C14" s="439" t="s">
+      <c r="C14" s="438" t="s">
         <v>1922</v>
       </c>
-      <c r="D14" s="439" t="s">
+      <c r="D14" s="438" t="s">
         <v>1923</v>
       </c>
-      <c r="E14" s="439" t="s">
+      <c r="E14" s="438" t="s">
         <v>1924</v>
       </c>
-      <c r="F14" s="438"/>
-      <c r="G14" s="438"/>
+      <c r="F14" s="437"/>
+      <c r="G14" s="437"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="76" t="s">
         <v>1773</v>
       </c>
-      <c r="B15" s="439" t="s">
+      <c r="B15" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="C15" s="439"/>
-      <c r="D15" s="439"/>
-      <c r="E15" s="439"/>
-      <c r="F15" s="438"/>
-      <c r="G15" s="438"/>
+      <c r="C15" s="438"/>
+      <c r="D15" s="438"/>
+      <c r="E15" s="438"/>
+      <c r="F15" s="437"/>
+      <c r="G15" s="437"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="436" t="s">
+      <c r="A16" s="435" t="s">
         <v>1777</v>
       </c>
-      <c r="B16" s="439" t="s">
+      <c r="B16" s="438" t="s">
         <v>1778</v>
       </c>
-      <c r="C16" s="439" t="s">
+      <c r="C16" s="438" t="s">
         <v>1925</v>
       </c>
-      <c r="D16" s="439" t="s">
+      <c r="D16" s="438" t="s">
         <v>1926</v>
       </c>
-      <c r="E16" s="439" t="s">
+      <c r="E16" s="438" t="s">
         <v>1926</v>
       </c>
-      <c r="F16" s="438"/>
-      <c r="G16" s="438"/>
+      <c r="F16" s="437"/>
+      <c r="G16" s="437"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1">
-      <c r="A17" s="436" t="s">
+      <c r="A17" s="435" t="s">
         <v>1783</v>
       </c>
-      <c r="B17" s="439" t="s">
+      <c r="B17" s="438" t="s">
         <v>1784</v>
       </c>
-      <c r="C17" s="439" t="s">
+      <c r="C17" s="438" t="s">
         <v>1927</v>
       </c>
-      <c r="D17" s="439" t="s">
+      <c r="D17" s="438" t="s">
         <v>1926</v>
       </c>
-      <c r="E17" s="439" t="s">
+      <c r="E17" s="438" t="s">
         <v>1926</v>
       </c>
-      <c r="F17" s="438"/>
-      <c r="G17" s="438"/>
+      <c r="F17" s="437"/>
+      <c r="G17" s="437"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="436" t="s">
+      <c r="A18" s="435" t="s">
         <v>1787</v>
       </c>
-      <c r="B18" s="439" t="s">
+      <c r="B18" s="438" t="s">
         <v>1788</v>
       </c>
-      <c r="C18" s="439" t="s">
+      <c r="C18" s="438" t="s">
         <v>1928</v>
       </c>
-      <c r="D18" s="439" t="s">
+      <c r="D18" s="438" t="s">
         <v>1929</v>
       </c>
-      <c r="E18" s="439" t="s">
+      <c r="E18" s="438" t="s">
         <v>1930</v>
       </c>
-      <c r="F18" s="438"/>
-      <c r="G18" s="438"/>
+      <c r="F18" s="437"/>
+      <c r="G18" s="437"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="436" t="s">
+      <c r="A19" s="435" t="s">
         <v>1792</v>
       </c>
-      <c r="B19" s="439" t="s">
+      <c r="B19" s="438" t="s">
         <v>1793</v>
       </c>
-      <c r="C19" s="439" t="s">
+      <c r="C19" s="438" t="s">
         <v>1794</v>
       </c>
-      <c r="D19" s="439" t="s">
+      <c r="D19" s="438" t="s">
         <v>1931</v>
       </c>
-      <c r="E19" s="439" t="s">
+      <c r="E19" s="438" t="s">
         <v>1932</v>
       </c>
-      <c r="F19" s="438"/>
-      <c r="G19" s="438"/>
+      <c r="F19" s="437"/>
+      <c r="G19" s="437"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="76" t="s">
@@ -33083,414 +32971,414 @@
       <c r="B20" s="72" t="s">
         <v>1798</v>
       </c>
-      <c r="C20" s="439"/>
-      <c r="D20" s="439"/>
-      <c r="E20" s="439"/>
-      <c r="F20" s="438"/>
-      <c r="G20" s="438"/>
+      <c r="C20" s="438"/>
+      <c r="D20" s="438"/>
+      <c r="E20" s="438"/>
+      <c r="F20" s="437"/>
+      <c r="G20" s="437"/>
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1">
-      <c r="A21" s="436" t="s">
+      <c r="A21" s="435" t="s">
         <v>1803</v>
       </c>
-      <c r="B21" s="439" t="s">
+      <c r="B21" s="438" t="s">
         <v>1752</v>
       </c>
-      <c r="C21" s="439" t="s">
+      <c r="C21" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="D21" s="439" t="s">
+      <c r="D21" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="E21" s="439"/>
-      <c r="F21" s="438"/>
-      <c r="G21" s="438"/>
+      <c r="E21" s="438"/>
+      <c r="F21" s="437"/>
+      <c r="G21" s="437"/>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="436" t="s">
+      <c r="A22" s="435" t="s">
         <v>1808</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>1809</v>
       </c>
-      <c r="C22" s="439" t="s">
+      <c r="C22" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="D22" s="439" t="s">
+      <c r="D22" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="E22" s="439" t="s">
+      <c r="E22" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="F22" s="438"/>
-      <c r="G22" s="438"/>
+      <c r="F22" s="437"/>
+      <c r="G22" s="437"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="436" t="s">
+      <c r="A23" s="435" t="s">
         <v>1814</v>
       </c>
-      <c r="B23" s="439" t="s">
+      <c r="B23" s="438" t="s">
         <v>1752</v>
       </c>
-      <c r="C23" s="439" t="s">
+      <c r="C23" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="D23" s="439" t="s">
+      <c r="D23" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="E23" s="439" t="s">
+      <c r="E23" s="438" t="s">
         <v>1933</v>
       </c>
-      <c r="F23" s="438"/>
-      <c r="G23" s="438"/>
+      <c r="F23" s="437"/>
+      <c r="G23" s="437"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="436" t="s">
+      <c r="A24" s="435" t="s">
         <v>1818</v>
       </c>
-      <c r="B24" s="439" t="s">
+      <c r="B24" s="438" t="s">
         <v>1752</v>
       </c>
-      <c r="C24" s="439" t="s">
+      <c r="C24" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="D24" s="439" t="s">
+      <c r="D24" s="438" t="s">
         <v>1737</v>
       </c>
-      <c r="E24" s="439"/>
-      <c r="F24" s="438"/>
-      <c r="G24" s="438"/>
+      <c r="E24" s="438"/>
+      <c r="F24" s="437"/>
+      <c r="G24" s="437"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="436" t="s">
+      <c r="A25" s="435" t="s">
         <v>1821</v>
       </c>
-      <c r="B25" s="439">
+      <c r="B25" s="438">
         <v>0.05</v>
       </c>
-      <c r="C25" s="439" t="s">
+      <c r="C25" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="D25" s="439" t="s">
+      <c r="D25" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E25" s="439"/>
-      <c r="F25" s="438"/>
-      <c r="G25" s="438"/>
+      <c r="E25" s="438"/>
+      <c r="F25" s="437"/>
+      <c r="G25" s="437"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="436" t="s">
+      <c r="A26" s="435" t="s">
         <v>1823</v>
       </c>
-      <c r="B26" s="439" t="s">
+      <c r="B26" s="438" t="s">
         <v>1824</v>
       </c>
-      <c r="C26" s="439" t="s">
+      <c r="C26" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="D26" s="439" t="s">
+      <c r="D26" s="438" t="s">
         <v>1934</v>
       </c>
-      <c r="E26" s="439"/>
-      <c r="F26" s="438"/>
-      <c r="G26" s="438"/>
+      <c r="E26" s="438"/>
+      <c r="F26" s="437"/>
+      <c r="G26" s="437"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="436" t="s">
+      <c r="A27" s="435" t="s">
         <v>1827</v>
       </c>
-      <c r="B27" s="439" t="s">
+      <c r="B27" s="438" t="s">
         <v>1828</v>
       </c>
-      <c r="C27" s="439" t="s">
+      <c r="C27" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="D27" s="439" t="s">
+      <c r="D27" s="438" t="s">
         <v>1935</v>
       </c>
-      <c r="E27" s="439"/>
-      <c r="F27" s="438"/>
-      <c r="G27" s="438"/>
+      <c r="E27" s="438"/>
+      <c r="F27" s="437"/>
+      <c r="G27" s="437"/>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="436" t="s">
+      <c r="A28" s="435" t="s">
         <v>1830</v>
       </c>
-      <c r="B28" s="439" t="s">
+      <c r="B28" s="438" t="s">
         <v>1831</v>
       </c>
-      <c r="C28" s="439" t="s">
+      <c r="C28" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="D28" s="439" t="s">
+      <c r="D28" s="438" t="s">
         <v>1936</v>
       </c>
-      <c r="E28" s="439"/>
-      <c r="F28" s="438"/>
-      <c r="G28" s="438"/>
+      <c r="E28" s="438"/>
+      <c r="F28" s="437"/>
+      <c r="G28" s="437"/>
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
-      <c r="A29" s="436" t="s">
+      <c r="A29" s="435" t="s">
         <v>1834</v>
       </c>
-      <c r="B29" s="439" t="s">
+      <c r="B29" s="438" t="s">
         <v>1835</v>
       </c>
-      <c r="C29" s="439" t="s">
+      <c r="C29" s="438" t="s">
         <v>1937</v>
       </c>
-      <c r="D29" s="439" t="s">
+      <c r="D29" s="438" t="s">
         <v>1938</v>
       </c>
-      <c r="E29" s="439"/>
-      <c r="F29" s="438"/>
-      <c r="G29" s="438"/>
+      <c r="E29" s="438"/>
+      <c r="F29" s="437"/>
+      <c r="G29" s="437"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="436" t="s">
+      <c r="A30" s="435" t="s">
         <v>1750</v>
       </c>
-      <c r="B30" s="439" t="s">
+      <c r="B30" s="438" t="s">
         <v>1840</v>
       </c>
-      <c r="C30" s="439" t="s">
+      <c r="C30" s="438" t="s">
         <v>1937</v>
       </c>
-      <c r="D30" s="439" t="s">
+      <c r="D30" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E30" s="439"/>
-      <c r="F30" s="438"/>
-      <c r="G30" s="438"/>
+      <c r="E30" s="438"/>
+      <c r="F30" s="437"/>
+      <c r="G30" s="437"/>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="436" t="s">
+      <c r="A31" s="435" t="s">
         <v>1845</v>
       </c>
-      <c r="B31" s="439" t="s">
+      <c r="B31" s="438" t="s">
         <v>1846</v>
       </c>
-      <c r="C31" s="439" t="s">
+      <c r="C31" s="438" t="s">
         <v>1937</v>
       </c>
-      <c r="D31" s="439" t="s">
+      <c r="D31" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E31" s="439"/>
-      <c r="F31" s="438"/>
-      <c r="G31" s="438"/>
+      <c r="E31" s="438"/>
+      <c r="F31" s="437"/>
+      <c r="G31" s="437"/>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="436" t="s">
+      <c r="A32" s="435" t="s">
         <v>1851</v>
       </c>
-      <c r="B32" s="439" t="s">
+      <c r="B32" s="438" t="s">
         <v>1226</v>
       </c>
-      <c r="C32" s="439" t="s">
+      <c r="C32" s="438" t="s">
         <v>1937</v>
       </c>
-      <c r="D32" s="439" t="s">
+      <c r="D32" s="438" t="s">
         <v>1902</v>
       </c>
-      <c r="E32" s="439"/>
-      <c r="F32" s="438"/>
-      <c r="G32" s="438"/>
+      <c r="E32" s="438"/>
+      <c r="F32" s="437"/>
+      <c r="G32" s="437"/>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="436" t="s">
+      <c r="A33" s="435" t="s">
         <v>1855</v>
       </c>
-      <c r="B33" s="439" t="s">
+      <c r="B33" s="438" t="s">
         <v>1856</v>
       </c>
-      <c r="C33" s="439" t="s">
+      <c r="C33" s="438" t="s">
         <v>1937</v>
       </c>
-      <c r="D33" s="439" t="s">
+      <c r="D33" s="438" t="s">
         <v>1939</v>
       </c>
-      <c r="E33" s="439"/>
-      <c r="F33" s="438"/>
-      <c r="G33" s="438"/>
+      <c r="E33" s="438"/>
+      <c r="F33" s="437"/>
+      <c r="G33" s="437"/>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="436" t="s">
+      <c r="A34" s="435" t="s">
         <v>1861</v>
       </c>
-      <c r="B34" s="439" t="s">
+      <c r="B34" s="438" t="s">
         <v>1862</v>
       </c>
-      <c r="C34" s="439">
+      <c r="C34" s="438">
         <v>1000</v>
       </c>
-      <c r="D34" s="439">
+      <c r="D34" s="438">
         <v>1200</v>
       </c>
-      <c r="E34" s="439">
+      <c r="E34" s="438">
         <v>1700</v>
       </c>
-      <c r="F34" s="438"/>
-      <c r="G34" s="438"/>
+      <c r="F34" s="437"/>
+      <c r="G34" s="437"/>
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
-      <c r="A35" s="436" t="s">
+      <c r="A35" s="435" t="s">
         <v>1865</v>
       </c>
-      <c r="B35" s="439">
+      <c r="B35" s="438">
         <v>1.75</v>
       </c>
-      <c r="C35" s="439">
+      <c r="C35" s="438">
         <v>1.75</v>
       </c>
-      <c r="D35" s="439">
+      <c r="D35" s="438">
         <v>1.75</v>
       </c>
-      <c r="E35" s="439">
+      <c r="E35" s="438">
         <v>1.75</v>
       </c>
-      <c r="F35" s="438"/>
-      <c r="G35" s="438"/>
+      <c r="F35" s="437"/>
+      <c r="G35" s="437"/>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="436"/>
-      <c r="B36" s="439"/>
-      <c r="C36" s="439"/>
-      <c r="D36" s="439"/>
-      <c r="E36" s="439"/>
-      <c r="F36" s="438"/>
-      <c r="G36" s="438"/>
+      <c r="A36" s="435"/>
+      <c r="B36" s="438"/>
+      <c r="C36" s="438"/>
+      <c r="D36" s="438"/>
+      <c r="E36" s="438"/>
+      <c r="F36" s="437"/>
+      <c r="G36" s="437"/>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="174" t="s">
         <v>411</v>
       </c>
-      <c r="B37" s="439"/>
-      <c r="C37" s="439"/>
-      <c r="D37" s="439"/>
-      <c r="E37" s="439"/>
-      <c r="F37" s="438"/>
-      <c r="G37" s="438"/>
+      <c r="B37" s="438"/>
+      <c r="C37" s="438"/>
+      <c r="D37" s="438"/>
+      <c r="E37" s="438"/>
+      <c r="F37" s="437"/>
+      <c r="G37" s="437"/>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="436"/>
-      <c r="B38" s="439"/>
-      <c r="C38" s="439"/>
-      <c r="D38" s="439"/>
-      <c r="E38" s="439"/>
-      <c r="F38" s="438"/>
-      <c r="G38" s="438"/>
+      <c r="A38" s="435"/>
+      <c r="B38" s="438"/>
+      <c r="C38" s="438"/>
+      <c r="D38" s="438"/>
+      <c r="E38" s="438"/>
+      <c r="F38" s="437"/>
+      <c r="G38" s="437"/>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="436"/>
-      <c r="B39" s="439"/>
-      <c r="C39" s="439"/>
-      <c r="D39" s="439"/>
-      <c r="E39" s="439"/>
-      <c r="F39" s="438"/>
-      <c r="G39" s="438"/>
+      <c r="A39" s="435"/>
+      <c r="B39" s="438"/>
+      <c r="C39" s="438"/>
+      <c r="D39" s="438"/>
+      <c r="E39" s="438"/>
+      <c r="F39" s="437"/>
+      <c r="G39" s="437"/>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="436"/>
-      <c r="B40" s="439"/>
-      <c r="C40" s="439"/>
-      <c r="D40" s="439"/>
-      <c r="E40" s="439"/>
-      <c r="F40" s="438"/>
-      <c r="G40" s="438"/>
+      <c r="A40" s="435"/>
+      <c r="B40" s="438"/>
+      <c r="C40" s="438"/>
+      <c r="D40" s="438"/>
+      <c r="E40" s="438"/>
+      <c r="F40" s="437"/>
+      <c r="G40" s="437"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="436"/>
-      <c r="B41" s="439"/>
-      <c r="C41" s="439"/>
-      <c r="D41" s="439"/>
-      <c r="E41" s="439"/>
-      <c r="F41" s="438"/>
-      <c r="G41" s="438"/>
+      <c r="A41" s="435"/>
+      <c r="B41" s="438"/>
+      <c r="C41" s="438"/>
+      <c r="D41" s="438"/>
+      <c r="E41" s="438"/>
+      <c r="F41" s="437"/>
+      <c r="G41" s="437"/>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="436"/>
-      <c r="B42" s="439"/>
-      <c r="C42" s="439"/>
-      <c r="D42" s="439"/>
-      <c r="E42" s="439"/>
-      <c r="F42" s="438"/>
-      <c r="G42" s="438"/>
+      <c r="A42" s="435"/>
+      <c r="B42" s="438"/>
+      <c r="C42" s="438"/>
+      <c r="D42" s="438"/>
+      <c r="E42" s="438"/>
+      <c r="F42" s="437"/>
+      <c r="G42" s="437"/>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" s="436"/>
-      <c r="B43" s="439"/>
-      <c r="C43" s="439"/>
-      <c r="D43" s="439"/>
-      <c r="E43" s="439"/>
-      <c r="F43" s="438"/>
-      <c r="G43" s="438"/>
+      <c r="A43" s="435"/>
+      <c r="B43" s="438"/>
+      <c r="C43" s="438"/>
+      <c r="D43" s="438"/>
+      <c r="E43" s="438"/>
+      <c r="F43" s="437"/>
+      <c r="G43" s="437"/>
     </row>
     <row r="44" spans="1:7">
-      <c r="A44" s="436"/>
-      <c r="B44" s="439"/>
-      <c r="C44" s="439"/>
-      <c r="D44" s="439"/>
-      <c r="E44" s="439"/>
-      <c r="F44" s="438"/>
-      <c r="G44" s="438"/>
+      <c r="A44" s="435"/>
+      <c r="B44" s="438"/>
+      <c r="C44" s="438"/>
+      <c r="D44" s="438"/>
+      <c r="E44" s="438"/>
+      <c r="F44" s="437"/>
+      <c r="G44" s="437"/>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="436"/>
-      <c r="B45" s="439"/>
-      <c r="C45" s="439"/>
-      <c r="D45" s="439"/>
-      <c r="E45" s="439"/>
-      <c r="F45" s="438"/>
-      <c r="G45" s="438"/>
+      <c r="A45" s="435"/>
+      <c r="B45" s="438"/>
+      <c r="C45" s="438"/>
+      <c r="D45" s="438"/>
+      <c r="E45" s="438"/>
+      <c r="F45" s="437"/>
+      <c r="G45" s="437"/>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="436"/>
-      <c r="B46" s="439"/>
-      <c r="C46" s="439"/>
-      <c r="D46" s="439"/>
-      <c r="E46" s="439"/>
-      <c r="F46" s="438"/>
-      <c r="G46" s="438"/>
+      <c r="A46" s="435"/>
+      <c r="B46" s="438"/>
+      <c r="C46" s="438"/>
+      <c r="D46" s="438"/>
+      <c r="E46" s="438"/>
+      <c r="F46" s="437"/>
+      <c r="G46" s="437"/>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="436"/>
-      <c r="B47" s="439"/>
-      <c r="C47" s="439"/>
-      <c r="D47" s="439"/>
-      <c r="E47" s="439"/>
-      <c r="F47" s="438"/>
-      <c r="G47" s="438"/>
+      <c r="A47" s="435"/>
+      <c r="B47" s="438"/>
+      <c r="C47" s="438"/>
+      <c r="D47" s="438"/>
+      <c r="E47" s="438"/>
+      <c r="F47" s="437"/>
+      <c r="G47" s="437"/>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="436"/>
-      <c r="B48" s="439"/>
-      <c r="C48" s="439"/>
-      <c r="D48" s="439"/>
-      <c r="E48" s="439"/>
-      <c r="F48" s="438"/>
-      <c r="G48" s="438"/>
+      <c r="A48" s="435"/>
+      <c r="B48" s="438"/>
+      <c r="C48" s="438"/>
+      <c r="D48" s="438"/>
+      <c r="E48" s="438"/>
+      <c r="F48" s="437"/>
+      <c r="G48" s="437"/>
     </row>
     <row r="49" spans="7:7">
-      <c r="G49" s="438"/>
+      <c r="G49" s="437"/>
     </row>
     <row r="50" spans="7:7">
-      <c r="G50" s="438"/>
+      <c r="G50" s="437"/>
     </row>
     <row r="51" spans="7:7">
-      <c r="G51" s="438"/>
+      <c r="G51" s="437"/>
     </row>
     <row r="52" spans="7:7">
-      <c r="G52" s="438"/>
+      <c r="G52" s="437"/>
     </row>
     <row r="53" spans="7:7">
-      <c r="G53" s="438"/>
+      <c r="G53" s="437"/>
     </row>
     <row r="54" spans="7:7">
-      <c r="G54" s="438"/>
+      <c r="G54" s="437"/>
     </row>
     <row r="55" spans="7:7">
-      <c r="G55" s="438"/>
+      <c r="G55" s="437"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -33940,13 +33828,13 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>414</v>
       </c>
-      <c r="E1" s="382" t="s">
+      <c r="E1" s="381" t="s">
         <v>415</v>
       </c>
       <c r="F1" s="20"/>
@@ -33961,7 +33849,7 @@
       <c r="C2" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="D2" s="406">
+      <c r="D2" s="405">
         <v>420</v>
       </c>
       <c r="E2" s="1">
@@ -33970,10 +33858,10 @@
       <c r="F2" s="24" t="s">
         <v>419</v>
       </c>
-      <c r="G2" s="407"/>
-      <c r="H2" s="407"/>
-      <c r="I2" s="407"/>
-      <c r="J2" s="407"/>
+      <c r="G2" s="406"/>
+      <c r="H2" s="406"/>
+      <c r="I2" s="406"/>
+      <c r="J2" s="406"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="167" t="s">
@@ -33985,19 +33873,19 @@
       <c r="C3" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="D3" s="406">
+      <c r="D3" s="405">
         <v>368</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="408" t="s">
+      <c r="F3" s="407" t="s">
         <v>422</v>
       </c>
-      <c r="G3" s="407"/>
-      <c r="H3" s="407"/>
-      <c r="I3" s="407"/>
-      <c r="J3" s="407"/>
+      <c r="G3" s="406"/>
+      <c r="H3" s="406"/>
+      <c r="I3" s="406"/>
+      <c r="J3" s="406"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="167" t="s">
@@ -34009,19 +33897,19 @@
       <c r="C4" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="D4" s="406">
+      <c r="D4" s="405">
         <v>172</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="408" t="s">
+      <c r="F4" s="407" t="s">
         <v>425</v>
       </c>
-      <c r="G4" s="407"/>
-      <c r="H4" s="407"/>
-      <c r="I4" s="407"/>
-      <c r="J4" s="407"/>
+      <c r="G4" s="406"/>
+      <c r="H4" s="406"/>
+      <c r="I4" s="406"/>
+      <c r="J4" s="406"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="167" t="s">
@@ -34033,17 +33921,17 @@
       <c r="C5" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="D5" s="406">
+      <c r="D5" s="405">
         <v>420</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="408"/>
-      <c r="G5" s="407"/>
-      <c r="H5" s="407"/>
-      <c r="I5" s="407"/>
-      <c r="J5" s="407"/>
+      <c r="F5" s="407"/>
+      <c r="G5" s="406"/>
+      <c r="H5" s="406"/>
+      <c r="I5" s="406"/>
+      <c r="J5" s="406"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="11"/>
@@ -34053,17 +33941,17 @@
       <c r="C6" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="D6" s="406">
+      <c r="D6" s="405">
         <v>480</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="25"/>
-      <c r="G6" s="407"/>
-      <c r="H6" s="407"/>
-      <c r="I6" s="407"/>
-      <c r="J6" s="407"/>
+      <c r="G6" s="406"/>
+      <c r="H6" s="406"/>
+      <c r="I6" s="406"/>
+      <c r="J6" s="406"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="11"/>
@@ -34073,17 +33961,17 @@
       <c r="C7" t="s">
         <v>430</v>
       </c>
-      <c r="D7" s="406">
+      <c r="D7" s="405">
         <v>750</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="25"/>
-      <c r="G7" s="407"/>
-      <c r="H7" s="407"/>
-      <c r="I7" s="407"/>
-      <c r="J7" s="407"/>
+      <c r="G7" s="406"/>
+      <c r="H7" s="406"/>
+      <c r="I7" s="406"/>
+      <c r="J7" s="406"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="11"/>
@@ -34093,15 +33981,15 @@
       <c r="C8" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D8" s="406"/>
+      <c r="D8" s="405"/>
       <c r="E8" s="1">
         <v>34</v>
       </c>
       <c r="F8" s="25"/>
-      <c r="G8" s="407"/>
-      <c r="H8" s="407"/>
-      <c r="I8" s="407"/>
-      <c r="J8" s="407"/>
+      <c r="G8" s="406"/>
+      <c r="H8" s="406"/>
+      <c r="I8" s="406"/>
+      <c r="J8" s="406"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="11"/>
@@ -34111,51 +33999,51 @@
       <c r="C9" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D9" s="406"/>
+      <c r="D9" s="405"/>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="25"/>
-      <c r="G9" s="407"/>
-      <c r="H9" s="407"/>
-      <c r="I9" s="407"/>
-      <c r="J9" s="407"/>
+      <c r="G9" s="406"/>
+      <c r="H9" s="406"/>
+      <c r="I9" s="406"/>
+      <c r="J9" s="406"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="11"/>
       <c r="B10" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C10" s="390" t="s">
+      <c r="C10" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="D10" s="406"/>
+      <c r="D10" s="405"/>
       <c r="E10" s="1">
         <v>81</v>
       </c>
       <c r="F10" s="25"/>
-      <c r="G10" s="407"/>
-      <c r="H10" s="407"/>
-      <c r="I10" s="407"/>
-      <c r="J10" s="407"/>
+      <c r="G10" s="406"/>
+      <c r="H10" s="406"/>
+      <c r="I10" s="406"/>
+      <c r="J10" s="406"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="11"/>
       <c r="B11" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C11" s="390" t="s">
+      <c r="C11" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="D11" s="406"/>
+      <c r="D11" s="405"/>
       <c r="E11" s="1">
         <v>8</v>
       </c>
       <c r="F11" s="151"/>
-      <c r="G11" s="407"/>
-      <c r="H11" s="407"/>
-      <c r="I11" s="407"/>
-      <c r="J11" s="407"/>
+      <c r="G11" s="406"/>
+      <c r="H11" s="406"/>
+      <c r="I11" s="406"/>
+      <c r="J11" s="406"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="167" t="s">
@@ -34164,72 +34052,72 @@
       <c r="B12" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C12" s="390" t="s">
+      <c r="C12" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="D12" s="406"/>
+      <c r="D12" s="405"/>
       <c r="E12" s="1">
         <v>78</v>
       </c>
       <c r="F12" s="152"/>
-      <c r="G12" s="407"/>
-      <c r="H12" s="407"/>
-      <c r="I12" s="407"/>
-      <c r="J12" s="407"/>
+      <c r="G12" s="406"/>
+      <c r="H12" s="406"/>
+      <c r="I12" s="406"/>
+      <c r="J12" s="406"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="11"/>
       <c r="B13" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C13" s="390" t="s">
+      <c r="C13" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="D13" s="406"/>
+      <c r="D13" s="405"/>
       <c r="E13" s="1">
         <v>81</v>
       </c>
       <c r="F13" s="153"/>
-      <c r="G13" s="407"/>
-      <c r="H13" s="407"/>
-      <c r="I13" s="407"/>
-      <c r="J13" s="407"/>
+      <c r="G13" s="406"/>
+      <c r="H13" s="406"/>
+      <c r="I13" s="406"/>
+      <c r="J13" s="406"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="11"/>
       <c r="B14" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="C14" s="390" t="s">
+      <c r="C14" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="D14" s="406"/>
+      <c r="D14" s="405"/>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="151"/>
-      <c r="G14" s="407"/>
-      <c r="H14" s="407"/>
-      <c r="I14" s="407"/>
-      <c r="J14" s="407"/>
+      <c r="G14" s="406"/>
+      <c r="H14" s="406"/>
+      <c r="I14" s="406"/>
+      <c r="J14" s="406"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="11"/>
       <c r="B15" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C15" s="390" t="s">
+      <c r="C15" s="389" t="s">
         <v>204</v>
       </c>
-      <c r="D15" s="406"/>
+      <c r="D15" s="405"/>
       <c r="E15" s="1">
         <v>42</v>
       </c>
       <c r="F15" s="153"/>
-      <c r="G15" s="407"/>
-      <c r="H15" s="407"/>
-      <c r="I15" s="407"/>
-      <c r="J15" s="407"/>
+      <c r="G15" s="406"/>
+      <c r="H15" s="406"/>
+      <c r="I15" s="406"/>
+      <c r="J15" s="406"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="154" t="s">
@@ -34241,15 +34129,15 @@
       <c r="C16" s="150" t="s">
         <v>441</v>
       </c>
-      <c r="D16" s="406"/>
+      <c r="D16" s="405"/>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="130"/>
-      <c r="G16" s="407"/>
-      <c r="H16" s="407"/>
-      <c r="I16" s="407"/>
-      <c r="J16" s="407"/>
+      <c r="G16" s="406"/>
+      <c r="H16" s="406"/>
+      <c r="I16" s="406"/>
+      <c r="J16" s="406"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="11"/>
@@ -34259,15 +34147,15 @@
       <c r="C17" s="33" t="s">
         <v>443</v>
       </c>
-      <c r="D17" s="406"/>
+      <c r="D17" s="405"/>
       <c r="E17" s="1">
         <v>4</v>
       </c>
       <c r="F17" s="151"/>
-      <c r="G17" s="407"/>
-      <c r="H17" s="407"/>
-      <c r="I17" s="407"/>
-      <c r="J17" s="407"/>
+      <c r="G17" s="406"/>
+      <c r="H17" s="406"/>
+      <c r="I17" s="406"/>
+      <c r="J17" s="406"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="11"/>
@@ -34277,15 +34165,15 @@
       <c r="C18" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="D18" s="406"/>
+      <c r="D18" s="405"/>
       <c r="E18" s="1">
         <v>4</v>
       </c>
       <c r="F18" s="151"/>
-      <c r="G18" s="407"/>
-      <c r="H18" s="407"/>
-      <c r="I18" s="407"/>
-      <c r="J18" s="407"/>
+      <c r="G18" s="406"/>
+      <c r="H18" s="406"/>
+      <c r="I18" s="406"/>
+      <c r="J18" s="406"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1">
       <c r="A19" s="27"/>
@@ -34295,33 +34183,33 @@
       <c r="C19" s="17" t="s">
         <v>441</v>
       </c>
-      <c r="D19" s="409"/>
+      <c r="D19" s="408"/>
       <c r="E19" s="17">
         <v>4</v>
       </c>
       <c r="F19" s="155"/>
-      <c r="G19" s="407"/>
-      <c r="H19" s="407"/>
-      <c r="I19" s="407"/>
-      <c r="J19" s="407"/>
+      <c r="G19" s="406"/>
+      <c r="H19" s="406"/>
+      <c r="I19" s="406"/>
+      <c r="J19" s="406"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="B20" s="407"/>
-      <c r="C20" s="407"/>
-      <c r="E20" s="407"/>
-      <c r="G20" s="407"/>
-      <c r="H20" s="407"/>
-      <c r="I20" s="407"/>
-      <c r="J20" s="407"/>
+      <c r="B20" s="406"/>
+      <c r="C20" s="406"/>
+      <c r="E20" s="406"/>
+      <c r="G20" s="406"/>
+      <c r="H20" s="406"/>
+      <c r="I20" s="406"/>
+      <c r="J20" s="406"/>
     </row>
     <row r="21" spans="1:10">
-      <c r="B21" s="407"/>
-      <c r="C21" s="407"/>
-      <c r="E21" s="407"/>
-      <c r="G21" s="407"/>
-      <c r="H21" s="407"/>
-      <c r="I21" s="407"/>
-      <c r="J21" s="407"/>
+      <c r="B21" s="406"/>
+      <c r="C21" s="406"/>
+      <c r="E21" s="406"/>
+      <c r="G21" s="406"/>
+      <c r="H21" s="406"/>
+      <c r="I21" s="406"/>
+      <c r="J21" s="406"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -34377,10 +34265,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -34389,7 +34277,7 @@
       <c r="A2" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="B2" s="390" t="s">
+      <c r="B2" s="389" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="12"/>
@@ -34410,7 +34298,7 @@
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="408" t="s">
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -34418,14 +34306,14 @@
       <c r="A4" s="167" t="s">
         <v>423</v>
       </c>
-      <c r="B4" s="390" t="s">
+      <c r="B4" s="389" t="s">
         <v>211</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="7">
         <v>36</v>
       </c>
-      <c r="E4" s="408" t="s">
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -34433,18 +34321,18 @@
       <c r="A5" s="167" t="s">
         <v>426</v>
       </c>
-      <c r="B5" s="390" t="s">
+      <c r="B5" s="389" t="s">
         <v>38</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="7">
         <v>24</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="390" t="s">
+      <c r="B6" s="389" t="s">
         <v>376</v>
       </c>
       <c r="C6" s="12"/>
@@ -34455,7 +34343,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="390" t="s">
+      <c r="B7" s="389" t="s">
         <v>378</v>
       </c>
       <c r="C7" s="12"/>
@@ -34511,7 +34399,7 @@
       <c r="A12" s="167" t="s">
         <v>436</v>
       </c>
-      <c r="B12" s="390" t="s">
+      <c r="B12" s="389" t="s">
         <v>451</v>
       </c>
       <c r="C12" s="12"/>
@@ -34587,7 +34475,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="11"/>
-      <c r="B19" s="390" t="s">
+      <c r="B19" s="389" t="s">
         <v>260</v>
       </c>
       <c r="C19" s="12"/>
@@ -34653,7 +34541,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="11"/>
-      <c r="B25" s="390" t="s">
+      <c r="B25" s="389" t="s">
         <v>455</v>
       </c>
       <c r="C25" s="129" t="s">
@@ -34666,7 +34554,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="11"/>
-      <c r="B26" s="390" t="s">
+      <c r="B26" s="389" t="s">
         <v>457</v>
       </c>
       <c r="C26" s="129" t="s">
@@ -34679,7 +34567,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="11"/>
-      <c r="B27" s="390" t="s">
+      <c r="B27" s="389" t="s">
         <v>459</v>
       </c>
       <c r="C27" s="12"/>
@@ -34706,189 +34594,189 @@
       <c r="B29" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C29" s="390" t="s">
+      <c r="C29" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D29" s="7">
         <v>2</v>
       </c>
       <c r="E29" s="25"/>
-      <c r="F29" s="390"/>
+      <c r="F29" s="389"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="11"/>
       <c r="B30" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="C30" s="390" t="s">
+      <c r="C30" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D30" s="7">
         <v>1</v>
       </c>
       <c r="E30" s="25"/>
-      <c r="F30" s="390"/>
+      <c r="F30" s="389"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="11"/>
       <c r="B31" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="C31" s="390" t="s">
+      <c r="C31" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D31" s="7">
         <v>1</v>
       </c>
       <c r="E31" s="25"/>
-      <c r="F31" s="390"/>
+      <c r="F31" s="389"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="11"/>
       <c r="B32" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C32" s="390" t="s">
+      <c r="C32" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D32" s="7">
         <v>1</v>
       </c>
       <c r="E32" s="25"/>
-      <c r="F32" s="390"/>
+      <c r="F32" s="389"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="11"/>
       <c r="B33" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C33" s="390" t="s">
+      <c r="C33" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D33" s="7">
         <v>1</v>
       </c>
       <c r="E33" s="25"/>
-      <c r="F33" s="390"/>
+      <c r="F33" s="389"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="11"/>
       <c r="B34" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C34" s="390" t="s">
+      <c r="C34" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D34" s="7">
         <v>1</v>
       </c>
       <c r="E34" s="25"/>
-      <c r="F34" s="390"/>
+      <c r="F34" s="389"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="11"/>
       <c r="B35" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C35" s="390" t="s">
+      <c r="C35" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D35" s="7">
         <v>1</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="390"/>
+      <c r="F35" s="389"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="11"/>
       <c r="B36" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C36" s="390" t="s">
+      <c r="C36" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D36" s="7">
         <v>2</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="390"/>
+      <c r="F36" s="389"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="11"/>
       <c r="B37" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C37" s="390" t="s">
+      <c r="C37" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D37" s="7">
         <v>4</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="390"/>
+      <c r="F37" s="389"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="11"/>
       <c r="B38" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C38" s="390" t="s">
+      <c r="C38" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D38" s="7">
         <v>1</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="390"/>
+      <c r="F38" s="389"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="11"/>
       <c r="B39" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C39" s="390" t="s">
+      <c r="C39" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D39" s="7">
         <v>1</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="390"/>
+      <c r="F39" s="389"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="11"/>
       <c r="B40" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="C40" s="390" t="s">
+      <c r="C40" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D40" s="7">
         <v>1</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="390"/>
+      <c r="F40" s="389"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="11"/>
       <c r="B41" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="C41" s="390" t="s">
+      <c r="C41" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D41" s="7">
         <v>1</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="390"/>
+      <c r="F41" s="389"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="11"/>
       <c r="B42" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="C42" s="390" t="s">
+      <c r="C42" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D42" s="7">
@@ -34901,7 +34789,7 @@
       <c r="B43" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="C43" s="390" t="s">
+      <c r="C43" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D43" s="7">
@@ -34914,7 +34802,7 @@
       <c r="B44" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="C44" s="390" t="s">
+      <c r="C44" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D44" s="7">
@@ -34927,7 +34815,7 @@
       <c r="B45" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="C45" s="390" t="s">
+      <c r="C45" s="389" t="s">
         <v>441</v>
       </c>
       <c r="D45" s="7">
@@ -35012,10 +34900,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -35027,8 +34915,8 @@
       <c r="B2" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="C2" s="402"/>
-      <c r="D2" s="397">
+      <c r="C2" s="401"/>
+      <c r="D2" s="396">
         <v>2</v>
       </c>
       <c r="E2" s="24" t="s">
@@ -35048,7 +34936,7 @@
       <c r="D3" s="140">
         <v>1</v>
       </c>
-      <c r="E3" s="408" t="s">
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -35065,7 +34953,7 @@
       <c r="D4" s="7">
         <v>12</v>
       </c>
-      <c r="E4" s="408" t="s">
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -35073,7 +34961,7 @@
       <c r="A5" s="169" t="s">
         <v>426</v>
       </c>
-      <c r="B5" s="390" t="s">
+      <c r="B5" s="389" t="s">
         <v>486</v>
       </c>
       <c r="C5" s="12" t="s">
@@ -35082,11 +34970,11 @@
       <c r="D5" s="7">
         <v>12</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="390" t="s">
+      <c r="B6" s="389" t="s">
         <v>371</v>
       </c>
       <c r="C6" s="12" t="s">
@@ -35099,7 +34987,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="390" t="s">
+      <c r="B7" s="389" t="s">
         <v>374</v>
       </c>
       <c r="C7" s="12" t="s">
@@ -35125,20 +35013,20 @@
       <c r="B9" s="18" t="s">
         <v>490</v>
       </c>
-      <c r="C9" s="390" t="s">
+      <c r="C9" s="389" t="s">
         <v>491</v>
       </c>
-      <c r="D9" s="389">
+      <c r="D9" s="388">
         <v>1</v>
       </c>
       <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11"/>
-      <c r="B10" s="387" t="s">
+      <c r="B10" s="386" t="s">
         <v>492</v>
       </c>
-      <c r="C10" s="390"/>
+      <c r="C10" s="389"/>
       <c r="D10" s="7">
         <v>1</v>
       </c>
@@ -35149,8 +35037,8 @@
       <c r="B11" s="18" t="s">
         <v>493</v>
       </c>
-      <c r="C11" s="390"/>
-      <c r="D11" s="389">
+      <c r="C11" s="389"/>
+      <c r="D11" s="388">
         <v>1</v>
       </c>
       <c r="E11" s="25"/>
@@ -35175,20 +35063,20 @@
       <c r="B13" s="6" t="s">
         <v>496</v>
       </c>
-      <c r="C13" s="390" t="s">
+      <c r="C13" s="389" t="s">
         <v>497</v>
       </c>
-      <c r="D13" s="389">
+      <c r="D13" s="388">
         <v>36</v>
       </c>
       <c r="E13" s="25"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="11"/>
-      <c r="B14" s="390" t="s">
+      <c r="B14" s="389" t="s">
         <v>498</v>
       </c>
-      <c r="C14" s="390"/>
+      <c r="C14" s="389"/>
       <c r="D14" s="7">
         <v>1</v>
       </c>
@@ -35206,22 +35094,22 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="11"/>
-      <c r="B16" s="390" t="s">
+      <c r="B16" s="389" t="s">
         <v>500</v>
       </c>
-      <c r="C16" s="390"/>
-      <c r="D16" s="389">
+      <c r="C16" s="389"/>
+      <c r="D16" s="388">
         <v>3</v>
       </c>
       <c r="E16" s="25"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="11"/>
-      <c r="B17" s="390" t="s">
+      <c r="B17" s="389" t="s">
         <v>284</v>
       </c>
-      <c r="C17" s="390"/>
-      <c r="D17" s="389">
+      <c r="C17" s="389"/>
+      <c r="D17" s="388">
         <v>6</v>
       </c>
       <c r="E17" s="25"/>
@@ -35251,10 +35139,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="11"/>
-      <c r="B20" s="390" t="s">
+      <c r="B20" s="389" t="s">
         <v>450</v>
       </c>
-      <c r="C20" s="390"/>
+      <c r="C20" s="389"/>
       <c r="D20" s="7">
         <v>42</v>
       </c>
@@ -35262,7 +35150,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="11"/>
-      <c r="B21" s="390" t="s">
+      <c r="B21" s="389" t="s">
         <v>503</v>
       </c>
       <c r="D21" s="7">
@@ -35272,7 +35160,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="11"/>
-      <c r="B22" s="390" t="s">
+      <c r="B22" s="389" t="s">
         <v>228</v>
       </c>
       <c r="D22" s="7">
@@ -35282,7 +35170,7 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="11"/>
-      <c r="B23" s="390" t="s">
+      <c r="B23" s="389" t="s">
         <v>230</v>
       </c>
       <c r="D23" s="7">
@@ -35302,7 +35190,7 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="11"/>
-      <c r="B25" s="390" t="s">
+      <c r="B25" s="389" t="s">
         <v>236</v>
       </c>
       <c r="D25" s="7">
@@ -35322,7 +35210,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11"/>
-      <c r="B27" s="390" t="s">
+      <c r="B27" s="389" t="s">
         <v>504</v>
       </c>
       <c r="D27" s="7">
@@ -35332,7 +35220,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="11"/>
-      <c r="B28" s="390" t="s">
+      <c r="B28" s="389" t="s">
         <v>505</v>
       </c>
       <c r="D28" s="7">
@@ -35342,7 +35230,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="11"/>
-      <c r="B29" s="390" t="s">
+      <c r="B29" s="389" t="s">
         <v>506</v>
       </c>
       <c r="D29" s="7"/>
@@ -35350,7 +35238,7 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="11"/>
-      <c r="B30" s="390" t="s">
+      <c r="B30" s="389" t="s">
         <v>507</v>
       </c>
       <c r="D30" s="7">
@@ -35373,15 +35261,15 @@
       <c r="B32" t="s">
         <v>508</v>
       </c>
-      <c r="C32" s="390"/>
-      <c r="D32" s="389">
+      <c r="C32" s="389"/>
+      <c r="D32" s="388">
         <v>1</v>
       </c>
       <c r="E32" s="25"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="11"/>
-      <c r="B33" s="390" t="s">
+      <c r="B33" s="389" t="s">
         <v>509</v>
       </c>
       <c r="D33" s="7">
@@ -35401,7 +35289,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="11"/>
-      <c r="B35" s="390" t="s">
+      <c r="B35" s="389" t="s">
         <v>510</v>
       </c>
       <c r="D35" s="7">
@@ -35411,10 +35299,10 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="11"/>
-      <c r="B36" s="390" t="s">
+      <c r="B36" s="389" t="s">
         <v>437</v>
       </c>
-      <c r="C36" s="390"/>
+      <c r="C36" s="389"/>
       <c r="D36" s="7">
         <v>6</v>
       </c>
@@ -35422,10 +35310,10 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="11"/>
-      <c r="B37" s="390" t="s">
+      <c r="B37" s="389" t="s">
         <v>268</v>
       </c>
-      <c r="C37" s="390"/>
+      <c r="C37" s="389"/>
       <c r="D37" s="7">
         <v>14</v>
       </c>
@@ -35463,7 +35351,7 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="11"/>
-      <c r="B41" s="390" t="s">
+      <c r="B41" s="389" t="s">
         <v>513</v>
       </c>
       <c r="D41" s="7">
@@ -35512,7 +35400,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="11"/>
-      <c r="B45" s="390" t="s">
+      <c r="B45" s="389" t="s">
         <v>518</v>
       </c>
       <c r="C45" s="2" t="s">
@@ -35525,7 +35413,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="11"/>
-      <c r="B46" s="390" t="s">
+      <c r="B46" s="389" t="s">
         <v>519</v>
       </c>
       <c r="C46" s="2" t="s">
@@ -35538,7 +35426,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="11"/>
-      <c r="B47" s="390" t="s">
+      <c r="B47" s="389" t="s">
         <v>520</v>
       </c>
       <c r="C47" s="2" t="s">
@@ -35551,7 +35439,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="11"/>
-      <c r="B48" s="390" t="s">
+      <c r="B48" s="389" t="s">
         <v>521</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -35564,7 +35452,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="11"/>
-      <c r="B49" s="390" t="s">
+      <c r="B49" s="389" t="s">
         <v>522</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -35577,7 +35465,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="11"/>
-      <c r="B50" s="390" t="s">
+      <c r="B50" s="389" t="s">
         <v>523</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -35590,7 +35478,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="11"/>
-      <c r="B51" s="390" t="s">
+      <c r="B51" s="389" t="s">
         <v>524</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -35603,7 +35491,7 @@
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="11"/>
-      <c r="B52" s="390" t="s">
+      <c r="B52" s="389" t="s">
         <v>525</v>
       </c>
       <c r="C52" s="2" t="s">
@@ -35616,7 +35504,7 @@
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="11"/>
-      <c r="B53" s="390" t="s">
+      <c r="B53" s="389" t="s">
         <v>526</v>
       </c>
       <c r="C53" s="2" t="s">
@@ -35629,7 +35517,7 @@
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="11"/>
-      <c r="B54" s="390" t="s">
+      <c r="B54" s="389" t="s">
         <v>527</v>
       </c>
       <c r="C54" s="2" t="s">
@@ -35655,7 +35543,7 @@
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="11"/>
-      <c r="B56" s="390" t="s">
+      <c r="B56" s="389" t="s">
         <v>529</v>
       </c>
       <c r="C56" s="2" t="s">
@@ -35668,7 +35556,7 @@
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="11"/>
-      <c r="B57" s="390" t="s">
+      <c r="B57" s="389" t="s">
         <v>530</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -35681,7 +35569,7 @@
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="11"/>
-      <c r="B58" s="390" t="s">
+      <c r="B58" s="389" t="s">
         <v>531</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -35694,7 +35582,7 @@
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1">
       <c r="A59" s="27"/>
-      <c r="B59" s="410" t="s">
+      <c r="B59" s="409" t="s">
         <v>532</v>
       </c>
       <c r="C59" s="22" t="s">
@@ -35755,10 +35643,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -35771,7 +35659,7 @@
         <v>483</v>
       </c>
       <c r="C2"/>
-      <c r="D2" s="389">
+      <c r="D2" s="388">
         <v>1</v>
       </c>
       <c r="E2" s="24" t="s">
@@ -35786,10 +35674,10 @@
         <v>447</v>
       </c>
       <c r="C3" s="50"/>
-      <c r="D3" s="389">
+      <c r="D3" s="388">
         <v>4</v>
       </c>
-      <c r="E3" s="408" t="s">
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -35801,10 +35689,10 @@
         <v>533</v>
       </c>
       <c r="C4" s="50"/>
-      <c r="D4" s="389">
-        <v>1</v>
-      </c>
-      <c r="E4" s="408" t="s">
+      <c r="D4" s="388">
+        <v>1</v>
+      </c>
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -35816,29 +35704,29 @@
         <v>534</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="389">
+      <c r="D5" s="388">
         <v>2</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="394" t="s">
+      <c r="B6" s="393" t="s">
         <v>391</v>
       </c>
-      <c r="C6" s="394"/>
-      <c r="D6" s="389">
+      <c r="C6" s="393"/>
+      <c r="D6" s="388">
         <v>1</v>
       </c>
       <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="394" t="s">
+      <c r="B7" s="393" t="s">
         <v>535</v>
       </c>
-      <c r="C7" s="394"/>
-      <c r="D7" s="389">
+      <c r="C7" s="393"/>
+      <c r="D7" s="388">
         <v>1</v>
       </c>
       <c r="E7" s="25"/>
@@ -35851,7 +35739,7 @@
       <c r="C8" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="D8" s="389">
+      <c r="D8" s="388">
         <v>1</v>
       </c>
       <c r="E8" s="25"/>
@@ -35864,7 +35752,7 @@
       <c r="C9" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D9" s="389">
+      <c r="D9" s="388">
         <v>1</v>
       </c>
       <c r="E9" s="25"/>
@@ -35877,7 +35765,7 @@
       <c r="C10" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D10" s="389">
+      <c r="D10" s="388">
         <v>1</v>
       </c>
       <c r="E10" s="25"/>
@@ -35887,8 +35775,8 @@
       <c r="B11" t="s">
         <v>542</v>
       </c>
-      <c r="C11" s="411"/>
-      <c r="D11" s="389">
+      <c r="C11" s="410"/>
+      <c r="D11" s="388">
         <v>8</v>
       </c>
       <c r="E11" s="25"/>
@@ -35901,7 +35789,7 @@
         <v>220</v>
       </c>
       <c r="C12"/>
-      <c r="D12" s="389">
+      <c r="D12" s="388">
         <v>18</v>
       </c>
       <c r="E12" s="25"/>
@@ -35912,7 +35800,7 @@
         <v>222</v>
       </c>
       <c r="C13"/>
-      <c r="D13" s="389">
+      <c r="D13" s="388">
         <v>7</v>
       </c>
       <c r="E13" s="25"/>
@@ -35923,7 +35811,7 @@
         <v>226</v>
       </c>
       <c r="C14"/>
-      <c r="D14" s="389">
+      <c r="D14" s="388">
         <v>6</v>
       </c>
       <c r="E14" s="25"/>
@@ -35934,7 +35822,7 @@
         <v>228</v>
       </c>
       <c r="C15"/>
-      <c r="D15" s="389">
+      <c r="D15" s="388">
         <v>5</v>
       </c>
       <c r="E15" s="25"/>
@@ -35945,7 +35833,7 @@
         <v>230</v>
       </c>
       <c r="C16"/>
-      <c r="D16" s="389">
+      <c r="D16" s="388">
         <v>4</v>
       </c>
       <c r="E16" s="25"/>
@@ -35956,7 +35844,7 @@
         <v>234</v>
       </c>
       <c r="C17"/>
-      <c r="D17" s="389">
+      <c r="D17" s="388">
         <v>10</v>
       </c>
       <c r="E17" s="25"/>
@@ -35967,7 +35855,7 @@
         <v>543</v>
       </c>
       <c r="C18"/>
-      <c r="D18" s="389">
+      <c r="D18" s="388">
         <v>1</v>
       </c>
       <c r="E18" s="25"/>
@@ -35978,7 +35866,7 @@
         <v>544</v>
       </c>
       <c r="C19"/>
-      <c r="D19" s="389">
+      <c r="D19" s="388">
         <v>1</v>
       </c>
       <c r="E19" s="25"/>
@@ -35989,7 +35877,7 @@
         <v>252</v>
       </c>
       <c r="C20"/>
-      <c r="D20" s="389">
+      <c r="D20" s="388">
         <v>1</v>
       </c>
       <c r="E20" s="25"/>
@@ -35999,19 +35887,19 @@
       <c r="B21" t="s">
         <v>545</v>
       </c>
-      <c r="C21" s="411"/>
-      <c r="D21" s="389">
+      <c r="C21" s="410"/>
+      <c r="D21" s="388">
         <v>1</v>
       </c>
       <c r="E21" s="25"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="11"/>
-      <c r="B22" s="390" t="s">
+      <c r="B22" s="389" t="s">
         <v>546</v>
       </c>
       <c r="C22"/>
-      <c r="D22" s="389">
+      <c r="D22" s="388">
         <v>1</v>
       </c>
       <c r="E22" s="25"/>
@@ -36021,8 +35909,8 @@
       <c r="B23" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="C23" s="411"/>
-      <c r="D23" s="389">
+      <c r="C23" s="410"/>
+      <c r="D23" s="388">
         <v>1</v>
       </c>
       <c r="E23" s="25"/>
@@ -36032,8 +35920,8 @@
       <c r="B24" t="s">
         <v>548</v>
       </c>
-      <c r="C24" s="411"/>
-      <c r="D24" s="389">
+      <c r="C24" s="410"/>
+      <c r="D24" s="388">
         <v>1</v>
       </c>
       <c r="E24" s="25"/>
@@ -36043,8 +35931,8 @@
       <c r="B25" t="s">
         <v>549</v>
       </c>
-      <c r="C25" s="411"/>
-      <c r="D25" s="389">
+      <c r="C25" s="410"/>
+      <c r="D25" s="388">
         <v>1</v>
       </c>
       <c r="E25" s="25"/>
@@ -36055,7 +35943,7 @@
         <v>550</v>
       </c>
       <c r="C26" s="135"/>
-      <c r="D26" s="389">
+      <c r="D26" s="388">
         <v>1</v>
       </c>
       <c r="E26" s="25"/>
@@ -36066,7 +35954,7 @@
         <v>551</v>
       </c>
       <c r="C27" s="32"/>
-      <c r="D27" s="389">
+      <c r="D27" s="388">
         <v>1</v>
       </c>
       <c r="E27" s="25"/>
@@ -36077,7 +35965,7 @@
         <v>552</v>
       </c>
       <c r="C28" s="32"/>
-      <c r="D28" s="389">
+      <c r="D28" s="388">
         <v>1</v>
       </c>
       <c r="E28" s="25"/>
@@ -36088,7 +35976,7 @@
         <v>553</v>
       </c>
       <c r="C29" s="32"/>
-      <c r="D29" s="389">
+      <c r="D29" s="388">
         <v>1</v>
       </c>
       <c r="E29" s="25"/>
@@ -36098,8 +35986,8 @@
       <c r="B30" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="C30" s="411"/>
-      <c r="D30" s="389">
+      <c r="C30" s="410"/>
+      <c r="D30" s="388">
         <v>1</v>
       </c>
       <c r="E30" s="25"/>
@@ -36110,7 +35998,7 @@
         <v>555</v>
       </c>
       <c r="C31" s="32"/>
-      <c r="D31" s="389">
+      <c r="D31" s="388">
         <v>1</v>
       </c>
       <c r="E31" s="25"/>
@@ -36121,7 +36009,7 @@
         <v>556</v>
       </c>
       <c r="C32" s="32"/>
-      <c r="D32" s="389">
+      <c r="D32" s="388">
         <v>1</v>
       </c>
       <c r="E32" s="25"/>
@@ -36132,27 +36020,27 @@
         <v>557</v>
       </c>
       <c r="C33" s="137"/>
-      <c r="D33" s="400">
+      <c r="D33" s="399">
         <v>1</v>
       </c>
       <c r="E33" s="29"/>
     </row>
     <row r="34" spans="1:5" ht="19.5" thickBot="1">
-      <c r="B34" s="380" t="s">
+      <c r="B34" s="442" t="s">
         <v>558</v>
       </c>
-      <c r="C34" s="380"/>
-      <c r="D34" s="380"/>
+      <c r="C34" s="442"/>
+      <c r="D34" s="442"/>
     </row>
     <row r="35" spans="1:5" ht="30">
       <c r="A35" s="136"/>
       <c r="B35" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C35" s="382" t="s">
+      <c r="C35" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D35" s="382" t="s">
+      <c r="D35" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E35" s="20"/>
@@ -36173,7 +36061,7 @@
       <c r="B37" t="s">
         <v>560</v>
       </c>
-      <c r="C37" s="402"/>
+      <c r="C37" s="401"/>
       <c r="D37" s="2">
         <v>2</v>
       </c>
@@ -36191,7 +36079,7 @@
       <c r="E38" s="25"/>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="412"/>
+      <c r="A39" s="411"/>
       <c r="B39" s="6" t="s">
         <v>562</v>
       </c>
@@ -36199,21 +36087,21 @@
       <c r="D39" s="7">
         <v>1</v>
       </c>
-      <c r="E39" s="413"/>
+      <c r="E39" s="412"/>
     </row>
     <row r="40" spans="1:5">
-      <c r="A40" s="412"/>
+      <c r="A40" s="411"/>
       <c r="B40" s="134" t="s">
         <v>563</v>
       </c>
-      <c r="C40" s="411"/>
+      <c r="C40" s="410"/>
       <c r="D40" s="7">
         <v>1</v>
       </c>
-      <c r="E40" s="413"/>
+      <c r="E40" s="412"/>
     </row>
     <row r="41" spans="1:5">
-      <c r="A41" s="412"/>
+      <c r="A41" s="411"/>
       <c r="B41" t="s">
         <v>564</v>
       </c>
@@ -36221,10 +36109,10 @@
       <c r="D41" s="7">
         <v>1</v>
       </c>
-      <c r="E41" s="413"/>
+      <c r="E41" s="412"/>
     </row>
     <row r="42" spans="1:5">
-      <c r="A42" s="412"/>
+      <c r="A42" s="411"/>
       <c r="B42" s="1" t="s">
         <v>565</v>
       </c>
@@ -36232,10 +36120,10 @@
       <c r="D42" s="7">
         <v>1</v>
       </c>
-      <c r="E42" s="413"/>
+      <c r="E42" s="412"/>
     </row>
     <row r="43" spans="1:5">
-      <c r="A43" s="412"/>
+      <c r="A43" s="411"/>
       <c r="B43" s="1" t="s">
         <v>406</v>
       </c>
@@ -36243,7 +36131,7 @@
       <c r="D43" s="7">
         <v>1</v>
       </c>
-      <c r="E43" s="413"/>
+      <c r="E43" s="412"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1">
       <c r="A44" s="27"/>
@@ -36312,10 +36200,10 @@
       <c r="B1" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -36327,10 +36215,10 @@
       <c r="B2" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="390" t="s">
+      <c r="C2" s="389" t="s">
         <v>568</v>
       </c>
-      <c r="D2" s="389">
+      <c r="D2" s="388">
         <v>1</v>
       </c>
       <c r="E2" s="24" t="s">
@@ -36344,13 +36232,13 @@
       <c r="B3" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="C3" s="390" t="s">
+      <c r="C3" s="389" t="s">
         <v>569</v>
       </c>
-      <c r="D3" s="389">
-        <v>1</v>
-      </c>
-      <c r="E3" s="408" t="s">
+      <c r="D3" s="388">
+        <v>1</v>
+      </c>
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -36361,13 +36249,13 @@
       <c r="B4" s="14" t="s">
         <v>567</v>
       </c>
-      <c r="C4" s="390" t="s">
+      <c r="C4" s="389" t="s">
         <v>570</v>
       </c>
-      <c r="D4" s="389">
-        <v>1</v>
-      </c>
-      <c r="E4" s="408" t="s">
+      <c r="D4" s="388">
+        <v>1</v>
+      </c>
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -36378,23 +36266,23 @@
       <c r="B5" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="C5" s="390" t="s">
+      <c r="C5" s="389" t="s">
         <v>572</v>
       </c>
-      <c r="D5" s="389">
+      <c r="D5" s="388">
         <v>2</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="414" t="s">
+      <c r="B6" s="413" t="s">
         <v>571</v>
       </c>
-      <c r="C6" s="390" t="s">
+      <c r="C6" s="389" t="s">
         <v>573</v>
       </c>
-      <c r="D6" s="389">
+      <c r="D6" s="388">
         <v>5</v>
       </c>
       <c r="E6" s="25"/>
@@ -36404,23 +36292,23 @@
       <c r="B7" s="13" t="s">
         <v>571</v>
       </c>
-      <c r="C7" s="390" t="s">
+      <c r="C7" s="389" t="s">
         <v>574</v>
       </c>
-      <c r="D7" s="389">
+      <c r="D7" s="388">
         <v>2</v>
       </c>
       <c r="E7" s="25"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="11"/>
-      <c r="B8" s="414" t="s">
+      <c r="B8" s="413" t="s">
         <v>571</v>
       </c>
-      <c r="C8" s="390" t="s">
+      <c r="C8" s="389" t="s">
         <v>575</v>
       </c>
-      <c r="D8" s="389">
+      <c r="D8" s="388">
         <v>2</v>
       </c>
       <c r="E8" s="25"/>
@@ -36430,10 +36318,10 @@
       <c r="B9" s="10" t="s">
         <v>576</v>
       </c>
-      <c r="C9" s="390" t="s">
+      <c r="C9" s="389" t="s">
         <v>572</v>
       </c>
-      <c r="D9" s="389">
+      <c r="D9" s="388">
         <v>2</v>
       </c>
       <c r="E9" s="25"/>
@@ -36443,10 +36331,10 @@
       <c r="B10" t="s">
         <v>576</v>
       </c>
-      <c r="C10" s="390" t="s">
+      <c r="C10" s="389" t="s">
         <v>573</v>
       </c>
-      <c r="D10" s="389">
+      <c r="D10" s="388">
         <v>2</v>
       </c>
       <c r="E10" s="25"/>
@@ -36456,10 +36344,10 @@
       <c r="B11" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="C11" s="390" t="s">
+      <c r="C11" s="389" t="s">
         <v>577</v>
       </c>
-      <c r="D11" s="389">
+      <c r="D11" s="388">
         <v>2</v>
       </c>
       <c r="E11" s="25"/>
@@ -36471,23 +36359,23 @@
       <c r="B12" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="390" t="s">
+      <c r="C12" s="389" t="s">
         <v>578</v>
       </c>
-      <c r="D12" s="389">
+      <c r="D12" s="388">
         <v>1</v>
       </c>
       <c r="E12" s="25"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="21"/>
-      <c r="B13" s="390" t="s">
+      <c r="B13" s="389" t="s">
         <v>102</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="D13" s="389">
+      <c r="D13" s="388">
         <v>1</v>
       </c>
       <c r="E13" s="25"/>
@@ -36497,10 +36385,10 @@
       <c r="B14" s="11" t="s">
         <v>580</v>
       </c>
-      <c r="C14" s="390" t="s">
+      <c r="C14" s="389" t="s">
         <v>577</v>
       </c>
-      <c r="D14" s="389">
+      <c r="D14" s="388">
         <v>1</v>
       </c>
       <c r="E14" s="25"/>
@@ -36510,10 +36398,10 @@
       <c r="B15" s="11" t="s">
         <v>581</v>
       </c>
-      <c r="C15" s="390" t="s">
+      <c r="C15" s="389" t="s">
         <v>577</v>
       </c>
-      <c r="D15" s="389">
+      <c r="D15" s="388">
         <v>1</v>
       </c>
       <c r="E15" s="25"/>
@@ -36523,10 +36411,10 @@
       <c r="B16" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="C16" s="390" t="s">
+      <c r="C16" s="389" t="s">
         <v>572</v>
       </c>
-      <c r="D16" s="389">
+      <c r="D16" s="388">
         <v>2</v>
       </c>
       <c r="E16" s="25"/>
@@ -36536,10 +36424,10 @@
       <c r="B17" s="13" t="s">
         <v>582</v>
       </c>
-      <c r="C17" s="390" t="s">
+      <c r="C17" s="389" t="s">
         <v>573</v>
       </c>
-      <c r="D17" s="389">
+      <c r="D17" s="388">
         <v>2</v>
       </c>
       <c r="E17" s="25"/>
@@ -36549,10 +36437,10 @@
       <c r="B18" s="11" t="s">
         <v>583</v>
       </c>
-      <c r="C18" s="390" t="s">
+      <c r="C18" s="389" t="s">
         <v>584</v>
       </c>
-      <c r="D18" s="389">
+      <c r="D18" s="388">
         <v>3</v>
       </c>
       <c r="E18" s="25"/>
@@ -36562,10 +36450,10 @@
       <c r="B19" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="C19" s="390" t="s">
+      <c r="C19" s="389" t="s">
         <v>584</v>
       </c>
-      <c r="D19" s="389">
+      <c r="D19" s="388">
         <v>3</v>
       </c>
       <c r="E19" s="25"/>
@@ -36575,23 +36463,23 @@
       <c r="B20" s="11" t="s">
         <v>586</v>
       </c>
-      <c r="C20" s="390" t="s">
+      <c r="C20" s="389" t="s">
         <v>584</v>
       </c>
-      <c r="D20" s="389">
+      <c r="D20" s="388">
         <v>3</v>
       </c>
       <c r="E20" s="25"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="11"/>
-      <c r="B21" s="412" t="s">
+      <c r="B21" s="411" t="s">
         <v>587</v>
       </c>
-      <c r="C21" s="390" t="s">
+      <c r="C21" s="389" t="s">
         <v>588</v>
       </c>
-      <c r="D21" s="389">
+      <c r="D21" s="388">
         <v>5</v>
       </c>
       <c r="E21" s="25"/>
@@ -36601,10 +36489,10 @@
       <c r="B22" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="C22" s="390" t="s">
+      <c r="C22" s="389" t="s">
         <v>574</v>
       </c>
-      <c r="D22" s="389">
+      <c r="D22" s="388">
         <v>2</v>
       </c>
       <c r="E22" s="25"/>
@@ -36614,10 +36502,10 @@
       <c r="B23" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="C23" s="390" t="s">
+      <c r="C23" s="389" t="s">
         <v>572</v>
       </c>
-      <c r="D23" s="389">
+      <c r="D23" s="388">
         <v>2</v>
       </c>
       <c r="E23" s="25"/>
@@ -36627,10 +36515,10 @@
       <c r="B24" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="C24" s="390" t="s">
+      <c r="C24" s="389" t="s">
         <v>573</v>
       </c>
-      <c r="D24" s="389">
+      <c r="D24" s="388">
         <v>5</v>
       </c>
       <c r="E24" s="25"/>
@@ -36640,73 +36528,73 @@
       <c r="B25" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="C25" s="390" t="s">
+      <c r="C25" s="389" t="s">
         <v>575</v>
       </c>
-      <c r="D25" s="389">
+      <c r="D25" s="388">
         <v>2</v>
       </c>
       <c r="E25" s="25"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="11"/>
-      <c r="B26" s="390" t="s">
+      <c r="B26" s="389" t="s">
         <v>590</v>
       </c>
-      <c r="C26" s="390" t="s">
+      <c r="C26" s="389" t="s">
         <v>591</v>
       </c>
-      <c r="D26" s="389">
+      <c r="D26" s="388">
         <v>5</v>
       </c>
       <c r="E26" s="25"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="11"/>
-      <c r="B27" s="390" t="s">
+      <c r="B27" s="389" t="s">
         <v>590</v>
       </c>
-      <c r="C27" s="390" t="s">
+      <c r="C27" s="389" t="s">
         <v>573</v>
       </c>
-      <c r="D27" s="389">
+      <c r="D27" s="388">
         <v>5</v>
       </c>
       <c r="E27" s="25"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="11"/>
-      <c r="B28" s="390" t="s">
+      <c r="B28" s="389" t="s">
         <v>592</v>
       </c>
-      <c r="C28" s="390" t="s">
+      <c r="C28" s="389" t="s">
         <v>593</v>
       </c>
-      <c r="D28" s="390">
+      <c r="D28" s="389">
         <v>1</v>
       </c>
       <c r="E28" s="25"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="11"/>
-      <c r="B29" s="390" t="s">
+      <c r="B29" s="389" t="s">
         <v>116</v>
       </c>
-      <c r="C29" s="390" t="s">
+      <c r="C29" s="389" t="s">
         <v>594</v>
       </c>
-      <c r="D29" s="390">
+      <c r="D29" s="389">
         <v>1</v>
       </c>
       <c r="E29" s="25"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="11"/>
-      <c r="B30" s="390" t="s">
+      <c r="B30" s="389" t="s">
         <v>595</v>
       </c>
-      <c r="C30" s="390"/>
-      <c r="D30" s="389">
+      <c r="C30" s="389"/>
+      <c r="D30" s="388">
         <v>1</v>
       </c>
       <c r="E30" s="25"/>
@@ -36742,8 +36630,8 @@
       <c r="B33" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="C33" s="390"/>
-      <c r="D33" s="389">
+      <c r="C33" s="389"/>
+      <c r="D33" s="388">
         <v>6</v>
       </c>
       <c r="E33" s="68"/>
@@ -36753,8 +36641,8 @@
       <c r="B34" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="C34" s="390"/>
-      <c r="D34" s="389">
+      <c r="C34" s="389"/>
+      <c r="D34" s="388">
         <v>2</v>
       </c>
       <c r="E34" s="25"/>
@@ -36764,8 +36652,8 @@
       <c r="B35" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="390"/>
-      <c r="D35" s="389">
+      <c r="C35" s="389"/>
+      <c r="D35" s="388">
         <v>1</v>
       </c>
       <c r="E35" s="25"/>
@@ -36826,7 +36714,7 @@
       <c r="C40" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="D40" s="390">
+      <c r="D40" s="389">
         <v>1</v>
       </c>
       <c r="E40" s="25"/>
@@ -36858,8 +36746,8 @@
       <c r="B43" t="s">
         <v>230</v>
       </c>
-      <c r="C43" s="390"/>
-      <c r="D43" s="389">
+      <c r="C43" s="389"/>
+      <c r="D43" s="388">
         <v>3</v>
       </c>
       <c r="E43" s="25"/>
@@ -36870,7 +36758,7 @@
         <v>604</v>
       </c>
       <c r="C44"/>
-      <c r="D44" s="389">
+      <c r="D44" s="388">
         <v>6</v>
       </c>
       <c r="E44" s="25"/>
@@ -36881,7 +36769,7 @@
         <v>544</v>
       </c>
       <c r="C45"/>
-      <c r="D45" s="389">
+      <c r="D45" s="388">
         <v>13</v>
       </c>
       <c r="E45" s="25"/>
@@ -36892,7 +36780,7 @@
         <v>246</v>
       </c>
       <c r="C46"/>
-      <c r="D46" s="389">
+      <c r="D46" s="388">
         <v>7</v>
       </c>
       <c r="E46" s="25"/>
@@ -36943,13 +36831,13 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="11"/>
-      <c r="B51" s="390" t="s">
+      <c r="B51" s="389" t="s">
         <v>605</v>
       </c>
-      <c r="C51" s="390" t="s">
+      <c r="C51" s="389" t="s">
         <v>606</v>
       </c>
-      <c r="D51" s="389">
+      <c r="D51" s="388">
         <v>1</v>
       </c>
       <c r="E51" s="25"/>
@@ -36959,23 +36847,23 @@
       <c r="B52" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C52" s="390" t="s">
+      <c r="C52" s="389" t="s">
         <v>606</v>
       </c>
-      <c r="D52" s="389">
+      <c r="D52" s="388">
         <v>1</v>
       </c>
       <c r="E52" s="25"/>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="11"/>
-      <c r="B53" s="390" t="s">
+      <c r="B53" s="389" t="s">
         <v>183</v>
       </c>
-      <c r="C53" s="390" t="s">
+      <c r="C53" s="389" t="s">
         <v>607</v>
       </c>
-      <c r="D53" s="389">
+      <c r="D53" s="388">
         <v>1</v>
       </c>
       <c r="E53" s="25"/>
@@ -36988,7 +36876,7 @@
       <c r="C54" s="12" t="s">
         <v>606</v>
       </c>
-      <c r="D54" s="389">
+      <c r="D54" s="388">
         <v>1</v>
       </c>
       <c r="E54" s="25"/>
@@ -36998,23 +36886,23 @@
       <c r="B55" s="50" t="s">
         <v>609</v>
       </c>
-      <c r="C55" s="390" t="s">
+      <c r="C55" s="389" t="s">
         <v>610</v>
       </c>
-      <c r="D55" s="390">
+      <c r="D55" s="389">
         <v>1</v>
       </c>
       <c r="E55" s="25"/>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="11"/>
-      <c r="B56" s="412" t="s">
+      <c r="B56" s="411" t="s">
         <v>191</v>
       </c>
-      <c r="C56" s="390" t="s">
+      <c r="C56" s="389" t="s">
         <v>611</v>
       </c>
-      <c r="D56" s="390">
+      <c r="D56" s="389">
         <v>1</v>
       </c>
       <c r="E56" s="25"/>
@@ -37027,7 +36915,7 @@
       <c r="C57" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="D57" s="389">
+      <c r="D57" s="388">
         <v>1</v>
       </c>
       <c r="E57" s="25"/>
@@ -37040,20 +36928,20 @@
       <c r="C58" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="D58" s="389">
+      <c r="D58" s="388">
         <v>1</v>
       </c>
       <c r="E58" s="25"/>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="11"/>
-      <c r="B59" s="390" t="s">
+      <c r="B59" s="389" t="s">
         <v>615</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="D59" s="389">
+      <c r="D59" s="388">
         <v>3</v>
       </c>
       <c r="E59" s="25"/>
@@ -37066,7 +36954,7 @@
       <c r="C60" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D60" s="389">
+      <c r="D60" s="388">
         <v>1</v>
       </c>
       <c r="E60" s="25"/>
@@ -37079,7 +36967,7 @@
       <c r="C61" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D61" s="389">
+      <c r="D61" s="388">
         <v>1</v>
       </c>
       <c r="E61" s="25"/>
@@ -37092,7 +36980,7 @@
       <c r="C62" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D62" s="389">
+      <c r="D62" s="388">
         <v>1</v>
       </c>
       <c r="E62" s="25"/>
@@ -37105,7 +36993,7 @@
       <c r="C63" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D63" s="389">
+      <c r="D63" s="388">
         <v>1</v>
       </c>
       <c r="E63" s="25"/>
@@ -37118,7 +37006,7 @@
       <c r="C64" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D64" s="389">
+      <c r="D64" s="388">
         <v>1</v>
       </c>
       <c r="E64" s="25"/>
@@ -37131,17 +37019,17 @@
       <c r="C65" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D65" s="389">
+      <c r="D65" s="388">
         <v>2</v>
       </c>
       <c r="E65" s="25"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="11"/>
-      <c r="B66" s="390" t="s">
+      <c r="B66" s="389" t="s">
         <v>623</v>
       </c>
-      <c r="C66" s="390" t="s">
+      <c r="C66" s="389" t="s">
         <v>624</v>
       </c>
       <c r="D66" s="7">
@@ -37157,7 +37045,7 @@
       <c r="C67" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="D67" s="389">
+      <c r="D67" s="388">
         <v>1</v>
       </c>
       <c r="E67" s="25"/>
@@ -37176,7 +37064,7 @@
       <c r="E68" s="29"/>
     </row>
     <row r="72" spans="1:5">
-      <c r="A72" s="390"/>
+      <c r="A72" s="389"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -37226,10 +37114,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="20"/>
@@ -37241,8 +37129,8 @@
       <c r="B2" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="C2" s="390"/>
-      <c r="D2" s="390">
+      <c r="C2" s="389"/>
+      <c r="D2" s="389">
         <v>6</v>
       </c>
       <c r="E2" s="24" t="s">
@@ -37253,13 +37141,13 @@
       <c r="A3" s="167" t="s">
         <v>420</v>
       </c>
-      <c r="B3" s="392" t="s">
+      <c r="B3" s="391" t="s">
         <v>309</v>
       </c>
-      <c r="D3" s="390">
-        <v>1</v>
-      </c>
-      <c r="E3" s="408" t="s">
+      <c r="D3" s="389">
+        <v>1</v>
+      </c>
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -37267,14 +37155,14 @@
       <c r="A4" s="167" t="s">
         <v>423</v>
       </c>
-      <c r="B4" s="390" t="s">
+      <c r="B4" s="389" t="s">
         <v>628</v>
       </c>
-      <c r="C4" s="390"/>
-      <c r="D4" s="390">
-        <v>1</v>
-      </c>
-      <c r="E4" s="408" t="s">
+      <c r="C4" s="389"/>
+      <c r="D4" s="389">
+        <v>1</v>
+      </c>
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -37282,32 +37170,32 @@
       <c r="A5" s="167" t="s">
         <v>426</v>
       </c>
-      <c r="B5" s="392" t="s">
+      <c r="B5" s="391" t="s">
         <v>315</v>
       </c>
-      <c r="C5" s="390"/>
-      <c r="D5" s="390">
-        <v>1</v>
-      </c>
-      <c r="E5" s="408"/>
+      <c r="C5" s="389"/>
+      <c r="D5" s="389">
+        <v>1</v>
+      </c>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
-      <c r="B6" s="392" t="s">
+      <c r="B6" s="391" t="s">
         <v>629</v>
       </c>
-      <c r="D6" s="390">
+      <c r="D6" s="389">
         <v>1</v>
       </c>
       <c r="E6" s="25"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="11"/>
-      <c r="B7" s="390" t="s">
+      <c r="B7" s="389" t="s">
         <v>630</v>
       </c>
-      <c r="C7" s="390"/>
-      <c r="D7" s="390">
+      <c r="C7" s="389"/>
+      <c r="D7" s="389">
         <v>5</v>
       </c>
       <c r="E7" s="25"/>
@@ -37317,7 +37205,7 @@
       <c r="B8" t="s">
         <v>435</v>
       </c>
-      <c r="D8" s="390">
+      <c r="D8" s="389">
         <v>2</v>
       </c>
       <c r="E8" s="25"/>
@@ -37327,17 +37215,17 @@
       <c r="B9" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D9" s="390">
+      <c r="D9" s="389">
         <v>2</v>
       </c>
       <c r="E9" s="25"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="11"/>
-      <c r="B10" s="387" t="s">
+      <c r="B10" s="386" t="s">
         <v>631</v>
       </c>
-      <c r="D10" s="390">
+      <c r="D10" s="389">
         <v>1</v>
       </c>
       <c r="E10" s="25"/>
@@ -37346,11 +37234,11 @@
       <c r="A11" s="171" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="410" t="s">
+      <c r="B11" s="409" t="s">
         <v>632</v>
       </c>
       <c r="C11" s="22"/>
-      <c r="D11" s="410">
+      <c r="D11" s="409">
         <v>1</v>
       </c>
       <c r="E11" s="29"/>
@@ -37406,10 +37294,10 @@
       <c r="B1" s="31" t="s">
         <v>412</v>
       </c>
-      <c r="C1" s="382" t="s">
+      <c r="C1" s="381" t="s">
         <v>413</v>
       </c>
-      <c r="D1" s="382" t="s">
+      <c r="D1" s="381" t="s">
         <v>446</v>
       </c>
       <c r="E1" s="148"/>
@@ -37421,7 +37309,7 @@
       <c r="B2" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="C2" s="390"/>
+      <c r="C2" s="389"/>
       <c r="D2">
         <v>1</v>
       </c>
@@ -37436,11 +37324,11 @@
       <c r="B3" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C3" s="390"/>
+      <c r="C3" s="389"/>
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="408" t="s">
+      <c r="E3" s="407" t="s">
         <v>422</v>
       </c>
     </row>
@@ -37451,11 +37339,11 @@
       <c r="B4" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="C4" s="390"/>
+      <c r="C4" s="389"/>
       <c r="D4">
         <v>4</v>
       </c>
-      <c r="E4" s="408" t="s">
+      <c r="E4" s="407" t="s">
         <v>425</v>
       </c>
     </row>
@@ -37466,18 +37354,18 @@
       <c r="B5" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C5" s="390"/>
+      <c r="C5" s="389"/>
       <c r="D5">
         <v>8</v>
       </c>
-      <c r="E5" s="408"/>
+      <c r="E5" s="407"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="11"/>
       <c r="B6" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C6" s="390"/>
+      <c r="C6" s="389"/>
       <c r="D6">
         <v>4</v>
       </c>
@@ -37488,7 +37376,7 @@
       <c r="B7" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C7" s="390"/>
+      <c r="C7" s="389"/>
       <c r="D7">
         <v>4</v>
       </c>
@@ -37499,7 +37387,7 @@
       <c r="B8" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="C8" s="390"/>
+      <c r="C8" s="389"/>
       <c r="D8">
         <v>1</v>
       </c>
@@ -37510,7 +37398,7 @@
       <c r="B9" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C9" s="390" t="s">
+      <c r="C9" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D9">
@@ -37523,7 +37411,7 @@
       <c r="B10" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C10" s="390" t="s">
+      <c r="C10" s="389" t="s">
         <v>636</v>
       </c>
       <c r="D10">
@@ -37534,7 +37422,7 @@
     <row r="11" spans="1:5">
       <c r="A11" s="11"/>
       <c r="B11" s="1"/>
-      <c r="C11" s="390"/>
+      <c r="C11" s="389"/>
       <c r="D11"/>
       <c r="E11" s="25"/>
     </row>
@@ -37543,7 +37431,7 @@
         <v>436</v>
       </c>
       <c r="B12" s="1"/>
-      <c r="C12" s="390"/>
+      <c r="C12" s="389"/>
       <c r="D12"/>
       <c r="E12" s="29"/>
     </row>

--- a/BOM/Valkyrie V2 Build Guide.xlsx
+++ b/BOM/Valkyrie V2 Build Guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12366" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B6C6212-4565-40F2-AA0F-C6BA973B6F63}"/>
+  <xr:revisionPtr revIDLastSave="12367" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB0E9A9F-48A4-4432-8E4B-319FAD3CA03B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="14" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="52" r:id="rId1"/>
@@ -2872,9 +2872,6 @@
     <t>cancel.g</t>
   </si>
   <si>
-    <t>Cancel print and reset</t>
-  </si>
-  <si>
     <t>config.g</t>
   </si>
   <si>
@@ -5414,6 +5411,9 @@
   </si>
   <si>
     <t>Records last filament loaded in the extruder</t>
+  </si>
+  <si>
+    <t>;cancel.g runs when canceling a job midprint</t>
   </si>
 </sst>
 </file>
@@ -17252,1103 +17252,1103 @@
         <v>21</v>
       </c>
       <c r="B1" s="194" t="s">
+        <v>976</v>
+      </c>
+      <c r="C1" s="194" t="s">
         <v>977</v>
       </c>
-      <c r="C1" s="194" t="s">
+      <c r="D1" s="194" t="s">
         <v>978</v>
       </c>
-      <c r="D1" s="194" t="s">
+      <c r="E1" s="193" t="s">
         <v>979</v>
       </c>
-      <c r="E1" s="193" t="s">
+      <c r="F1" s="195" t="s">
         <v>980</v>
       </c>
-      <c r="F1" s="195" t="s">
+      <c r="G1" s="196" t="s">
         <v>981</v>
       </c>
-      <c r="G1" s="196" t="s">
+      <c r="H1" s="195" t="s">
         <v>982</v>
       </c>
-      <c r="H1" s="195" t="s">
+      <c r="I1" s="197" t="s">
         <v>983</v>
       </c>
-      <c r="I1" s="197" t="s">
+      <c r="J1" s="194" t="s">
         <v>984</v>
       </c>
-      <c r="J1" s="194" t="s">
-        <v>985</v>
-      </c>
       <c r="K1" s="194" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="218" t="s">
+        <v>985</v>
+      </c>
+      <c r="B2" s="376" t="s">
         <v>986</v>
       </c>
-      <c r="B2" s="376" t="s">
+      <c r="C2" s="220" t="s">
         <v>987</v>
       </c>
-      <c r="C2" s="220" t="s">
+      <c r="D2" s="377" t="s">
         <v>988</v>
       </c>
-      <c r="D2" s="377" t="s">
+      <c r="E2" s="221" t="s">
         <v>989</v>
-      </c>
-      <c r="E2" s="221" t="s">
-        <v>990</v>
       </c>
       <c r="F2" s="222">
         <v>14</v>
       </c>
       <c r="G2" s="221" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2" s="222">
         <v>500</v>
       </c>
       <c r="I2" s="377" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="J2" s="223"/>
       <c r="K2" s="418" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="226" t="s">
+        <v>985</v>
+      </c>
+      <c r="B3" s="378" t="s">
         <v>986</v>
       </c>
-      <c r="B3" s="378" t="s">
-        <v>987</v>
-      </c>
       <c r="C3" s="379" t="s">
+        <v>992</v>
+      </c>
+      <c r="D3" s="380" t="s">
+        <v>988</v>
+      </c>
+      <c r="E3" s="229" t="s">
         <v>993</v>
-      </c>
-      <c r="D3" s="380" t="s">
-        <v>989</v>
-      </c>
-      <c r="E3" s="229" t="s">
-        <v>994</v>
       </c>
       <c r="F3" s="230">
         <v>14</v>
       </c>
       <c r="G3" s="229" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H3" s="230">
         <v>500</v>
       </c>
       <c r="I3" s="380" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="J3" s="231"/>
       <c r="K3" s="418" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="381" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B4" s="382" t="s">
+        <v>996</v>
+      </c>
+      <c r="C4" s="220" t="s">
+        <v>992</v>
+      </c>
+      <c r="D4" s="382" t="s">
         <v>997</v>
       </c>
-      <c r="C4" s="220" t="s">
-        <v>993</v>
-      </c>
-      <c r="D4" s="382" t="s">
+      <c r="E4" s="221" t="s">
         <v>998</v>
-      </c>
-      <c r="E4" s="221" t="s">
-        <v>999</v>
       </c>
       <c r="F4" s="222">
         <v>14</v>
       </c>
       <c r="G4" s="221" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H4" s="222">
         <v>750</v>
       </c>
       <c r="I4" s="221" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="J4" s="223"/>
       <c r="K4" s="418" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="383" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B5" s="384" t="s">
+        <v>996</v>
+      </c>
+      <c r="C5" s="228" t="s">
+        <v>987</v>
+      </c>
+      <c r="D5" s="384" t="s">
         <v>997</v>
       </c>
-      <c r="C5" s="228" t="s">
-        <v>988</v>
-      </c>
-      <c r="D5" s="384" t="s">
-        <v>998</v>
-      </c>
       <c r="E5" s="229" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F5" s="230">
         <v>14</v>
       </c>
       <c r="G5" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H5" s="230">
         <v>750</v>
       </c>
       <c r="I5" s="229" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="J5" s="231"/>
       <c r="K5" s="418" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="381" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B6" s="219" t="s">
         <v>1002</v>
       </c>
-      <c r="B6" s="219" t="s">
+      <c r="C6" s="220" t="s">
+        <v>992</v>
+      </c>
+      <c r="D6" s="377" t="s">
         <v>1003</v>
       </c>
-      <c r="C6" s="220" t="s">
-        <v>993</v>
-      </c>
-      <c r="D6" s="377" t="s">
-        <v>1004</v>
-      </c>
       <c r="E6" s="221" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F6" s="222">
         <v>18</v>
       </c>
       <c r="G6" s="221" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H6" s="385" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I6" s="386" t="s">
         <v>1005</v>
-      </c>
-      <c r="I6" s="386" t="s">
-        <v>1006</v>
       </c>
       <c r="J6" s="387"/>
       <c r="K6" s="418" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="388" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B7" s="81" t="s">
         <v>1002</v>
       </c>
-      <c r="B7" s="81" t="s">
+      <c r="C7" s="389" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D7" s="386" t="s">
         <v>1003</v>
       </c>
-      <c r="C7" s="389" t="s">
+      <c r="E7" s="390" t="s">
         <v>1007</v>
-      </c>
-      <c r="D7" s="386" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E7" s="390" t="s">
-        <v>1008</v>
       </c>
       <c r="F7" s="86">
         <v>18</v>
       </c>
       <c r="G7" s="82" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H7" s="391" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="I7" s="386" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="J7" s="392"/>
       <c r="K7" s="418" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="388" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B8" s="390" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C8" s="192" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D8" s="386" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E8" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F8" s="86">
         <v>14</v>
       </c>
       <c r="G8" s="82" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H8" s="86">
         <v>750</v>
       </c>
       <c r="I8" s="386" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="J8" s="225"/>
       <c r="K8" s="418" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="383" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B9" s="384" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="C9" s="379" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D9" s="380" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E9" s="384" t="s">
         <v>1007</v>
-      </c>
-      <c r="D9" s="380" t="s">
-        <v>1004</v>
-      </c>
-      <c r="E9" s="384" t="s">
-        <v>1008</v>
       </c>
       <c r="F9" s="230">
         <v>14</v>
       </c>
       <c r="G9" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H9" s="230">
         <v>750</v>
       </c>
       <c r="I9" s="380" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="J9" s="231"/>
       <c r="K9" s="418" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="218" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B10" s="219" t="s">
         <v>1013</v>
       </c>
-      <c r="B10" s="219" t="s">
+      <c r="C10" s="220" t="s">
         <v>1014</v>
       </c>
-      <c r="C10" s="220" t="s">
+      <c r="D10" s="221" t="s">
         <v>1015</v>
       </c>
-      <c r="D10" s="221" t="s">
+      <c r="E10" s="221" t="s">
         <v>1016</v>
       </c>
-      <c r="E10" s="221" t="s">
+      <c r="F10" s="385" t="s">
         <v>1017</v>
       </c>
-      <c r="F10" s="385" t="s">
+      <c r="G10" s="221" t="s">
         <v>1018</v>
-      </c>
-      <c r="G10" s="221" t="s">
-        <v>1019</v>
       </c>
       <c r="H10" s="222">
         <v>300</v>
       </c>
       <c r="I10" s="221" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J10" s="223"/>
       <c r="K10" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="224" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B11" s="81" t="s">
         <v>1013</v>
       </c>
-      <c r="B11" s="81" t="s">
-        <v>1014</v>
-      </c>
       <c r="C11" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D11" s="82" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E11" s="82" t="s">
         <v>1021</v>
       </c>
-      <c r="D11" s="82" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E11" s="82" t="s">
+      <c r="F11" s="391" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G11" s="82" t="s">
         <v>1022</v>
-      </c>
-      <c r="F11" s="391" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G11" s="82" t="s">
-        <v>1023</v>
       </c>
       <c r="H11" s="86">
         <v>300</v>
       </c>
       <c r="I11" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J11" s="225"/>
       <c r="K11" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="224" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B12" s="81" t="s">
         <v>1013</v>
       </c>
-      <c r="B12" s="81" t="s">
-        <v>1014</v>
-      </c>
       <c r="C12" s="192" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E12" s="82" t="s">
         <v>1024</v>
       </c>
-      <c r="D12" s="82" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E12" s="82" t="s">
+      <c r="F12" s="391" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G12" s="82" t="s">
         <v>1025</v>
-      </c>
-      <c r="F12" s="391" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G12" s="82" t="s">
-        <v>1026</v>
       </c>
       <c r="H12" s="86">
         <v>300</v>
       </c>
       <c r="I12" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J12" s="225"/>
       <c r="K12" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="226" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B13" s="227" t="s">
         <v>1013</v>
       </c>
-      <c r="B13" s="227" t="s">
-        <v>1014</v>
-      </c>
       <c r="C13" s="228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D13" s="229" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E13" s="229" t="s">
         <v>1027</v>
       </c>
-      <c r="D13" s="229" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E13" s="229" t="s">
+      <c r="F13" s="393" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G13" s="229" t="s">
         <v>1028</v>
-      </c>
-      <c r="F13" s="393" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G13" s="229" t="s">
-        <v>1029</v>
       </c>
       <c r="H13" s="230">
         <v>300</v>
       </c>
       <c r="I13" s="229" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J13" s="231"/>
       <c r="K13" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="218" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B14" s="219" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C14" s="220" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D14" s="221" t="s">
         <v>1030</v>
       </c>
-      <c r="C14" s="220" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D14" s="221" t="s">
-        <v>1031</v>
-      </c>
       <c r="E14" s="221" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F14" s="385" t="s">
         <v>1017</v>
       </c>
-      <c r="F14" s="385" t="s">
+      <c r="G14" s="221" t="s">
         <v>1018</v>
-      </c>
-      <c r="G14" s="221" t="s">
-        <v>1019</v>
       </c>
       <c r="H14" s="222">
         <v>300</v>
       </c>
       <c r="I14" s="221" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J14" s="223"/>
       <c r="K14" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B15" s="81" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C15" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D15" s="82" t="s">
         <v>1030</v>
       </c>
-      <c r="C15" s="192" t="s">
+      <c r="E15" s="82" t="s">
         <v>1021</v>
       </c>
-      <c r="D15" s="82" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E15" s="82" t="s">
+      <c r="F15" s="391" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G15" s="82" t="s">
         <v>1022</v>
-      </c>
-      <c r="F15" s="391" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G15" s="82" t="s">
-        <v>1023</v>
       </c>
       <c r="H15" s="86">
         <v>300</v>
       </c>
       <c r="I15" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J15" s="225"/>
       <c r="K15" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B16" s="81" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C16" s="192" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D16" s="82" t="s">
         <v>1030</v>
       </c>
-      <c r="C16" s="192" t="s">
+      <c r="E16" s="82" t="s">
         <v>1024</v>
       </c>
-      <c r="D16" s="82" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E16" s="82" t="s">
+      <c r="F16" s="391" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G16" s="82" t="s">
         <v>1025</v>
-      </c>
-      <c r="F16" s="391" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G16" s="82" t="s">
-        <v>1026</v>
       </c>
       <c r="H16" s="86">
         <v>300</v>
       </c>
       <c r="I16" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J16" s="225"/>
       <c r="K16" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="226" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B17" s="227" t="s">
+        <v>1029</v>
+      </c>
+      <c r="C17" s="228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D17" s="229" t="s">
         <v>1030</v>
       </c>
-      <c r="C17" s="228" t="s">
+      <c r="E17" s="229" t="s">
         <v>1027</v>
       </c>
-      <c r="D17" s="229" t="s">
-        <v>1031</v>
-      </c>
-      <c r="E17" s="229" t="s">
+      <c r="F17" s="393" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G17" s="229" t="s">
         <v>1028</v>
-      </c>
-      <c r="F17" s="393" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G17" s="229" t="s">
-        <v>1029</v>
       </c>
       <c r="H17" s="230">
         <v>300</v>
       </c>
       <c r="I17" s="229" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J17" s="231"/>
       <c r="K17" s="412" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="218" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B18" s="219" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C18" s="220" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D18" s="221" t="s">
         <v>1032</v>
       </c>
-      <c r="C18" s="220" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D18" s="221" t="s">
-        <v>1033</v>
-      </c>
       <c r="E18" s="221" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="F18" s="222">
         <v>18</v>
       </c>
       <c r="G18" s="221" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H18" s="222">
         <v>600</v>
       </c>
       <c r="I18" s="221" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="J18" s="223"/>
       <c r="K18" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B19" s="81" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C19" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D19" s="82" t="s">
         <v>1032</v>
       </c>
-      <c r="C19" s="192" t="s">
+      <c r="E19" s="82" t="s">
         <v>1021</v>
-      </c>
-      <c r="D19" s="82" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E19" s="82" t="s">
-        <v>1022</v>
       </c>
       <c r="F19" s="86">
         <v>18</v>
       </c>
       <c r="G19" s="82" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H19" s="86">
         <v>600</v>
       </c>
       <c r="I19" s="82" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="J19" s="225"/>
       <c r="K19" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B20" s="81" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C20" s="192" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D20" s="82" t="s">
         <v>1032</v>
       </c>
-      <c r="C20" s="192" t="s">
+      <c r="E20" s="82" t="s">
         <v>1024</v>
-      </c>
-      <c r="D20" s="82" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E20" s="82" t="s">
-        <v>1025</v>
       </c>
       <c r="F20" s="86">
         <v>18</v>
       </c>
       <c r="G20" s="82" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H20" s="86">
         <v>600</v>
       </c>
       <c r="I20" s="82" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="J20" s="225"/>
       <c r="K20" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="226" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B21" s="227" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C21" s="228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D21" s="229" t="s">
         <v>1032</v>
       </c>
-      <c r="C21" s="228" t="s">
+      <c r="E21" s="229" t="s">
         <v>1027</v>
-      </c>
-      <c r="D21" s="229" t="s">
-        <v>1033</v>
-      </c>
-      <c r="E21" s="229" t="s">
-        <v>1028</v>
       </c>
       <c r="F21" s="230">
         <v>18</v>
       </c>
       <c r="G21" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H21" s="230">
         <v>600</v>
       </c>
       <c r="I21" s="229" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="J21" s="231"/>
       <c r="K21" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="218" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B22" s="219" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C22" s="220" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D22" s="221" t="s">
         <v>1040</v>
       </c>
-      <c r="C22" s="220" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D22" s="221" t="s">
+      <c r="E22" s="221" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F22" s="385" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G22" s="221" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H22" s="385" t="s">
         <v>1041</v>
       </c>
-      <c r="E22" s="221" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F22" s="385" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G22" s="221" t="s">
-        <v>1035</v>
-      </c>
-      <c r="H22" s="385" t="s">
-        <v>1042</v>
-      </c>
       <c r="I22" s="221" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J22" s="223"/>
       <c r="K22" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B23" s="81" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C23" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D23" s="82" t="s">
         <v>1040</v>
       </c>
-      <c r="C23" s="192" t="s">
+      <c r="E23" s="82" t="s">
         <v>1021</v>
       </c>
-      <c r="D23" s="82" t="s">
+      <c r="F23" s="391" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G23" s="82" t="s">
+        <v>994</v>
+      </c>
+      <c r="H23" s="391" t="s">
         <v>1041</v>
       </c>
-      <c r="E23" s="82" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F23" s="391" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G23" s="82" t="s">
-        <v>995</v>
-      </c>
-      <c r="H23" s="391" t="s">
-        <v>1042</v>
-      </c>
       <c r="I23" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J23" s="225"/>
       <c r="K23" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B24" s="81" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C24" s="192" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D24" s="82" t="s">
         <v>1040</v>
       </c>
-      <c r="C24" s="192" t="s">
+      <c r="E24" s="82" t="s">
         <v>1024</v>
       </c>
-      <c r="D24" s="82" t="s">
+      <c r="F24" s="391" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G24" s="82" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H24" s="391" t="s">
         <v>1041</v>
       </c>
-      <c r="E24" s="82" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F24" s="391" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G24" s="82" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H24" s="391" t="s">
-        <v>1042</v>
-      </c>
       <c r="I24" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J24" s="225"/>
       <c r="K24" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="226" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B25" s="227" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C25" s="228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D25" s="229" t="s">
         <v>1040</v>
       </c>
-      <c r="C25" s="228" t="s">
+      <c r="E25" s="229" t="s">
         <v>1027</v>
       </c>
-      <c r="D25" s="229" t="s">
+      <c r="F25" s="393" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G25" s="229" t="s">
+        <v>990</v>
+      </c>
+      <c r="H25" s="393" t="s">
         <v>1041</v>
       </c>
-      <c r="E25" s="229" t="s">
-        <v>1028</v>
-      </c>
-      <c r="F25" s="393" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G25" s="229" t="s">
-        <v>991</v>
-      </c>
-      <c r="H25" s="393" t="s">
-        <v>1042</v>
-      </c>
       <c r="I25" s="229" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J25" s="231"/>
       <c r="K25" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="218" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B26" s="219" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C26" s="220" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D26" s="221" t="s">
         <v>1043</v>
       </c>
-      <c r="C26" s="220" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D26" s="221" t="s">
-        <v>1044</v>
-      </c>
       <c r="E26" s="221" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F26" s="385" t="s">
         <v>1017</v>
       </c>
-      <c r="F26" s="385" t="s">
-        <v>1018</v>
-      </c>
       <c r="G26" s="221" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H26" s="385" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I26" s="221" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J26" s="223"/>
       <c r="K26" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B27" s="81" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C27" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D27" s="82" t="s">
         <v>1043</v>
       </c>
-      <c r="C27" s="192" t="s">
+      <c r="E27" s="82" t="s">
         <v>1021</v>
       </c>
-      <c r="D27" s="82" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E27" s="82" t="s">
-        <v>1022</v>
-      </c>
       <c r="F27" s="391" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G27" s="82" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H27" s="391" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I27" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J27" s="225"/>
       <c r="K27" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B28" s="81" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C28" s="192" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D28" s="82" t="s">
         <v>1043</v>
       </c>
-      <c r="C28" s="192" t="s">
+      <c r="E28" s="82" t="s">
         <v>1024</v>
       </c>
-      <c r="D28" s="82" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E28" s="82" t="s">
-        <v>1025</v>
-      </c>
       <c r="F28" s="391" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G28" s="82" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H28" s="391" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I28" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J28" s="225"/>
       <c r="K28" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="226" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B29" s="227" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C29" s="228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D29" s="229" t="s">
         <v>1043</v>
       </c>
-      <c r="C29" s="228" t="s">
+      <c r="E29" s="229" t="s">
         <v>1027</v>
       </c>
-      <c r="D29" s="229" t="s">
-        <v>1044</v>
-      </c>
-      <c r="E29" s="229" t="s">
-        <v>1028</v>
-      </c>
       <c r="F29" s="393" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G29" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H29" s="393" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I29" s="229" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J29" s="231"/>
       <c r="K29" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="218" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B30" s="219" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C30" s="220" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D30" s="221" t="s">
         <v>1045</v>
       </c>
-      <c r="C30" s="220" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D30" s="221" t="s">
-        <v>1046</v>
-      </c>
       <c r="E30" s="221" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F30" s="385" t="s">
         <v>1017</v>
       </c>
-      <c r="F30" s="385" t="s">
-        <v>1018</v>
-      </c>
       <c r="G30" s="221" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H30" s="385" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I30" s="221" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J30" s="223"/>
       <c r="K30" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B31" s="81" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C31" s="192" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D31" s="82" t="s">
         <v>1045</v>
       </c>
-      <c r="C31" s="192" t="s">
+      <c r="E31" s="82" t="s">
         <v>1021</v>
       </c>
-      <c r="D31" s="82" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E31" s="82" t="s">
-        <v>1022</v>
-      </c>
       <c r="F31" s="391" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G31" s="82" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H31" s="391" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I31" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J31" s="225"/>
       <c r="K31" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="224" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B32" s="81" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C32" s="192" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D32" s="82" t="s">
         <v>1045</v>
       </c>
-      <c r="C32" s="192" t="s">
+      <c r="E32" s="82" t="s">
         <v>1024</v>
       </c>
-      <c r="D32" s="82" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E32" s="82" t="s">
-        <v>1025</v>
-      </c>
       <c r="F32" s="391" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G32" s="82" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H32" s="391" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I32" s="82" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J32" s="225"/>
       <c r="K32" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="226" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B33" s="227" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C33" s="228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D33" s="229" t="s">
         <v>1045</v>
       </c>
-      <c r="C33" s="228" t="s">
+      <c r="E33" s="229" t="s">
         <v>1027</v>
       </c>
-      <c r="D33" s="229" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E33" s="229" t="s">
-        <v>1028</v>
-      </c>
       <c r="F33" s="393" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G33" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H33" s="393" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I33" s="229" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="J33" s="231"/>
       <c r="K33" s="412" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="381" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B34" s="219"/>
       <c r="C34" s="220"/>
       <c r="D34" s="377" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E34" s="221" t="s">
         <v>1048</v>
-      </c>
-      <c r="E34" s="221" t="s">
-        <v>1049</v>
       </c>
       <c r="F34" s="222"/>
       <c r="G34" s="221"/>
@@ -18359,14 +18359,14 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C35" s="192"/>
       <c r="D35" s="386" t="s">
+        <v>1049</v>
+      </c>
+      <c r="E35" s="386" t="s">
         <v>1050</v>
-      </c>
-      <c r="E35" s="386" t="s">
-        <v>1051</v>
       </c>
       <c r="F35" s="86"/>
       <c r="H35" s="86"/>
@@ -18376,14 +18376,14 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C36" s="192"/>
       <c r="D36" s="386" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="E36" s="386" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F36" s="86"/>
       <c r="H36" s="86"/>
@@ -18393,14 +18393,14 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="390" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C37" s="192"/>
       <c r="D37" s="386" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E37" s="386" t="s">
         <v>1053</v>
-      </c>
-      <c r="E37" s="386" t="s">
-        <v>1054</v>
       </c>
       <c r="F37" s="86"/>
       <c r="H37" s="86"/>
@@ -18410,15 +18410,15 @@
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="383" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B38" s="227"/>
       <c r="C38" s="228"/>
       <c r="D38" s="380" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E38" s="380" t="s">
         <v>1055</v>
-      </c>
-      <c r="E38" s="380" t="s">
-        <v>1056</v>
       </c>
       <c r="F38" s="230"/>
       <c r="G38" s="229"/>
@@ -18429,15 +18429,15 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="381" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B39" s="219"/>
       <c r="C39" s="220"/>
       <c r="D39" s="377" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E39" s="221" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F39" s="222"/>
       <c r="G39" s="221"/>
@@ -18448,14 +18448,14 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C40" s="192"/>
       <c r="D40" s="386" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E40" s="386" t="s">
         <v>1058</v>
-      </c>
-      <c r="E40" s="386" t="s">
-        <v>1059</v>
       </c>
       <c r="F40" s="86"/>
       <c r="H40" s="86"/>
@@ -18465,14 +18465,14 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C41" s="192"/>
       <c r="D41" s="386" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E41" s="386" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F41" s="86"/>
       <c r="H41" s="86"/>
@@ -18482,14 +18482,14 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C42" s="192"/>
       <c r="D42" s="386" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E42" s="386" t="s">
         <v>1061</v>
-      </c>
-      <c r="E42" s="386" t="s">
-        <v>1062</v>
       </c>
       <c r="F42" s="86"/>
       <c r="H42" s="86"/>
@@ -18499,15 +18499,15 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="383" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B43" s="227"/>
       <c r="C43" s="228"/>
       <c r="D43" s="380" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E43" s="380" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F43" s="230"/>
       <c r="G43" s="229"/>
@@ -18518,48 +18518,48 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="218" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B44" s="219" t="s">
         <v>1064</v>
       </c>
-      <c r="B44" s="219" t="s">
+      <c r="C44" s="220" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D44" s="377" t="s">
         <v>1065</v>
       </c>
-      <c r="C44" s="220" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D44" s="377" t="s">
-        <v>1066</v>
-      </c>
       <c r="E44" s="221" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F44" s="222">
         <v>22</v>
       </c>
       <c r="G44" s="221" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H44" s="385" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I44" s="234" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="J44" s="223"/>
       <c r="K44" s="412" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B45" s="390"/>
       <c r="C45" s="389"/>
       <c r="D45" s="386" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E45" s="386" t="s">
         <v>1068</v>
-      </c>
-      <c r="E45" s="386" t="s">
-        <v>1069</v>
       </c>
       <c r="F45" s="391"/>
       <c r="G45" s="386"/>
@@ -18570,81 +18570,81 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="224" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B46" s="81" t="s">
         <v>1064</v>
       </c>
-      <c r="B46" s="81" t="s">
-        <v>1065</v>
-      </c>
       <c r="C46" s="192" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D46" s="386" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E46" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F46" s="86">
         <v>22</v>
       </c>
       <c r="G46" s="82" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H46" s="391" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I46" s="235" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="J46" s="225"/>
       <c r="K46" s="412" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="224" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B47" s="81" t="s">
         <v>1064</v>
       </c>
-      <c r="B47" s="81" t="s">
-        <v>1065</v>
-      </c>
       <c r="C47" s="192" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D47" s="386" t="s">
         <v>1072</v>
       </c>
-      <c r="D47" s="386" t="s">
+      <c r="E47" s="386" t="s">
         <v>1073</v>
-      </c>
-      <c r="E47" s="386" t="s">
-        <v>1074</v>
       </c>
       <c r="F47" s="86">
         <v>22</v>
       </c>
       <c r="G47" s="82" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H47" s="391" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I47" s="235" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="J47" s="225"/>
       <c r="K47" s="412" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="383" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B48" s="227"/>
       <c r="C48" s="228"/>
       <c r="D48" s="380" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E48" s="380" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F48" s="230"/>
       <c r="G48" s="229"/>
@@ -18655,15 +18655,15 @@
     </row>
     <row r="49" spans="1:18">
       <c r="A49" s="381" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B49" s="219"/>
       <c r="C49" s="220"/>
       <c r="D49" s="377" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E49" s="221" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F49" s="222"/>
       <c r="G49" s="221"/>
@@ -18674,80 +18674,80 @@
     </row>
     <row r="50" spans="1:18">
       <c r="A50" s="224" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B50" s="81" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C50" s="192" t="s">
         <v>1078</v>
       </c>
-      <c r="C50" s="192" t="s">
+      <c r="D50" s="386" t="s">
         <v>1079</v>
       </c>
-      <c r="D50" s="386" t="s">
+      <c r="E50" s="82" t="s">
         <v>1080</v>
-      </c>
-      <c r="E50" s="82" t="s">
-        <v>1081</v>
       </c>
       <c r="F50" s="86">
         <v>22</v>
       </c>
       <c r="G50" s="82" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H50" s="86">
         <v>600</v>
       </c>
       <c r="I50" s="82" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="J50" s="225"/>
       <c r="K50" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="51" spans="1:18">
       <c r="A51" s="224" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B51" s="81" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C51" s="192" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D51" s="386" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="E51" s="82" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F51" s="86">
         <v>22</v>
       </c>
       <c r="G51" s="82" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H51" s="86">
         <v>600</v>
       </c>
       <c r="I51" s="82" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="J51" s="225"/>
       <c r="K51" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="52" spans="1:18">
       <c r="A52" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C52" s="192"/>
       <c r="D52" s="386" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E52" s="386" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="F52" s="86"/>
       <c r="H52" s="86"/>
@@ -18757,15 +18757,15 @@
     </row>
     <row r="53" spans="1:18">
       <c r="A53" s="383" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B53" s="227"/>
       <c r="C53" s="228"/>
       <c r="D53" s="380" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E53" s="380" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F53" s="230"/>
       <c r="G53" s="229"/>
@@ -18776,15 +18776,15 @@
     </row>
     <row r="54" spans="1:18">
       <c r="A54" s="381" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B54" s="219"/>
       <c r="C54" s="220"/>
       <c r="D54" s="377" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E54" s="221" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F54" s="222"/>
       <c r="G54" s="221"/>
@@ -18795,80 +18795,80 @@
     </row>
     <row r="55" spans="1:18">
       <c r="A55" s="224" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B55" s="81" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C55" s="192" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D55" s="386" t="s">
         <v>1089</v>
       </c>
-      <c r="C55" s="192" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D55" s="386" t="s">
+      <c r="E55" s="82" t="s">
         <v>1090</v>
-      </c>
-      <c r="E55" s="82" t="s">
-        <v>1091</v>
       </c>
       <c r="F55" s="86">
         <v>22</v>
       </c>
       <c r="G55" s="82" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H55" s="86">
         <v>600</v>
       </c>
       <c r="I55" s="82" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="J55" s="225"/>
       <c r="K55" s="412" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="56" spans="1:18">
       <c r="A56" s="224" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B56" s="81" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="C56" s="192" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D56" s="386" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E56" s="386" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F56" s="86">
         <v>22</v>
       </c>
       <c r="G56" s="82" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H56" s="86">
         <v>600</v>
       </c>
       <c r="I56" s="82" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="J56" s="225"/>
       <c r="K56" s="412" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="57" spans="1:18">
       <c r="A57" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C57" s="192"/>
       <c r="D57" s="386" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E57" s="386" t="s">
         <v>1095</v>
-      </c>
-      <c r="E57" s="386" t="s">
-        <v>1096</v>
       </c>
       <c r="F57" s="86"/>
       <c r="H57" s="86"/>
@@ -18878,15 +18878,15 @@
     </row>
     <row r="58" spans="1:18">
       <c r="A58" s="383" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B58" s="227"/>
       <c r="C58" s="228"/>
       <c r="D58" s="380" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="E58" s="380" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F58" s="230"/>
       <c r="G58" s="229"/>
@@ -18897,15 +18897,15 @@
     </row>
     <row r="59" spans="1:18">
       <c r="A59" s="381" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B59" s="219"/>
       <c r="C59" s="220"/>
       <c r="D59" s="377" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="E59" s="221" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F59" s="222"/>
       <c r="G59" s="221"/>
@@ -18916,14 +18916,14 @@
     </row>
     <row r="60" spans="1:18">
       <c r="A60" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C60" s="192"/>
       <c r="D60" s="386" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E60" s="386" t="s">
         <v>1099</v>
-      </c>
-      <c r="E60" s="386" t="s">
-        <v>1100</v>
       </c>
       <c r="F60" s="86"/>
       <c r="H60" s="86"/>
@@ -18933,14 +18933,14 @@
     </row>
     <row r="61" spans="1:18">
       <c r="A61" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C61" s="192"/>
       <c r="D61" s="386" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="E61" s="386" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F61" s="86"/>
       <c r="H61" s="86"/>
@@ -18951,25 +18951,25 @@
     </row>
     <row r="62" spans="1:18">
       <c r="A62" s="388" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B62" s="390" t="s">
         <v>1102</v>
       </c>
-      <c r="B62" s="390" t="s">
+      <c r="C62" s="389" t="s">
         <v>1103</v>
       </c>
-      <c r="C62" s="389" t="s">
+      <c r="D62" s="235" t="s">
         <v>1104</v>
       </c>
-      <c r="D62" s="235" t="s">
+      <c r="E62" s="235" t="s">
         <v>1105</v>
-      </c>
-      <c r="E62" s="235" t="s">
-        <v>1106</v>
       </c>
       <c r="F62" s="86">
         <v>22</v>
       </c>
       <c r="G62" s="386" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H62" s="86">
         <v>800</v>
@@ -18977,21 +18977,21 @@
       <c r="I62" s="240"/>
       <c r="J62" s="225"/>
       <c r="K62" s="412" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="R62" s="88"/>
     </row>
     <row r="63" spans="1:18">
       <c r="A63" s="241" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B63" s="242"/>
       <c r="C63" s="243"/>
       <c r="D63" s="244" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="E63" s="244" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F63" s="245"/>
       <c r="G63" s="244"/>
@@ -19002,15 +19002,15 @@
     </row>
     <row r="64" spans="1:18">
       <c r="A64" s="247" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B64" s="248"/>
       <c r="C64" s="249"/>
       <c r="D64" s="234" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="E64" s="234" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F64" s="250"/>
       <c r="G64" s="234"/>
@@ -19021,48 +19021,48 @@
     </row>
     <row r="65" spans="1:12" s="214" customFormat="1">
       <c r="A65" s="236" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B65" s="237" t="s">
         <v>1109</v>
       </c>
-      <c r="B65" s="237" t="s">
+      <c r="C65" s="238" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D65" s="235" t="s">
         <v>1110</v>
       </c>
-      <c r="C65" s="238" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D65" s="235" t="s">
+      <c r="E65" s="235" t="s">
         <v>1111</v>
-      </c>
-      <c r="E65" s="235" t="s">
-        <v>1112</v>
       </c>
       <c r="F65" s="239">
         <v>22</v>
       </c>
       <c r="G65" s="235" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H65" s="239">
         <v>1400</v>
       </c>
       <c r="I65" s="235" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="J65" s="252"/>
       <c r="K65" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" s="236" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B66" s="237"/>
       <c r="C66" s="238"/>
       <c r="D66" s="235" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="E66" s="235" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F66" s="239"/>
       <c r="G66" s="235"/>
@@ -19073,15 +19073,15 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" s="236" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B67" s="237"/>
       <c r="C67" s="238"/>
       <c r="D67" s="235" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E67" s="235" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="F67" s="239"/>
       <c r="G67" s="235"/>
@@ -19092,15 +19092,15 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" s="241" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B68" s="242"/>
       <c r="C68" s="243"/>
       <c r="D68" s="244" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E68" s="244" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F68" s="245"/>
       <c r="G68" s="244"/>
@@ -19111,15 +19111,15 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" s="247" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B69" s="248"/>
       <c r="C69" s="249"/>
       <c r="D69" s="234" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E69" s="234" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F69" s="250"/>
       <c r="G69" s="234"/>
@@ -19130,114 +19130,114 @@
     </row>
     <row r="70" spans="1:12" s="214" customFormat="1">
       <c r="A70" s="236" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B70" s="237" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C70" s="238" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D70" s="235" t="s">
         <v>1118</v>
       </c>
-      <c r="C70" s="238" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D70" s="235" t="s">
+      <c r="E70" s="235" t="s">
         <v>1119</v>
-      </c>
-      <c r="E70" s="235" t="s">
-        <v>1120</v>
       </c>
       <c r="F70" s="239">
         <v>22</v>
       </c>
       <c r="G70" s="235" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H70" s="239">
         <v>1400</v>
       </c>
       <c r="I70" s="235" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J70" s="252"/>
       <c r="K70" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" s="236" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B71" s="237" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C71" s="238" t="s">
+        <v>992</v>
+      </c>
+      <c r="D71" s="235" t="s">
         <v>1122</v>
       </c>
-      <c r="C71" s="238" t="s">
-        <v>993</v>
-      </c>
-      <c r="D71" s="235" t="s">
-        <v>1123</v>
-      </c>
       <c r="E71" s="235" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F71" s="239">
         <v>22</v>
       </c>
       <c r="G71" s="235" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H71" s="239">
         <v>1400</v>
       </c>
       <c r="I71" s="235" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="J71" s="225"/>
       <c r="K71" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="72" spans="1:12" s="214" customFormat="1">
       <c r="A72" s="236" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B72" s="237" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C72" s="238" t="s">
         <v>1125</v>
       </c>
-      <c r="C72" s="238" t="s">
+      <c r="D72" s="235" t="s">
         <v>1126</v>
       </c>
-      <c r="D72" s="235" t="s">
+      <c r="E72" s="235" t="s">
         <v>1127</v>
-      </c>
-      <c r="E72" s="235" t="s">
-        <v>1128</v>
       </c>
       <c r="F72" s="239">
         <v>24</v>
       </c>
       <c r="G72" s="235" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H72" s="239">
         <v>1400</v>
       </c>
       <c r="I72" s="235" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="J72" s="252"/>
       <c r="K72" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" s="241" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B73" s="242"/>
       <c r="C73" s="243"/>
       <c r="D73" s="244" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="E73" s="244" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F73" s="245"/>
       <c r="G73" s="244"/>
@@ -19248,15 +19248,15 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74" s="247" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B74" s="248"/>
       <c r="C74" s="249"/>
       <c r="D74" s="234" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="E74" s="234" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="F74" s="250"/>
       <c r="G74" s="234"/>
@@ -19267,45 +19267,45 @@
     </row>
     <row r="75" spans="1:12" s="214" customFormat="1">
       <c r="A75" s="236" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B75" s="237" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C75" s="238" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D75" s="235" t="s">
         <v>1132</v>
       </c>
-      <c r="C75" s="238" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D75" s="235" t="s">
+      <c r="E75" s="235" t="s">
         <v>1133</v>
-      </c>
-      <c r="E75" s="235" t="s">
-        <v>1134</v>
       </c>
       <c r="F75" s="239">
         <v>22</v>
       </c>
       <c r="G75" s="235" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H75" s="239">
         <v>1400</v>
       </c>
       <c r="I75" s="235" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="J75" s="252"/>
       <c r="K75" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" s="236" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B76" s="237"/>
       <c r="C76" s="238"/>
       <c r="D76" s="235" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E76" s="235"/>
       <c r="F76" s="239"/>
@@ -19317,49 +19317,49 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" s="236" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B77" s="237" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C77" s="238" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D77" s="235" t="s">
         <v>1137</v>
       </c>
-      <c r="C77" s="238" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D77" s="235" t="s">
+      <c r="E77" s="235" t="s">
         <v>1138</v>
-      </c>
-      <c r="E77" s="235" t="s">
-        <v>1139</v>
       </c>
       <c r="F77" s="239">
         <v>24</v>
       </c>
       <c r="G77" s="235" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H77" s="239">
         <v>1400</v>
       </c>
       <c r="I77" s="235" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="J77" s="252"/>
       <c r="K77" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="L77" s="390"/>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" s="383" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B78" s="227"/>
       <c r="C78" s="228"/>
       <c r="D78" s="380" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E78" s="380" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F78" s="230"/>
       <c r="G78" s="229"/>
@@ -19370,91 +19370,91 @@
     </row>
     <row r="79" spans="1:12">
       <c r="A79" s="381" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B79" s="219" t="s">
         <v>1142</v>
       </c>
-      <c r="B79" s="219" t="s">
+      <c r="C79" s="220" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="377" t="s">
         <v>1143</v>
       </c>
-      <c r="C79" s="220" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="377" t="s">
+      <c r="E79" s="221" t="s">
         <v>1144</v>
-      </c>
-      <c r="E79" s="221" t="s">
-        <v>1145</v>
       </c>
       <c r="F79" s="222">
         <v>18</v>
       </c>
       <c r="G79" s="221" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H79" s="222">
         <v>600</v>
       </c>
       <c r="I79" s="221" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="J79" s="223"/>
       <c r="K79" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" s="383" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B80" s="227" t="s">
         <v>1142</v>
       </c>
-      <c r="B80" s="227" t="s">
-        <v>1143</v>
-      </c>
       <c r="C80" s="228" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D80" s="380" t="s">
         <v>1147</v>
       </c>
-      <c r="D80" s="380" t="s">
+      <c r="E80" s="229" t="s">
         <v>1148</v>
-      </c>
-      <c r="E80" s="229" t="s">
-        <v>1149</v>
       </c>
       <c r="F80" s="230">
         <v>18</v>
       </c>
       <c r="G80" s="229" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="H80" s="230">
         <v>600</v>
       </c>
       <c r="I80" s="229" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="J80" s="231"/>
       <c r="K80" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="381" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B81" s="382" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C81" s="394" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="377" t="s">
         <v>1151</v>
       </c>
-      <c r="C81" s="394" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="377" t="s">
-        <v>1152</v>
-      </c>
       <c r="E81" s="221" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F81" s="222">
         <v>22</v>
       </c>
       <c r="G81" s="221" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H81" s="385">
         <v>800</v>
@@ -19462,30 +19462,30 @@
       <c r="I81" s="377"/>
       <c r="J81" s="387"/>
       <c r="K81" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="383" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B82" s="384" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="C82" s="379" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D82" s="380" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E82" s="229" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F82" s="230">
         <v>22</v>
       </c>
       <c r="G82" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H82" s="393">
         <v>800</v>
@@ -19493,26 +19493,26 @@
       <c r="I82" s="380"/>
       <c r="J82" s="231"/>
       <c r="K82" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="381" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B83" s="219"/>
       <c r="C83" s="220" t="s">
         <v>1</v>
       </c>
       <c r="D83" s="377" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E83" s="221" t="s">
         <v>1154</v>
-      </c>
-      <c r="E83" s="221" t="s">
-        <v>1155</v>
       </c>
       <c r="F83" s="222"/>
       <c r="G83" s="221" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H83" s="222"/>
       <c r="I83" s="221"/>
@@ -19521,20 +19521,20 @@
     </row>
     <row r="84" spans="1:14" ht="15.75" thickBot="1">
       <c r="A84" s="388" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C84" s="192" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D84" s="386" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="E84" s="82" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F84" s="86"/>
       <c r="G84" s="82" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H84" s="86"/>
       <c r="I84" s="82"/>
@@ -19543,71 +19543,71 @@
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="206" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B85" s="207"/>
       <c r="C85" s="208" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D85" s="209" t="s">
         <v>1158</v>
       </c>
-      <c r="D85" s="209" t="s">
-        <v>1159</v>
-      </c>
       <c r="E85" s="209" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F85" s="210"/>
       <c r="G85" s="209"/>
       <c r="H85" s="210"/>
       <c r="I85" s="416"/>
       <c r="J85" s="212" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="K85" s="418"/>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="198" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B86" s="408"/>
       <c r="C86" s="414" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D86" s="414" t="s">
         <v>1164</v>
       </c>
-      <c r="D86" s="414" t="s">
-        <v>1165</v>
-      </c>
       <c r="E86" s="414" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F86" s="411"/>
       <c r="G86" s="410"/>
       <c r="H86" s="411"/>
       <c r="I86" s="413"/>
       <c r="J86" s="199" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="K86" s="418"/>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="198" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B87" s="408" t="s">
         <v>1178</v>
       </c>
-      <c r="B87" s="408" t="s">
-        <v>1179</v>
-      </c>
       <c r="C87" s="409" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D87" s="410" t="s">
         <v>1168</v>
       </c>
-      <c r="D87" s="410" t="s">
-        <v>1169</v>
-      </c>
       <c r="E87" s="410" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F87" s="411">
         <v>22</v>
       </c>
       <c r="G87" s="410" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H87" s="411">
         <v>800</v>
@@ -19615,30 +19615,30 @@
       <c r="I87" s="410"/>
       <c r="J87" s="200"/>
       <c r="K87" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="88" spans="1:14" ht="15.75" thickBot="1">
       <c r="A88" s="198" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B88" s="408" t="s">
         <v>1178</v>
       </c>
-      <c r="B88" s="408" t="s">
-        <v>1179</v>
-      </c>
       <c r="C88" s="409" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D88" s="410" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E88" s="410" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F88" s="411">
         <v>22</v>
       </c>
       <c r="G88" s="410" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H88" s="411">
         <v>800</v>
@@ -19646,901 +19646,901 @@
       <c r="I88" s="410"/>
       <c r="J88" s="200"/>
       <c r="K88" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="206" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B89" s="207" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C89" s="208" t="s">
         <v>1157</v>
       </c>
-      <c r="C89" s="208" t="s">
-        <v>1158</v>
-      </c>
       <c r="D89" s="209" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="E89" s="209" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F89" s="210">
         <v>22</v>
       </c>
       <c r="G89" s="209" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H89" s="210" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I89" s="211" t="s">
+        <v>1159</v>
+      </c>
+      <c r="J89" s="212" t="s">
         <v>1160</v>
       </c>
-      <c r="J89" s="212" t="s">
-        <v>1161</v>
-      </c>
       <c r="K89" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="L89" s="253">
         <v>8</v>
       </c>
       <c r="M89" s="254" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N89" s="387" t="s">
         <v>1162</v>
-      </c>
-      <c r="N89" s="387" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="198" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B90" s="408" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C90" s="414" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D90" s="414" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E90" s="414" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F90" s="411">
         <v>22</v>
       </c>
       <c r="G90" s="410" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H90" s="411" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I90" s="415" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J90" s="199" t="s">
         <v>1166</v>
       </c>
-      <c r="J90" s="199" t="s">
-        <v>1167</v>
-      </c>
       <c r="K90" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="L90" s="255">
         <v>4</v>
       </c>
       <c r="M90" s="256" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N90" s="392" t="s">
         <v>1162</v>
-      </c>
-      <c r="N90" s="392" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="198" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B91" s="408" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C91" s="409" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D91" s="410" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="E91" s="410" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="F91" s="411">
         <v>22</v>
       </c>
       <c r="G91" s="410" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H91" s="411" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I91" s="415" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="J91" s="200"/>
       <c r="K91" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="L91" s="255">
         <v>7</v>
       </c>
       <c r="M91" s="256" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N91" s="392" t="s">
         <v>1162</v>
-      </c>
-      <c r="N91" s="392" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="92" spans="1:14" ht="15.75" thickBot="1">
       <c r="A92" s="201" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B92" s="202" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C92" s="203" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D92" s="205" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="E92" s="205" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F92" s="204">
         <v>22</v>
       </c>
       <c r="G92" s="205" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H92" s="204" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I92" s="417" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="J92" s="213"/>
       <c r="K92" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="L92" s="257">
         <v>10</v>
       </c>
       <c r="M92" s="258" t="s">
+        <v>1161</v>
+      </c>
+      <c r="N92" s="395" t="s">
         <v>1162</v>
-      </c>
-      <c r="N92" s="395" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="198" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B93" s="408"/>
       <c r="C93" s="409"/>
       <c r="D93" s="410" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="E93" s="410" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F93" s="411"/>
       <c r="G93" s="410"/>
       <c r="H93" s="411"/>
       <c r="I93" s="413"/>
       <c r="J93" s="199" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="K93" s="418"/>
       <c r="N93" s="390"/>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="198" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B94" s="408"/>
       <c r="C94" s="409"/>
       <c r="D94" s="414" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="E94" s="414" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F94" s="411"/>
       <c r="G94" s="410"/>
       <c r="H94" s="411"/>
       <c r="I94" s="413"/>
       <c r="J94" s="199" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="K94" s="418"/>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="198" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B95" s="408" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C95" s="409" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D95" s="410" t="s">
         <v>1186</v>
       </c>
-      <c r="C95" s="409" t="s">
-        <v>1168</v>
-      </c>
-      <c r="D95" s="410" t="s">
+      <c r="E95" s="410" t="s">
         <v>1187</v>
-      </c>
-      <c r="E95" s="410" t="s">
-        <v>1188</v>
       </c>
       <c r="F95" s="411">
         <v>22</v>
       </c>
       <c r="G95" s="410" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H95" s="411">
         <v>500</v>
       </c>
       <c r="I95" s="410" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="J95" s="200"/>
       <c r="K95" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="96" spans="1:14" ht="15.75" thickBot="1">
       <c r="A96" s="201" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B96" s="202" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="C96" s="203" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D96" s="205" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E96" s="205" t="s">
         <v>1190</v>
-      </c>
-      <c r="E96" s="205" t="s">
-        <v>1191</v>
       </c>
       <c r="F96" s="204">
         <v>22</v>
       </c>
       <c r="G96" s="205" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H96" s="204">
         <v>500</v>
       </c>
       <c r="I96" s="202" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="J96" s="213"/>
       <c r="K96" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="224" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B97" s="81" t="s">
         <v>1193</v>
       </c>
-      <c r="B97" s="81" t="s">
+      <c r="C97" s="192" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D97" s="386" t="s">
         <v>1194</v>
       </c>
-      <c r="C97" s="192" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D97" s="386" t="s">
+      <c r="E97" s="82" t="s">
         <v>1195</v>
-      </c>
-      <c r="E97" s="82" t="s">
-        <v>1196</v>
       </c>
       <c r="F97" s="86">
         <v>22</v>
       </c>
       <c r="G97" s="82" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H97" s="86">
         <v>500</v>
       </c>
       <c r="I97" s="82" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="J97" s="225"/>
       <c r="K97" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="226" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B98" s="227" t="s">
         <v>1193</v>
       </c>
-      <c r="B98" s="227" t="s">
-        <v>1194</v>
-      </c>
       <c r="C98" s="228" t="s">
         <v>1</v>
       </c>
       <c r="D98" s="380" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E98" s="229" t="s">
         <v>1198</v>
-      </c>
-      <c r="E98" s="229" t="s">
-        <v>1199</v>
       </c>
       <c r="F98" s="230">
         <v>22</v>
       </c>
       <c r="G98" s="229" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H98" s="230">
         <v>500</v>
       </c>
       <c r="I98" s="259" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="J98" s="231"/>
       <c r="K98" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="218" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B99" s="219" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C99" s="220" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D99" s="377" t="s">
         <v>1201</v>
       </c>
-      <c r="C99" s="220" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D99" s="377" t="s">
-        <v>1202</v>
-      </c>
       <c r="E99" s="221" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F99" s="222">
         <v>22</v>
       </c>
       <c r="G99" s="221" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H99" s="222">
         <v>500</v>
       </c>
       <c r="I99" s="221" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="J99" s="223"/>
       <c r="K99" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="226" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B100" s="227" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C100" s="228" t="s">
         <v>1</v>
       </c>
       <c r="D100" s="380" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E100" s="229" t="s">
         <v>1204</v>
-      </c>
-      <c r="E100" s="229" t="s">
-        <v>1205</v>
       </c>
       <c r="F100" s="230">
         <v>22</v>
       </c>
       <c r="G100" s="229" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H100" s="230">
         <v>500</v>
       </c>
       <c r="I100" s="259" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="J100" s="231"/>
       <c r="K100" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="218" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B101" s="219" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C101" s="220" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D101" s="377" t="s">
         <v>1207</v>
       </c>
-      <c r="C101" s="220" t="s">
-        <v>1147</v>
-      </c>
-      <c r="D101" s="377" t="s">
-        <v>1208</v>
-      </c>
       <c r="E101" s="221" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F101" s="222">
         <v>22</v>
       </c>
       <c r="G101" s="221" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H101" s="222">
         <v>500</v>
       </c>
       <c r="I101" s="221" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="J101" s="223"/>
       <c r="K101" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="226" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B102" s="227" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="C102" s="228" t="s">
         <v>1</v>
       </c>
       <c r="D102" s="380" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E102" s="229" t="s">
         <v>1210</v>
-      </c>
-      <c r="E102" s="229" t="s">
-        <v>1211</v>
       </c>
       <c r="F102" s="230">
         <v>22</v>
       </c>
       <c r="G102" s="229" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H102" s="230">
         <v>500</v>
       </c>
       <c r="I102" s="259" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="J102" s="231"/>
       <c r="K102" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="381" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B103" s="382" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C103" s="220" t="s">
         <v>1213</v>
       </c>
-      <c r="C103" s="220" t="s">
+      <c r="D103" s="221" t="s">
         <v>1214</v>
       </c>
-      <c r="D103" s="221" t="s">
+      <c r="E103" s="221" t="s">
         <v>1215</v>
-      </c>
-      <c r="E103" s="221" t="s">
-        <v>1216</v>
       </c>
       <c r="F103" s="222">
         <v>22</v>
       </c>
       <c r="G103" s="221" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H103" s="222">
         <v>600</v>
       </c>
       <c r="I103" s="221" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="J103" s="223"/>
       <c r="K103" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="383" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B104" s="384" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="C104" s="228" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D104" s="229" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E104" s="229" t="s">
         <v>1218</v>
-      </c>
-      <c r="D104" s="229" t="s">
-        <v>1215</v>
-      </c>
-      <c r="E104" s="229" t="s">
-        <v>1219</v>
       </c>
       <c r="F104" s="230">
         <v>22</v>
       </c>
       <c r="G104" s="229" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H104" s="230">
         <v>600</v>
       </c>
       <c r="I104" s="229" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="J104" s="231"/>
       <c r="K104" s="418" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="381" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B105" s="219" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C105" s="220" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D105" s="221" t="s">
         <v>1221</v>
       </c>
-      <c r="C105" s="220" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D105" s="221" t="s">
-        <v>1222</v>
-      </c>
       <c r="E105" s="221" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F105" s="222">
         <v>22</v>
       </c>
       <c r="G105" s="221" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H105" s="222">
         <v>600</v>
       </c>
       <c r="I105" s="221" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="J105" s="223"/>
       <c r="K105" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="383" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B106" s="227" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C106" s="228" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D106" s="229" t="s">
         <v>1221</v>
       </c>
-      <c r="C106" s="228" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D106" s="229" t="s">
-        <v>1222</v>
-      </c>
       <c r="E106" s="229" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="F106" s="230">
         <v>22</v>
       </c>
       <c r="G106" s="229" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H106" s="230">
         <v>600</v>
       </c>
       <c r="I106" s="229" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="J106" s="231"/>
       <c r="K106" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="381" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B107" s="219" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C107" s="220" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D107" s="221" t="s">
         <v>1226</v>
       </c>
-      <c r="C107" s="220" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D107" s="221" t="s">
+      <c r="E107" s="221" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F107" s="385" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G107" s="221" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H107" s="385" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I107" s="221" t="s">
         <v>1227</v>
-      </c>
-      <c r="E107" s="221" t="s">
-        <v>1216</v>
-      </c>
-      <c r="F107" s="385" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G107" s="221" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H107" s="385" t="s">
-        <v>1042</v>
-      </c>
-      <c r="I107" s="221" t="s">
-        <v>1228</v>
       </c>
       <c r="J107" s="223"/>
       <c r="K107" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="383" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B108" s="227" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C108" s="228" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D108" s="229" t="s">
         <v>1226</v>
       </c>
-      <c r="C108" s="228" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D108" s="229" t="s">
+      <c r="E108" s="229" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F108" s="393" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G108" s="229" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H108" s="393" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I108" s="229" t="s">
         <v>1227</v>
-      </c>
-      <c r="E108" s="229" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F108" s="393" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G108" s="229" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H108" s="393" t="s">
-        <v>1042</v>
-      </c>
-      <c r="I108" s="229" t="s">
-        <v>1228</v>
       </c>
       <c r="J108" s="231"/>
       <c r="K108" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="381" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B109" s="219" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C109" s="220" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D109" s="221" t="s">
         <v>1230</v>
       </c>
-      <c r="C109" s="220" t="s">
-        <v>1214</v>
-      </c>
-      <c r="D109" s="221" t="s">
-        <v>1231</v>
-      </c>
       <c r="E109" s="221" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="F109" s="222">
         <v>22</v>
       </c>
       <c r="G109" s="221" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H109" s="222">
         <v>600</v>
       </c>
       <c r="I109" s="221" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="J109" s="223"/>
       <c r="K109" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="383" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B110" s="227" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C110" s="228" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D110" s="229" t="s">
         <v>1230</v>
       </c>
-      <c r="C110" s="228" t="s">
-        <v>1218</v>
-      </c>
-      <c r="D110" s="229" t="s">
-        <v>1231</v>
-      </c>
       <c r="E110" s="229" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="F110" s="230">
         <v>22</v>
       </c>
       <c r="G110" s="229" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="H110" s="230">
         <v>600</v>
       </c>
       <c r="I110" s="229" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="J110" s="231"/>
       <c r="K110" s="418" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="218" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B111" s="219" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C111" s="220" t="s">
         <v>1235</v>
       </c>
-      <c r="C111" s="220" t="s">
+      <c r="D111" s="221" t="s">
         <v>1236</v>
       </c>
-      <c r="D111" s="221" t="s">
-        <v>1237</v>
-      </c>
       <c r="E111" s="221" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F111" s="385" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G111" s="221" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H111" s="222">
         <v>150</v>
       </c>
       <c r="I111" s="221" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="J111" s="223"/>
       <c r="K111" s="418" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="226" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B112" s="227" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="C112" s="228" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="D112" s="229" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="E112" s="229" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F112" s="393" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G112" s="229" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H112" s="230">
         <v>150</v>
       </c>
       <c r="I112" s="380" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="J112" s="231"/>
       <c r="K112" s="418" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="218" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B113" s="219" t="s">
         <v>1240</v>
       </c>
-      <c r="B113" s="219" t="s">
+      <c r="C113" s="220" t="s">
+        <v>992</v>
+      </c>
+      <c r="D113" s="377" t="s">
         <v>1241</v>
       </c>
-      <c r="C113" s="220" t="s">
-        <v>993</v>
-      </c>
-      <c r="D113" s="377" t="s">
-        <v>1242</v>
-      </c>
       <c r="E113" s="221" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F113" s="385" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G113" s="221"/>
       <c r="H113" s="385" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I113" s="221" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="J113" s="223"/>
       <c r="K113" s="418" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="226" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B114" s="227" t="s">
         <v>1240</v>
       </c>
-      <c r="B114" s="227" t="s">
-        <v>1241</v>
-      </c>
       <c r="C114" s="228" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="D114" s="380" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="E114" s="229">
         <v>12</v>
       </c>
       <c r="F114" s="393" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="G114" s="229"/>
       <c r="H114" s="393" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="I114" s="229" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="J114" s="231"/>
       <c r="K114" s="418" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="390" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B115" s="390" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C115" s="192"/>
       <c r="D115" s="386" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="E115" s="82" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="F115" s="86"/>
       <c r="H115" s="86"/>
       <c r="I115" s="386" t="s">
+        <v>1248</v>
+      </c>
+      <c r="J115" s="190" t="s">
         <v>1249</v>
-      </c>
-      <c r="J115" s="190" t="s">
-        <v>1250</v>
       </c>
       <c r="K115" s="192"/>
     </row>
@@ -20593,52 +20593,52 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="I1" t="s">
         <v>1251</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="18.75">
       <c r="A2" s="120" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="I2" s="120" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75">
       <c r="A3" s="116" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B3" s="117" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C3" s="117" t="s">
+        <v>982</v>
+      </c>
+      <c r="D3" s="117" t="s">
         <v>1255</v>
       </c>
-      <c r="C3" s="117" t="s">
-        <v>983</v>
-      </c>
-      <c r="D3" s="117" t="s">
+      <c r="I3" s="121" t="s">
         <v>1256</v>
       </c>
-      <c r="I3" s="121" t="s">
+      <c r="J3" s="117" t="s">
         <v>1257</v>
       </c>
-      <c r="J3" s="117" t="s">
-        <v>1258</v>
-      </c>
       <c r="K3" s="117" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="L3" s="122" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="118" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B4" s="119" t="s">
         <v>1259</v>
-      </c>
-      <c r="B4" s="119" t="s">
-        <v>1260</v>
       </c>
       <c r="C4" s="119">
         <v>500</v>
@@ -20650,21 +20650,21 @@
         <v>1</v>
       </c>
       <c r="J4" s="124" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="K4" s="124">
         <v>700</v>
       </c>
       <c r="L4" s="124" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="118" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B5" s="119" t="s">
         <v>1262</v>
-      </c>
-      <c r="B5" s="119" t="s">
-        <v>1263</v>
       </c>
       <c r="C5" s="119">
         <v>500</v>
@@ -20676,21 +20676,21 @@
         <v>2</v>
       </c>
       <c r="J5" s="124" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="K5" s="124">
         <v>400</v>
       </c>
       <c r="L5" s="124" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="118" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B6" s="119" t="s">
         <v>1266</v>
-      </c>
-      <c r="B6" s="119" t="s">
-        <v>1267</v>
       </c>
       <c r="C6" s="119">
         <v>500</v>
@@ -20702,18 +20702,18 @@
         <v>3</v>
       </c>
       <c r="J6" s="124" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="K6" s="124">
         <v>400</v>
       </c>
       <c r="L6" s="124" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B7" s="119"/>
       <c r="C7" s="119"/>
@@ -20724,16 +20724,16 @@
         <v>4</v>
       </c>
       <c r="J7" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K7" s="124"/>
       <c r="L7" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B8" s="119"/>
       <c r="C8" s="119"/>
@@ -20744,16 +20744,16 @@
         <v>5</v>
       </c>
       <c r="J8" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K8" s="124"/>
       <c r="L8" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B9" s="119"/>
       <c r="C9" s="119"/>
@@ -20764,50 +20764,50 @@
         <v>6</v>
       </c>
       <c r="J9" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K9" s="124"/>
       <c r="L9" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="18.75">
       <c r="A11" s="120" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="I11" s="120" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75">
       <c r="A12" s="116" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B12" s="117" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C12" s="117" t="s">
+        <v>982</v>
+      </c>
+      <c r="D12" s="117" t="s">
         <v>983</v>
       </c>
-      <c r="D12" s="117" t="s">
-        <v>984</v>
-      </c>
       <c r="I12" s="121" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="J12" s="122" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="K12" s="122" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="L12" s="122" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B13" s="119"/>
       <c r="C13" s="119"/>
@@ -20818,16 +20818,16 @@
         <v>1</v>
       </c>
       <c r="J13" s="119" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K13" s="124"/>
       <c r="L13" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B14" s="119"/>
       <c r="C14" s="119"/>
@@ -20838,19 +20838,19 @@
         <v>2</v>
       </c>
       <c r="J14" s="119" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K14" s="124"/>
       <c r="L14" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="118" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B15" s="119" t="s">
         <v>1272</v>
-      </c>
-      <c r="B15" s="119" t="s">
-        <v>1273</v>
       </c>
       <c r="C15" s="119">
         <v>500</v>
@@ -20862,21 +20862,21 @@
         <v>3</v>
       </c>
       <c r="J15" s="119" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="K15" s="124">
         <v>700</v>
       </c>
       <c r="L15" s="124" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="118" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B16" s="119" t="s">
         <v>1274</v>
-      </c>
-      <c r="B16" s="119" t="s">
-        <v>1275</v>
       </c>
       <c r="C16" s="119">
         <v>500</v>
@@ -20888,21 +20888,21 @@
         <v>4</v>
       </c>
       <c r="J16" s="119" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="K16" s="124">
         <v>700</v>
       </c>
       <c r="L16" s="124" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="118" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B17" s="119" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="C17" s="119">
         <v>500</v>
@@ -20914,21 +20914,21 @@
         <v>5</v>
       </c>
       <c r="J17" s="119" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="K17" s="124">
         <v>400</v>
       </c>
       <c r="L17" s="124" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="118" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B18" s="119" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="C18" s="119">
         <v>500</v>
@@ -20940,55 +20940,55 @@
         <v>6</v>
       </c>
       <c r="J18" s="119" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="K18" s="124">
         <v>400</v>
       </c>
       <c r="L18" s="124" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="18.75">
       <c r="A20" s="120" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="I20" s="120" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15.75">
       <c r="A21" s="116" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B21" s="117" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C21" s="117" t="s">
+        <v>982</v>
+      </c>
+      <c r="D21" s="117" t="s">
         <v>1255</v>
       </c>
-      <c r="C21" s="117" t="s">
-        <v>983</v>
-      </c>
-      <c r="D21" s="117" t="s">
-        <v>1256</v>
-      </c>
       <c r="I21" s="121" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="J21" s="122" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="K21" s="122" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="L21" s="122" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75">
       <c r="A22" s="118" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B22" s="119" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="C22" s="119">
         <v>500</v>
@@ -21000,21 +21000,21 @@
         <v>1</v>
       </c>
       <c r="J22" s="124" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="K22" s="125">
         <v>700</v>
       </c>
       <c r="L22" s="124" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75">
       <c r="A23" s="118" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B23" s="119" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C23" s="119">
         <v>500</v>
@@ -21026,21 +21026,21 @@
         <v>2</v>
       </c>
       <c r="J23" s="124" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="K23" s="125">
         <v>400</v>
       </c>
       <c r="L23" s="124" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75">
       <c r="A24" s="118" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B24" s="119" t="s">
         <v>1284</v>
-      </c>
-      <c r="B24" s="119" t="s">
-        <v>1285</v>
       </c>
       <c r="C24" s="119">
         <v>500</v>
@@ -21052,18 +21052,18 @@
         <v>3</v>
       </c>
       <c r="J24" s="124" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="K24" s="125">
         <v>400</v>
       </c>
       <c r="L24" s="124" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75">
       <c r="A25" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B25" s="119"/>
       <c r="C25" s="119"/>
@@ -21074,16 +21074,16 @@
         <v>4</v>
       </c>
       <c r="J25" s="125" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K25" s="125"/>
       <c r="L25" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75">
       <c r="A26" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B26" s="119"/>
       <c r="C26" s="119"/>
@@ -21094,19 +21094,19 @@
         <v>5</v>
       </c>
       <c r="J26" s="125" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K26" s="125"/>
       <c r="L26" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75">
       <c r="A27" s="118" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B27" s="119" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C27" s="119">
         <v>500</v>
@@ -21118,21 +21118,21 @@
         <v>6</v>
       </c>
       <c r="J27" s="125" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="K27" s="125">
         <v>700</v>
       </c>
       <c r="L27" s="124" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75">
       <c r="A28" s="118" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B28" s="119" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C28" s="119">
         <v>500</v>
@@ -21144,18 +21144,18 @@
         <v>7</v>
       </c>
       <c r="J28" s="125" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="K28" s="125">
         <v>700</v>
       </c>
       <c r="L28" s="124" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75">
       <c r="A29" s="118" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B29" s="119"/>
       <c r="C29" s="119"/>
@@ -21166,19 +21166,19 @@
         <v>8</v>
       </c>
       <c r="J29" s="125" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K29" s="125"/>
       <c r="L29" s="124" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75">
       <c r="A30" s="118" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B30" s="119" t="s">
         <v>1290</v>
-      </c>
-      <c r="B30" s="119" t="s">
-        <v>1291</v>
       </c>
       <c r="C30" s="119">
         <v>800</v>
@@ -21190,21 +21190,21 @@
         <v>9</v>
       </c>
       <c r="J30" s="125" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="K30" s="125">
         <v>700</v>
       </c>
       <c r="L30" s="124" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75">
       <c r="A31" s="118" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B31" s="119" t="s">
         <v>1290</v>
-      </c>
-      <c r="B31" s="119" t="s">
-        <v>1291</v>
       </c>
       <c r="C31" s="119">
         <v>800</v>
@@ -21216,13 +21216,13 @@
         <v>10</v>
       </c>
       <c r="J31" s="125" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="K31" s="125">
         <v>700</v>
       </c>
       <c r="L31" s="124" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="33" spans="12:12">
@@ -21257,15 +21257,15 @@
   <sheetData>
     <row r="1" spans="1:8" ht="26.25" customHeight="1">
       <c r="A1" s="260" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F1" s="340" t="s">
         <v>1295</v>
-      </c>
-      <c r="F1" s="340" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18.75">
       <c r="A2" s="261" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="E2" s="262" t="s">
         <v>402</v>
@@ -21276,12 +21276,12 @@
     <row r="3" spans="1:8" ht="18.75">
       <c r="A3" s="261"/>
       <c r="B3" s="264" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="D3" s="264"/>
       <c r="F3" s="263"/>
       <c r="G3" s="265" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="H3" s="86"/>
     </row>
@@ -21290,671 +21290,671 @@
         <v>21</v>
       </c>
       <c r="B4" s="81" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C4" s="81" t="s">
         <v>1299</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="D4" s="83" t="s">
         <v>1300</v>
       </c>
-      <c r="D4" s="83" t="s">
+      <c r="E4" s="266" t="s">
         <v>1301</v>
       </c>
-      <c r="E4" s="266" t="s">
+      <c r="F4" s="269" t="s">
         <v>1302</v>
       </c>
-      <c r="F4" s="269" t="s">
+      <c r="G4" s="82" t="s">
         <v>1303</v>
-      </c>
-      <c r="G4" s="82" t="s">
-        <v>1304</v>
       </c>
       <c r="H4" s="86"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="81" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B5" s="81" t="s">
         <v>1305</v>
       </c>
-      <c r="B5" s="81" t="s">
+      <c r="C5" s="81" t="s">
         <v>1306</v>
-      </c>
-      <c r="C5" s="81" t="s">
-        <v>1307</v>
       </c>
       <c r="D5" s="83">
         <v>18</v>
       </c>
       <c r="E5" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F5" s="269">
         <v>300</v>
       </c>
       <c r="G5" s="82" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="H5" s="86"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D6" s="83">
         <v>18</v>
       </c>
       <c r="E6" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F6" s="269">
         <v>300</v>
       </c>
       <c r="G6" s="82" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="H6" s="86"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B7" s="81" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C7" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D7" s="83">
         <v>18</v>
       </c>
       <c r="E7" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F7" s="269">
         <v>300</v>
       </c>
       <c r="G7" s="82" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H7" s="86"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B8" s="81" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C8" s="81" t="s">
         <v>1314</v>
-      </c>
-      <c r="C8" s="81" t="s">
-        <v>1315</v>
       </c>
       <c r="D8" s="83">
         <v>18</v>
       </c>
       <c r="E8" s="266" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F8" s="269">
         <v>300</v>
       </c>
       <c r="G8" s="82" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="H8" s="86"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D9" s="83">
         <v>18</v>
       </c>
       <c r="E9" s="266" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F9" s="269">
         <v>300</v>
       </c>
       <c r="G9" s="82" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H9" s="86"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="390" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B10" s="390" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C10" s="390" t="s">
         <v>1320</v>
-      </c>
-      <c r="C10" s="390" t="s">
-        <v>1321</v>
       </c>
       <c r="D10" s="396">
         <v>18</v>
       </c>
       <c r="E10" s="397" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F10" s="398">
         <v>300</v>
       </c>
       <c r="G10" s="399" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H10" s="86"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="81" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B11" s="81" t="s">
         <v>1324</v>
       </c>
-      <c r="B11" s="81" t="s">
-        <v>1325</v>
-      </c>
       <c r="C11" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D11" s="83">
         <v>18</v>
       </c>
       <c r="E11" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F11" s="269">
         <v>400</v>
       </c>
       <c r="G11" s="268" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H11" s="86"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="81" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D12" s="83">
         <v>18</v>
       </c>
       <c r="E12" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F12" s="269">
         <v>300</v>
       </c>
       <c r="G12" s="268" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H12" s="86"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="81" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B13" s="82" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D13" s="83">
         <v>18</v>
       </c>
       <c r="E13" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F13" s="269">
         <v>200</v>
       </c>
       <c r="G13" s="268" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="H13" s="86"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D14" s="83">
         <v>18</v>
       </c>
       <c r="E14" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F14" s="269">
         <v>400</v>
       </c>
       <c r="G14" s="82" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H14" s="86"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B15" s="81" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C15" s="81" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D15" s="83">
         <v>18</v>
       </c>
       <c r="E15" s="266" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F15" s="269">
         <v>400</v>
       </c>
       <c r="G15" s="82" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H15" s="86"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B16" s="81" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D16" s="83">
         <v>18</v>
       </c>
       <c r="E16" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F16" s="269">
         <v>400</v>
       </c>
       <c r="G16" s="82" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H16" s="86"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D17" s="83">
         <v>18</v>
       </c>
       <c r="E17" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F17" s="269">
         <v>400</v>
       </c>
       <c r="G17" s="82" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H17" s="86"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B18" s="81" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D18" s="83">
         <v>18</v>
       </c>
       <c r="E18" s="266" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F18" s="269">
         <v>400</v>
       </c>
       <c r="G18" s="82" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H18" s="86"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B19" s="81" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D19" s="83">
         <v>18</v>
       </c>
       <c r="E19" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F19" s="269">
         <v>400</v>
       </c>
       <c r="G19" s="82" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H19" s="86"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B20" s="390" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D20" s="83">
         <v>18</v>
       </c>
       <c r="E20" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F20" s="269">
         <v>400</v>
       </c>
       <c r="G20" s="82" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H20" s="86"/>
       <c r="I20" s="390"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B21" s="386" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D21" s="83">
         <v>18</v>
       </c>
       <c r="E21" s="266" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F21" s="269" t="s">
         <v>1332</v>
       </c>
-      <c r="F21" s="269" t="s">
+      <c r="G21" s="400" t="s">
         <v>1333</v>
-      </c>
-      <c r="G21" s="400" t="s">
-        <v>1334</v>
       </c>
       <c r="H21" s="86"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B22" s="386" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D22" s="83">
         <v>18</v>
       </c>
       <c r="E22" s="266" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F22" s="269" t="s">
         <v>1332</v>
       </c>
-      <c r="F22" s="269" t="s">
-        <v>1333</v>
-      </c>
       <c r="G22" s="390" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="H22" s="86"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B23" s="386" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="C23" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D23" s="83">
         <v>18</v>
       </c>
       <c r="E23" s="266" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F23" s="269" t="s">
         <v>1332</v>
       </c>
-      <c r="F23" s="269" t="s">
-        <v>1333</v>
-      </c>
       <c r="G23" s="400" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="H23" s="86"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B24" s="81" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D24" s="83">
         <v>18</v>
       </c>
       <c r="E24" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F24" s="269">
         <v>600</v>
       </c>
       <c r="G24" s="82" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H24" s="86"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B25" s="81" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D25" s="83">
         <v>18</v>
       </c>
       <c r="E25" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F25" s="269">
         <v>700</v>
       </c>
       <c r="G25" s="82" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="H25" s="86"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B26" s="81" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D26" s="83">
         <v>18</v>
       </c>
       <c r="E26" s="266" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F26" s="269">
         <v>300</v>
       </c>
       <c r="G26" s="82" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="H26" s="86"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B27" s="81" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D27" s="83">
         <v>18</v>
       </c>
       <c r="E27" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F27" s="269">
         <v>300</v>
       </c>
       <c r="G27" s="82" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="H27" s="86"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B28" s="81" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D28" s="83">
         <v>18</v>
       </c>
       <c r="E28" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F28" s="269">
         <v>600</v>
       </c>
       <c r="G28" s="82" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="H28" s="86"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B29" s="81" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D29" s="83">
         <v>18</v>
       </c>
       <c r="E29" s="266" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F29" s="269">
         <v>700</v>
       </c>
       <c r="G29" s="82" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="H29" s="86"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B30" s="81" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D30" s="83">
         <v>18</v>
       </c>
       <c r="E30" s="266" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F30" s="269">
         <v>300</v>
       </c>
       <c r="G30" s="82" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
       <c r="H30" s="86"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="81" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B31" s="81" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C31" s="81" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="D31" s="83">
         <v>18</v>
       </c>
       <c r="E31" s="267" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F31" s="269">
         <v>300</v>
       </c>
       <c r="G31" s="82" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="H31" s="86"/>
     </row>
@@ -22517,102 +22517,102 @@
       </c>
       <c r="B18" s="476"/>
       <c r="C18" s="476" t="s">
-        <v>933</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="477" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B19" s="110"/>
       <c r="C19" s="110" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="434" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B20" s="476"/>
       <c r="C20" s="476" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="434" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B21" s="476"/>
       <c r="C21" s="476" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="E21" s="69"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="477" t="s">
+        <v>938</v>
+      </c>
+      <c r="B22" s="110" t="s">
         <v>939</v>
       </c>
-      <c r="B22" s="110" t="s">
+      <c r="C22" s="110" t="s">
         <v>940</v>
-      </c>
-      <c r="C22" s="110" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="477" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B23" s="110"/>
       <c r="C23" s="110" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="477" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B24" s="110"/>
       <c r="C24" s="110" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="477" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B25" s="110"/>
       <c r="C25" s="110" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="477" t="s">
+        <v>947</v>
+      </c>
+      <c r="B26" s="110" t="s">
         <v>948</v>
       </c>
-      <c r="B26" s="110" t="s">
+      <c r="C26" s="110" t="s">
         <v>949</v>
-      </c>
-      <c r="C26" s="110" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="477" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B27" s="110"/>
       <c r="C27" s="110" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="477" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B28" s="110"/>
       <c r="C28" s="110" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -22628,7 +22628,7 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="30" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B32" t="s">
         <v>404</v>
@@ -22636,57 +22636,57 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
+        <v>955</v>
+      </c>
+      <c r="B33" t="s">
         <v>956</v>
-      </c>
-      <c r="B33" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B34" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B35" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B36" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="D37" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="B38" t="s">
+        <v>961</v>
+      </c>
+      <c r="D38" t="s">
         <v>962</v>
-      </c>
-      <c r="D38" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="B39" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="30" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B41" t="s">
         <v>404</v>
@@ -22694,82 +22694,82 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B42" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B43" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
+        <v>967</v>
+      </c>
+      <c r="B44" t="s">
         <v>968</v>
-      </c>
-      <c r="B44" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B45" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B46" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B47" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B48" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B49" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B50" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B51" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -22811,57 +22811,57 @@
         <v>738</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C1" s="177" t="s">
         <v>1346</v>
       </c>
-      <c r="C1" s="177" t="s">
+      <c r="D1" s="177" t="s">
         <v>1347</v>
       </c>
-      <c r="D1" s="177" t="s">
+      <c r="E1" s="177" t="s">
         <v>1348</v>
       </c>
-      <c r="E1" s="177" t="s">
+      <c r="F1" s="177" t="s">
         <v>1349</v>
       </c>
-      <c r="F1" s="177" t="s">
+      <c r="G1" s="182" t="s">
         <v>1350</v>
       </c>
-      <c r="G1" s="182" t="s">
+      <c r="H1" s="183" t="s">
         <v>1351</v>
       </c>
-      <c r="H1" s="183" t="s">
+      <c r="I1" s="4" t="s">
         <v>1352</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>1353</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>1354</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C2" s="173">
         <v>105</v>
       </c>
       <c r="D2" s="178" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E2" s="178" t="s">
         <v>1357</v>
       </c>
-      <c r="E2" s="178" t="s">
+      <c r="F2" s="178" t="s">
         <v>1358</v>
       </c>
-      <c r="F2" s="178" t="s">
+      <c r="G2" s="184" t="s">
         <v>1359</v>
-      </c>
-      <c r="G2" s="184" t="s">
-        <v>1360</v>
       </c>
       <c r="H2" s="185">
         <v>6</v>
@@ -22878,25 +22878,25 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B3" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C3" s="174">
         <v>102</v>
       </c>
       <c r="D3" s="179" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E3" s="179" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F3" s="179" t="s">
         <v>1362</v>
       </c>
-      <c r="E3" s="179" t="s">
-        <v>1358</v>
-      </c>
-      <c r="F3" s="179" t="s">
-        <v>1363</v>
-      </c>
       <c r="G3" s="186" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H3" s="187">
         <v>6</v>
@@ -22913,25 +22913,25 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B4" t="s">
         <v>1364</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1365</v>
       </c>
       <c r="C4" s="174">
         <v>85</v>
       </c>
       <c r="D4" s="179" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E4" s="179" t="s">
         <v>1366</v>
       </c>
-      <c r="E4" s="179" t="s">
+      <c r="F4" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="186" t="s">
         <v>1367</v>
-      </c>
-      <c r="F4" s="181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="186" t="s">
-        <v>1368</v>
       </c>
       <c r="H4" s="187">
         <v>6</v>
@@ -22951,22 +22951,22 @@
         <v>802</v>
       </c>
       <c r="B5" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C5" s="174">
         <v>80</v>
       </c>
       <c r="D5" s="179" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E5" s="179" t="s">
         <v>1369</v>
       </c>
-      <c r="E5" s="179" t="s">
+      <c r="F5" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="186" t="s">
         <v>1370</v>
-      </c>
-      <c r="F5" s="181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="186" t="s">
-        <v>1371</v>
       </c>
       <c r="H5" s="187">
         <v>6</v>
@@ -22983,25 +22983,25 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B6" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C6" s="174">
         <v>100</v>
       </c>
       <c r="D6" s="179" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E6" s="179" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F6" s="179" t="s">
+        <v>1362</v>
+      </c>
+      <c r="G6" s="186" t="s">
         <v>1373</v>
-      </c>
-      <c r="E6" s="179" t="s">
-        <v>1358</v>
-      </c>
-      <c r="F6" s="179" t="s">
-        <v>1363</v>
-      </c>
-      <c r="G6" s="186" t="s">
-        <v>1374</v>
       </c>
       <c r="H6" s="187">
         <v>6</v>
@@ -23018,25 +23018,25 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="B7" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C7" s="174">
         <v>40</v>
       </c>
       <c r="D7" s="179" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E7" s="179" t="s">
         <v>1376</v>
       </c>
-      <c r="E7" s="179" t="s">
+      <c r="F7" s="179" t="s">
         <v>1377</v>
       </c>
-      <c r="F7" s="179" t="s">
+      <c r="G7" s="186" t="s">
         <v>1378</v>
-      </c>
-      <c r="G7" s="186" t="s">
-        <v>1379</v>
       </c>
       <c r="H7" s="187">
         <v>10</v>
@@ -23053,25 +23053,25 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="B8" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C8" s="174">
         <v>50</v>
       </c>
       <c r="D8" s="179" t="s">
+        <v>1375</v>
+      </c>
+      <c r="E8" s="179" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F8" s="179" t="s">
         <v>1376</v>
       </c>
-      <c r="E8" s="179" t="s">
+      <c r="G8" s="186" t="s">
         <v>1381</v>
-      </c>
-      <c r="F8" s="179" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G8" s="186" t="s">
-        <v>1382</v>
       </c>
       <c r="H8" s="187">
         <v>12</v>
@@ -23088,25 +23088,25 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="B9" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C9" s="174">
         <v>50</v>
       </c>
       <c r="D9" s="179" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="E9" s="179" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F9" s="179" t="s">
+        <v>1366</v>
+      </c>
+      <c r="G9" s="186" t="s">
         <v>1381</v>
-      </c>
-      <c r="F9" s="179" t="s">
-        <v>1367</v>
-      </c>
-      <c r="G9" s="186" t="s">
-        <v>1382</v>
       </c>
       <c r="H9" s="187">
         <v>12</v>
@@ -23123,25 +23123,25 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B10" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C10" s="174">
         <v>147</v>
       </c>
       <c r="D10" s="179" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E10" s="179" t="s">
         <v>1386</v>
       </c>
-      <c r="E10" s="179" t="s">
+      <c r="F10" s="179" t="s">
         <v>1387</v>
       </c>
-      <c r="F10" s="179" t="s">
+      <c r="G10" s="186" t="s">
         <v>1388</v>
-      </c>
-      <c r="G10" s="186" t="s">
-        <v>1389</v>
       </c>
       <c r="H10" s="187">
         <v>8</v>
@@ -23158,25 +23158,25 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B11" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C11" s="174">
         <v>78</v>
       </c>
       <c r="D11" s="179" t="s">
+        <v>1368</v>
+      </c>
+      <c r="E11" s="179" t="s">
         <v>1369</v>
       </c>
-      <c r="E11" s="179" t="s">
+      <c r="F11" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="186" t="s">
         <v>1370</v>
-      </c>
-      <c r="F11" s="181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="186" t="s">
-        <v>1371</v>
       </c>
       <c r="H11" s="187">
         <v>6</v>
@@ -23193,25 +23193,25 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B12" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C12" s="174">
         <v>143</v>
       </c>
       <c r="D12" s="179" t="s">
+        <v>1391</v>
+      </c>
+      <c r="E12" s="179" t="s">
         <v>1392</v>
       </c>
-      <c r="E12" s="179" t="s">
+      <c r="F12" s="179" t="s">
         <v>1393</v>
       </c>
-      <c r="F12" s="179" t="s">
+      <c r="G12" s="186" t="s">
         <v>1394</v>
-      </c>
-      <c r="G12" s="186" t="s">
-        <v>1395</v>
       </c>
       <c r="H12" s="187">
         <v>8</v>
@@ -23228,25 +23228,25 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1397</v>
       </c>
       <c r="C13" s="174">
         <v>161</v>
       </c>
       <c r="D13" s="179" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E13" s="179" t="s">
         <v>1398</v>
       </c>
-      <c r="E13" s="179" t="s">
-        <v>1399</v>
-      </c>
       <c r="F13" s="179" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="G13" s="186" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H13" s="187">
         <v>8</v>
@@ -23263,25 +23263,25 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="B14" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C14" s="174">
         <v>225</v>
       </c>
       <c r="D14" s="179" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E14" s="179" t="s">
         <v>1401</v>
       </c>
-      <c r="E14" s="179" t="s">
+      <c r="F14" s="179" t="s">
         <v>1402</v>
       </c>
-      <c r="F14" s="179" t="s">
+      <c r="G14" s="186" t="s">
         <v>1403</v>
-      </c>
-      <c r="G14" s="186" t="s">
-        <v>1404</v>
       </c>
       <c r="H14" s="187">
         <v>6</v>
@@ -23298,25 +23298,25 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="B15" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C15" s="174">
         <v>77</v>
       </c>
       <c r="D15" s="179" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E15" s="179" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F15" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="186" t="s">
         <v>1406</v>
-      </c>
-      <c r="E15" s="179" t="s">
-        <v>1360</v>
-      </c>
-      <c r="F15" s="181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="186" t="s">
-        <v>1407</v>
       </c>
       <c r="H15" s="187">
         <v>6</v>
@@ -23333,25 +23333,25 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B16" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C16" s="174">
         <v>77</v>
       </c>
       <c r="D16" s="179" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="E16" s="179" t="s">
+        <v>1369</v>
+      </c>
+      <c r="F16" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="186" t="s">
         <v>1370</v>
-      </c>
-      <c r="F16" s="181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="186" t="s">
-        <v>1371</v>
       </c>
       <c r="H16" s="187">
         <v>6</v>
@@ -23368,25 +23368,25 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B17" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C17" s="174">
         <v>57</v>
       </c>
       <c r="D17" s="179" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="E17" s="179" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F17" s="181" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="186" t="s">
         <v>1409</v>
-      </c>
-      <c r="F17" s="181" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="186" t="s">
-        <v>1410</v>
       </c>
       <c r="H17" s="187">
         <v>6</v>
@@ -23403,25 +23403,25 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B18" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C18" s="174">
         <v>-60</v>
       </c>
       <c r="D18" s="179" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="E18" s="179" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="F18" s="179" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G18" s="186" t="s">
         <v>1381</v>
-      </c>
-      <c r="G18" s="186" t="s">
-        <v>1382</v>
       </c>
       <c r="H18" s="187">
         <v>6</v>
@@ -23438,25 +23438,25 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B19" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C19" s="174">
         <v>105</v>
       </c>
       <c r="D19" s="179" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E19" s="179" t="s">
         <v>1414</v>
       </c>
-      <c r="E19" s="179" t="s">
+      <c r="F19" s="179" t="s">
         <v>1415</v>
       </c>
-      <c r="F19" s="179" t="s">
-        <v>1416</v>
-      </c>
       <c r="G19" s="186" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="H19" s="187">
         <v>10</v>
@@ -23473,25 +23473,25 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B20" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C20" s="174">
         <v>85</v>
       </c>
       <c r="D20" s="179" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E20" s="179" t="s">
         <v>1418</v>
       </c>
-      <c r="E20" s="179" t="s">
-        <v>1419</v>
-      </c>
       <c r="F20" s="179" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G20" s="186" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H20" s="187">
         <v>8</v>
@@ -23511,22 +23511,22 @@
         <v>756</v>
       </c>
       <c r="B21" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C21" s="174">
         <v>85</v>
       </c>
       <c r="D21" s="179" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="E21" s="179" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="F21" s="179" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="G21" s="186" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H21" s="187">
         <v>8</v>
@@ -23543,25 +23543,25 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B22" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C22" s="174">
         <v>220</v>
       </c>
       <c r="D22" s="179" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E22" s="179" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F22" s="179" t="s">
         <v>1422</v>
       </c>
-      <c r="E22" s="179" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F22" s="179" t="s">
-        <v>1423</v>
-      </c>
       <c r="G22" s="186" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H22" s="187">
         <v>6</v>
@@ -23578,25 +23578,25 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B23" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C23" s="174">
         <v>185</v>
       </c>
       <c r="D23" s="179" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="E23" s="179" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="F23" s="179" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="G23" s="186" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H23" s="187">
         <v>6</v>
@@ -23613,23 +23613,23 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B24" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="C24" s="175"/>
       <c r="D24" s="179" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="E24" s="179" t="s">
+        <v>1426</v>
+      </c>
+      <c r="F24" s="179" t="s">
         <v>1427</v>
       </c>
-      <c r="F24" s="179" t="s">
-        <v>1428</v>
-      </c>
       <c r="G24" s="186" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="H24" s="187">
         <v>6</v>
@@ -23646,23 +23646,23 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B25" t="s">
         <v>1429</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1430</v>
       </c>
       <c r="C25" s="175"/>
       <c r="D25" s="179" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="E25" s="179" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F25" s="181" t="s">
         <v>1</v>
       </c>
       <c r="G25" s="186" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H25" s="187">
         <v>6</v>
@@ -23671,31 +23671,31 @@
         <v>1.18</v>
       </c>
       <c r="J25" s="172" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="K25" s="172" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B26" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="C26" s="175"/>
       <c r="D26" s="179" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="E26" s="179" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="F26" s="181" t="s">
         <v>1</v>
       </c>
       <c r="G26" s="186" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H26" s="187">
         <v>6</v>
@@ -23704,33 +23704,33 @@
         <v>1.22</v>
       </c>
       <c r="J26" s="172" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="K26" s="172" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B27" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C27" s="174">
         <v>216</v>
       </c>
       <c r="D27" s="179" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E27" s="179" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F27" s="179" t="s">
         <v>1434</v>
       </c>
-      <c r="E27" s="179" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F27" s="179" t="s">
-        <v>1435</v>
-      </c>
       <c r="G27" s="186" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H27" s="187">
         <v>6</v>
@@ -23747,25 +23747,25 @@
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1">
       <c r="A28" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B28" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C28" s="176">
         <v>181</v>
       </c>
       <c r="D28" s="180" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E28" s="180" t="s">
+        <v>1403</v>
+      </c>
+      <c r="F28" s="180" t="s">
         <v>1437</v>
       </c>
-      <c r="E28" s="180" t="s">
-        <v>1404</v>
-      </c>
-      <c r="F28" s="180" t="s">
-        <v>1438</v>
-      </c>
       <c r="G28" s="188" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H28" s="189">
         <v>6</v>
@@ -23782,77 +23782,77 @@
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1">
       <c r="A30" s="58" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="59" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="60" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="61" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="62" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="60" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="62" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="60" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="62" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="60" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="61" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="62" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="60" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="61" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="44" spans="1:1" ht="15.75" thickBot="1">
       <c r="A44" s="63" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
   </sheetData>
@@ -23883,76 +23883,76 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="401" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1" s="402" t="s">
         <v>887</v>
       </c>
       <c r="C1" s="402" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1" s="70" t="s">
         <v>1455</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>1456</v>
       </c>
       <c r="E1" s="403"/>
       <c r="F1" s="403" t="s">
+        <v>1456</v>
+      </c>
+      <c r="G1" s="403" t="s">
         <v>1457</v>
-      </c>
-      <c r="G1" s="403" t="s">
-        <v>1458</v>
       </c>
       <c r="H1" s="403"/>
       <c r="I1" s="403"/>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="401" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B2" s="404">
+        <v>1</v>
+      </c>
+      <c r="C2" s="404" t="s">
         <v>1459</v>
-      </c>
-      <c r="B2" s="404">
-        <v>1</v>
-      </c>
-      <c r="C2" s="404" t="s">
-        <v>1460</v>
       </c>
       <c r="D2" s="72">
         <v>2</v>
       </c>
       <c r="E2" s="403"/>
       <c r="F2" s="403" t="s">
+        <v>1460</v>
+      </c>
+      <c r="G2" s="403" t="s">
         <v>1461</v>
       </c>
-      <c r="G2" s="403" t="s">
+      <c r="H2" s="403" t="s">
         <v>1462</v>
-      </c>
-      <c r="H2" s="403" t="s">
-        <v>1463</v>
       </c>
       <c r="I2" s="403"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="401" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B3" s="404" t="s">
         <v>1464</v>
-      </c>
-      <c r="B3" s="404" t="s">
-        <v>1465</v>
       </c>
       <c r="C3" s="404"/>
       <c r="D3" s="72" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="E3" s="403"/>
       <c r="F3" s="403"/>
       <c r="G3" s="403" t="s">
+        <v>1466</v>
+      </c>
+      <c r="H3" s="403" t="s">
         <v>1467</v>
-      </c>
-      <c r="H3" s="403" t="s">
-        <v>1468</v>
       </c>
       <c r="I3" s="403"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="401" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B4" s="404">
         <v>450</v>
@@ -23961,48 +23961,48 @@
         <v>300</v>
       </c>
       <c r="D4" s="72" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E4" s="403"/>
       <c r="F4" s="405" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="G4" s="403" t="s">
         <v>766</v>
       </c>
       <c r="H4" s="403" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="I4" s="403"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="401" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B5" s="404" t="s">
         <v>1473</v>
-      </c>
-      <c r="B5" s="404" t="s">
-        <v>1474</v>
       </c>
       <c r="C5" s="404">
         <v>120</v>
       </c>
       <c r="D5" s="72" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="E5" s="403"/>
       <c r="F5" s="405" t="s">
+        <v>1475</v>
+      </c>
+      <c r="G5" s="403" t="s">
         <v>1476</v>
       </c>
-      <c r="G5" s="403" t="s">
+      <c r="H5" s="403" t="s">
         <v>1477</v>
-      </c>
-      <c r="H5" s="403" t="s">
-        <v>1478</v>
       </c>
       <c r="I5" s="403"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1">
       <c r="A6" s="401" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B6" s="404">
         <v>100</v>
@@ -24011,11 +24011,11 @@
         <v>60</v>
       </c>
       <c r="D6" s="72" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="E6" s="403"/>
       <c r="F6" s="405" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="G6" s="403" t="s">
         <v>636</v>
@@ -24025,417 +24025,417 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="401" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B7" s="404" t="s">
         <v>1482</v>
       </c>
-      <c r="B7" s="404" t="s">
+      <c r="C7" s="404" t="s">
         <v>1483</v>
       </c>
-      <c r="C7" s="404" t="s">
+      <c r="D7" s="72" t="s">
         <v>1484</v>
-      </c>
-      <c r="D7" s="72" t="s">
-        <v>1485</v>
       </c>
       <c r="E7" s="403"/>
       <c r="F7" s="405" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G7" s="403" t="s">
         <v>1486</v>
       </c>
-      <c r="G7" s="403" t="s">
+      <c r="H7" s="403" t="s">
         <v>1487</v>
-      </c>
-      <c r="H7" s="403" t="s">
-        <v>1488</v>
       </c>
       <c r="I7" s="403"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="401" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B8" s="404" t="s">
         <v>1489</v>
       </c>
-      <c r="B8" s="404" t="s">
+      <c r="C8" s="404" t="s">
         <v>1490</v>
       </c>
-      <c r="C8" s="404" t="s">
+      <c r="D8" s="72" t="s">
         <v>1491</v>
-      </c>
-      <c r="D8" s="72" t="s">
-        <v>1492</v>
       </c>
       <c r="E8" s="403"/>
       <c r="F8" s="403"/>
       <c r="G8" s="403" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H8" s="403" t="s">
         <v>1493</v>
-      </c>
-      <c r="H8" s="403" t="s">
-        <v>1494</v>
       </c>
       <c r="I8" s="403"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="401" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B9" s="406" t="s">
         <v>1495</v>
       </c>
-      <c r="B9" s="406" t="s">
+      <c r="C9" s="74" t="s">
         <v>1496</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="D9" s="72" t="s">
         <v>1497</v>
-      </c>
-      <c r="D9" s="72" t="s">
-        <v>1498</v>
       </c>
       <c r="E9" s="403"/>
       <c r="F9" s="403"/>
       <c r="G9" s="403" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H9" s="403" t="s">
         <v>1499</v>
-      </c>
-      <c r="H9" s="403" t="s">
-        <v>1500</v>
       </c>
       <c r="I9" s="403"/>
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1">
       <c r="A10" s="401" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B10" s="404" t="s">
         <v>1501</v>
       </c>
-      <c r="B10" s="404" t="s">
-        <v>1502</v>
-      </c>
       <c r="C10" s="404" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="D10" s="72" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="E10" s="403"/>
       <c r="F10" s="403"/>
       <c r="G10" s="403" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H10" s="403"/>
       <c r="I10" s="403"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="401" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B11" s="404" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C11" s="404" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D11" s="72" t="s">
         <v>1504</v>
-      </c>
-      <c r="B11" s="404" t="s">
-        <v>1502</v>
-      </c>
-      <c r="C11" s="404" t="s">
-        <v>1491</v>
-      </c>
-      <c r="D11" s="72" t="s">
-        <v>1505</v>
       </c>
       <c r="E11" s="403"/>
       <c r="F11" s="405" t="s">
+        <v>1505</v>
+      </c>
+      <c r="G11" s="403" t="s">
+        <v>1502</v>
+      </c>
+      <c r="H11" s="403" t="s">
         <v>1506</v>
-      </c>
-      <c r="G11" s="403" t="s">
-        <v>1503</v>
-      </c>
-      <c r="H11" s="403" t="s">
-        <v>1507</v>
       </c>
       <c r="I11" s="403"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="407" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B12" s="406" t="s">
         <v>1508</v>
-      </c>
-      <c r="B12" s="406" t="s">
-        <v>1509</v>
       </c>
       <c r="C12" s="404"/>
       <c r="D12" s="72" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="E12" s="403"/>
       <c r="F12" s="405" t="s">
+        <v>1510</v>
+      </c>
+      <c r="G12" s="403" t="s">
         <v>1511</v>
       </c>
-      <c r="G12" s="403" t="s">
+      <c r="H12" s="403" t="s">
         <v>1512</v>
-      </c>
-      <c r="H12" s="403" t="s">
-        <v>1513</v>
       </c>
       <c r="I12" s="403"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="401" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B13" s="404" t="s">
         <v>1514</v>
       </c>
-      <c r="B13" s="404" t="s">
+      <c r="C13" s="404" t="s">
         <v>1515</v>
       </c>
-      <c r="C13" s="404" t="s">
-        <v>1516</v>
-      </c>
       <c r="D13" s="72" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="E13" s="403"/>
       <c r="F13" s="405" t="s">
+        <v>1516</v>
+      </c>
+      <c r="G13" s="403" t="s">
         <v>1517</v>
       </c>
-      <c r="G13" s="403" t="s">
+      <c r="H13" s="403" t="s">
         <v>1518</v>
-      </c>
-      <c r="H13" s="403" t="s">
-        <v>1519</v>
       </c>
       <c r="I13" s="403"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="401" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B14" s="404" t="s">
         <v>1520</v>
       </c>
-      <c r="B14" s="404" t="s">
+      <c r="C14" s="404" t="s">
         <v>1521</v>
       </c>
-      <c r="C14" s="404" t="s">
+      <c r="D14" s="72" t="s">
         <v>1522</v>
-      </c>
-      <c r="D14" s="72" t="s">
-        <v>1523</v>
       </c>
       <c r="E14" s="403"/>
       <c r="F14" s="403"/>
       <c r="G14" s="403" t="s">
+        <v>1523</v>
+      </c>
+      <c r="H14" s="403" t="s">
         <v>1524</v>
-      </c>
-      <c r="H14" s="403" t="s">
-        <v>1525</v>
       </c>
       <c r="I14" s="403"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="76" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B15" s="404" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C15" s="404"/>
       <c r="D15" s="72" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E15" s="403"/>
       <c r="F15" s="405" t="s">
+        <v>1526</v>
+      </c>
+      <c r="G15" s="403" t="s">
         <v>1527</v>
       </c>
-      <c r="G15" s="403" t="s">
+      <c r="H15" s="403" t="s">
         <v>1528</v>
-      </c>
-      <c r="H15" s="403" t="s">
-        <v>1529</v>
       </c>
       <c r="I15" s="403"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="401" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B16" s="404" t="s">
         <v>1530</v>
-      </c>
-      <c r="B16" s="404" t="s">
-        <v>1531</v>
       </c>
       <c r="C16" s="404"/>
       <c r="D16" s="72" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="E16" s="403"/>
       <c r="F16" s="405" t="s">
+        <v>1532</v>
+      </c>
+      <c r="G16" s="403" t="s">
         <v>1533</v>
       </c>
-      <c r="G16" s="403" t="s">
+      <c r="H16" s="403" t="s">
         <v>1534</v>
-      </c>
-      <c r="H16" s="403" t="s">
-        <v>1535</v>
       </c>
       <c r="I16" s="403"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
       <c r="A17" s="401" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B17" s="404" t="s">
         <v>1536</v>
-      </c>
-      <c r="B17" s="404" t="s">
-        <v>1537</v>
       </c>
       <c r="C17" s="404"/>
       <c r="D17" s="72" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="E17" s="403"/>
       <c r="F17" s="403"/>
       <c r="G17" s="403" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H17" s="403"/>
       <c r="I17" s="403"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="401" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B18" s="404" t="s">
         <v>1540</v>
-      </c>
-      <c r="B18" s="404" t="s">
-        <v>1541</v>
       </c>
       <c r="C18" s="404"/>
       <c r="D18" s="72" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="E18" s="403"/>
       <c r="F18" s="403"/>
       <c r="G18" s="403" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H18" s="403" t="s">
         <v>1543</v>
-      </c>
-      <c r="H18" s="403" t="s">
-        <v>1544</v>
       </c>
       <c r="I18" s="403"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="401" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B19" s="404" t="s">
         <v>1545</v>
       </c>
-      <c r="B19" s="404" t="s">
+      <c r="C19" s="404" t="s">
         <v>1546</v>
       </c>
-      <c r="C19" s="404" t="s">
-        <v>1547</v>
-      </c>
       <c r="D19" s="404" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="E19" s="403"/>
       <c r="F19" s="403"/>
       <c r="G19" s="403" t="s">
+        <v>1547</v>
+      </c>
+      <c r="H19" s="403" t="s">
         <v>1548</v>
-      </c>
-      <c r="H19" s="403" t="s">
-        <v>1549</v>
       </c>
       <c r="I19" s="403"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="76" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B20" s="72" t="s">
         <v>1550</v>
       </c>
-      <c r="B20" s="72" t="s">
+      <c r="C20" s="404" t="s">
         <v>1551</v>
       </c>
-      <c r="C20" s="404" t="s">
+      <c r="D20" s="72" t="s">
         <v>1552</v>
-      </c>
-      <c r="D20" s="72" t="s">
-        <v>1553</v>
       </c>
       <c r="E20" s="403"/>
       <c r="F20" s="403"/>
       <c r="G20" s="403" t="s">
+        <v>1553</v>
+      </c>
+      <c r="H20" s="403" t="s">
         <v>1554</v>
-      </c>
-      <c r="H20" s="403" t="s">
-        <v>1555</v>
       </c>
       <c r="I20" s="403"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
       <c r="A21" s="401" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B21" s="404" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C21" s="77" t="s">
         <v>1556</v>
       </c>
-      <c r="B21" s="404" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C21" s="77" t="s">
+      <c r="D21" s="72" t="s">
         <v>1557</v>
-      </c>
-      <c r="D21" s="72" t="s">
-        <v>1558</v>
       </c>
       <c r="E21" s="403"/>
       <c r="F21" s="405" t="s">
+        <v>1558</v>
+      </c>
+      <c r="G21" s="403" t="s">
         <v>1559</v>
-      </c>
-      <c r="G21" s="403" t="s">
-        <v>1560</v>
       </c>
       <c r="H21" s="403"/>
       <c r="I21" s="403"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="401" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B22" s="404" t="s">
         <v>1561</v>
       </c>
-      <c r="B22" s="404" t="s">
+      <c r="C22" s="404" t="s">
         <v>1562</v>
       </c>
-      <c r="C22" s="404" t="s">
+      <c r="D22" s="72" t="s">
         <v>1563</v>
-      </c>
-      <c r="D22" s="72" t="s">
-        <v>1564</v>
       </c>
       <c r="E22" s="403"/>
       <c r="F22" s="403"/>
       <c r="G22" s="403" t="s">
+        <v>1564</v>
+      </c>
+      <c r="H22" s="403" t="s">
         <v>1565</v>
-      </c>
-      <c r="H22" s="403" t="s">
-        <v>1566</v>
       </c>
       <c r="I22" s="403"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="401" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B23" s="404" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C23" s="404" t="s">
         <v>1567</v>
       </c>
-      <c r="B23" s="404" t="s">
-        <v>1505</v>
-      </c>
-      <c r="C23" s="404" t="s">
-        <v>1568</v>
-      </c>
       <c r="D23" s="72" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E23" s="403"/>
       <c r="F23" s="403"/>
       <c r="G23" s="403" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H23" s="403" t="s">
         <v>1569</v>
-      </c>
-      <c r="H23" s="403" t="s">
-        <v>1570</v>
       </c>
       <c r="I23" s="403"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="401" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B24" s="404" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C24" s="404"/>
       <c r="D24" s="72" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="E24" s="403"/>
       <c r="F24" s="403"/>
       <c r="G24" s="403" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H24" s="403" t="s">
         <v>1572</v>
-      </c>
-      <c r="H24" s="403" t="s">
-        <v>1573</v>
       </c>
       <c r="I24" s="403"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="401" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B25" s="404">
         <v>0.05</v>
@@ -24449,209 +24449,209 @@
       <c r="E25" s="403"/>
       <c r="F25" s="403"/>
       <c r="G25" s="403" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H25" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I25" s="403"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="401" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B26" s="404" t="s">
         <v>1576</v>
       </c>
-      <c r="B26" s="404" t="s">
+      <c r="C26" s="404" t="s">
         <v>1577</v>
       </c>
-      <c r="C26" s="404" t="s">
-        <v>1578</v>
-      </c>
       <c r="D26" s="72" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E26" s="403"/>
       <c r="F26" s="403"/>
       <c r="G26" s="403" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H26" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I26" s="403"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="401" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B27" s="404" t="s">
         <v>1580</v>
-      </c>
-      <c r="B27" s="404" t="s">
-        <v>1581</v>
       </c>
       <c r="C27" s="404"/>
       <c r="D27" s="404" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="E27" s="403"/>
       <c r="F27" s="403"/>
       <c r="G27" s="403" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H27" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I27" s="403"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="401" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B28" s="404" t="s">
         <v>1583</v>
       </c>
-      <c r="B28" s="404" t="s">
+      <c r="C28" s="404" t="s">
         <v>1584</v>
       </c>
-      <c r="C28" s="404" t="s">
-        <v>1585</v>
-      </c>
       <c r="D28" s="72" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="E28" s="403"/>
       <c r="F28" s="403" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="G28" s="403" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H28" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I28" s="403"/>
     </row>
     <row r="29" spans="1:9" ht="15" customHeight="1">
       <c r="A29" s="401" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B29" s="404" t="s">
         <v>1587</v>
       </c>
-      <c r="B29" s="404" t="s">
+      <c r="C29" s="404" t="s">
         <v>1588</v>
       </c>
-      <c r="C29" s="404" t="s">
+      <c r="D29" s="72" t="s">
         <v>1589</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>1590</v>
       </c>
       <c r="E29" s="403"/>
       <c r="F29" s="405" t="s">
+        <v>1590</v>
+      </c>
+      <c r="G29" s="403" t="s">
         <v>1591</v>
-      </c>
-      <c r="G29" s="403" t="s">
-        <v>1592</v>
       </c>
       <c r="H29" s="403"/>
       <c r="I29" s="403"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="401" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B30" s="404" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C30" s="404" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D30" s="72" t="s">
         <v>1593</v>
-      </c>
-      <c r="C30" s="404" t="s">
-        <v>1568</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>1594</v>
       </c>
       <c r="E30" s="403"/>
       <c r="F30" s="405" t="s">
+        <v>1594</v>
+      </c>
+      <c r="G30" s="403" t="s">
         <v>1595</v>
       </c>
-      <c r="G30" s="403" t="s">
+      <c r="H30" s="403" t="s">
         <v>1596</v>
-      </c>
-      <c r="H30" s="403" t="s">
-        <v>1597</v>
       </c>
       <c r="I30" s="403"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="401" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B31" s="404" t="s">
         <v>1598</v>
       </c>
-      <c r="B31" s="404" t="s">
+      <c r="C31" s="404" t="s">
         <v>1599</v>
       </c>
-      <c r="C31" s="404" t="s">
-        <v>1600</v>
-      </c>
       <c r="D31" s="404" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="E31" s="403"/>
       <c r="F31" s="405" t="s">
+        <v>1600</v>
+      </c>
+      <c r="G31" s="403" t="s">
         <v>1601</v>
       </c>
-      <c r="G31" s="403" t="s">
+      <c r="H31" s="403" t="s">
         <v>1602</v>
-      </c>
-      <c r="H31" s="403" t="s">
-        <v>1603</v>
       </c>
       <c r="I31" s="403"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="401" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B32" s="404" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C32" s="404" t="s">
         <v>1604</v>
       </c>
-      <c r="B32" s="404" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C32" s="404" t="s">
-        <v>1605</v>
-      </c>
       <c r="D32" s="72" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="E32" s="403"/>
       <c r="F32" s="403"/>
       <c r="G32" s="403" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H32" s="403" t="s">
         <v>1606</v>
-      </c>
-      <c r="H32" s="403" t="s">
-        <v>1607</v>
       </c>
       <c r="I32" s="403"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="401" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B33" s="404" t="s">
         <v>1608</v>
       </c>
-      <c r="B33" s="404" t="s">
+      <c r="C33" s="404" t="s">
         <v>1609</v>
       </c>
-      <c r="C33" s="404" t="s">
+      <c r="D33" s="72" t="s">
         <v>1610</v>
-      </c>
-      <c r="D33" s="72" t="s">
-        <v>1611</v>
       </c>
       <c r="E33" s="403"/>
       <c r="F33" s="405" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G33" s="403" t="s">
         <v>1612</v>
       </c>
-      <c r="G33" s="403" t="s">
-        <v>1613</v>
-      </c>
       <c r="H33" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I33" s="403"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="401" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B34" s="404" t="s">
         <v>1614</v>
-      </c>
-      <c r="B34" s="404" t="s">
-        <v>1615</v>
       </c>
       <c r="C34" s="404">
         <v>10305</v>
@@ -24662,16 +24662,16 @@
       <c r="E34" s="403"/>
       <c r="F34" s="403"/>
       <c r="G34" s="403" t="s">
+        <v>1615</v>
+      </c>
+      <c r="H34" s="403" t="s">
         <v>1616</v>
-      </c>
-      <c r="H34" s="403" t="s">
-        <v>1617</v>
       </c>
       <c r="I34" s="403"/>
     </row>
     <row r="35" spans="1:9" ht="15" customHeight="1">
       <c r="A35" s="401" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B35" s="404">
         <v>1.75</v>
@@ -24684,10 +24684,10 @@
       </c>
       <c r="E35" s="403"/>
       <c r="F35" s="403" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G35" s="403" t="s">
         <v>1619</v>
-      </c>
-      <c r="G35" s="403" t="s">
-        <v>1620</v>
       </c>
       <c r="H35" s="403"/>
       <c r="I35" s="403"/>
@@ -24699,10 +24699,10 @@
       <c r="E36" s="403"/>
       <c r="F36" s="403"/>
       <c r="G36" s="403" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H36" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I36" s="403"/>
     </row>
@@ -24715,10 +24715,10 @@
       <c r="E37" s="403"/>
       <c r="F37" s="403"/>
       <c r="G37" s="403" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H37" s="403" t="s">
         <v>1622</v>
-      </c>
-      <c r="H37" s="403" t="s">
-        <v>1623</v>
       </c>
       <c r="I37" s="403"/>
     </row>
@@ -24729,7 +24729,7 @@
       <c r="E38" s="403"/>
       <c r="F38" s="403"/>
       <c r="G38" s="403" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H38" s="403"/>
       <c r="I38" s="403"/>
@@ -24741,10 +24741,10 @@
       <c r="E39" s="403"/>
       <c r="F39" s="403"/>
       <c r="G39" s="403" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H39" s="403" t="s">
         <v>1625</v>
-      </c>
-      <c r="H39" s="403" t="s">
-        <v>1626</v>
       </c>
       <c r="I39" s="403"/>
     </row>
@@ -24755,10 +24755,10 @@
       <c r="E40" s="403"/>
       <c r="F40" s="403"/>
       <c r="G40" s="403" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H40" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I40" s="403"/>
     </row>
@@ -24769,10 +24769,10 @@
       <c r="E41" s="403"/>
       <c r="F41" s="403"/>
       <c r="G41" s="403" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H41" s="403" t="s">
         <v>1628</v>
-      </c>
-      <c r="H41" s="403" t="s">
-        <v>1629</v>
       </c>
       <c r="I41" s="403"/>
     </row>
@@ -24783,10 +24783,10 @@
       <c r="E42" s="403"/>
       <c r="F42" s="403"/>
       <c r="G42" s="403" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H42" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I42" s="403"/>
     </row>
@@ -24797,10 +24797,10 @@
       <c r="E43" s="403"/>
       <c r="F43" s="403"/>
       <c r="G43" s="403" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H43" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I43" s="403"/>
     </row>
@@ -24811,7 +24811,7 @@
       <c r="E44" s="403"/>
       <c r="F44" s="403"/>
       <c r="G44" s="403" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H44" s="403"/>
       <c r="I44" s="403"/>
@@ -24823,10 +24823,10 @@
       <c r="E45" s="403"/>
       <c r="F45" s="403"/>
       <c r="G45" s="403" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H45" s="403" t="s">
         <v>1633</v>
-      </c>
-      <c r="H45" s="403" t="s">
-        <v>1634</v>
       </c>
       <c r="I45" s="403"/>
     </row>
@@ -24837,10 +24837,10 @@
       <c r="E46" s="403"/>
       <c r="F46" s="403"/>
       <c r="G46" s="403" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H46" s="403" t="s">
         <v>1635</v>
-      </c>
-      <c r="H46" s="403" t="s">
-        <v>1636</v>
       </c>
       <c r="I46" s="403"/>
     </row>
@@ -24851,10 +24851,10 @@
       <c r="E47" s="403"/>
       <c r="F47" s="403"/>
       <c r="G47" s="403" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H47" s="403" t="s">
         <v>1637</v>
-      </c>
-      <c r="H47" s="403" t="s">
-        <v>1638</v>
       </c>
       <c r="I47" s="403"/>
     </row>
@@ -24865,47 +24865,47 @@
       <c r="E48" s="403"/>
       <c r="F48" s="403"/>
       <c r="G48" s="403" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H48" s="403" t="s">
         <v>1639</v>
-      </c>
-      <c r="H48" s="403" t="s">
-        <v>1640</v>
       </c>
       <c r="I48" s="403"/>
     </row>
     <row r="49" spans="6:9">
       <c r="F49" s="403"/>
       <c r="G49" s="403" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H49" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I49" s="403"/>
     </row>
     <row r="50" spans="6:9">
       <c r="F50" s="403"/>
       <c r="G50" s="403" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H50" s="403" t="s">
         <v>1642</v>
-      </c>
-      <c r="H50" s="403" t="s">
-        <v>1643</v>
       </c>
       <c r="I50" s="403"/>
     </row>
     <row r="51" spans="6:9">
       <c r="F51" s="403"/>
       <c r="G51" s="403" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H51" s="403" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="I51" s="403"/>
     </row>
     <row r="52" spans="6:9">
       <c r="F52" s="403"/>
       <c r="G52" s="403" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H52" s="403"/>
       <c r="I52" s="403"/>
@@ -24913,30 +24913,30 @@
     <row r="53" spans="6:9">
       <c r="F53" s="403"/>
       <c r="G53" s="403" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H53" s="403" t="s">
         <v>1646</v>
-      </c>
-      <c r="H53" s="403" t="s">
-        <v>1647</v>
       </c>
       <c r="I53" s="403"/>
     </row>
     <row r="54" spans="6:9">
       <c r="F54" s="403"/>
       <c r="G54" s="403" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H54" s="403" t="s">
         <v>1648</v>
-      </c>
-      <c r="H54" s="403" t="s">
-        <v>1649</v>
       </c>
       <c r="I54" s="403"/>
     </row>
     <row r="55" spans="6:9">
       <c r="F55" s="403"/>
       <c r="G55" s="403" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H55" s="403" t="s">
         <v>1650</v>
-      </c>
-      <c r="H55" s="403" t="s">
-        <v>1651</v>
       </c>
       <c r="I55" s="403"/>
     </row>
@@ -24967,26 +24967,26 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="401" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B1" s="402" t="s">
         <v>887</v>
       </c>
       <c r="C1" s="402" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D1" s="402" t="s">
         <v>1652</v>
       </c>
-      <c r="D1" s="402" t="s">
+      <c r="E1" s="402" t="s">
         <v>1653</v>
-      </c>
-      <c r="E1" s="402" t="s">
-        <v>1654</v>
       </c>
       <c r="F1" s="403"/>
       <c r="G1" s="403"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="401" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B2" s="404">
         <v>1</v>
@@ -25005,32 +25005,32 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="401" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B3" s="404" t="s">
         <v>1464</v>
       </c>
-      <c r="B3" s="404" t="s">
+      <c r="C3" s="73" t="s">
         <v>1465</v>
       </c>
-      <c r="C3" s="73" t="s">
-        <v>1466</v>
-      </c>
       <c r="D3" s="73" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="E3" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="F3" s="403"/>
       <c r="G3" s="403"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="401" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B4" s="404">
         <v>450</v>
       </c>
       <c r="C4" s="404" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="D4" s="404">
         <v>285</v>
@@ -25043,16 +25043,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="401" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B5" s="404" t="s">
         <v>1473</v>
-      </c>
-      <c r="B5" s="404" t="s">
-        <v>1474</v>
       </c>
       <c r="C5" s="404">
         <v>150</v>
       </c>
       <c r="D5" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E5" s="404">
         <v>157</v>
@@ -25062,181 +25062,181 @@
     </row>
     <row r="6" spans="1:7" ht="15" customHeight="1">
       <c r="A6" s="401" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B6" s="404">
         <v>100</v>
       </c>
       <c r="C6" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D6" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E6" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="F6" s="403"/>
       <c r="G6" s="403"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="401" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B7" s="404" t="s">
         <v>1482</v>
       </c>
-      <c r="B7" s="404" t="s">
-        <v>1483</v>
-      </c>
       <c r="C7" s="404" t="s">
+        <v>1656</v>
+      </c>
+      <c r="D7" s="404" t="s">
         <v>1657</v>
       </c>
-      <c r="D7" s="404" t="s">
+      <c r="E7" s="404" t="s">
         <v>1658</v>
-      </c>
-      <c r="E7" s="404" t="s">
-        <v>1659</v>
       </c>
       <c r="F7" s="403"/>
       <c r="G7" s="403"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="401" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B8" s="404" t="s">
         <v>1489</v>
       </c>
-      <c r="B8" s="404" t="s">
-        <v>1490</v>
-      </c>
       <c r="C8" s="404" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="404" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E8" s="404" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="F8" s="403"/>
       <c r="G8" s="403"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="401" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B9" s="404" t="s">
         <v>1660</v>
       </c>
-      <c r="B9" s="404" t="s">
+      <c r="C9" s="404" t="s">
         <v>1661</v>
       </c>
-      <c r="C9" s="404" t="s">
+      <c r="D9" s="404" t="s">
         <v>1662</v>
       </c>
-      <c r="D9" s="404" t="s">
+      <c r="E9" s="404" t="s">
         <v>1663</v>
-      </c>
-      <c r="E9" s="404" t="s">
-        <v>1664</v>
       </c>
       <c r="F9" s="403"/>
       <c r="G9" s="403"/>
     </row>
     <row r="10" spans="1:7" ht="15" customHeight="1">
       <c r="A10" s="401" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B10" s="406" t="s">
         <v>1495</v>
       </c>
-      <c r="B10" s="406" t="s">
-        <v>1496</v>
-      </c>
       <c r="C10" s="406" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D10" s="406" t="s">
         <v>1665</v>
       </c>
-      <c r="D10" s="406" t="s">
+      <c r="E10" s="404" t="s">
         <v>1666</v>
-      </c>
-      <c r="E10" s="404" t="s">
-        <v>1667</v>
       </c>
       <c r="F10" s="403"/>
       <c r="G10" s="403"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="401" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B11" s="404" t="s">
         <v>1501</v>
       </c>
-      <c r="B11" s="404" t="s">
-        <v>1502</v>
-      </c>
       <c r="C11" s="404" t="s">
+        <v>1667</v>
+      </c>
+      <c r="D11" s="404" t="s">
         <v>1668</v>
       </c>
-      <c r="D11" s="404" t="s">
+      <c r="E11" s="404" t="s">
         <v>1669</v>
-      </c>
-      <c r="E11" s="404" t="s">
-        <v>1670</v>
       </c>
       <c r="F11" s="403"/>
       <c r="G11" s="403"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="407" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B12" s="406" t="s">
         <v>1508</v>
       </c>
-      <c r="B12" s="406" t="s">
-        <v>1509</v>
-      </c>
       <c r="C12" s="75" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D12" s="406" t="s">
         <v>1671</v>
       </c>
-      <c r="D12" s="406" t="s">
+      <c r="E12" s="75" t="s">
         <v>1672</v>
-      </c>
-      <c r="E12" s="75" t="s">
-        <v>1673</v>
       </c>
       <c r="F12" s="403"/>
       <c r="G12" s="403"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="401" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B13" s="404" t="s">
         <v>1514</v>
-      </c>
-      <c r="B13" s="404" t="s">
-        <v>1515</v>
       </c>
       <c r="C13" s="404">
         <v>120</v>
       </c>
       <c r="D13" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E13" s="404" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="F13" s="403"/>
       <c r="G13" s="403"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="401" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B14" s="404" t="s">
         <v>1520</v>
       </c>
-      <c r="B14" s="404" t="s">
-        <v>1521</v>
-      </c>
       <c r="C14" s="404" t="s">
+        <v>1674</v>
+      </c>
+      <c r="D14" s="404" t="s">
         <v>1675</v>
       </c>
-      <c r="D14" s="404" t="s">
+      <c r="E14" s="404" t="s">
         <v>1676</v>
-      </c>
-      <c r="E14" s="404" t="s">
-        <v>1677</v>
       </c>
       <c r="F14" s="403"/>
       <c r="G14" s="403"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="76" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B15" s="404" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="C15" s="404"/>
       <c r="D15" s="404"/>
@@ -25246,86 +25246,86 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="401" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B16" s="404" t="s">
         <v>1530</v>
       </c>
-      <c r="B16" s="404" t="s">
-        <v>1531</v>
-      </c>
       <c r="C16" s="404" t="s">
+        <v>1677</v>
+      </c>
+      <c r="D16" s="404" t="s">
         <v>1678</v>
       </c>
-      <c r="D16" s="404" t="s">
-        <v>1679</v>
-      </c>
       <c r="E16" s="404" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F16" s="403"/>
       <c r="G16" s="403"/>
     </row>
     <row r="17" spans="1:7" ht="15" customHeight="1">
       <c r="A17" s="401" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B17" s="404" t="s">
         <v>1536</v>
       </c>
-      <c r="B17" s="404" t="s">
-        <v>1537</v>
-      </c>
       <c r="C17" s="404" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="D17" s="404" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="E17" s="404" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F17" s="403"/>
       <c r="G17" s="403"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="401" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B18" s="404" t="s">
         <v>1540</v>
       </c>
-      <c r="B18" s="404" t="s">
-        <v>1541</v>
-      </c>
       <c r="C18" s="404" t="s">
+        <v>1680</v>
+      </c>
+      <c r="D18" s="404" t="s">
         <v>1681</v>
       </c>
-      <c r="D18" s="404" t="s">
+      <c r="E18" s="404" t="s">
         <v>1682</v>
-      </c>
-      <c r="E18" s="404" t="s">
-        <v>1683</v>
       </c>
       <c r="F18" s="403"/>
       <c r="G18" s="403"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="401" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B19" s="404" t="s">
         <v>1545</v>
       </c>
-      <c r="B19" s="404" t="s">
+      <c r="C19" s="404" t="s">
         <v>1546</v>
       </c>
-      <c r="C19" s="404" t="s">
-        <v>1547</v>
-      </c>
       <c r="D19" s="404" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E19" s="404" t="s">
         <v>1684</v>
-      </c>
-      <c r="E19" s="404" t="s">
-        <v>1685</v>
       </c>
       <c r="F19" s="403"/>
       <c r="G19" s="403"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="76" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B20" s="72" t="s">
         <v>1550</v>
-      </c>
-      <c r="B20" s="72" t="s">
-        <v>1551</v>
       </c>
       <c r="C20" s="404"/>
       <c r="D20" s="404"/>
@@ -25335,16 +25335,16 @@
     </row>
     <row r="21" spans="1:7" ht="15" customHeight="1">
       <c r="A21" s="401" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B21" s="404" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C21" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D21" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E21" s="404"/>
       <c r="F21" s="403"/>
@@ -25352,54 +25352,54 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="401" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B22" s="404" t="s">
         <v>1561</v>
       </c>
-      <c r="B22" s="404" t="s">
-        <v>1562</v>
-      </c>
       <c r="C22" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D22" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E22" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="F22" s="403"/>
       <c r="G22" s="403"/>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="401" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B23" s="404" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C23" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D23" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="E23" s="404" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="F23" s="403"/>
       <c r="G23" s="403"/>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="401" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B24" s="404" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="C24" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D24" s="404" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="E24" s="404"/>
       <c r="F24" s="403"/>
@@ -25407,16 +25407,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="401" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B25" s="404">
         <v>0.05</v>
       </c>
       <c r="C25" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D25" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E25" s="404"/>
       <c r="F25" s="403"/>
@@ -25424,16 +25424,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="401" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B26" s="404" t="s">
         <v>1576</v>
       </c>
-      <c r="B26" s="404" t="s">
-        <v>1577</v>
-      </c>
       <c r="C26" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D26" s="404" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="E26" s="404"/>
       <c r="F26" s="403"/>
@@ -25441,16 +25441,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="401" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B27" s="404" t="s">
         <v>1580</v>
       </c>
-      <c r="B27" s="404" t="s">
-        <v>1581</v>
-      </c>
       <c r="C27" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D27" s="404" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="E27" s="404"/>
       <c r="F27" s="403"/>
@@ -25458,16 +25458,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="401" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B28" s="404" t="s">
         <v>1583</v>
       </c>
-      <c r="B28" s="404" t="s">
-        <v>1584</v>
-      </c>
       <c r="C28" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="D28" s="404" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="E28" s="404"/>
       <c r="F28" s="403"/>
@@ -25475,16 +25475,16 @@
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
       <c r="A29" s="401" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B29" s="404" t="s">
         <v>1587</v>
       </c>
-      <c r="B29" s="404" t="s">
-        <v>1588</v>
-      </c>
       <c r="C29" s="404" t="s">
+        <v>1689</v>
+      </c>
+      <c r="D29" s="404" t="s">
         <v>1690</v>
-      </c>
-      <c r="D29" s="404" t="s">
-        <v>1691</v>
       </c>
       <c r="E29" s="404"/>
       <c r="F29" s="403"/>
@@ -25492,16 +25492,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="401" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="B30" s="404" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="C30" s="404" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D30" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E30" s="404"/>
       <c r="F30" s="403"/>
@@ -25509,16 +25509,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="401" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B31" s="404" t="s">
         <v>1598</v>
       </c>
-      <c r="B31" s="404" t="s">
-        <v>1599</v>
-      </c>
       <c r="C31" s="404" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D31" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E31" s="404"/>
       <c r="F31" s="403"/>
@@ -25526,16 +25526,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="401" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B32" s="404" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="C32" s="404" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D32" s="404" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="E32" s="404"/>
       <c r="F32" s="403"/>
@@ -25543,16 +25543,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="401" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B33" s="404" t="s">
         <v>1608</v>
       </c>
-      <c r="B33" s="404" t="s">
-        <v>1609</v>
-      </c>
       <c r="C33" s="404" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="D33" s="404" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="E33" s="404"/>
       <c r="F33" s="403"/>
@@ -25560,10 +25560,10 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="401" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B34" s="404" t="s">
         <v>1614</v>
-      </c>
-      <c r="B34" s="404" t="s">
-        <v>1615</v>
       </c>
       <c r="C34" s="404">
         <v>1000</v>
@@ -25579,7 +25579,7 @@
     </row>
     <row r="35" spans="1:7" ht="15" customHeight="1">
       <c r="A35" s="401" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B35" s="404">
         <v>1.75</v>
@@ -25864,7 +25864,7 @@
       </c>
       <c r="J3" s="276"/>
       <c r="L3" s="419" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="M3" s="419"/>
     </row>
@@ -25899,7 +25899,7 @@
       </c>
       <c r="J4" s="276"/>
       <c r="L4" s="420" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="M4" s="420"/>
     </row>
@@ -26213,7 +26213,7 @@
       </c>
       <c r="J14" s="276"/>
       <c r="L14" s="450" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -27473,7 +27473,7 @@
         <v>30</v>
       </c>
       <c r="G55" s="447" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="H55" s="443" t="s">
         <v>156</v>
@@ -27735,7 +27735,7 @@
         <v>55</v>
       </c>
       <c r="B64" s="460" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="C64" s="461">
         <v>1</v>
@@ -27814,7 +27814,7 @@
         <v>10</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="H66" s="473" t="s">
         <v>118</v>
@@ -28355,7 +28355,7 @@
         <v>2225</v>
       </c>
       <c r="N82" s="50" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="83" spans="1:14">
@@ -28424,14 +28424,14 @@
         <v>7991</v>
       </c>
       <c r="L84" s="50" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="M84" s="50">
         <f>M82/230</f>
         <v>9.6739130434782616</v>
       </c>
       <c r="N84" s="50" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="85" spans="1:14">
@@ -28467,7 +28467,7 @@
         <v>912</v>
       </c>
       <c r="L85" s="50" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="M85" s="50">
         <f>M82/110</f>
@@ -29566,7 +29566,7 @@
         <v>3.49</v>
       </c>
       <c r="G119" s="56" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="H119" s="339" t="s">
         <v>301</v>
@@ -30823,7 +30823,7 @@
         <v>55</v>
       </c>
       <c r="B165" s="425" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="C165" s="426">
         <v>2</v>
@@ -30853,7 +30853,7 @@
         <v>55</v>
       </c>
       <c r="B166" s="425" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C166" s="426">
         <v>2</v>
@@ -30883,7 +30883,7 @@
         <v>55</v>
       </c>
       <c r="B167" s="425" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="C167" s="426">
         <v>2</v>
@@ -30928,7 +30928,7 @@
         <v>30</v>
       </c>
       <c r="G168" s="449" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="H168" s="444" t="s">
         <v>156</v>
@@ -30938,7 +30938,7 @@
       </c>
       <c r="J168" s="432"/>
       <c r="L168" s="450" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="169" spans="1:12">
@@ -30962,7 +30962,7 @@
         <v>13.9</v>
       </c>
       <c r="G169" s="445" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="H169" s="444" t="s">
         <v>160</v>
@@ -30977,7 +30977,7 @@
         <v>55</v>
       </c>
       <c r="B170" s="454" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="C170" s="455">
         <v>1</v>
@@ -30993,7 +30993,7 @@
         <v>4.82</v>
       </c>
       <c r="G170" s="449" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="H170" s="458" t="s">
         <v>177</v>
@@ -31381,7 +31381,7 @@
         <v>403</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>404</v>
@@ -31390,12 +31390,12 @@
         <v>28</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="49" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="B2" s="49"/>
       <c r="C2" s="49"/>
@@ -31404,117 +31404,117 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
         <v>1699</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" s="45" t="s">
         <v>1700</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>1701</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
         <v>1702</v>
       </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>1703</v>
-      </c>
-      <c r="E7" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1">
       <c r="A8" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E8" s="45" t="s">
         <v>1705</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="35" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
         <v>1708</v>
       </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="E11" s="45" t="s">
         <v>1709</v>
-      </c>
-      <c r="E11" s="45" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="35" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>1711</v>
       </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" t="s">
         <v>1712</v>
-      </c>
-      <c r="E12" t="s">
-        <v>1713</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>1716</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C16" t="s">
         <v>1718</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -31522,7 +31522,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -31530,78 +31530,78 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="66" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E20" s="45" t="s">
         <v>1722</v>
-      </c>
-      <c r="E20" s="45" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75">
       <c r="A22" s="5" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>1725</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="E24" s="45" t="s">
         <v>1727</v>
-      </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25" customHeight="1">
       <c r="A25" s="4" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>1729</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.75">
       <c r="A30" s="5" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B31" t="s">
         <v>1732</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>1733</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>1734</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" s="36" t="s">
         <v>1735</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.75">
       <c r="A32" s="48" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="E32" t="s">
         <v>1737</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -31611,7 +31611,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="30" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
     </row>
   </sheetData>
